--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\neusa1\FinDPlanEstrateFinan\SYSTEM4\TASAS DIARIAS\2026\tasas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D55456-C0C0-4CB8-843B-F5AB17A4CA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5768961F-D77A-4E10-B1C0-53FC3726DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="20">
   <si>
     <t>AÑO</t>
   </si>
@@ -117,12 +117,6 @@
     <t xml:space="preserve">estimar una regresion lineal hasta el año 2026 dic, Arima </t>
   </si>
   <si>
-    <t>variable exogena a la proyección y ver el Beta, elasticdad de la tasa sobre el margen Arimax</t>
-  </si>
-  <si>
-    <t>falta completar a 2026</t>
-  </si>
-  <si>
     <t>proyeccion</t>
   </si>
 </sst>
@@ -175,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -246,23 +240,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -271,32 +255,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -306,9 +281,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2269,44 +2241,6 @@
           </cell>
           <cell r="O63">
             <v>79405.445935437034</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="D87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="E87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="F87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="G87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="H87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="I87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="J87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="K87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="L87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="M87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="N87" t="e">
-            <v>#REF!</v>
-          </cell>
-          <cell r="O87" t="e">
-            <v>#REF!</v>
           </cell>
         </row>
       </sheetData>
@@ -2816,6187 +2750,5348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:IT20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:IT17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5">
+      <c r="B1" s="4">
         <v>2005</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1" s="4">
         <v>2005</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1" s="4">
         <v>2005</v>
       </c>
-      <c r="E1" s="5">
+      <c r="E1" s="4">
         <v>2005</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1" s="4">
         <v>2005</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1" s="4">
         <v>2005</v>
       </c>
-      <c r="H1" s="5">
+      <c r="H1" s="4">
         <v>2005</v>
       </c>
-      <c r="I1" s="5">
+      <c r="I1" s="4">
         <v>2005</v>
       </c>
-      <c r="J1" s="5">
+      <c r="J1" s="4">
         <v>2005</v>
       </c>
-      <c r="K1" s="5">
+      <c r="K1" s="4">
         <v>2005</v>
       </c>
-      <c r="L1" s="5">
+      <c r="L1" s="4">
         <v>2005</v>
       </c>
-      <c r="M1" s="10">
+      <c r="M1" s="8">
         <v>2005</v>
       </c>
-      <c r="N1" s="5">
+      <c r="N1" s="4">
         <v>2006</v>
       </c>
-      <c r="O1" s="5">
+      <c r="O1" s="4">
         <v>2006</v>
       </c>
-      <c r="P1" s="5">
+      <c r="P1" s="4">
         <v>2006</v>
       </c>
-      <c r="Q1" s="5">
+      <c r="Q1" s="4">
         <v>2006</v>
       </c>
-      <c r="R1" s="5">
+      <c r="R1" s="4">
         <v>2006</v>
       </c>
-      <c r="S1" s="5">
+      <c r="S1" s="4">
         <v>2006</v>
       </c>
-      <c r="T1" s="5">
+      <c r="T1" s="4">
         <v>2006</v>
       </c>
-      <c r="U1" s="5">
+      <c r="U1" s="4">
         <v>2006</v>
       </c>
-      <c r="V1" s="5">
+      <c r="V1" s="4">
         <v>2006</v>
       </c>
-      <c r="W1" s="5">
+      <c r="W1" s="4">
         <v>2006</v>
       </c>
-      <c r="X1" s="5">
+      <c r="X1" s="4">
         <v>2006</v>
       </c>
-      <c r="Y1" s="10">
+      <c r="Y1" s="8">
         <v>2006</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="Z1" s="4">
         <v>2007</v>
       </c>
-      <c r="AA1" s="5">
+      <c r="AA1" s="4">
         <v>2007</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="AB1" s="4">
         <v>2007</v>
       </c>
-      <c r="AC1" s="5">
+      <c r="AC1" s="4">
         <v>2007</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AD1" s="4">
         <v>2007</v>
       </c>
-      <c r="AE1" s="5">
+      <c r="AE1" s="4">
         <v>2007</v>
       </c>
-      <c r="AF1" s="5">
+      <c r="AF1" s="4">
         <v>2007</v>
       </c>
-      <c r="AG1" s="5">
+      <c r="AG1" s="4">
         <v>2007</v>
       </c>
-      <c r="AH1" s="5">
+      <c r="AH1" s="4">
         <v>2007</v>
       </c>
-      <c r="AI1" s="5">
+      <c r="AI1" s="4">
         <v>2007</v>
       </c>
-      <c r="AJ1" s="5">
+      <c r="AJ1" s="4">
         <v>2007</v>
       </c>
-      <c r="AK1" s="10">
+      <c r="AK1" s="8">
         <v>2007</v>
       </c>
-      <c r="AL1" s="16">
+      <c r="AL1" s="13">
         <v>2008</v>
       </c>
-      <c r="AM1" s="16">
+      <c r="AM1" s="13">
         <v>2008</v>
       </c>
-      <c r="AN1" s="16">
+      <c r="AN1" s="13">
         <v>2008</v>
       </c>
-      <c r="AO1" s="16">
+      <c r="AO1" s="13">
         <v>2008</v>
       </c>
-      <c r="AP1" s="16">
+      <c r="AP1" s="13">
         <v>2008</v>
       </c>
-      <c r="AQ1" s="16">
+      <c r="AQ1" s="13">
         <v>2008</v>
       </c>
-      <c r="AR1" s="16">
+      <c r="AR1" s="13">
         <v>2008</v>
       </c>
-      <c r="AS1" s="16">
+      <c r="AS1" s="13">
         <v>2008</v>
       </c>
-      <c r="AT1" s="16">
+      <c r="AT1" s="13">
         <v>2008</v>
       </c>
-      <c r="AU1" s="16">
+      <c r="AU1" s="13">
         <v>2008</v>
       </c>
-      <c r="AV1" s="16">
+      <c r="AV1" s="13">
         <v>2008</v>
       </c>
-      <c r="AW1" s="10">
+      <c r="AW1" s="8">
         <v>2008</v>
       </c>
-      <c r="AX1" s="16">
+      <c r="AX1" s="13">
         <v>2009</v>
       </c>
-      <c r="AY1" s="16">
+      <c r="AY1" s="13">
         <v>2009</v>
       </c>
-      <c r="AZ1" s="16">
+      <c r="AZ1" s="13">
         <v>2009</v>
       </c>
-      <c r="BA1" s="16">
+      <c r="BA1" s="13">
         <v>2009</v>
       </c>
-      <c r="BB1" s="16">
+      <c r="BB1" s="13">
         <v>2009</v>
       </c>
-      <c r="BC1" s="16">
+      <c r="BC1" s="13">
         <v>2009</v>
       </c>
-      <c r="BD1" s="16">
+      <c r="BD1" s="13">
         <v>2009</v>
       </c>
-      <c r="BE1" s="16">
+      <c r="BE1" s="13">
         <v>2009</v>
       </c>
-      <c r="BF1" s="16">
+      <c r="BF1" s="13">
         <v>2009</v>
       </c>
-      <c r="BG1" s="16">
+      <c r="BG1" s="13">
         <v>2009</v>
       </c>
-      <c r="BH1" s="16">
+      <c r="BH1" s="13">
         <v>2009</v>
       </c>
-      <c r="BI1" s="10">
+      <c r="BI1" s="8">
         <v>2009</v>
       </c>
-      <c r="BJ1" s="16">
+      <c r="BJ1" s="13">
         <v>2010</v>
       </c>
-      <c r="BK1" s="16">
+      <c r="BK1" s="13">
         <v>2010</v>
       </c>
-      <c r="BL1" s="16">
+      <c r="BL1" s="13">
         <v>2010</v>
       </c>
-      <c r="BM1" s="16">
+      <c r="BM1" s="13">
         <v>2010</v>
       </c>
-      <c r="BN1" s="16">
+      <c r="BN1" s="13">
         <v>2010</v>
       </c>
-      <c r="BO1" s="16">
+      <c r="BO1" s="13">
         <v>2010</v>
       </c>
-      <c r="BP1" s="16">
+      <c r="BP1" s="13">
         <v>2010</v>
       </c>
-      <c r="BQ1" s="16">
+      <c r="BQ1" s="13">
         <v>2010</v>
       </c>
-      <c r="BR1" s="16">
+      <c r="BR1" s="13">
         <v>2010</v>
       </c>
-      <c r="BS1" s="16">
+      <c r="BS1" s="13">
         <v>2010</v>
       </c>
-      <c r="BT1" s="16">
+      <c r="BT1" s="13">
         <v>2010</v>
       </c>
-      <c r="BU1" s="10">
+      <c r="BU1" s="8">
         <v>2010</v>
       </c>
-      <c r="BV1" s="16">
+      <c r="BV1" s="13">
         <v>2011</v>
       </c>
-      <c r="BW1" s="16">
+      <c r="BW1" s="13">
         <v>2011</v>
       </c>
-      <c r="BX1" s="16">
+      <c r="BX1" s="13">
         <v>2011</v>
       </c>
-      <c r="BY1" s="16">
+      <c r="BY1" s="13">
         <v>2011</v>
       </c>
-      <c r="BZ1" s="16">
+      <c r="BZ1" s="13">
         <v>2011</v>
       </c>
-      <c r="CA1" s="16">
+      <c r="CA1" s="13">
         <v>2011</v>
       </c>
-      <c r="CB1" s="16">
+      <c r="CB1" s="13">
         <v>2011</v>
       </c>
-      <c r="CC1" s="16">
+      <c r="CC1" s="13">
         <v>2011</v>
       </c>
-      <c r="CD1" s="16">
+      <c r="CD1" s="13">
         <v>2011</v>
       </c>
-      <c r="CE1" s="16">
+      <c r="CE1" s="13">
         <v>2011</v>
       </c>
-      <c r="CF1" s="16">
+      <c r="CF1" s="13">
         <v>2011</v>
       </c>
-      <c r="CG1" s="10">
+      <c r="CG1" s="8">
         <v>2011</v>
       </c>
-      <c r="CH1" s="16">
+      <c r="CH1" s="13">
         <v>2012</v>
       </c>
-      <c r="CI1" s="16">
+      <c r="CI1" s="13">
         <v>2012</v>
       </c>
-      <c r="CJ1" s="16">
+      <c r="CJ1" s="13">
         <v>2012</v>
       </c>
-      <c r="CK1" s="16">
+      <c r="CK1" s="13">
         <v>2012</v>
       </c>
-      <c r="CL1" s="16">
+      <c r="CL1" s="13">
         <v>2012</v>
       </c>
-      <c r="CM1" s="16">
+      <c r="CM1" s="13">
         <v>2012</v>
       </c>
-      <c r="CN1" s="16">
+      <c r="CN1" s="13">
         <v>2012</v>
       </c>
-      <c r="CO1" s="16">
+      <c r="CO1" s="13">
         <v>2012</v>
       </c>
-      <c r="CP1" s="16">
+      <c r="CP1" s="13">
         <v>2012</v>
       </c>
-      <c r="CQ1" s="16">
+      <c r="CQ1" s="13">
         <v>2012</v>
       </c>
-      <c r="CR1" s="16">
+      <c r="CR1" s="13">
         <v>2012</v>
       </c>
-      <c r="CS1" s="10">
+      <c r="CS1" s="8">
         <v>2012</v>
       </c>
-      <c r="CT1" s="16">
+      <c r="CT1" s="13">
         <v>2013</v>
       </c>
-      <c r="CU1" s="16">
+      <c r="CU1" s="13">
         <v>2013</v>
       </c>
-      <c r="CV1" s="16">
+      <c r="CV1" s="13">
         <v>2013</v>
       </c>
-      <c r="CW1" s="16">
+      <c r="CW1" s="13">
         <v>2013</v>
       </c>
-      <c r="CX1" s="16">
+      <c r="CX1" s="13">
         <v>2013</v>
       </c>
-      <c r="CY1" s="16">
+      <c r="CY1" s="13">
         <v>2013</v>
       </c>
-      <c r="CZ1" s="16">
+      <c r="CZ1" s="13">
         <v>2013</v>
       </c>
-      <c r="DA1" s="16">
+      <c r="DA1" s="13">
         <v>2013</v>
       </c>
-      <c r="DB1" s="16">
+      <c r="DB1" s="13">
         <v>2013</v>
       </c>
-      <c r="DC1" s="16">
+      <c r="DC1" s="13">
         <v>2013</v>
       </c>
-      <c r="DD1" s="16">
+      <c r="DD1" s="13">
         <v>2013</v>
       </c>
-      <c r="DE1" s="10">
+      <c r="DE1" s="8">
         <v>2013</v>
       </c>
-      <c r="DF1" s="16">
+      <c r="DF1" s="13">
         <v>2014</v>
       </c>
-      <c r="DG1" s="16">
+      <c r="DG1" s="13">
         <v>2014</v>
       </c>
-      <c r="DH1" s="16">
+      <c r="DH1" s="13">
         <v>2014</v>
       </c>
-      <c r="DI1" s="16">
+      <c r="DI1" s="13">
         <v>2014</v>
       </c>
-      <c r="DJ1" s="16">
+      <c r="DJ1" s="13">
         <v>2014</v>
       </c>
-      <c r="DK1" s="16">
+      <c r="DK1" s="13">
         <v>2014</v>
       </c>
-      <c r="DL1" s="16">
+      <c r="DL1" s="13">
         <v>2014</v>
       </c>
-      <c r="DM1" s="16">
+      <c r="DM1" s="13">
         <v>2014</v>
       </c>
-      <c r="DN1" s="16">
+      <c r="DN1" s="13">
         <v>2014</v>
       </c>
-      <c r="DO1" s="16">
+      <c r="DO1" s="13">
         <v>2014</v>
       </c>
-      <c r="DP1" s="16">
+      <c r="DP1" s="13">
         <v>2014</v>
       </c>
-      <c r="DQ1" s="10">
+      <c r="DQ1" s="8">
         <v>2014</v>
       </c>
-      <c r="DR1" s="16">
+      <c r="DR1" s="13">
         <v>2015</v>
       </c>
-      <c r="DS1" s="16">
+      <c r="DS1" s="13">
         <v>2015</v>
       </c>
-      <c r="DT1" s="16">
+      <c r="DT1" s="13">
         <v>2015</v>
       </c>
-      <c r="DU1" s="16">
+      <c r="DU1" s="13">
         <v>2015</v>
       </c>
-      <c r="DV1" s="16">
+      <c r="DV1" s="13">
         <v>2015</v>
       </c>
-      <c r="DW1" s="16">
+      <c r="DW1" s="13">
         <v>2015</v>
       </c>
-      <c r="DX1" s="16">
+      <c r="DX1" s="13">
         <v>2015</v>
       </c>
-      <c r="DY1" s="16">
+      <c r="DY1" s="13">
         <v>2015</v>
       </c>
-      <c r="DZ1" s="16">
+      <c r="DZ1" s="13">
         <v>2015</v>
       </c>
-      <c r="EA1" s="16">
+      <c r="EA1" s="13">
         <v>2015</v>
       </c>
-      <c r="EB1" s="16">
+      <c r="EB1" s="13">
         <v>2015</v>
       </c>
-      <c r="EC1" s="10">
+      <c r="EC1" s="8">
         <v>2015</v>
       </c>
-      <c r="ED1" s="16">
+      <c r="ED1" s="13">
         <v>2016</v>
       </c>
-      <c r="EE1" s="16">
+      <c r="EE1" s="13">
         <v>2016</v>
       </c>
-      <c r="EF1" s="16">
+      <c r="EF1" s="13">
         <v>2016</v>
       </c>
-      <c r="EG1" s="16">
+      <c r="EG1" s="13">
         <v>2016</v>
       </c>
-      <c r="EH1" s="16">
+      <c r="EH1" s="13">
         <v>2016</v>
       </c>
-      <c r="EI1" s="16">
+      <c r="EI1" s="13">
         <v>2016</v>
       </c>
-      <c r="EJ1" s="16">
+      <c r="EJ1" s="13">
         <v>2016</v>
       </c>
-      <c r="EK1" s="16">
+      <c r="EK1" s="13">
         <v>2016</v>
       </c>
-      <c r="EL1" s="16">
+      <c r="EL1" s="13">
         <v>2016</v>
       </c>
-      <c r="EM1" s="16">
+      <c r="EM1" s="13">
         <v>2016</v>
       </c>
-      <c r="EN1" s="16">
+      <c r="EN1" s="13">
         <v>2016</v>
       </c>
-      <c r="EO1" s="10">
+      <c r="EO1" s="8">
         <v>2016</v>
       </c>
-      <c r="EP1" s="16">
+      <c r="EP1" s="13">
         <v>2017</v>
       </c>
-      <c r="EQ1" s="16">
+      <c r="EQ1" s="13">
         <v>2017</v>
       </c>
-      <c r="ER1" s="16">
+      <c r="ER1" s="13">
         <v>2017</v>
       </c>
-      <c r="ES1" s="16">
+      <c r="ES1" s="13">
         <v>2017</v>
       </c>
-      <c r="ET1" s="16">
+      <c r="ET1" s="13">
         <v>2017</v>
       </c>
-      <c r="EU1" s="16">
+      <c r="EU1" s="13">
         <v>2017</v>
       </c>
-      <c r="EV1" s="16">
+      <c r="EV1" s="13">
         <v>2017</v>
       </c>
-      <c r="EW1" s="16">
+      <c r="EW1" s="13">
         <v>2017</v>
       </c>
-      <c r="EX1" s="16">
+      <c r="EX1" s="13">
         <v>2017</v>
       </c>
-      <c r="EY1" s="16">
+      <c r="EY1" s="13">
         <v>2017</v>
       </c>
-      <c r="EZ1" s="16">
+      <c r="EZ1" s="13">
         <v>2017</v>
       </c>
-      <c r="FA1" s="10">
+      <c r="FA1" s="8">
         <v>2017</v>
       </c>
-      <c r="FB1" s="16">
+      <c r="FB1" s="13">
         <v>2018</v>
       </c>
-      <c r="FC1" s="16">
+      <c r="FC1" s="13">
         <v>2018</v>
       </c>
-      <c r="FD1" s="16">
+      <c r="FD1" s="13">
         <v>2018</v>
       </c>
-      <c r="FE1" s="16">
+      <c r="FE1" s="13">
         <v>2018</v>
       </c>
-      <c r="FF1" s="16">
+      <c r="FF1" s="13">
         <v>2018</v>
       </c>
-      <c r="FG1" s="16">
+      <c r="FG1" s="13">
         <v>2018</v>
       </c>
-      <c r="FH1" s="16">
+      <c r="FH1" s="13">
         <v>2018</v>
       </c>
-      <c r="FI1" s="16">
+      <c r="FI1" s="13">
         <v>2018</v>
       </c>
-      <c r="FJ1" s="16">
+      <c r="FJ1" s="13">
         <v>2018</v>
       </c>
-      <c r="FK1" s="16">
+      <c r="FK1" s="13">
         <v>2018</v>
       </c>
-      <c r="FL1" s="16">
+      <c r="FL1" s="13">
         <v>2018</v>
       </c>
-      <c r="FM1" s="10">
+      <c r="FM1" s="8">
         <v>2018</v>
       </c>
-      <c r="FN1" s="16">
+      <c r="FN1" s="13">
         <v>2019</v>
       </c>
-      <c r="FO1" s="16">
+      <c r="FO1" s="13">
         <v>2019</v>
       </c>
-      <c r="FP1" s="16">
+      <c r="FP1" s="13">
         <v>2019</v>
       </c>
-      <c r="FQ1" s="16">
+      <c r="FQ1" s="13">
         <v>2019</v>
       </c>
-      <c r="FR1" s="16">
+      <c r="FR1" s="13">
         <v>2019</v>
       </c>
-      <c r="FS1" s="16">
+      <c r="FS1" s="13">
         <v>2019</v>
       </c>
-      <c r="FT1" s="16">
+      <c r="FT1" s="13">
         <v>2019</v>
       </c>
-      <c r="FU1" s="16">
+      <c r="FU1" s="13">
         <v>2019</v>
       </c>
-      <c r="FV1" s="16">
+      <c r="FV1" s="13">
         <v>2019</v>
       </c>
-      <c r="FW1" s="16">
+      <c r="FW1" s="13">
         <v>2019</v>
       </c>
-      <c r="FX1" s="16">
+      <c r="FX1" s="13">
         <v>2019</v>
       </c>
-      <c r="FY1" s="10">
+      <c r="FY1" s="8">
         <v>2019</v>
       </c>
-      <c r="FZ1" s="16">
+      <c r="FZ1" s="13">
         <v>2020</v>
       </c>
-      <c r="GA1" s="16">
+      <c r="GA1" s="13">
         <v>2020</v>
       </c>
-      <c r="GB1" s="16">
+      <c r="GB1" s="13">
         <v>2020</v>
       </c>
-      <c r="GC1" s="16">
+      <c r="GC1" s="13">
         <v>2020</v>
       </c>
-      <c r="GD1" s="16">
+      <c r="GD1" s="13">
         <v>2020</v>
       </c>
-      <c r="GE1" s="16">
+      <c r="GE1" s="13">
         <v>2020</v>
       </c>
-      <c r="GF1" s="16">
+      <c r="GF1" s="13">
         <v>2020</v>
       </c>
-      <c r="GG1" s="16">
+      <c r="GG1" s="13">
         <v>2020</v>
       </c>
-      <c r="GH1" s="16">
+      <c r="GH1" s="13">
         <v>2020</v>
       </c>
-      <c r="GI1" s="16">
+      <c r="GI1" s="13">
         <v>2020</v>
       </c>
-      <c r="GJ1" s="16">
+      <c r="GJ1" s="13">
         <v>2020</v>
       </c>
-      <c r="GK1" s="10">
+      <c r="GK1" s="8">
         <v>2020</v>
       </c>
-      <c r="GL1" s="16">
+      <c r="GL1" s="13">
         <v>2021</v>
       </c>
-      <c r="GM1" s="16">
+      <c r="GM1" s="13">
         <v>2021</v>
       </c>
-      <c r="GN1" s="16">
+      <c r="GN1" s="13">
         <v>2021</v>
       </c>
-      <c r="GO1" s="16">
+      <c r="GO1" s="13">
         <v>2021</v>
       </c>
-      <c r="GP1" s="16">
+      <c r="GP1" s="13">
         <v>2021</v>
       </c>
-      <c r="GQ1" s="16">
+      <c r="GQ1" s="13">
         <v>2021</v>
       </c>
-      <c r="GR1" s="16">
+      <c r="GR1" s="13">
         <v>2021</v>
       </c>
-      <c r="GS1" s="16">
+      <c r="GS1" s="13">
         <v>2021</v>
       </c>
-      <c r="GT1" s="16">
+      <c r="GT1" s="13">
         <v>2021</v>
       </c>
-      <c r="GU1" s="16">
+      <c r="GU1" s="13">
         <v>2021</v>
       </c>
-      <c r="GV1" s="16">
+      <c r="GV1" s="13">
         <v>2021</v>
       </c>
-      <c r="GW1" s="10">
+      <c r="GW1" s="8">
         <v>2021</v>
       </c>
-      <c r="GX1" s="16">
+      <c r="GX1" s="13">
         <v>2022</v>
       </c>
-      <c r="GY1" s="16">
+      <c r="GY1" s="13">
         <v>2022</v>
       </c>
-      <c r="GZ1" s="16">
+      <c r="GZ1" s="13">
         <v>2022</v>
       </c>
-      <c r="HA1" s="16">
+      <c r="HA1" s="13">
         <v>2022</v>
       </c>
-      <c r="HB1" s="16">
+      <c r="HB1" s="13">
         <v>2022</v>
       </c>
-      <c r="HC1" s="16">
+      <c r="HC1" s="13">
         <v>2022</v>
       </c>
-      <c r="HD1" s="16">
+      <c r="HD1" s="13">
         <v>2022</v>
       </c>
-      <c r="HE1" s="16">
+      <c r="HE1" s="13">
         <v>2022</v>
       </c>
-      <c r="HF1" s="16">
+      <c r="HF1" s="13">
         <v>2022</v>
       </c>
-      <c r="HG1" s="16">
+      <c r="HG1" s="13">
         <v>2022</v>
       </c>
-      <c r="HH1" s="16">
+      <c r="HH1" s="13">
         <v>2022</v>
       </c>
-      <c r="HI1" s="10">
+      <c r="HI1" s="8">
         <v>2022</v>
       </c>
-      <c r="HJ1" s="16">
+      <c r="HJ1" s="13">
         <v>2023</v>
       </c>
-      <c r="HK1" s="16">
+      <c r="HK1" s="13">
         <v>2023</v>
       </c>
-      <c r="HL1" s="16">
+      <c r="HL1" s="13">
         <v>2023</v>
       </c>
-      <c r="HM1" s="16">
+      <c r="HM1" s="13">
         <v>2023</v>
       </c>
-      <c r="HN1" s="16">
+      <c r="HN1" s="13">
         <v>2023</v>
       </c>
-      <c r="HO1" s="16">
+      <c r="HO1" s="13">
         <v>2023</v>
       </c>
-      <c r="HP1" s="16">
+      <c r="HP1" s="13">
         <v>2023</v>
       </c>
-      <c r="HQ1" s="16">
+      <c r="HQ1" s="13">
         <v>2023</v>
       </c>
-      <c r="HR1" s="16">
+      <c r="HR1" s="13">
         <v>2023</v>
       </c>
-      <c r="HS1" s="16">
+      <c r="HS1" s="13">
         <v>2023</v>
       </c>
-      <c r="HT1" s="16">
+      <c r="HT1" s="13">
         <v>2023</v>
       </c>
-      <c r="HU1" s="10">
+      <c r="HU1" s="8">
         <v>2023</v>
       </c>
-      <c r="HV1" s="16">
+      <c r="HV1" s="13">
         <v>2024</v>
       </c>
-      <c r="HW1" s="16">
+      <c r="HW1" s="13">
         <v>2024</v>
       </c>
-      <c r="HX1" s="16">
+      <c r="HX1" s="13">
         <v>2024</v>
       </c>
-      <c r="HY1" s="16">
+      <c r="HY1" s="13">
         <v>2024</v>
       </c>
-      <c r="HZ1" s="16">
+      <c r="HZ1" s="13">
         <v>2024</v>
       </c>
-      <c r="IA1" s="16">
+      <c r="IA1" s="13">
         <v>2024</v>
       </c>
-      <c r="IB1" s="16">
+      <c r="IB1" s="13">
         <v>2024</v>
       </c>
-      <c r="IC1" s="16">
+      <c r="IC1" s="13">
         <v>2024</v>
       </c>
-      <c r="ID1" s="16">
+      <c r="ID1" s="13">
         <v>2024</v>
       </c>
-      <c r="IE1" s="16">
+      <c r="IE1" s="13">
         <v>2024</v>
       </c>
-      <c r="IF1" s="16">
+      <c r="IF1" s="13">
         <v>2024</v>
       </c>
-      <c r="IG1" s="10">
+      <c r="IG1" s="8">
         <v>2024</v>
       </c>
-      <c r="IH1" s="16">
+      <c r="IH1" s="13">
         <v>2025</v>
       </c>
-      <c r="II1" s="16">
+      <c r="II1" s="13">
         <v>2025</v>
       </c>
-      <c r="IJ1" s="16">
+      <c r="IJ1" s="13">
         <v>2025</v>
       </c>
-      <c r="IK1" s="16">
+      <c r="IK1" s="13">
         <v>2025</v>
       </c>
-      <c r="IL1" s="16">
+      <c r="IL1" s="13">
         <v>2025</v>
       </c>
-      <c r="IM1" s="16">
+      <c r="IM1" s="13">
         <v>2025</v>
       </c>
-      <c r="IN1" s="16">
+      <c r="IN1" s="13">
         <v>2025</v>
       </c>
-      <c r="IO1" s="16">
+      <c r="IO1" s="13">
         <v>2025</v>
       </c>
-      <c r="IP1" s="16">
+      <c r="IP1" s="13">
         <v>2025</v>
       </c>
-      <c r="IQ1" s="16">
+      <c r="IQ1" s="13">
         <v>2025</v>
       </c>
-      <c r="IR1" s="16">
+      <c r="IR1" s="13">
         <v>2025</v>
       </c>
-      <c r="IS1" s="10">
+      <c r="IS1" s="8">
         <v>2025</v>
       </c>
       <c r="IT1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="T2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="X2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Y2" s="11" t="s">
+      <c r="Y2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="Z2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AA2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AB2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AC2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AD2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AE2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AF2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AG2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AH2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AI2" s="6" t="s">
+      <c r="AI2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AK2" s="11" t="s">
+      <c r="AK2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AL2" s="17" t="s">
+      <c r="AL2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AM2" s="6" t="s">
+      <c r="AM2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AN2" s="6" t="s">
+      <c r="AN2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AO2" s="6" t="s">
+      <c r="AO2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="AP2" s="6" t="s">
+      <c r="AP2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="AQ2" s="6" t="s">
+      <c r="AQ2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="AR2" s="6" t="s">
+      <c r="AR2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AS2" s="6" t="s">
+      <c r="AS2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AT2" s="6" t="s">
+      <c r="AT2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="AU2" s="6" t="s">
+      <c r="AU2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AV2" s="6" t="s">
+      <c r="AV2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="AW2" s="11" t="s">
+      <c r="AW2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AX2" s="17" t="s">
+      <c r="AX2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="AY2" s="6" t="s">
+      <c r="AY2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AZ2" s="6" t="s">
+      <c r="AZ2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BA2" s="6" t="s">
+      <c r="BA2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="6" t="s">
+      <c r="BB2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="BC2" s="6" t="s">
+      <c r="BC2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="BD2" s="6" t="s">
+      <c r="BD2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="BE2" s="6" t="s">
+      <c r="BE2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="BF2" s="6" t="s">
+      <c r="BF2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="BG2" s="6" t="s">
+      <c r="BG2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="BH2" s="6" t="s">
+      <c r="BH2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="BI2" s="11" t="s">
+      <c r="BI2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="BJ2" s="17" t="s">
+      <c r="BJ2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="BK2" s="6" t="s">
+      <c r="BK2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="BL2" s="6" t="s">
+      <c r="BL2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BM2" s="6" t="s">
+      <c r="BM2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="BN2" s="6" t="s">
+      <c r="BN2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="BO2" s="6" t="s">
+      <c r="BO2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="BP2" s="6" t="s">
+      <c r="BP2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="BQ2" s="6" t="s">
+      <c r="BQ2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="BR2" s="6" t="s">
+      <c r="BR2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="BS2" s="6" t="s">
+      <c r="BS2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="BT2" s="6" t="s">
+      <c r="BT2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="BU2" s="11" t="s">
+      <c r="BU2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="BV2" s="17" t="s">
+      <c r="BV2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="BW2" s="6" t="s">
+      <c r="BW2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="BX2" s="6" t="s">
+      <c r="BX2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BY2" s="6" t="s">
+      <c r="BY2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="BZ2" s="6" t="s">
+      <c r="BZ2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="CA2" s="6" t="s">
+      <c r="CA2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="CB2" s="6" t="s">
+      <c r="CB2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="CC2" s="6" t="s">
+      <c r="CC2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="CD2" s="6" t="s">
+      <c r="CD2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="CE2" s="6" t="s">
+      <c r="CE2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="CF2" s="6" t="s">
+      <c r="CF2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="CG2" s="11" t="s">
+      <c r="CG2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="CH2" s="17" t="s">
+      <c r="CH2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="CI2" s="6" t="s">
+      <c r="CI2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="CJ2" s="6" t="s">
+      <c r="CJ2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="CK2" s="6" t="s">
+      <c r="CK2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="CL2" s="6" t="s">
+      <c r="CL2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="CM2" s="6" t="s">
+      <c r="CM2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="CN2" s="6" t="s">
+      <c r="CN2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="CO2" s="6" t="s">
+      <c r="CO2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="CP2" s="6" t="s">
+      <c r="CP2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="CQ2" s="6" t="s">
+      <c r="CQ2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="CR2" s="6" t="s">
+      <c r="CR2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="CS2" s="11" t="s">
+      <c r="CS2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="CT2" s="17" t="s">
+      <c r="CT2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="CU2" s="6" t="s">
+      <c r="CU2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="CV2" s="6" t="s">
+      <c r="CV2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="CW2" s="6" t="s">
+      <c r="CW2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="CX2" s="6" t="s">
+      <c r="CX2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="CY2" s="6" t="s">
+      <c r="CY2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="CZ2" s="6" t="s">
+      <c r="CZ2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="DA2" s="6" t="s">
+      <c r="DA2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="DB2" s="6" t="s">
+      <c r="DB2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="DC2" s="6" t="s">
+      <c r="DC2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="DD2" s="6" t="s">
+      <c r="DD2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="DE2" s="11" t="s">
+      <c r="DE2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="DF2" s="17" t="s">
+      <c r="DF2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="DG2" s="6" t="s">
+      <c r="DG2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="DH2" s="6" t="s">
+      <c r="DH2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="DI2" s="6" t="s">
+      <c r="DI2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="DJ2" s="6" t="s">
+      <c r="DJ2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="DK2" s="6" t="s">
+      <c r="DK2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="DL2" s="6" t="s">
+      <c r="DL2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="DM2" s="6" t="s">
+      <c r="DM2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="DN2" s="6" t="s">
+      <c r="DN2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="DO2" s="6" t="s">
+      <c r="DO2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="DP2" s="6" t="s">
+      <c r="DP2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="DQ2" s="11" t="s">
+      <c r="DQ2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="DR2" s="17" t="s">
+      <c r="DR2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="DS2" s="6" t="s">
+      <c r="DS2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="DT2" s="6" t="s">
+      <c r="DT2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="DU2" s="6" t="s">
+      <c r="DU2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="DV2" s="6" t="s">
+      <c r="DV2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="DW2" s="6" t="s">
+      <c r="DW2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="DX2" s="6" t="s">
+      <c r="DX2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="DY2" s="6" t="s">
+      <c r="DY2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="DZ2" s="6" t="s">
+      <c r="DZ2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="EA2" s="6" t="s">
+      <c r="EA2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="EB2" s="6" t="s">
+      <c r="EB2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="EC2" s="11" t="s">
+      <c r="EC2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="ED2" s="17" t="s">
+      <c r="ED2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="EE2" s="6" t="s">
+      <c r="EE2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="EF2" s="6" t="s">
+      <c r="EF2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="EG2" s="6" t="s">
+      <c r="EG2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="EH2" s="6" t="s">
+      <c r="EH2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="EI2" s="6" t="s">
+      <c r="EI2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="EJ2" s="6" t="s">
+      <c r="EJ2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="EK2" s="6" t="s">
+      <c r="EK2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="EL2" s="6" t="s">
+      <c r="EL2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="EM2" s="6" t="s">
+      <c r="EM2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="EN2" s="6" t="s">
+      <c r="EN2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="EO2" s="11" t="s">
+      <c r="EO2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="EP2" s="17" t="s">
+      <c r="EP2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="EQ2" s="6" t="s">
+      <c r="EQ2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="ER2" s="6" t="s">
+      <c r="ER2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="ES2" s="6" t="s">
+      <c r="ES2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="ET2" s="6" t="s">
+      <c r="ET2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="EU2" s="6" t="s">
+      <c r="EU2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="EV2" s="6" t="s">
+      <c r="EV2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="EW2" s="6" t="s">
+      <c r="EW2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="EX2" s="6" t="s">
+      <c r="EX2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="EY2" s="6" t="s">
+      <c r="EY2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="EZ2" s="6" t="s">
+      <c r="EZ2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="FA2" s="11" t="s">
+      <c r="FA2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="FB2" s="17" t="s">
+      <c r="FB2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="FC2" s="6" t="s">
+      <c r="FC2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="FD2" s="6" t="s">
+      <c r="FD2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="FE2" s="6" t="s">
+      <c r="FE2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="FF2" s="6" t="s">
+      <c r="FF2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="FG2" s="6" t="s">
+      <c r="FG2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="FH2" s="6" t="s">
+      <c r="FH2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="FI2" s="6" t="s">
+      <c r="FI2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="FJ2" s="6" t="s">
+      <c r="FJ2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="FK2" s="6" t="s">
+      <c r="FK2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="FL2" s="6" t="s">
+      <c r="FL2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="FM2" s="11" t="s">
+      <c r="FM2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="FN2" s="17" t="s">
+      <c r="FN2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="FO2" s="6" t="s">
+      <c r="FO2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="FP2" s="6" t="s">
+      <c r="FP2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="FQ2" s="6" t="s">
+      <c r="FQ2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="FR2" s="6" t="s">
+      <c r="FR2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="FS2" s="6" t="s">
+      <c r="FS2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="FT2" s="6" t="s">
+      <c r="FT2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="FU2" s="6" t="s">
+      <c r="FU2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="FV2" s="6" t="s">
+      <c r="FV2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="FW2" s="6" t="s">
+      <c r="FW2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="FX2" s="6" t="s">
+      <c r="FX2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="FY2" s="11" t="s">
+      <c r="FY2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="FZ2" s="17" t="s">
+      <c r="FZ2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="GA2" s="6" t="s">
+      <c r="GA2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="GB2" s="6" t="s">
+      <c r="GB2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="GC2" s="6" t="s">
+      <c r="GC2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="GD2" s="6" t="s">
+      <c r="GD2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="GE2" s="6" t="s">
+      <c r="GE2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="GF2" s="6" t="s">
+      <c r="GF2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="GG2" s="6" t="s">
+      <c r="GG2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="GH2" s="6" t="s">
+      <c r="GH2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="GI2" s="6" t="s">
+      <c r="GI2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="GJ2" s="6" t="s">
+      <c r="GJ2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="GK2" s="11" t="s">
+      <c r="GK2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="GL2" s="17" t="s">
+      <c r="GL2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="GM2" s="6" t="s">
+      <c r="GM2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="GN2" s="6" t="s">
+      <c r="GN2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="GO2" s="6" t="s">
+      <c r="GO2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="GP2" s="6" t="s">
+      <c r="GP2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="GQ2" s="6" t="s">
+      <c r="GQ2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="GR2" s="6" t="s">
+      <c r="GR2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="GS2" s="6" t="s">
+      <c r="GS2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="GT2" s="6" t="s">
+      <c r="GT2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="GU2" s="6" t="s">
+      <c r="GU2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="GV2" s="6" t="s">
+      <c r="GV2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="GW2" s="11" t="s">
+      <c r="GW2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="GX2" s="17" t="s">
+      <c r="GX2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="GY2" s="6" t="s">
+      <c r="GY2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="GZ2" s="6" t="s">
+      <c r="GZ2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="HA2" s="6" t="s">
+      <c r="HA2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="HB2" s="6" t="s">
+      <c r="HB2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="HC2" s="6" t="s">
+      <c r="HC2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="HD2" s="6" t="s">
+      <c r="HD2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="HE2" s="6" t="s">
+      <c r="HE2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="HF2" s="6" t="s">
+      <c r="HF2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="HG2" s="6" t="s">
+      <c r="HG2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="HH2" s="6" t="s">
+      <c r="HH2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="HI2" s="11" t="s">
+      <c r="HI2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="HJ2" s="17" t="s">
+      <c r="HJ2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="HK2" s="6" t="s">
+      <c r="HK2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="HL2" s="6" t="s">
+      <c r="HL2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="HM2" s="6" t="s">
+      <c r="HM2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="HN2" s="6" t="s">
+      <c r="HN2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="HO2" s="6" t="s">
+      <c r="HO2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="HP2" s="6" t="s">
+      <c r="HP2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="HQ2" s="6" t="s">
+      <c r="HQ2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="HR2" s="6" t="s">
+      <c r="HR2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="HS2" s="6" t="s">
+      <c r="HS2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="HT2" s="6" t="s">
+      <c r="HT2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="HU2" s="11" t="s">
+      <c r="HU2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="HV2" s="17" t="s">
+      <c r="HV2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="HW2" s="6" t="s">
+      <c r="HW2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="HX2" s="6" t="s">
+      <c r="HX2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="HY2" s="6" t="s">
+      <c r="HY2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="HZ2" s="6" t="s">
+      <c r="HZ2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="IA2" s="6" t="s">
+      <c r="IA2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="IB2" s="6" t="s">
+      <c r="IB2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="IC2" s="6" t="s">
+      <c r="IC2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="ID2" s="6" t="s">
+      <c r="ID2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="IE2" s="6" t="s">
+      <c r="IE2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="IF2" s="6" t="s">
+      <c r="IF2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="IG2" s="11" t="s">
+      <c r="IG2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="IH2" s="17" t="s">
+      <c r="IH2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="II2" s="6" t="s">
+      <c r="II2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="IJ2" s="6" t="s">
+      <c r="IJ2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="IK2" s="6" t="s">
+      <c r="IK2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="IL2" s="6" t="s">
+      <c r="IL2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="IM2" s="6" t="s">
+      <c r="IM2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="IN2" s="6" t="s">
+      <c r="IN2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="IO2" s="6" t="s">
+      <c r="IO2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="IP2" s="6" t="s">
+      <c r="IP2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="IQ2" s="6" t="s">
+      <c r="IQ2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="IR2" s="6" t="s">
+      <c r="IR2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="IS2" s="11" t="s">
+      <c r="IS2" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <f>'[1]PYG PRESUPUESTO'!D$57</f>
         <v>32790.077908983025</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <f>'[1]PYG PRESUPUESTO'!E$57</f>
         <v>32128.51999336536</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>'[1]PYG PRESUPUESTO'!F$57</f>
         <v>37128.281537396892</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f>'[1]PYG PRESUPUESTO'!G$57</f>
         <v>36248.373382015947</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f>'[1]PYG PRESUPUESTO'!H$57</f>
         <v>35987.711776337484</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <f>'[1]PYG PRESUPUESTO'!I$57</f>
         <v>34904.228120450076</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <f>'[1]PYG PRESUPUESTO'!J$57</f>
         <v>36037.159659434183</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <f>'[1]PYG PRESUPUESTO'!K$57</f>
         <v>34312.458634863899</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <f>'[1]PYG PRESUPUESTO'!L$57</f>
         <v>33945.279755463183</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <f>'[1]PYG PRESUPUESTO'!M$57</f>
         <v>35289.013715147557</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <f>'[1]PYG PRESUPUESTO'!N$57</f>
         <v>34484.083313307143</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="10">
         <f>'[1]PYG PRESUPUESTO'!O$57</f>
         <v>36786.444008420447</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <f>'[2]PYG PRESUPUESTO'!D$60</f>
         <v>30695.298207016058</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <f>'[2]PYG PRESUPUESTO'!E$60</f>
         <v>30416.557877666655</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <f>'[2]PYG PRESUPUESTO'!F$60</f>
         <v>33697.311141683407</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <f>'[2]PYG PRESUPUESTO'!G$60</f>
         <v>34520.567238962773</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <f>'[2]PYG PRESUPUESTO'!H$60</f>
         <v>33517.787777975129</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <f>'[2]PYG PRESUPUESTO'!I$60</f>
         <v>33378.235074134049</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <f>'[2]PYG PRESUPUESTO'!J$60</f>
         <v>34680.569732790282</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <f>'[2]PYG PRESUPUESTO'!K$60</f>
         <v>34500.370875939581</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <f>'[2]PYG PRESUPUESTO'!L$60</f>
         <v>34105.142513812476</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <f>'[2]PYG PRESUPUESTO'!M$60</f>
         <v>35446.46405673134</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <f>'[2]PYG PRESUPUESTO'!N$60</f>
         <v>35438.632976379384</v>
       </c>
-      <c r="Y3" s="12">
+      <c r="Y3" s="10">
         <f>'[2]PYG PRESUPUESTO'!O$60</f>
         <v>35205.804590990723</v>
       </c>
-      <c r="Z3" s="15"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="15">
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+      <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="12">
         <f>'[3]PYG PRESUPUESTO'!D$61</f>
         <v>48702.885915624407</v>
       </c>
-      <c r="AM3" s="15">
+      <c r="AM3" s="12">
         <f>'[3]PYG PRESUPUESTO'!E$61</f>
         <v>49126.667453218142</v>
       </c>
-      <c r="AN3" s="15">
+      <c r="AN3" s="12">
         <f>'[3]PYG PRESUPUESTO'!F$61</f>
         <v>52658.899769440875</v>
       </c>
-      <c r="AO3" s="15">
+      <c r="AO3" s="12">
         <f>'[3]PYG PRESUPUESTO'!G$61</f>
         <v>52171.507684440585</v>
       </c>
-      <c r="AP3" s="15">
+      <c r="AP3" s="12">
         <f>'[3]PYG PRESUPUESTO'!H$61</f>
         <v>53819.20806508878</v>
       </c>
-      <c r="AQ3" s="15">
+      <c r="AQ3" s="12">
         <f>'[3]PYG PRESUPUESTO'!I$61</f>
         <v>54771.35983740518</v>
       </c>
-      <c r="AR3" s="15">
+      <c r="AR3" s="12">
         <f>'[3]PYG PRESUPUESTO'!J$61</f>
         <v>57141.011161915405</v>
       </c>
-      <c r="AS3" s="15">
+      <c r="AS3" s="12">
         <f>'[3]PYG PRESUPUESTO'!K$61</f>
         <v>58398.548847401966</v>
       </c>
-      <c r="AT3" s="15">
+      <c r="AT3" s="12">
         <f>'[3]PYG PRESUPUESTO'!L$61</f>
         <v>59436.635763009799</v>
       </c>
-      <c r="AU3" s="15">
+      <c r="AU3" s="12">
         <f>'[3]PYG PRESUPUESTO'!M$61</f>
         <v>61032.265569597606</v>
       </c>
-      <c r="AV3" s="15">
+      <c r="AV3" s="12">
         <f>'[3]PYG PRESUPUESTO'!N$61</f>
         <v>61699.402000504619</v>
       </c>
-      <c r="AW3" s="12">
+      <c r="AW3" s="10">
         <f>'[3]PYG PRESUPUESTO'!O$61</f>
         <v>62378.801356091462</v>
       </c>
-      <c r="AX3" s="15">
+      <c r="AX3" s="12">
         <f>'[4]PYG PRESUPUESTO'!D$63</f>
         <v>61331.798002306605</v>
       </c>
-      <c r="AY3" s="15">
+      <c r="AY3" s="12">
         <f>'[4]PYG PRESUPUESTO'!E$63</f>
         <v>60674.786562767847</v>
       </c>
-      <c r="AZ3" s="15">
+      <c r="AZ3" s="12">
         <f>'[4]PYG PRESUPUESTO'!F$63</f>
         <v>65608.881801703508</v>
       </c>
-      <c r="BA3" s="15">
+      <c r="BA3" s="12">
         <f>'[4]PYG PRESUPUESTO'!G$63</f>
         <v>64808.020317109447</v>
       </c>
-      <c r="BB3" s="15">
+      <c r="BB3" s="12">
         <f>'[4]PYG PRESUPUESTO'!H$63</f>
         <v>66398.538399304147</v>
       </c>
-      <c r="BC3" s="15">
+      <c r="BC3" s="12">
         <f>'[4]PYG PRESUPUESTO'!I$63</f>
         <v>66731.439805295973</v>
       </c>
-      <c r="BD3" s="15">
+      <c r="BD3" s="12">
         <f>'[4]PYG PRESUPUESTO'!J$63</f>
         <v>67152.326625880232</v>
       </c>
-      <c r="BE3" s="15">
+      <c r="BE3" s="12">
         <f>'[4]PYG PRESUPUESTO'!K$63</f>
         <v>69223.898253083564</v>
       </c>
-      <c r="BF3" s="15">
+      <c r="BF3" s="12">
         <f>'[4]PYG PRESUPUESTO'!L$63</f>
         <v>69391.287762713371</v>
       </c>
-      <c r="BG3" s="15">
+      <c r="BG3" s="12">
         <f>'[4]PYG PRESUPUESTO'!M$63</f>
         <v>71003.94222564307</v>
       </c>
-      <c r="BH3" s="15">
+      <c r="BH3" s="12">
         <f>'[4]PYG PRESUPUESTO'!N$63</f>
         <v>72013.463669955192</v>
       </c>
-      <c r="BI3" s="12">
+      <c r="BI3" s="10">
         <f>'[4]PYG PRESUPUESTO'!O$63</f>
         <v>82593.712888649694</v>
       </c>
-      <c r="BJ3" s="15">
+      <c r="BJ3" s="12">
         <f>'[5]PYG PRESUPUESTO'!D$63</f>
         <v>56511.270921737152</v>
       </c>
-      <c r="BK3" s="15">
+      <c r="BK3" s="12">
         <f>'[5]PYG PRESUPUESTO'!E$63</f>
         <v>55643.0021232695</v>
       </c>
-      <c r="BL3" s="15">
+      <c r="BL3" s="12">
         <f>'[5]PYG PRESUPUESTO'!F$63</f>
         <v>63497.384954216272</v>
       </c>
-      <c r="BM3" s="15">
+      <c r="BM3" s="12">
         <f>'[5]PYG PRESUPUESTO'!G$63</f>
         <v>58537.33033389756</v>
       </c>
-      <c r="BN3" s="15">
+      <c r="BN3" s="12">
         <f>'[5]PYG PRESUPUESTO'!H$63</f>
         <v>60571.264168359397</v>
       </c>
-      <c r="BO3" s="15">
+      <c r="BO3" s="12">
         <f>'[5]PYG PRESUPUESTO'!I$63</f>
         <v>61455.772903641722</v>
       </c>
-      <c r="BP3" s="15">
+      <c r="BP3" s="12">
         <f>'[5]PYG PRESUPUESTO'!J$63</f>
         <v>66337.000703474798</v>
       </c>
-      <c r="BQ3" s="15">
+      <c r="BQ3" s="12">
         <f>'[5]PYG PRESUPUESTO'!K$63</f>
         <v>66243.467107830395</v>
       </c>
-      <c r="BR3" s="15">
+      <c r="BR3" s="12">
         <f>'[5]PYG PRESUPUESTO'!L$63</f>
         <v>65126.618559629576</v>
       </c>
-      <c r="BS3" s="15">
+      <c r="BS3" s="12">
         <f>'[5]PYG PRESUPUESTO'!M$63</f>
         <v>65809.724506028433</v>
       </c>
-      <c r="BT3" s="15">
+      <c r="BT3" s="12">
         <f>'[5]PYG PRESUPUESTO'!N$63</f>
         <v>68812.047016905606</v>
       </c>
-      <c r="BU3" s="12">
+      <c r="BU3" s="10">
         <f>'[5]PYG PRESUPUESTO'!O$63</f>
         <v>75367.344535418175</v>
       </c>
-      <c r="BV3" s="15">
+      <c r="BV3" s="12">
         <f>'[6]PYG PRESUPUESTO'!D$63</f>
         <v>61650.117977190799</v>
       </c>
-      <c r="BW3" s="15">
+      <c r="BW3" s="12">
         <f>'[6]PYG PRESUPUESTO'!E$63</f>
         <v>69276.649879479344</v>
       </c>
-      <c r="BX3" s="15">
+      <c r="BX3" s="12">
         <f>'[6]PYG PRESUPUESTO'!F$63</f>
         <v>58076.795237136474</v>
       </c>
-      <c r="BY3" s="15">
+      <c r="BY3" s="12">
         <f>'[6]PYG PRESUPUESTO'!G$63</f>
         <v>57135.374455117715</v>
       </c>
-      <c r="BZ3" s="15">
+      <c r="BZ3" s="12">
         <f>'[6]PYG PRESUPUESTO'!H$63</f>
         <v>62480.582996670542</v>
       </c>
-      <c r="CA3" s="15">
+      <c r="CA3" s="12">
         <f>'[6]PYG PRESUPUESTO'!I$63</f>
         <v>58484.775860981325</v>
       </c>
-      <c r="CB3" s="15">
+      <c r="CB3" s="12">
         <f>'[6]PYG PRESUPUESTO'!J$63</f>
         <v>59196.954618506999</v>
       </c>
-      <c r="CC3" s="15">
+      <c r="CC3" s="12">
         <f>'[6]PYG PRESUPUESTO'!K$63</f>
         <v>60484.095847184246</v>
       </c>
-      <c r="CD3" s="15">
+      <c r="CD3" s="12">
         <f>'[6]PYG PRESUPUESTO'!L$63</f>
         <v>61384.625898967228</v>
       </c>
-      <c r="CE3" s="15">
+      <c r="CE3" s="12">
         <f>'[6]PYG PRESUPUESTO'!M$63</f>
         <v>62885.479902983796</v>
       </c>
-      <c r="CF3" s="15">
+      <c r="CF3" s="12">
         <f>'[6]PYG PRESUPUESTO'!N$63</f>
         <v>63364.685394820444</v>
       </c>
-      <c r="CG3" s="12">
+      <c r="CG3" s="10">
         <f>'[6]PYG PRESUPUESTO'!O$63</f>
         <v>65927.099982887041</v>
       </c>
-      <c r="CH3" s="15">
+      <c r="CH3" s="12">
         <f>'[7]PYG PRESUPUESTO'!D$63</f>
         <v>63725.229914205935</v>
       </c>
-      <c r="CI3" s="15">
+      <c r="CI3" s="12">
         <f>'[7]PYG PRESUPUESTO'!E$63</f>
         <v>65415.265259352978</v>
       </c>
-      <c r="CJ3" s="15">
+      <c r="CJ3" s="12">
         <f>'[7]PYG PRESUPUESTO'!F$63</f>
         <v>70368.514697734805</v>
       </c>
-      <c r="CK3" s="15">
+      <c r="CK3" s="12">
         <f>'[7]PYG PRESUPUESTO'!G$63</f>
         <v>69374.077526891735</v>
       </c>
-      <c r="CL3" s="15">
+      <c r="CL3" s="12">
         <f>'[7]PYG PRESUPUESTO'!H$63</f>
         <v>70818.204072076362</v>
       </c>
-      <c r="CM3" s="15">
+      <c r="CM3" s="12">
         <f>'[7]PYG PRESUPUESTO'!I$63</f>
         <v>69888.728750856215</v>
       </c>
-      <c r="CN3" s="15">
+      <c r="CN3" s="12">
         <f>'[7]PYG PRESUPUESTO'!J$63</f>
         <v>71207.490530704876</v>
       </c>
-      <c r="CO3" s="15">
+      <c r="CO3" s="12">
         <f>'[7]PYG PRESUPUESTO'!K$63</f>
         <v>72055.689724337324</v>
       </c>
-      <c r="CP3" s="15">
+      <c r="CP3" s="12">
         <f>'[7]PYG PRESUPUESTO'!L$63</f>
         <v>72919.743963731147</v>
       </c>
-      <c r="CQ3" s="15">
+      <c r="CQ3" s="12">
         <f>'[7]PYG PRESUPUESTO'!M$63</f>
         <v>75234.579967030309</v>
       </c>
-      <c r="CR3" s="15">
+      <c r="CR3" s="12">
         <f>'[7]PYG PRESUPUESTO'!N$63</f>
         <v>75289.523450518114</v>
       </c>
-      <c r="CS3" s="12">
+      <c r="CS3" s="10">
         <f>'[7]PYG PRESUPUESTO'!O$63</f>
         <v>79405.445935437034</v>
       </c>
-      <c r="CT3" s="15">
+      <c r="CT3" s="12">
         <f>'[8]PYG PRESUPUESTO'!C$65</f>
         <v>82128.103555092719</v>
       </c>
-      <c r="CU3" s="15">
+      <c r="CU3" s="12">
         <f>'[8]PYG PRESUPUESTO'!D$65</f>
         <v>79724.534947023261</v>
       </c>
-      <c r="CV3" s="15">
+      <c r="CV3" s="12">
         <f>'[8]PYG PRESUPUESTO'!E$65</f>
         <v>90636.787861366858</v>
       </c>
-      <c r="CW3" s="15">
+      <c r="CW3" s="12">
         <f>'[8]PYG PRESUPUESTO'!F$65</f>
         <v>78875.848020440608</v>
       </c>
-      <c r="CX3" s="15">
+      <c r="CX3" s="12">
         <f>'[8]PYG PRESUPUESTO'!G$65</f>
         <v>84316.561715054748</v>
       </c>
-      <c r="CY3" s="15">
+      <c r="CY3" s="12">
         <f>'[8]PYG PRESUPUESTO'!H$65</f>
         <v>81591.628930762308</v>
       </c>
-      <c r="CZ3" s="15">
+      <c r="CZ3" s="12">
         <f>'[8]PYG PRESUPUESTO'!I$65</f>
         <v>82143.602919138953</v>
       </c>
-      <c r="DA3" s="15">
+      <c r="DA3" s="12">
         <f>'[8]PYG PRESUPUESTO'!J$65</f>
         <v>82372.110876232255</v>
       </c>
-      <c r="DB3" s="15">
+      <c r="DB3" s="12">
         <f>'[8]PYG PRESUPUESTO'!K$65</f>
         <v>83426.735220732327</v>
       </c>
-      <c r="DC3" s="15">
+      <c r="DC3" s="12">
         <f>'[8]PYG PRESUPUESTO'!L$65</f>
         <v>85756.241653853765</v>
       </c>
-      <c r="DD3" s="15">
+      <c r="DD3" s="12">
         <f>'[8]PYG PRESUPUESTO'!M$65</f>
         <v>86588.919003799107</v>
       </c>
-      <c r="DE3" s="12">
+      <c r="DE3" s="10">
         <f>'[8]PYG PRESUPUESTO'!N$65</f>
         <v>87389.131249876067</v>
       </c>
-      <c r="DF3" s="15">
+      <c r="DF3" s="12">
         <f>'[9]PYG PRESUPUESTO'!C$65</f>
         <v>75661.628297290517</v>
       </c>
-      <c r="DG3" s="15">
+      <c r="DG3" s="12">
         <f>'[9]PYG PRESUPUESTO'!D$65</f>
         <v>74663.431089441758</v>
       </c>
-      <c r="DH3" s="15">
+      <c r="DH3" s="12">
         <f>'[9]PYG PRESUPUESTO'!E$65</f>
         <v>77748.724676647937</v>
       </c>
-      <c r="DI3" s="15">
+      <c r="DI3" s="12">
         <f>'[9]PYG PRESUPUESTO'!F$65</f>
         <v>81918.32014703007</v>
       </c>
-      <c r="DJ3" s="15">
+      <c r="DJ3" s="12">
         <f>'[9]PYG PRESUPUESTO'!G$65</f>
         <v>79936.927433566729</v>
       </c>
-      <c r="DK3" s="15">
+      <c r="DK3" s="12">
         <f>'[9]PYG PRESUPUESTO'!H$65</f>
         <v>80986.672704775876</v>
       </c>
-      <c r="DL3" s="15">
+      <c r="DL3" s="12">
         <f>'[9]PYG PRESUPUESTO'!I$65</f>
         <v>82157.333083374542</v>
       </c>
-      <c r="DM3" s="15">
+      <c r="DM3" s="12">
         <f>'[9]PYG PRESUPUESTO'!J$65</f>
         <v>83188.122126282455</v>
       </c>
-      <c r="DN3" s="15">
+      <c r="DN3" s="12">
         <f>'[9]PYG PRESUPUESTO'!K$65</f>
         <v>85693.698487573871</v>
       </c>
-      <c r="DO3" s="15">
+      <c r="DO3" s="12">
         <f>'[9]PYG PRESUPUESTO'!L$65</f>
         <v>86354.455163383638</v>
       </c>
-      <c r="DP3" s="15">
+      <c r="DP3" s="12">
         <f>'[9]PYG PRESUPUESTO'!M$65</f>
         <v>92969.208679682037</v>
       </c>
-      <c r="DQ3" s="12">
+      <c r="DQ3" s="10">
         <f>'[9]PYG PRESUPUESTO'!N$65</f>
         <v>88718.739659897241</v>
       </c>
-      <c r="DR3" s="15">
+      <c r="DR3" s="12">
         <f>'[10]PYG PRESUPUESTO'!C$65</f>
         <v>81104.713611400774</v>
       </c>
-      <c r="DS3" s="15">
+      <c r="DS3" s="12">
         <f>'[10]PYG PRESUPUESTO'!D$65</f>
         <v>79129.257307517881</v>
       </c>
-      <c r="DT3" s="15">
+      <c r="DT3" s="12">
         <f>'[10]PYG PRESUPUESTO'!E$65</f>
         <v>83137.781314644322</v>
       </c>
-      <c r="DU3" s="15">
+      <c r="DU3" s="12">
         <f>'[10]PYG PRESUPUESTO'!F$65</f>
         <v>85086.874362168484</v>
       </c>
-      <c r="DV3" s="15">
+      <c r="DV3" s="12">
         <f>'[10]PYG PRESUPUESTO'!G$65</f>
         <v>85512.985221940908</v>
       </c>
-      <c r="DW3" s="15">
+      <c r="DW3" s="12">
         <f>'[10]PYG PRESUPUESTO'!H$65</f>
         <v>85712.329610397734</v>
       </c>
-      <c r="DX3" s="15">
+      <c r="DX3" s="12">
         <f>'[10]PYG PRESUPUESTO'!I$65</f>
         <v>87644.021569282559</v>
       </c>
-      <c r="DY3" s="15">
+      <c r="DY3" s="12">
         <f>'[10]PYG PRESUPUESTO'!J$65</f>
         <v>88634.974852048166</v>
       </c>
-      <c r="DZ3" s="15">
+      <c r="DZ3" s="12">
         <f>'[10]PYG PRESUPUESTO'!K$65</f>
         <v>89190.834807761785</v>
       </c>
-      <c r="EA3" s="15">
+      <c r="EA3" s="12">
         <f>'[10]PYG PRESUPUESTO'!L$65</f>
         <v>93530.233742057608</v>
       </c>
-      <c r="EB3" s="15">
+      <c r="EB3" s="12">
         <f>'[10]PYG PRESUPUESTO'!M$65</f>
         <v>91582.97620584078</v>
       </c>
-      <c r="EC3" s="12">
+      <c r="EC3" s="10">
         <f>'[10]PYG PRESUPUESTO'!N$65</f>
         <v>92675.767449560211</v>
       </c>
-      <c r="ED3" s="15">
+      <c r="ED3" s="12">
         <f>'[11]PYG PRESUPUESTO'!C$65</f>
         <v>94002.141922815194</v>
       </c>
-      <c r="EE3" s="15">
+      <c r="EE3" s="12">
         <f>'[11]PYG PRESUPUESTO'!D$65</f>
         <v>105113.82329688196</v>
       </c>
-      <c r="EF3" s="15">
+      <c r="EF3" s="12">
         <f>'[11]PYG PRESUPUESTO'!E$65</f>
         <v>99048.733206051271</v>
       </c>
-      <c r="EG3" s="15">
+      <c r="EG3" s="12">
         <f>'[11]PYG PRESUPUESTO'!F$65</f>
         <v>100308.00900040563</v>
       </c>
-      <c r="EH3" s="15">
+      <c r="EH3" s="12">
         <f>'[11]PYG PRESUPUESTO'!G$65</f>
         <v>102346.79246108439</v>
       </c>
-      <c r="EI3" s="15">
+      <c r="EI3" s="12">
         <f>'[11]PYG PRESUPUESTO'!H$65</f>
         <v>109585.26537884009</v>
       </c>
-      <c r="EJ3" s="15">
+      <c r="EJ3" s="12">
         <f>'[11]PYG PRESUPUESTO'!I$65</f>
         <v>104784.66335598506</v>
       </c>
-      <c r="EK3" s="15">
+      <c r="EK3" s="12">
         <f>'[11]PYG PRESUPUESTO'!J$65</f>
         <v>105669.02344344066</v>
       </c>
-      <c r="EL3" s="15">
+      <c r="EL3" s="12">
         <f>'[11]PYG PRESUPUESTO'!K$65</f>
         <v>106979.28137642935</v>
       </c>
-      <c r="EM3" s="15">
+      <c r="EM3" s="12">
         <f>'[11]PYG PRESUPUESTO'!L$65</f>
         <v>109727.74996320512</v>
       </c>
-      <c r="EN3" s="15">
+      <c r="EN3" s="12">
         <f>'[11]PYG PRESUPUESTO'!M$65</f>
         <v>109428.79851727575</v>
       </c>
-      <c r="EO3" s="12">
+      <c r="EO3" s="10">
         <f>'[11]PYG PRESUPUESTO'!N$65</f>
         <v>110919.09727981225</v>
       </c>
-      <c r="EP3" s="15">
+      <c r="EP3" s="12">
         <f>'[12]PYG PRESUPUESTO'!C$65</f>
         <v>110046.25041353916</v>
       </c>
-      <c r="EQ3" s="15">
+      <c r="EQ3" s="12">
         <f>'[12]PYG PRESUPUESTO'!D$65</f>
         <v>110451.60967493658</v>
       </c>
-      <c r="ER3" s="15">
+      <c r="ER3" s="12">
         <f>'[12]PYG PRESUPUESTO'!E$65</f>
         <v>116046.67053989266</v>
       </c>
-      <c r="ES3" s="15">
+      <c r="ES3" s="12">
         <f>'[12]PYG PRESUPUESTO'!F$65</f>
         <v>116278.28494302968</v>
       </c>
-      <c r="ET3" s="15">
+      <c r="ET3" s="12">
         <f>'[12]PYG PRESUPUESTO'!G$65</f>
         <v>118270.08682325455</v>
       </c>
-      <c r="EU3" s="15">
+      <c r="EU3" s="12">
         <f>'[12]PYG PRESUPUESTO'!H$65</f>
         <v>117211.40887783363</v>
       </c>
-      <c r="EV3" s="15">
+      <c r="EV3" s="12">
         <f>'[12]PYG PRESUPUESTO'!I$65</f>
         <v>118196.96254894293</v>
       </c>
-      <c r="EW3" s="15">
+      <c r="EW3" s="12">
         <f>'[12]PYG PRESUPUESTO'!J$65</f>
         <v>120037.29332810911</v>
       </c>
-      <c r="EX3" s="15">
+      <c r="EX3" s="12">
         <f>'[12]PYG PRESUPUESTO'!K$65</f>
         <v>120845.25650947778</v>
       </c>
-      <c r="EY3" s="15">
+      <c r="EY3" s="12">
         <f>'[12]PYG PRESUPUESTO'!L$65</f>
         <v>123472.37037692472</v>
       </c>
-      <c r="EZ3" s="15">
+      <c r="EZ3" s="12">
         <f>'[12]PYG PRESUPUESTO'!M$65</f>
         <v>123229.85774917391</v>
       </c>
-      <c r="FA3" s="12">
+      <c r="FA3" s="10">
         <f>'[12]PYG PRESUPUESTO'!N$65</f>
         <v>124781.59192890166</v>
       </c>
-      <c r="FB3" s="15">
+      <c r="FB3" s="12">
         <f>'[13]PYG PRESUPUESTO'!C$65</f>
         <v>111766.75973875808</v>
       </c>
-      <c r="FC3" s="15">
+      <c r="FC3" s="12">
         <f>'[13]PYG PRESUPUESTO'!D$65</f>
         <v>111455.1811916062</v>
       </c>
-      <c r="FD3" s="15">
+      <c r="FD3" s="12">
         <f>'[13]PYG PRESUPUESTO'!E$65</f>
         <v>114055.37609214673</v>
       </c>
-      <c r="FE3" s="15">
+      <c r="FE3" s="12">
         <f>'[13]PYG PRESUPUESTO'!F$65</f>
         <v>115746.66478627927</v>
       </c>
-      <c r="FF3" s="15">
+      <c r="FF3" s="12">
         <f>'[13]PYG PRESUPUESTO'!G$65</f>
         <v>115144.86392548197</v>
       </c>
-      <c r="FG3" s="15">
+      <c r="FG3" s="12">
         <f>'[13]PYG PRESUPUESTO'!H$65</f>
         <v>115913.91510009723</v>
       </c>
-      <c r="FH3" s="15">
+      <c r="FH3" s="12">
         <f>'[13]PYG PRESUPUESTO'!I$65</f>
         <v>117374.50767059723</v>
       </c>
-      <c r="FI3" s="15">
+      <c r="FI3" s="12">
         <f>'[13]PYG PRESUPUESTO'!J$65</f>
         <v>119147.34203527408</v>
       </c>
-      <c r="FJ3" s="15">
+      <c r="FJ3" s="12">
         <f>'[13]PYG PRESUPUESTO'!K$65</f>
         <v>120192.36494956026</v>
       </c>
-      <c r="FK3" s="15">
+      <c r="FK3" s="12">
         <f>'[13]PYG PRESUPUESTO'!L$65</f>
         <v>122677.65001584658</v>
       </c>
-      <c r="FL3" s="15">
+      <c r="FL3" s="12">
         <f>'[13]PYG PRESUPUESTO'!M$65</f>
         <v>123233.65715497665</v>
       </c>
-      <c r="FM3" s="12">
+      <c r="FM3" s="10">
         <f>'[13]PYG PRESUPUESTO'!N$65</f>
         <v>124854.34105056558</v>
       </c>
-      <c r="FN3" s="15">
+      <c r="FN3" s="12">
         <f>'[14]PYG PRESUPUESTO'!C$65</f>
         <v>121465.31637029511</v>
       </c>
-      <c r="FO3" s="15">
+      <c r="FO3" s="12">
         <f>'[14]PYG PRESUPUESTO'!D$65</f>
         <v>121648.62054242735</v>
       </c>
-      <c r="FP3" s="15">
+      <c r="FP3" s="12">
         <f>'[14]PYG PRESUPUESTO'!E$65</f>
         <v>126746.69000807041</v>
       </c>
-      <c r="FQ3" s="15">
+      <c r="FQ3" s="12">
         <f>'[14]PYG PRESUPUESTO'!F$65</f>
         <v>123751.86369757801</v>
       </c>
-      <c r="FR3" s="15">
+      <c r="FR3" s="12">
         <f>'[14]PYG PRESUPUESTO'!G$65</f>
         <v>125891.86988606205</v>
       </c>
-      <c r="FS3" s="15">
+      <c r="FS3" s="12">
         <f>'[14]PYG PRESUPUESTO'!H$65</f>
         <v>127389.52684381041</v>
       </c>
-      <c r="FT3" s="15">
+      <c r="FT3" s="12">
         <f>'[14]PYG PRESUPUESTO'!I$65</f>
         <v>128289.67096645222</v>
       </c>
-      <c r="FU3" s="15">
+      <c r="FU3" s="12">
         <f>'[14]PYG PRESUPUESTO'!J$65</f>
         <v>130315.2769492926</v>
       </c>
-      <c r="FV3" s="15">
+      <c r="FV3" s="12">
         <f>'[14]PYG PRESUPUESTO'!K$65</f>
         <v>131617.87462823477</v>
       </c>
-      <c r="FW3" s="15">
+      <c r="FW3" s="12">
         <f>'[14]PYG PRESUPUESTO'!L$65</f>
         <v>133381.38044527266</v>
       </c>
-      <c r="FX3" s="15">
+      <c r="FX3" s="12">
         <f>'[14]PYG PRESUPUESTO'!M$65</f>
         <v>135099.31163825435</v>
       </c>
-      <c r="FY3" s="12">
+      <c r="FY3" s="10">
         <f>'[14]PYG PRESUPUESTO'!N$65</f>
         <v>135786.94734105302</v>
       </c>
-      <c r="FZ3" s="15">
+      <c r="FZ3" s="12">
         <f>'[15]PYG PRESUPUESTO'!C$65</f>
         <v>124923.91745179573</v>
       </c>
-      <c r="GA3" s="15">
+      <c r="GA3" s="12">
         <f>'[15]PYG PRESUPUESTO'!D$65</f>
         <v>124827.16979065583</v>
       </c>
-      <c r="GB3" s="15">
+      <c r="GB3" s="12">
         <f>'[15]PYG PRESUPUESTO'!E$65</f>
         <v>131211.29938636711</v>
       </c>
-      <c r="GC3" s="15">
+      <c r="GC3" s="12">
         <f>'[15]PYG PRESUPUESTO'!F$65</f>
         <v>128177.39678431301</v>
       </c>
-      <c r="GD3" s="15">
+      <c r="GD3" s="12">
         <f>'[15]PYG PRESUPUESTO'!G$65</f>
         <v>131102.6252164295</v>
       </c>
-      <c r="GE3" s="15">
+      <c r="GE3" s="12">
         <f>'[15]PYG PRESUPUESTO'!H$65</f>
         <v>131499.05851101718</v>
       </c>
-      <c r="GF3" s="15">
+      <c r="GF3" s="12">
         <f>'[15]PYG PRESUPUESTO'!I$65</f>
         <v>133792.32531281721</v>
       </c>
-      <c r="GG3" s="15">
+      <c r="GG3" s="12">
         <f>'[15]PYG PRESUPUESTO'!J$65</f>
         <v>137941.92761732748</v>
       </c>
-      <c r="GH3" s="15">
+      <c r="GH3" s="12">
         <f>'[15]PYG PRESUPUESTO'!K$65</f>
         <v>138650.5588539459</v>
       </c>
-      <c r="GI3" s="15">
+      <c r="GI3" s="12">
         <f>'[15]PYG PRESUPUESTO'!L$65</f>
         <v>144109.76682101368</v>
       </c>
-      <c r="GJ3" s="15">
+      <c r="GJ3" s="12">
         <f>'[15]PYG PRESUPUESTO'!M$65</f>
         <v>146772.79121668485</v>
       </c>
-      <c r="GK3" s="12">
+      <c r="GK3" s="10">
         <f>'[15]PYG PRESUPUESTO'!N$65</f>
         <v>149062.19419518736</v>
       </c>
-      <c r="GL3" s="15">
+      <c r="GL3" s="12">
         <f>'[16]PYG PRESUPUESTO'!C$65</f>
         <v>110671.71154399018</v>
       </c>
-      <c r="GM3" s="15">
+      <c r="GM3" s="12">
         <f>'[16]PYG PRESUPUESTO'!D$65</f>
         <v>109789.74791661922</v>
       </c>
-      <c r="GN3" s="15">
+      <c r="GN3" s="12">
         <f>'[16]PYG PRESUPUESTO'!E$65</f>
         <v>114855.02821951879</v>
       </c>
-      <c r="GO3" s="15">
+      <c r="GO3" s="12">
         <f>'[16]PYG PRESUPUESTO'!F$65</f>
         <v>112220.30526581018</v>
       </c>
-      <c r="GP3" s="15">
+      <c r="GP3" s="12">
         <f>'[16]PYG PRESUPUESTO'!G$65</f>
         <v>113494.85434162416</v>
       </c>
-      <c r="GQ3" s="15">
+      <c r="GQ3" s="12">
         <f>'[16]PYG PRESUPUESTO'!H$65</f>
         <v>114477.43824170801</v>
       </c>
-      <c r="GR3" s="15">
+      <c r="GR3" s="12">
         <f>'[16]PYG PRESUPUESTO'!I$65</f>
         <v>115497.71400717743</v>
       </c>
-      <c r="GS3" s="15">
+      <c r="GS3" s="12">
         <f>'[16]PYG PRESUPUESTO'!J$65</f>
         <v>116669.23089703386</v>
       </c>
-      <c r="GT3" s="15">
+      <c r="GT3" s="12">
         <f>'[16]PYG PRESUPUESTO'!K$65</f>
         <v>118003.68620703403</v>
       </c>
-      <c r="GU3" s="15">
+      <c r="GU3" s="12">
         <f>'[16]PYG PRESUPUESTO'!L$65</f>
         <v>118447.8430856968</v>
       </c>
-      <c r="GV3" s="15">
+      <c r="GV3" s="12">
         <f>'[16]PYG PRESUPUESTO'!M$65</f>
         <v>120127.62189555583</v>
       </c>
-      <c r="GW3" s="12">
+      <c r="GW3" s="10">
         <f>'[16]PYG PRESUPUESTO'!N$65</f>
         <v>120606.2958580289</v>
       </c>
-      <c r="GX3" s="15">
+      <c r="GX3" s="12">
         <f>'[17]PYG PRESUPUESTO'!C$65</f>
         <v>115220.00252379446</v>
       </c>
-      <c r="GY3" s="15">
+      <c r="GY3" s="12">
         <f>'[17]PYG PRESUPUESTO'!D$65</f>
         <v>116159.96166897743</v>
       </c>
-      <c r="GZ3" s="15">
+      <c r="GZ3" s="12">
         <f>'[17]PYG PRESUPUESTO'!E$65</f>
         <v>126448.1769818617</v>
       </c>
-      <c r="HA3" s="15">
+      <c r="HA3" s="12">
         <f>'[17]PYG PRESUPUESTO'!F$65</f>
         <v>123123.12980628374</v>
       </c>
-      <c r="HB3" s="15">
+      <c r="HB3" s="12">
         <f>'[17]PYG PRESUPUESTO'!G$65</f>
         <v>126329.88046460063</v>
       </c>
-      <c r="HC3" s="15">
+      <c r="HC3" s="12">
         <f>'[17]PYG PRESUPUESTO'!H$65</f>
         <v>129474.71135746018</v>
       </c>
-      <c r="HD3" s="15">
+      <c r="HD3" s="12">
         <f>'[17]PYG PRESUPUESTO'!I$65</f>
         <v>130692.43069344833</v>
       </c>
-      <c r="HE3" s="15">
+      <c r="HE3" s="12">
         <f>'[17]PYG PRESUPUESTO'!J$65</f>
         <v>134278.89391026655</v>
       </c>
-      <c r="HF3" s="15">
+      <c r="HF3" s="12">
         <f>'[17]PYG PRESUPUESTO'!K$65</f>
         <v>136149.26468689731</v>
       </c>
-      <c r="HG3" s="15">
+      <c r="HG3" s="12">
         <f>'[17]PYG PRESUPUESTO'!L$65</f>
         <v>139919.22720250391</v>
       </c>
-      <c r="HH3" s="15">
+      <c r="HH3" s="12">
         <f>'[17]PYG PRESUPUESTO'!M$65</f>
         <v>142288.46809269104</v>
       </c>
-      <c r="HI3" s="12">
+      <c r="HI3" s="10">
         <f>'[17]PYG PRESUPUESTO'!N$65</f>
         <v>145135.13501523802</v>
       </c>
-      <c r="HJ3" s="15">
+      <c r="HJ3" s="12">
         <f>'[18]PYG PRESUPUESTO'!C$65</f>
         <v>172145.82076901247</v>
       </c>
-      <c r="HK3" s="15">
+      <c r="HK3" s="12">
         <f>'[18]PYG PRESUPUESTO'!D$65</f>
         <v>173635.77103101369</v>
       </c>
-      <c r="HL3" s="15">
+      <c r="HL3" s="12">
         <f>'[18]PYG PRESUPUESTO'!E$65</f>
         <v>189277.99339600446</v>
       </c>
-      <c r="HM3" s="15">
+      <c r="HM3" s="12">
         <f>'[18]PYG PRESUPUESTO'!F$65</f>
         <v>184012.47116155495</v>
       </c>
-      <c r="HN3" s="15">
+      <c r="HN3" s="12">
         <f>'[18]PYG PRESUPUESTO'!G$65</f>
         <v>190200.48085718963</v>
       </c>
-      <c r="HO3" s="15">
+      <c r="HO3" s="12">
         <f>'[18]PYG PRESUPUESTO'!H$65</f>
         <v>192344.12311074746</v>
       </c>
-      <c r="HP3" s="15">
+      <c r="HP3" s="12">
         <f>'[18]PYG PRESUPUESTO'!I$65</f>
         <v>194560.40690211888</v>
       </c>
-      <c r="HQ3" s="15">
+      <c r="HQ3" s="12">
         <f>'[18]PYG PRESUPUESTO'!J$65</f>
         <v>198257.70303915458</v>
       </c>
-      <c r="HR3" s="15">
+      <c r="HR3" s="12">
         <f>'[18]PYG PRESUPUESTO'!K$65</f>
         <v>197783.92632597953</v>
       </c>
-      <c r="HS3" s="15">
+      <c r="HS3" s="12">
         <f>'[18]PYG PRESUPUESTO'!L$65</f>
         <v>201403.21685365605</v>
       </c>
-      <c r="HT3" s="15">
+      <c r="HT3" s="12">
         <f>'[18]PYG PRESUPUESTO'!M$65</f>
         <v>203302.19663741507</v>
       </c>
-      <c r="HU3" s="12">
+      <c r="HU3" s="10">
         <f>'[18]PYG PRESUPUESTO'!N$65</f>
         <v>202826.0394818903</v>
       </c>
-      <c r="HV3" s="15">
+      <c r="HV3" s="12">
         <f>'[19]PYG PRESUPUESTO'!C$65</f>
         <v>184151.09840316817</v>
       </c>
-      <c r="HW3" s="15">
+      <c r="HW3" s="12">
         <f>'[19]PYG PRESUPUESTO'!D$65</f>
         <v>177485.76815507616</v>
       </c>
-      <c r="HX3" s="15">
+      <c r="HX3" s="12">
         <f>'[19]PYG PRESUPUESTO'!E$65</f>
         <v>184853.61803973161</v>
       </c>
-      <c r="HY3" s="15">
+      <c r="HY3" s="12">
         <f>'[19]PYG PRESUPUESTO'!F$65</f>
         <v>188536.82765364769</v>
       </c>
-      <c r="HZ3" s="15">
+      <c r="HZ3" s="12">
         <f>'[19]PYG PRESUPUESTO'!G$65</f>
         <v>187880.85699738801</v>
       </c>
-      <c r="IA3" s="15">
+      <c r="IA3" s="12">
         <f>'[19]PYG PRESUPUESTO'!H$65</f>
         <v>182872.13028724998</v>
       </c>
-      <c r="IB3" s="15">
+      <c r="IB3" s="12">
         <f>'[19]PYG PRESUPUESTO'!I$65</f>
         <v>187245.8506458209</v>
       </c>
-      <c r="IC3" s="15">
+      <c r="IC3" s="12">
         <f>'[19]PYG PRESUPUESTO'!J$65</f>
         <v>197882.5025061295</v>
       </c>
-      <c r="ID3" s="15">
+      <c r="ID3" s="12">
         <f>'[19]PYG PRESUPUESTO'!K$65</f>
         <v>198711.18802637421</v>
       </c>
-      <c r="IE3" s="15">
+      <c r="IE3" s="12">
         <f>'[19]PYG PRESUPUESTO'!L$65</f>
         <v>204061.95118324066</v>
       </c>
-      <c r="IF3" s="15">
+      <c r="IF3" s="12">
         <f>'[19]PYG PRESUPUESTO'!M$65</f>
         <v>204386.91615829297</v>
       </c>
-      <c r="IG3" s="12">
+      <c r="IG3" s="10">
         <f>'[19]PYG PRESUPUESTO'!N$65</f>
         <v>209484.50737809532</v>
       </c>
-      <c r="IH3" s="15">
+      <c r="IH3" s="12">
         <f>'[20]PYG PRESUPUESTO'!C$65</f>
         <v>179970.62287676529</v>
       </c>
-      <c r="II3" s="15">
+      <c r="II3" s="12">
         <f>'[20]PYG PRESUPUESTO'!D$65</f>
         <v>176134.48565197026</v>
       </c>
-      <c r="IJ3" s="15">
+      <c r="IJ3" s="12">
         <f>'[20]PYG PRESUPUESTO'!E$65</f>
         <v>189675.95295006272</v>
       </c>
-      <c r="IK3" s="15">
+      <c r="IK3" s="12">
         <f>'[20]PYG PRESUPUESTO'!F$65</f>
         <v>182274.27632318679</v>
       </c>
-      <c r="IL3" s="15">
+      <c r="IL3" s="12">
         <f>'[20]PYG PRESUPUESTO'!G$65</f>
         <v>185302.18837719891</v>
       </c>
-      <c r="IM3" s="15">
+      <c r="IM3" s="12">
         <f>'[20]PYG PRESUPUESTO'!H$65</f>
         <v>182263.15441294626</v>
       </c>
-      <c r="IN3" s="15">
+      <c r="IN3" s="12">
         <f>'[20]PYG PRESUPUESTO'!I$65</f>
         <v>186291.0539210673</v>
       </c>
-      <c r="IO3" s="15">
+      <c r="IO3" s="12">
         <f>'[20]PYG PRESUPUESTO'!J$65</f>
         <v>188210.70411639023</v>
       </c>
-      <c r="IP3" s="15">
+      <c r="IP3" s="12">
         <f>'[20]PYG PRESUPUESTO'!K$65</f>
         <v>188328.31622986845</v>
       </c>
-      <c r="IQ3" s="15">
+      <c r="IQ3" s="12">
         <f>'[20]PYG PRESUPUESTO'!L$65</f>
         <v>189937.41801433597</v>
       </c>
-      <c r="IR3" s="15">
+      <c r="IR3" s="12">
         <f>'[20]PYG PRESUPUESTO'!M$65</f>
         <v>188438.82639765972</v>
       </c>
-      <c r="IS3" s="12">
+      <c r="IS3" s="10">
         <f>'[20]PYG PRESUPUESTO'!N$65</f>
         <v>192556.88572927966</v>
       </c>
     </row>
-    <row r="4" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <f>'[1]PYG PRESUPUESTO'!D$78</f>
         <v>14093.620264434951</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <f>'[1]PYG PRESUPUESTO'!E$78</f>
         <v>13900.049437858104</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>'[1]PYG PRESUPUESTO'!F$78</f>
         <v>14386.374721816268</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f>'[1]PYG PRESUPUESTO'!G$78</f>
         <v>14315.991990494918</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f>'[1]PYG PRESUPUESTO'!H$78</f>
         <v>14489.77260139857</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <f>'[1]PYG PRESUPUESTO'!I$78</f>
         <v>14418.028754992763</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f>'[1]PYG PRESUPUESTO'!J$78</f>
         <v>14617.887918750595</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f>'[1]PYG PRESUPUESTO'!K$78</f>
         <v>14679.565901569938</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f>'[1]PYG PRESUPUESTO'!L$78</f>
         <v>14598.086221905707</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <f>'[1]PYG PRESUPUESTO'!M$78</f>
         <v>14801.535549246313</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <f>'[1]PYG PRESUPUESTO'!N$78</f>
         <v>14709.143342629954</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="10">
         <f>'[1]PYG PRESUPUESTO'!O$78</f>
         <v>14927.300526272693</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <f>'[2]PYG PRESUPUESTO'!D$81</f>
         <v>11929.845301432179</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <f>'[2]PYG PRESUPUESTO'!E$81</f>
         <v>11612.756042107814</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <f>'[2]PYG PRESUPUESTO'!F$81</f>
         <v>12219.583536825376</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <f>'[2]PYG PRESUPUESTO'!G$81</f>
         <v>12256.670245216828</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <f>'[2]PYG PRESUPUESTO'!H$81</f>
         <v>12541.310986274913</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <f>'[2]PYG PRESUPUESTO'!I$81</f>
         <v>12569.501682184005</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <f>'[2]PYG PRESUPUESTO'!J$81</f>
         <v>12841.25629590105</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <f>'[2]PYG PRESUPUESTO'!K$81</f>
         <v>12965.784595218889</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <f>'[2]PYG PRESUPUESTO'!L$81</f>
         <v>12942.554453523537</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <f>'[2]PYG PRESUPUESTO'!M$81</f>
         <v>13227.573975810654</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <f>'[2]PYG PRESUPUESTO'!N$81</f>
         <v>13180.06665324112</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="10">
         <f>'[2]PYG PRESUPUESTO'!O$81</f>
         <v>13561.188079865475</v>
       </c>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="3"/>
-      <c r="AF4" s="3"/>
-      <c r="AG4" s="3"/>
-      <c r="AH4" s="3"/>
-      <c r="AI4" s="3"/>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="15">
+      <c r="Z4" s="12"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="12">
         <f>'[3]PYG PRESUPUESTO'!D$83</f>
         <v>16148.406349484414</v>
       </c>
-      <c r="AM4" s="15">
+      <c r="AM4" s="12">
         <f>'[3]PYG PRESUPUESTO'!E$83</f>
         <v>16443.325839939072</v>
       </c>
-      <c r="AN4" s="15">
+      <c r="AN4" s="12">
         <f>'[3]PYG PRESUPUESTO'!F$83</f>
         <v>17195.569465043904</v>
       </c>
-      <c r="AO4" s="15">
+      <c r="AO4" s="12">
         <f>'[3]PYG PRESUPUESTO'!G$83</f>
         <v>17324.651314703486</v>
       </c>
-      <c r="AP4" s="15">
+      <c r="AP4" s="12">
         <f>'[3]PYG PRESUPUESTO'!H$83</f>
         <v>17943.698743044526</v>
       </c>
-      <c r="AQ4" s="15">
+      <c r="AQ4" s="12">
         <f>'[3]PYG PRESUPUESTO'!I$83</f>
         <v>18257.877630002175</v>
       </c>
-      <c r="AR4" s="15">
+      <c r="AR4" s="12">
         <f>'[3]PYG PRESUPUESTO'!J$83</f>
         <v>18629.571163170131</v>
       </c>
-      <c r="AS4" s="15">
+      <c r="AS4" s="12">
         <f>'[3]PYG PRESUPUESTO'!K$83</f>
         <v>18862.976621251128</v>
       </c>
-      <c r="AT4" s="15">
+      <c r="AT4" s="12">
         <f>'[3]PYG PRESUPUESTO'!L$83</f>
         <v>18742.834521805442</v>
       </c>
-      <c r="AU4" s="15">
+      <c r="AU4" s="12">
         <f>'[3]PYG PRESUPUESTO'!M$83</f>
         <v>18969.628297434101</v>
       </c>
-      <c r="AV4" s="15">
+      <c r="AV4" s="12">
         <f>'[3]PYG PRESUPUESTO'!N$83</f>
         <v>18548.792210220268</v>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="10">
         <f>'[3]PYG PRESUPUESTO'!O$83</f>
         <v>18806.491239585608</v>
       </c>
-      <c r="AX4" s="15">
+      <c r="AX4" s="12">
         <f>'[4]PYG PRESUPUESTO'!D$85</f>
         <v>21230.248937401037</v>
       </c>
-      <c r="AY4" s="15">
+      <c r="AY4" s="12">
         <f>'[4]PYG PRESUPUESTO'!E$85</f>
         <v>20717.547625202518</v>
       </c>
-      <c r="AZ4" s="15">
+      <c r="AZ4" s="12">
         <f>'[4]PYG PRESUPUESTO'!F$85</f>
         <v>20494.133882468475</v>
       </c>
-      <c r="BA4" s="15">
+      <c r="BA4" s="12">
         <f>'[4]PYG PRESUPUESTO'!G$85</f>
         <v>21507.966944576099</v>
       </c>
-      <c r="BB4" s="15">
+      <c r="BB4" s="12">
         <f>'[4]PYG PRESUPUESTO'!H$85</f>
         <v>22099.402830220311</v>
       </c>
-      <c r="BC4" s="15">
+      <c r="BC4" s="12">
         <f>'[4]PYG PRESUPUESTO'!I$85</f>
         <v>21685.169748274333</v>
       </c>
-      <c r="BD4" s="15">
+      <c r="BD4" s="12">
         <f>'[4]PYG PRESUPUESTO'!J$85</f>
         <v>21792.670334259845</v>
       </c>
-      <c r="BE4" s="15">
+      <c r="BE4" s="12">
         <f>'[4]PYG PRESUPUESTO'!K$85</f>
         <v>22880.901615861691</v>
       </c>
-      <c r="BF4" s="15">
+      <c r="BF4" s="12">
         <f>'[4]PYG PRESUPUESTO'!L$85</f>
         <v>22594.048218141899</v>
       </c>
-      <c r="BG4" s="15">
+      <c r="BG4" s="12">
         <f>'[4]PYG PRESUPUESTO'!M$85</f>
         <v>22816.505932854223</v>
       </c>
-      <c r="BH4" s="15">
+      <c r="BH4" s="12">
         <f>'[4]PYG PRESUPUESTO'!N$85</f>
         <v>22396.657885139241</v>
       </c>
-      <c r="BI4" s="12">
+      <c r="BI4" s="10">
         <f>'[4]PYG PRESUPUESTO'!O$85</f>
         <v>23570.554673733128</v>
       </c>
-      <c r="BJ4" s="15">
+      <c r="BJ4" s="12">
         <f>'[5]PYG PRESUPUESTO'!D$85</f>
         <v>13973.354689899539</v>
       </c>
-      <c r="BK4" s="15">
+      <c r="BK4" s="12">
         <f>'[5]PYG PRESUPUESTO'!E$85</f>
         <v>13111.962749757122</v>
       </c>
-      <c r="BL4" s="15">
+      <c r="BL4" s="12">
         <f>'[5]PYG PRESUPUESTO'!F$85</f>
         <v>12987.052039227068</v>
       </c>
-      <c r="BM4" s="15">
+      <c r="BM4" s="12">
         <f>'[5]PYG PRESUPUESTO'!G$85</f>
         <v>13182.136468922454</v>
       </c>
-      <c r="BN4" s="15">
+      <c r="BN4" s="12">
         <f>'[5]PYG PRESUPUESTO'!H$85</f>
         <v>13793.82312956908</v>
       </c>
-      <c r="BO4" s="15">
+      <c r="BO4" s="12">
         <f>'[5]PYG PRESUPUESTO'!I$85</f>
         <v>14246.441988221199</v>
       </c>
-      <c r="BP4" s="15">
+      <c r="BP4" s="12">
         <f>'[5]PYG PRESUPUESTO'!J$85</f>
         <v>14766.058660192595</v>
       </c>
-      <c r="BQ4" s="15">
+      <c r="BQ4" s="12">
         <f>'[5]PYG PRESUPUESTO'!K$85</f>
         <v>15048.606484654056</v>
       </c>
-      <c r="BR4" s="15">
+      <c r="BR4" s="12">
         <f>'[5]PYG PRESUPUESTO'!L$85</f>
         <v>15210.191904310497</v>
       </c>
-      <c r="BS4" s="15">
+      <c r="BS4" s="12">
         <f>'[5]PYG PRESUPUESTO'!M$85</f>
         <v>15886.610114547811</v>
       </c>
-      <c r="BT4" s="15">
+      <c r="BT4" s="12">
         <f>'[5]PYG PRESUPUESTO'!N$85</f>
         <v>16182.411607081516</v>
       </c>
-      <c r="BU4" s="12">
+      <c r="BU4" s="10">
         <f>'[5]PYG PRESUPUESTO'!O$85</f>
         <v>16917.932998585416</v>
       </c>
-      <c r="BV4" s="15">
+      <c r="BV4" s="12">
         <f>'[6]PYG PRESUPUESTO'!D$85</f>
         <v>12096.026018327382</v>
       </c>
-      <c r="BW4" s="15">
+      <c r="BW4" s="12">
         <f>'[6]PYG PRESUPUESTO'!E$85</f>
         <v>11692.651175314717</v>
       </c>
-      <c r="BX4" s="15">
+      <c r="BX4" s="12">
         <f>'[6]PYG PRESUPUESTO'!F$85</f>
         <v>12217.076010635725</v>
       </c>
-      <c r="BY4" s="15">
+      <c r="BY4" s="12">
         <f>'[6]PYG PRESUPUESTO'!G$85</f>
         <v>12623.063472337913</v>
       </c>
-      <c r="BZ4" s="15">
+      <c r="BZ4" s="12">
         <f>'[6]PYG PRESUPUESTO'!H$85</f>
         <v>13079.571061754499</v>
       </c>
-      <c r="CA4" s="15">
+      <c r="CA4" s="12">
         <f>'[6]PYG PRESUPUESTO'!I$85</f>
         <v>13248.582537934368</v>
       </c>
-      <c r="CB4" s="15">
+      <c r="CB4" s="12">
         <f>'[6]PYG PRESUPUESTO'!J$85</f>
         <v>14099.122997477327</v>
       </c>
-      <c r="CC4" s="15">
+      <c r="CC4" s="12">
         <f>'[6]PYG PRESUPUESTO'!K$85</f>
         <v>14561.340864337599</v>
       </c>
-      <c r="CD4" s="15">
+      <c r="CD4" s="12">
         <f>'[6]PYG PRESUPUESTO'!L$85</f>
         <v>14758.735738501069</v>
       </c>
-      <c r="CE4" s="15">
+      <c r="CE4" s="12">
         <f>'[6]PYG PRESUPUESTO'!M$85</f>
         <v>15579.885690979034</v>
       </c>
-      <c r="CF4" s="15">
+      <c r="CF4" s="12">
         <f>'[6]PYG PRESUPUESTO'!N$85</f>
         <v>15498.626382091608</v>
       </c>
-      <c r="CG4" s="12">
+      <c r="CG4" s="10">
         <f>'[6]PYG PRESUPUESTO'!O$85</f>
         <v>15818.548852178592</v>
       </c>
-      <c r="CH4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!D$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CI4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!E$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CJ4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!F$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CK4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!G$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CL4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!H$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CM4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!I$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CN4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!J$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CO4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!K$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CP4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!L$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CQ4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!M$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CR4" s="15" t="e">
-        <f>'[7]PYG PRESUPUESTO'!N$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CS4" s="12" t="e">
-        <f>'[7]PYG PRESUPUESTO'!O$87</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CT4" s="15">
+      <c r="CH4" s="12"/>
+      <c r="CI4" s="12"/>
+      <c r="CJ4" s="12"/>
+      <c r="CK4" s="12"/>
+      <c r="CL4" s="12"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="12"/>
+      <c r="CO4" s="12"/>
+      <c r="CP4" s="12"/>
+      <c r="CQ4" s="12"/>
+      <c r="CR4" s="12"/>
+      <c r="CS4" s="10"/>
+      <c r="CT4" s="12">
         <f>'[8]PYG PRESUPUESTO'!C$89</f>
         <v>20606.475300367747</v>
       </c>
-      <c r="CU4" s="15">
+      <c r="CU4" s="12">
         <f>'[8]PYG PRESUPUESTO'!D$89</f>
         <v>19258.418337713854</v>
       </c>
-      <c r="CV4" s="15">
+      <c r="CV4" s="12">
         <f>'[8]PYG PRESUPUESTO'!E$89</f>
         <v>20352.877932465653</v>
       </c>
-      <c r="CW4" s="15">
+      <c r="CW4" s="12">
         <f>'[8]PYG PRESUPUESTO'!F$89</f>
         <v>20908.511983224253</v>
       </c>
-      <c r="CX4" s="15">
+      <c r="CX4" s="12">
         <f>'[8]PYG PRESUPUESTO'!G$89</f>
         <v>21464.27168116441</v>
       </c>
-      <c r="CY4" s="15">
+      <c r="CY4" s="12">
         <f>'[8]PYG PRESUPUESTO'!H$89</f>
         <v>20951.35566565302</v>
       </c>
-      <c r="CZ4" s="15">
+      <c r="CZ4" s="12">
         <f>'[8]PYG PRESUPUESTO'!I$89</f>
         <v>22312.822677317752</v>
       </c>
-      <c r="DA4" s="15">
+      <c r="DA4" s="12">
         <f>'[8]PYG PRESUPUESTO'!J$89</f>
         <v>22737.4821369575</v>
       </c>
-      <c r="DB4" s="15">
+      <c r="DB4" s="12">
         <f>'[8]PYG PRESUPUESTO'!K$89</f>
         <v>22464.958446245542</v>
       </c>
-      <c r="DC4" s="15">
+      <c r="DC4" s="12">
         <f>'[8]PYG PRESUPUESTO'!L$89</f>
         <v>23124.219879069002</v>
       </c>
-      <c r="DD4" s="15">
+      <c r="DD4" s="12">
         <f>'[8]PYG PRESUPUESTO'!M$89</f>
         <v>23246.408345336917</v>
       </c>
-      <c r="DE4" s="12">
+      <c r="DE4" s="10">
         <f>'[8]PYG PRESUPUESTO'!N$89</f>
         <v>23444.684997952456</v>
       </c>
-      <c r="DF4" s="15">
+      <c r="DF4" s="12">
         <f>'[9]PYG PRESUPUESTO'!C$89</f>
         <v>18254.639711403248</v>
       </c>
-      <c r="DG4" s="15">
+      <c r="DG4" s="12">
         <f>'[9]PYG PRESUPUESTO'!D$89</f>
         <v>17305.906696277838</v>
       </c>
-      <c r="DH4" s="15">
+      <c r="DH4" s="12">
         <f>'[9]PYG PRESUPUESTO'!E$89</f>
         <v>18360.549261275373</v>
       </c>
-      <c r="DI4" s="15">
+      <c r="DI4" s="12">
         <f>'[9]PYG PRESUPUESTO'!F$89</f>
         <v>18567.845016223509</v>
       </c>
-      <c r="DJ4" s="15">
+      <c r="DJ4" s="12">
         <f>'[9]PYG PRESUPUESTO'!G$89</f>
         <v>19333.665587871212</v>
       </c>
-      <c r="DK4" s="15">
+      <c r="DK4" s="12">
         <f>'[9]PYG PRESUPUESTO'!H$89</f>
         <v>19118.779101501372</v>
       </c>
-      <c r="DL4" s="15">
+      <c r="DL4" s="12">
         <f>'[9]PYG PRESUPUESTO'!I$89</f>
         <v>20520.263036306296</v>
       </c>
-      <c r="DM4" s="15">
+      <c r="DM4" s="12">
         <f>'[9]PYG PRESUPUESTO'!J$89</f>
         <v>21627.188010330829</v>
       </c>
-      <c r="DN4" s="15">
+      <c r="DN4" s="12">
         <f>'[9]PYG PRESUPUESTO'!K$89</f>
         <v>22248.690953455389</v>
       </c>
-      <c r="DO4" s="15">
+      <c r="DO4" s="12">
         <f>'[9]PYG PRESUPUESTO'!L$89</f>
         <v>24047.825938781352</v>
       </c>
-      <c r="DP4" s="15">
+      <c r="DP4" s="12">
         <f>'[9]PYG PRESUPUESTO'!M$89</f>
         <v>24016.71427782948</v>
       </c>
-      <c r="DQ4" s="12">
+      <c r="DQ4" s="10">
         <f>'[9]PYG PRESUPUESTO'!N$89</f>
         <v>24262.250361025668</v>
       </c>
-      <c r="DR4" s="15">
+      <c r="DR4" s="12">
         <f>'[10]PYG PRESUPUESTO'!C$89</f>
         <v>20618.745536820454</v>
       </c>
-      <c r="DS4" s="15">
+      <c r="DS4" s="12">
         <f>'[10]PYG PRESUPUESTO'!D$89</f>
         <v>19717.93212574756</v>
       </c>
-      <c r="DT4" s="15">
+      <c r="DT4" s="12">
         <f>'[10]PYG PRESUPUESTO'!E$89</f>
         <v>21010.605429227719</v>
       </c>
-      <c r="DU4" s="15">
+      <c r="DU4" s="12">
         <f>'[10]PYG PRESUPUESTO'!F$89</f>
         <v>21015.65532599821</v>
       </c>
-      <c r="DV4" s="15">
+      <c r="DV4" s="12">
         <f>'[10]PYG PRESUPUESTO'!G$89</f>
         <v>22092.662782568077</v>
       </c>
-      <c r="DW4" s="15">
+      <c r="DW4" s="12">
         <f>'[10]PYG PRESUPUESTO'!H$89</f>
         <v>21231.279706975824</v>
       </c>
-      <c r="DX4" s="15">
+      <c r="DX4" s="12">
         <f>'[10]PYG PRESUPUESTO'!I$89</f>
         <v>21767.603138499264</v>
       </c>
-      <c r="DY4" s="15">
+      <c r="DY4" s="12">
         <f>'[10]PYG PRESUPUESTO'!J$89</f>
         <v>22295.395717440166</v>
       </c>
-      <c r="DZ4" s="15">
+      <c r="DZ4" s="12">
         <f>'[10]PYG PRESUPUESTO'!K$89</f>
         <v>22240.169715475982</v>
       </c>
-      <c r="EA4" s="15">
+      <c r="EA4" s="12">
         <f>'[10]PYG PRESUPUESTO'!L$89</f>
         <v>23002.923832440949</v>
       </c>
-      <c r="EB4" s="15">
+      <c r="EB4" s="12">
         <f>'[10]PYG PRESUPUESTO'!M$89</f>
         <v>22149.374558965672</v>
       </c>
-      <c r="EC4" s="12">
+      <c r="EC4" s="10">
         <f>'[10]PYG PRESUPUESTO'!N$89</f>
         <v>21865.334606038112</v>
       </c>
-      <c r="ED4" s="15">
+      <c r="ED4" s="12">
         <f>'[11]PYG PRESUPUESTO'!C$89</f>
         <v>28644.23264091563</v>
       </c>
-      <c r="EE4" s="15">
+      <c r="EE4" s="12">
         <f>'[11]PYG PRESUPUESTO'!D$89</f>
         <v>28815.34341252529</v>
       </c>
-      <c r="EF4" s="15">
+      <c r="EF4" s="12">
         <f>'[11]PYG PRESUPUESTO'!E$89</f>
         <v>30496.199655977267</v>
       </c>
-      <c r="EG4" s="15">
+      <c r="EG4" s="12">
         <f>'[11]PYG PRESUPUESTO'!F$89</f>
         <v>31408.219383916057</v>
       </c>
-      <c r="EH4" s="15">
+      <c r="EH4" s="12">
         <f>'[11]PYG PRESUPUESTO'!G$89</f>
         <v>32895.200654814791</v>
       </c>
-      <c r="EI4" s="15">
+      <c r="EI4" s="12">
         <f>'[11]PYG PRESUPUESTO'!H$89</f>
         <v>32809.248716217415</v>
       </c>
-      <c r="EJ4" s="15">
+      <c r="EJ4" s="12">
         <f>'[11]PYG PRESUPUESTO'!I$89</f>
         <v>34334.164447190531</v>
       </c>
-      <c r="EK4" s="15">
+      <c r="EK4" s="12">
         <f>'[11]PYG PRESUPUESTO'!J$89</f>
         <v>35114.08246865384</v>
       </c>
-      <c r="EL4" s="15">
+      <c r="EL4" s="12">
         <f>'[11]PYG PRESUPUESTO'!K$89</f>
         <v>34824.354469781094</v>
       </c>
-      <c r="EM4" s="15">
+      <c r="EM4" s="12">
         <f>'[11]PYG PRESUPUESTO'!L$89</f>
         <v>35926.321646070472</v>
       </c>
-      <c r="EN4" s="15">
+      <c r="EN4" s="12">
         <f>'[11]PYG PRESUPUESTO'!M$89</f>
         <v>35069.596572112227</v>
       </c>
-      <c r="EO4" s="12">
+      <c r="EO4" s="10">
         <f>'[11]PYG PRESUPUESTO'!N$89</f>
         <v>34728.623868740986</v>
       </c>
-      <c r="EP4" s="15">
+      <c r="EP4" s="12">
         <f>'[12]PYG PRESUPUESTO'!C$89</f>
         <v>39097.508877360706</v>
       </c>
-      <c r="EQ4" s="15">
+      <c r="EQ4" s="12">
         <f>'[12]PYG PRESUPUESTO'!D$89</f>
         <v>37287.565966936141</v>
       </c>
-      <c r="ER4" s="15">
+      <c r="ER4" s="12">
         <f>'[12]PYG PRESUPUESTO'!E$89</f>
         <v>39334.541249228445</v>
       </c>
-      <c r="ES4" s="15">
+      <c r="ES4" s="12">
         <f>'[12]PYG PRESUPUESTO'!F$89</f>
         <v>39564.763228065116</v>
       </c>
-      <c r="ET4" s="15">
+      <c r="ET4" s="12">
         <f>'[12]PYG PRESUPUESTO'!G$89</f>
         <v>40153.993006036399</v>
       </c>
-      <c r="EU4" s="15">
+      <c r="EU4" s="12">
         <f>'[12]PYG PRESUPUESTO'!H$89</f>
         <v>38978.386601890292</v>
       </c>
-      <c r="EV4" s="15">
+      <c r="EV4" s="12">
         <f>'[12]PYG PRESUPUESTO'!I$89</f>
         <v>40086.638212155849</v>
       </c>
-      <c r="EW4" s="15">
+      <c r="EW4" s="12">
         <f>'[12]PYG PRESUPUESTO'!J$89</f>
         <v>41028.805196588721</v>
       </c>
-      <c r="EX4" s="15">
+      <c r="EX4" s="12">
         <f>'[12]PYG PRESUPUESTO'!K$89</f>
         <v>40784.662729151431</v>
       </c>
-      <c r="EY4" s="15">
+      <c r="EY4" s="12">
         <f>'[12]PYG PRESUPUESTO'!L$89</f>
         <v>41023.492091425251</v>
       </c>
-      <c r="EZ4" s="15">
+      <c r="EZ4" s="12">
         <f>'[12]PYG PRESUPUESTO'!M$89</f>
         <v>40017.900865222771</v>
       </c>
-      <c r="FA4" s="12">
+      <c r="FA4" s="10">
         <f>'[12]PYG PRESUPUESTO'!N$89</f>
         <v>40390.618655462909</v>
       </c>
-      <c r="FB4" s="15">
+      <c r="FB4" s="12">
         <f>'[13]PYG PRESUPUESTO'!C$89</f>
         <v>31099.12043573389</v>
       </c>
-      <c r="FC4" s="15">
+      <c r="FC4" s="12">
         <f>'[13]PYG PRESUPUESTO'!D$89</f>
         <v>29815.955438960074</v>
       </c>
-      <c r="FD4" s="15">
+      <c r="FD4" s="12">
         <f>'[13]PYG PRESUPUESTO'!E$89</f>
         <v>30681.523538953217</v>
       </c>
-      <c r="FE4" s="15">
+      <c r="FE4" s="12">
         <f>'[13]PYG PRESUPUESTO'!F$89</f>
         <v>30193.939376571991</v>
       </c>
-      <c r="FF4" s="15">
+      <c r="FF4" s="12">
         <f>'[13]PYG PRESUPUESTO'!G$89</f>
         <v>30133.595839636491</v>
       </c>
-      <c r="FG4" s="15">
+      <c r="FG4" s="12">
         <f>'[13]PYG PRESUPUESTO'!H$89</f>
         <v>29987.522561350521</v>
       </c>
-      <c r="FH4" s="15">
+      <c r="FH4" s="12">
         <f>'[13]PYG PRESUPUESTO'!I$89</f>
         <v>30705.965509925551</v>
       </c>
-      <c r="FI4" s="15">
+      <c r="FI4" s="12">
         <f>'[13]PYG PRESUPUESTO'!J$89</f>
         <v>31149.458726957899</v>
       </c>
-      <c r="FJ4" s="15">
+      <c r="FJ4" s="12">
         <f>'[13]PYG PRESUPUESTO'!K$89</f>
         <v>31153.507224654746</v>
       </c>
-      <c r="FK4" s="15">
+      <c r="FK4" s="12">
         <f>'[13]PYG PRESUPUESTO'!L$89</f>
         <v>31995.930667376728</v>
       </c>
-      <c r="FL4" s="15">
+      <c r="FL4" s="12">
         <f>'[13]PYG PRESUPUESTO'!M$89</f>
         <v>31707.011400087806</v>
       </c>
-      <c r="FM4" s="12">
+      <c r="FM4" s="10">
         <f>'[13]PYG PRESUPUESTO'!N$89</f>
         <v>32181.985177124989</v>
       </c>
-      <c r="FN4" s="15">
+      <c r="FN4" s="12">
         <f>'[14]PYG PRESUPUESTO'!C$89</f>
         <v>34189.212514180857</v>
       </c>
-      <c r="FO4" s="15">
+      <c r="FO4" s="12">
         <f>'[14]PYG PRESUPUESTO'!D$89</f>
         <v>33271.826532896201</v>
       </c>
-      <c r="FP4" s="15">
+      <c r="FP4" s="12">
         <f>'[14]PYG PRESUPUESTO'!E$89</f>
         <v>34701.616928750067</v>
       </c>
-      <c r="FQ4" s="15">
+      <c r="FQ4" s="12">
         <f>'[14]PYG PRESUPUESTO'!F$89</f>
         <v>34569.405728632933</v>
       </c>
-      <c r="FR4" s="15">
+      <c r="FR4" s="12">
         <f>'[14]PYG PRESUPUESTO'!G$89</f>
         <v>35422.80860154151</v>
       </c>
-      <c r="FS4" s="15">
+      <c r="FS4" s="12">
         <f>'[14]PYG PRESUPUESTO'!H$89</f>
         <v>35668.385815423462</v>
       </c>
-      <c r="FT4" s="15">
+      <c r="FT4" s="12">
         <f>'[14]PYG PRESUPUESTO'!I$89</f>
         <v>36782.187010754235</v>
       </c>
-      <c r="FU4" s="15">
+      <c r="FU4" s="12">
         <f>'[14]PYG PRESUPUESTO'!J$89</f>
         <v>37748.901291330883</v>
       </c>
-      <c r="FV4" s="15">
+      <c r="FV4" s="12">
         <f>'[14]PYG PRESUPUESTO'!K$89</f>
         <v>38297.230263750906</v>
       </c>
-      <c r="FW4" s="15">
+      <c r="FW4" s="12">
         <f>'[14]PYG PRESUPUESTO'!L$89</f>
         <v>39721.803196250825</v>
       </c>
-      <c r="FX4" s="15">
+      <c r="FX4" s="12">
         <f>'[14]PYG PRESUPUESTO'!M$89</f>
         <v>39562.784579625382</v>
       </c>
-      <c r="FY4" s="12">
+      <c r="FY4" s="10">
         <f>'[14]PYG PRESUPUESTO'!N$89</f>
         <v>40069.157911077462</v>
       </c>
-      <c r="FZ4" s="15">
+      <c r="FZ4" s="12">
         <f>'[15]PYG PRESUPUESTO'!C$89</f>
         <v>36076.822863523164</v>
       </c>
-      <c r="GA4" s="15">
+      <c r="GA4" s="12">
         <f>'[15]PYG PRESUPUESTO'!D$89</f>
         <v>35616.565777897238</v>
       </c>
-      <c r="GB4" s="15">
+      <c r="GB4" s="12">
         <f>'[15]PYG PRESUPUESTO'!E$89</f>
         <v>37125.374894986293</v>
       </c>
-      <c r="GC4" s="15">
+      <c r="GC4" s="12">
         <f>'[15]PYG PRESUPUESTO'!F$89</f>
         <v>37171.79612581175</v>
       </c>
-      <c r="GD4" s="15">
+      <c r="GD4" s="12">
         <f>'[15]PYG PRESUPUESTO'!G$89</f>
         <v>38300.821872303452</v>
       </c>
-      <c r="GE4" s="15">
+      <c r="GE4" s="12">
         <f>'[15]PYG PRESUPUESTO'!H$89</f>
         <v>38696.349934676095</v>
       </c>
-      <c r="GF4" s="15">
+      <c r="GF4" s="12">
         <f>'[15]PYG PRESUPUESTO'!I$89</f>
         <v>40400.678827009811</v>
       </c>
-      <c r="GG4" s="15">
+      <c r="GG4" s="12">
         <f>'[15]PYG PRESUPUESTO'!J$89</f>
         <v>41534.801094111142</v>
       </c>
-      <c r="GH4" s="15">
+      <c r="GH4" s="12">
         <f>'[15]PYG PRESUPUESTO'!K$89</f>
         <v>42223.391942766299</v>
       </c>
-      <c r="GI4" s="15">
+      <c r="GI4" s="12">
         <f>'[15]PYG PRESUPUESTO'!L$89</f>
         <v>44133.388720470175</v>
       </c>
-      <c r="GJ4" s="15">
+      <c r="GJ4" s="12">
         <f>'[15]PYG PRESUPUESTO'!M$89</f>
         <v>44829.254397331111</v>
       </c>
-      <c r="GK4" s="12">
+      <c r="GK4" s="10">
         <f>'[15]PYG PRESUPUESTO'!N$89</f>
         <v>46167.525316214211</v>
       </c>
-      <c r="GL4" s="15">
+      <c r="GL4" s="12">
         <f>'[16]PYG PRESUPUESTO'!C$89</f>
         <v>21868.675445590598</v>
       </c>
-      <c r="GM4" s="15">
+      <c r="GM4" s="12">
         <f>'[16]PYG PRESUPUESTO'!D$89</f>
         <v>22124.389865220044</v>
       </c>
-      <c r="GN4" s="15">
+      <c r="GN4" s="12">
         <f>'[16]PYG PRESUPUESTO'!E$89</f>
         <v>21867.661184391</v>
       </c>
-      <c r="GO4" s="15">
+      <c r="GO4" s="12">
         <f>'[16]PYG PRESUPUESTO'!F$89</f>
         <v>21390.390270057436</v>
       </c>
-      <c r="GP4" s="15">
+      <c r="GP4" s="12">
         <f>'[16]PYG PRESUPUESTO'!G$89</f>
         <v>21805.801610078466</v>
       </c>
-      <c r="GQ4" s="15">
+      <c r="GQ4" s="12">
         <f>'[16]PYG PRESUPUESTO'!H$89</f>
         <v>21485.784033675489</v>
       </c>
-      <c r="GR4" s="15">
+      <c r="GR4" s="12">
         <f>'[16]PYG PRESUPUESTO'!I$89</f>
         <v>22758.837681853536</v>
       </c>
-      <c r="GS4" s="15">
+      <c r="GS4" s="12">
         <f>'[16]PYG PRESUPUESTO'!J$89</f>
         <v>23017.798110886815</v>
       </c>
-      <c r="GT4" s="15">
+      <c r="GT4" s="12">
         <f>'[16]PYG PRESUPUESTO'!K$89</f>
         <v>22848.265331488594</v>
       </c>
-      <c r="GU4" s="15">
+      <c r="GU4" s="12">
         <f>'[16]PYG PRESUPUESTO'!L$89</f>
         <v>23489.790420457255</v>
       </c>
-      <c r="GV4" s="15">
+      <c r="GV4" s="12">
         <f>'[16]PYG PRESUPUESTO'!M$89</f>
         <v>24204.786344012995</v>
       </c>
-      <c r="GW4" s="12">
+      <c r="GW4" s="10">
         <f>'[16]PYG PRESUPUESTO'!N$89</f>
         <v>24663.8150851102</v>
       </c>
-      <c r="GX4" s="15">
+      <c r="GX4" s="12">
         <f>'[17]PYG PRESUPUESTO'!C$89</f>
         <v>29314.292825535005</v>
       </c>
-      <c r="GY4" s="15">
+      <c r="GY4" s="12">
         <f>'[17]PYG PRESUPUESTO'!D$89</f>
         <v>28173.465790652092</v>
       </c>
-      <c r="GZ4" s="15">
+      <c r="GZ4" s="12">
         <f>'[17]PYG PRESUPUESTO'!E$89</f>
         <v>31848.695203592666</v>
       </c>
-      <c r="HA4" s="15">
+      <c r="HA4" s="12">
         <f>'[17]PYG PRESUPUESTO'!F$89</f>
         <v>32876.32257645957</v>
       </c>
-      <c r="HB4" s="15">
+      <c r="HB4" s="12">
         <f>'[17]PYG PRESUPUESTO'!G$89</f>
         <v>35056.19781380018</v>
       </c>
-      <c r="HC4" s="15">
+      <c r="HC4" s="12">
         <f>'[17]PYG PRESUPUESTO'!H$89</f>
         <v>35074.178889353541</v>
       </c>
-      <c r="HD4" s="15">
+      <c r="HD4" s="12">
         <f>'[17]PYG PRESUPUESTO'!I$89</f>
         <v>37154.589424556536</v>
       </c>
-      <c r="HE4" s="15">
+      <c r="HE4" s="12">
         <f>'[17]PYG PRESUPUESTO'!J$89</f>
         <v>38696.075496413454</v>
       </c>
-      <c r="HF4" s="15">
+      <c r="HF4" s="12">
         <f>'[17]PYG PRESUPUESTO'!K$89</f>
         <v>39238.108440045573</v>
       </c>
-      <c r="HG4" s="15">
+      <c r="HG4" s="12">
         <f>'[17]PYG PRESUPUESTO'!L$89</f>
         <v>41610.989132002185</v>
       </c>
-      <c r="HH4" s="15">
+      <c r="HH4" s="12">
         <f>'[17]PYG PRESUPUESTO'!M$89</f>
         <v>41264.348590395217</v>
       </c>
-      <c r="HI4" s="12">
+      <c r="HI4" s="10">
         <f>'[17]PYG PRESUPUESTO'!N$89</f>
         <v>43547.799342553648</v>
       </c>
-      <c r="HJ4" s="15">
+      <c r="HJ4" s="12">
         <f>'[18]PYG PRESUPUESTO'!C$89</f>
         <v>105231.55030404028</v>
       </c>
-      <c r="HK4" s="15">
+      <c r="HK4" s="12">
         <f>'[18]PYG PRESUPUESTO'!D$89</f>
         <v>99974.577501029868</v>
       </c>
-      <c r="HL4" s="15">
+      <c r="HL4" s="12">
         <f>'[18]PYG PRESUPUESTO'!E$89</f>
         <v>107071.77255371067</v>
       </c>
-      <c r="HM4" s="15">
+      <c r="HM4" s="12">
         <f>'[18]PYG PRESUPUESTO'!F$89</f>
         <v>106229.70469137374</v>
       </c>
-      <c r="HN4" s="15">
+      <c r="HN4" s="12">
         <f>'[18]PYG PRESUPUESTO'!G$89</f>
         <v>109430.93865569722</v>
       </c>
-      <c r="HO4" s="15">
+      <c r="HO4" s="12">
         <f>'[18]PYG PRESUPUESTO'!H$89</f>
         <v>107690.45792285437</v>
       </c>
-      <c r="HP4" s="15">
+      <c r="HP4" s="12">
         <f>'[18]PYG PRESUPUESTO'!I$89</f>
         <v>104860.87717804995</v>
       </c>
-      <c r="HQ4" s="15">
+      <c r="HQ4" s="12">
         <f>'[18]PYG PRESUPUESTO'!J$89</f>
         <v>101291.56415997895</v>
       </c>
-      <c r="HR4" s="15">
+      <c r="HR4" s="12">
         <f>'[18]PYG PRESUPUESTO'!K$89</f>
         <v>97866.684437386459</v>
       </c>
-      <c r="HS4" s="15">
+      <c r="HS4" s="12">
         <f>'[18]PYG PRESUPUESTO'!L$89</f>
         <v>98173.648258162386</v>
       </c>
-      <c r="HT4" s="15">
+      <c r="HT4" s="12">
         <f>'[18]PYG PRESUPUESTO'!M$89</f>
         <v>92316.285937773282</v>
       </c>
-      <c r="HU4" s="12">
+      <c r="HU4" s="10">
         <f>'[18]PYG PRESUPUESTO'!N$89</f>
         <v>91864.726678867373</v>
       </c>
-      <c r="HV4" s="15">
+      <c r="HV4" s="12">
         <f>'[19]PYG PRESUPUESTO'!C$89</f>
         <v>115902.48129160175</v>
       </c>
-      <c r="HW4" s="15">
+      <c r="HW4" s="12">
         <f>'[19]PYG PRESUPUESTO'!D$89</f>
         <v>107944.35630411262</v>
       </c>
-      <c r="HX4" s="15">
+      <c r="HX4" s="12">
         <f>'[19]PYG PRESUPUESTO'!E$89</f>
         <v>109662.97934558504</v>
       </c>
-      <c r="HY4" s="15">
+      <c r="HY4" s="12">
         <f>'[19]PYG PRESUPUESTO'!F$89</f>
         <v>103396.34513934424</v>
       </c>
-      <c r="HZ4" s="15">
+      <c r="HZ4" s="12">
         <f>'[19]PYG PRESUPUESTO'!G$89</f>
         <v>98204.69247971478</v>
       </c>
-      <c r="IA4" s="15">
+      <c r="IA4" s="12">
         <f>'[19]PYG PRESUPUESTO'!H$89</f>
         <v>96441.639648433382</v>
       </c>
-      <c r="IB4" s="15">
+      <c r="IB4" s="12">
         <f>'[19]PYG PRESUPUESTO'!I$89</f>
         <v>96471.436547676683</v>
       </c>
-      <c r="IC4" s="15">
+      <c r="IC4" s="12">
         <f>'[19]PYG PRESUPUESTO'!J$89</f>
         <v>93104.377068108341</v>
       </c>
-      <c r="ID4" s="15">
+      <c r="ID4" s="12">
         <f>'[19]PYG PRESUPUESTO'!K$89</f>
         <v>91158.598000000537</v>
       </c>
-      <c r="IE4" s="15">
+      <c r="IE4" s="12">
         <f>'[19]PYG PRESUPUESTO'!L$89</f>
         <v>90261.951567698168</v>
       </c>
-      <c r="IF4" s="15">
+      <c r="IF4" s="12">
         <f>'[19]PYG PRESUPUESTO'!M$89</f>
         <v>85622.599369685529</v>
       </c>
-      <c r="IG4" s="12">
+      <c r="IG4" s="10">
         <f>'[19]PYG PRESUPUESTO'!N$89</f>
         <v>86908.376441476474</v>
       </c>
-      <c r="IH4" s="15">
+      <c r="IH4" s="12">
         <f>'[20]PYG PRESUPUESTO'!C$89</f>
         <v>85327.260523086487</v>
       </c>
-      <c r="II4" s="15">
+      <c r="II4" s="12">
         <f>'[20]PYG PRESUPUESTO'!D$89</f>
         <v>80330.906627408171</v>
       </c>
-      <c r="IJ4" s="15">
+      <c r="IJ4" s="12">
         <f>'[20]PYG PRESUPUESTO'!E$89</f>
         <v>83402.950553033384</v>
       </c>
-      <c r="IK4" s="15">
+      <c r="IK4" s="12">
         <f>'[20]PYG PRESUPUESTO'!F$89</f>
         <v>75987.7636603094</v>
       </c>
-      <c r="IL4" s="15">
+      <c r="IL4" s="12">
         <f>'[20]PYG PRESUPUESTO'!G$89</f>
         <v>74571.493847846185</v>
       </c>
-      <c r="IM4" s="15">
+      <c r="IM4" s="12">
         <f>'[20]PYG PRESUPUESTO'!H$89</f>
         <v>72846.202588755055</v>
       </c>
-      <c r="IN4" s="15">
+      <c r="IN4" s="12">
         <f>'[20]PYG PRESUPUESTO'!I$89</f>
         <v>71489.431834838557</v>
       </c>
-      <c r="IO4" s="15">
+      <c r="IO4" s="12">
         <f>'[20]PYG PRESUPUESTO'!J$89</f>
         <v>68879.031916300853</v>
       </c>
-      <c r="IP4" s="15">
+      <c r="IP4" s="12">
         <f>'[20]PYG PRESUPUESTO'!K$89</f>
         <v>67057.779358819869</v>
       </c>
-      <c r="IQ4" s="15">
+      <c r="IQ4" s="12">
         <f>'[20]PYG PRESUPUESTO'!L$89</f>
         <v>65698.14942016323</v>
       </c>
-      <c r="IR4" s="15">
+      <c r="IR4" s="12">
         <f>'[20]PYG PRESUPUESTO'!M$89</f>
         <v>64393.972409130743</v>
       </c>
-      <c r="IS4" s="12">
+      <c r="IS4" s="10">
         <f>'[20]PYG PRESUPUESTO'!N$89</f>
         <v>65443.390516804815</v>
       </c>
       <c r="IT4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="5" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <f>B3-B4</f>
         <v>18696.457644548074</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <f t="shared" ref="C5:M5" si="0">C3-C4</f>
         <v>18228.470555507258</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f t="shared" si="0"/>
         <v>22741.906815580624</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f t="shared" si="0"/>
         <v>21932.381391521027</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>21497.939174938914</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
         <v>20486.199365457313</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
         <v>21419.271740683587</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <f t="shared" si="0"/>
         <v>19632.89273329396</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <f t="shared" si="0"/>
         <v>19347.193533557474</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <f t="shared" si="0"/>
         <v>20487.478165901244</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <f t="shared" si="0"/>
         <v>19774.939970677187</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="10">
         <f t="shared" si="0"/>
         <v>21859.143482147752</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <f>N3-N4</f>
         <v>18765.452905583879</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <f t="shared" ref="O5:Y5" si="1">O3-O4</f>
         <v>18803.801835558843</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <f t="shared" si="1"/>
         <v>21477.727604858032</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <f t="shared" si="1"/>
         <v>22263.896993745944</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <f t="shared" si="1"/>
         <v>20976.476791700217</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <f t="shared" si="1"/>
         <v>20808.733391950045</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <f t="shared" si="1"/>
         <v>21839.313436889232</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <f t="shared" si="1"/>
         <v>21534.586280720694</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <f t="shared" si="1"/>
         <v>21162.588060288937</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <f t="shared" si="1"/>
         <v>22218.890080920686</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <f t="shared" si="1"/>
         <v>22258.566323138264</v>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="10">
         <f t="shared" si="1"/>
         <v>21644.616511125249</v>
       </c>
-      <c r="Z5" s="15"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="15">
+      <c r="Z5" s="12"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="12">
         <f>AL3-AL4</f>
         <v>32554.479566139991</v>
       </c>
-      <c r="AM5" s="15">
+      <c r="AM5" s="12">
         <f t="shared" ref="AM5:AX5" si="2">AM3-AM4</f>
         <v>32683.34161327907</v>
       </c>
-      <c r="AN5" s="15">
+      <c r="AN5" s="12">
         <f t="shared" si="2"/>
         <v>35463.330304396972</v>
       </c>
-      <c r="AO5" s="15">
+      <c r="AO5" s="12">
         <f t="shared" si="2"/>
         <v>34846.856369737099</v>
       </c>
-      <c r="AP5" s="15">
+      <c r="AP5" s="12">
         <f t="shared" si="2"/>
         <v>35875.50932204425</v>
       </c>
-      <c r="AQ5" s="15">
+      <c r="AQ5" s="12">
         <f t="shared" si="2"/>
         <v>36513.482207403009</v>
       </c>
-      <c r="AR5" s="15">
+      <c r="AR5" s="12">
         <f t="shared" si="2"/>
         <v>38511.439998745278</v>
       </c>
-      <c r="AS5" s="15">
+      <c r="AS5" s="12">
         <f t="shared" si="2"/>
         <v>39535.572226150834</v>
       </c>
-      <c r="AT5" s="15">
+      <c r="AT5" s="12">
         <f t="shared" si="2"/>
         <v>40693.801241204361</v>
       </c>
-      <c r="AU5" s="15">
+      <c r="AU5" s="12">
         <f t="shared" si="2"/>
         <v>42062.637272163505</v>
       </c>
-      <c r="AV5" s="15">
+      <c r="AV5" s="12">
         <f t="shared" si="2"/>
         <v>43150.609790284347</v>
       </c>
-      <c r="AW5" s="12">
+      <c r="AW5" s="10">
         <f t="shared" si="2"/>
         <v>43572.310116505854</v>
       </c>
-      <c r="AX5" s="15">
+      <c r="AX5" s="12">
         <f t="shared" si="2"/>
         <v>40101.549064905572</v>
       </c>
-      <c r="AY5" s="15">
+      <c r="AY5" s="12">
         <f t="shared" ref="AY5" si="3">AY3-AY4</f>
         <v>39957.238937565329</v>
       </c>
-      <c r="AZ5" s="15">
+      <c r="AZ5" s="12">
         <f t="shared" ref="AZ5" si="4">AZ3-AZ4</f>
         <v>45114.747919235029</v>
       </c>
-      <c r="BA5" s="15">
+      <c r="BA5" s="12">
         <f t="shared" ref="BA5" si="5">BA3-BA4</f>
         <v>43300.053372533352</v>
       </c>
-      <c r="BB5" s="15">
+      <c r="BB5" s="12">
         <f t="shared" ref="BB5" si="6">BB3-BB4</f>
         <v>44299.135569083839</v>
       </c>
-      <c r="BC5" s="15">
+      <c r="BC5" s="12">
         <f t="shared" ref="BC5" si="7">BC3-BC4</f>
         <v>45046.27005702164</v>
       </c>
-      <c r="BD5" s="15">
+      <c r="BD5" s="12">
         <f t="shared" ref="BD5" si="8">BD3-BD4</f>
         <v>45359.656291620384</v>
       </c>
-      <c r="BE5" s="15">
+      <c r="BE5" s="12">
         <f t="shared" ref="BE5" si="9">BE3-BE4</f>
         <v>46342.996637221877</v>
       </c>
-      <c r="BF5" s="15">
+      <c r="BF5" s="12">
         <f t="shared" ref="BF5" si="10">BF3-BF4</f>
         <v>46797.239544571472</v>
       </c>
-      <c r="BG5" s="15">
+      <c r="BG5" s="12">
         <f t="shared" ref="BG5" si="11">BG3-BG4</f>
         <v>48187.436292788843</v>
       </c>
-      <c r="BH5" s="15">
+      <c r="BH5" s="12">
         <f t="shared" ref="BH5" si="12">BH3-BH4</f>
         <v>49616.805784815951</v>
       </c>
-      <c r="BI5" s="12">
+      <c r="BI5" s="10">
         <f t="shared" ref="BI5" si="13">BI3-BI4</f>
         <v>59023.158214916562</v>
       </c>
-      <c r="BJ5" s="15">
+      <c r="BJ5" s="12">
         <f t="shared" ref="BJ5" si="14">BJ3-BJ4</f>
         <v>42537.916231837611</v>
       </c>
-      <c r="BK5" s="15">
+      <c r="BK5" s="12">
         <f t="shared" ref="BK5" si="15">BK3-BK4</f>
         <v>42531.03937351238</v>
       </c>
-      <c r="BL5" s="15">
+      <c r="BL5" s="12">
         <f t="shared" ref="BL5" si="16">BL3-BL4</f>
         <v>50510.332914989202</v>
       </c>
-      <c r="BM5" s="15">
+      <c r="BM5" s="12">
         <f t="shared" ref="BM5" si="17">BM3-BM4</f>
         <v>45355.19386497511</v>
       </c>
-      <c r="BN5" s="15">
+      <c r="BN5" s="12">
         <f t="shared" ref="BN5" si="18">BN3-BN4</f>
         <v>46777.441038790319</v>
       </c>
-      <c r="BO5" s="15">
+      <c r="BO5" s="12">
         <f t="shared" ref="BO5" si="19">BO3-BO4</f>
         <v>47209.33091542052</v>
       </c>
-      <c r="BP5" s="15">
+      <c r="BP5" s="12">
         <f t="shared" ref="BP5" si="20">BP3-BP4</f>
         <v>51570.942043282201</v>
       </c>
-      <c r="BQ5" s="15">
+      <c r="BQ5" s="12">
         <f t="shared" ref="BQ5" si="21">BQ3-BQ4</f>
         <v>51194.860623176341</v>
       </c>
-      <c r="BR5" s="15">
+      <c r="BR5" s="12">
         <f t="shared" ref="BR5" si="22">BR3-BR4</f>
         <v>49916.426655319083</v>
       </c>
-      <c r="BS5" s="15">
+      <c r="BS5" s="12">
         <f t="shared" ref="BS5" si="23">BS3-BS4</f>
         <v>49923.114391480623</v>
       </c>
-      <c r="BT5" s="15">
+      <c r="BT5" s="12">
         <f t="shared" ref="BT5" si="24">BT3-BT4</f>
         <v>52629.635409824092</v>
       </c>
-      <c r="BU5" s="12">
+      <c r="BU5" s="10">
         <f t="shared" ref="BU5:BV5" si="25">BU3-BU4</f>
         <v>58449.411536832762</v>
       </c>
-      <c r="BV5" s="15">
+      <c r="BV5" s="12">
         <f t="shared" si="25"/>
         <v>49554.091958863413</v>
       </c>
-      <c r="BW5" s="15">
+      <c r="BW5" s="12">
         <f t="shared" ref="BW5:CH5" si="26">BW3-BW4</f>
         <v>57583.998704164624</v>
       </c>
-      <c r="BX5" s="15">
+      <c r="BX5" s="12">
         <f t="shared" si="26"/>
         <v>45859.719226500747</v>
       </c>
-      <c r="BY5" s="15">
+      <c r="BY5" s="12">
         <f t="shared" si="26"/>
         <v>44512.310982779803</v>
       </c>
-      <c r="BZ5" s="15">
+      <c r="BZ5" s="12">
         <f t="shared" si="26"/>
         <v>49401.011934916045</v>
       </c>
-      <c r="CA5" s="15">
+      <c r="CA5" s="12">
         <f t="shared" si="26"/>
         <v>45236.193323046959</v>
       </c>
-      <c r="CB5" s="15">
+      <c r="CB5" s="12">
         <f t="shared" si="26"/>
         <v>45097.831621029676</v>
       </c>
-      <c r="CC5" s="15">
+      <c r="CC5" s="12">
         <f t="shared" si="26"/>
         <v>45922.754982846644</v>
       </c>
-      <c r="CD5" s="15">
+      <c r="CD5" s="12">
         <f t="shared" si="26"/>
         <v>46625.890160466159</v>
       </c>
-      <c r="CE5" s="15">
+      <c r="CE5" s="12">
         <f t="shared" si="26"/>
         <v>47305.594212004762</v>
       </c>
-      <c r="CF5" s="15">
+      <c r="CF5" s="12">
         <f t="shared" si="26"/>
         <v>47866.059012728838</v>
       </c>
-      <c r="CG5" s="12">
+      <c r="CG5" s="10">
         <f t="shared" si="26"/>
         <v>50108.551130708453</v>
       </c>
-      <c r="CH5" s="15" t="e">
-        <f t="shared" si="26"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CI5" s="15" t="e">
-        <f t="shared" ref="CI5:CT5" si="27">CI3-CI4</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CJ5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CK5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CL5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CM5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CN5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CO5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CP5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CQ5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CR5" s="15" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CS5" s="12" t="e">
-        <f t="shared" si="27"/>
-        <v>#REF!</v>
-      </c>
-      <c r="CT5" s="15">
-        <f t="shared" si="27"/>
+      <c r="CH5" s="12"/>
+      <c r="CI5" s="12"/>
+      <c r="CJ5" s="12"/>
+      <c r="CK5" s="12"/>
+      <c r="CL5" s="12"/>
+      <c r="CM5" s="12"/>
+      <c r="CN5" s="12"/>
+      <c r="CO5" s="12"/>
+      <c r="CP5" s="12"/>
+      <c r="CQ5" s="12"/>
+      <c r="CR5" s="12"/>
+      <c r="CS5" s="10"/>
+      <c r="CT5" s="12">
+        <f t="shared" ref="CI5:CT5" si="27">CT3-CT4</f>
         <v>61521.628254724972</v>
       </c>
-      <c r="CU5" s="15">
+      <c r="CU5" s="12">
         <f t="shared" ref="CU5:DF5" si="28">CU3-CU4</f>
         <v>60466.116609309407</v>
       </c>
-      <c r="CV5" s="15">
+      <c r="CV5" s="12">
         <f t="shared" si="28"/>
         <v>70283.909928901208</v>
       </c>
-      <c r="CW5" s="15">
+      <c r="CW5" s="12">
         <f t="shared" si="28"/>
         <v>57967.336037216359</v>
       </c>
-      <c r="CX5" s="15">
+      <c r="CX5" s="12">
         <f t="shared" si="28"/>
         <v>62852.290033890342</v>
       </c>
-      <c r="CY5" s="15">
+      <c r="CY5" s="12">
         <f t="shared" si="28"/>
         <v>60640.273265109288</v>
       </c>
-      <c r="CZ5" s="15">
+      <c r="CZ5" s="12">
         <f t="shared" si="28"/>
         <v>59830.780241821201</v>
       </c>
-      <c r="DA5" s="15">
+      <c r="DA5" s="12">
         <f t="shared" si="28"/>
         <v>59634.628739274754</v>
       </c>
-      <c r="DB5" s="15">
+      <c r="DB5" s="12">
         <f t="shared" si="28"/>
         <v>60961.776774486789</v>
       </c>
-      <c r="DC5" s="15">
+      <c r="DC5" s="12">
         <f t="shared" si="28"/>
         <v>62632.021774784764</v>
       </c>
-      <c r="DD5" s="15">
+      <c r="DD5" s="12">
         <f t="shared" si="28"/>
         <v>63342.51065846219</v>
       </c>
-      <c r="DE5" s="12">
+      <c r="DE5" s="10">
         <f t="shared" si="28"/>
         <v>63944.446251923611</v>
       </c>
-      <c r="DF5" s="15">
+      <c r="DF5" s="12">
         <f t="shared" si="28"/>
         <v>57406.988585887273</v>
       </c>
-      <c r="DG5" s="15">
+      <c r="DG5" s="12">
         <f t="shared" ref="DG5:DR5" si="29">DG3-DG4</f>
         <v>57357.52439316392</v>
       </c>
-      <c r="DH5" s="15">
+      <c r="DH5" s="12">
         <f t="shared" si="29"/>
         <v>59388.175415372563</v>
       </c>
-      <c r="DI5" s="15">
+      <c r="DI5" s="12">
         <f t="shared" si="29"/>
         <v>63350.475130806561</v>
       </c>
-      <c r="DJ5" s="15">
+      <c r="DJ5" s="12">
         <f t="shared" si="29"/>
         <v>60603.261845695517</v>
       </c>
-      <c r="DK5" s="15">
+      <c r="DK5" s="12">
         <f t="shared" si="29"/>
         <v>61867.893603274504</v>
       </c>
-      <c r="DL5" s="15">
+      <c r="DL5" s="12">
         <f t="shared" si="29"/>
         <v>61637.07004706825</v>
       </c>
-      <c r="DM5" s="15">
+      <c r="DM5" s="12">
         <f t="shared" si="29"/>
         <v>61560.934115951626</v>
       </c>
-      <c r="DN5" s="15">
+      <c r="DN5" s="12">
         <f t="shared" si="29"/>
         <v>63445.007534118486</v>
       </c>
-      <c r="DO5" s="15">
+      <c r="DO5" s="12">
         <f t="shared" si="29"/>
         <v>62306.629224602286</v>
       </c>
-      <c r="DP5" s="15">
+      <c r="DP5" s="12">
         <f t="shared" si="29"/>
         <v>68952.494401852557</v>
       </c>
-      <c r="DQ5" s="12">
+      <c r="DQ5" s="10">
         <f t="shared" si="29"/>
         <v>64456.489298871573</v>
       </c>
-      <c r="DR5" s="15">
+      <c r="DR5" s="12">
         <f t="shared" si="29"/>
         <v>60485.96807458032</v>
       </c>
-      <c r="DS5" s="15">
+      <c r="DS5" s="12">
         <f t="shared" ref="DS5:ED5" si="30">DS3-DS4</f>
         <v>59411.32518177032</v>
       </c>
-      <c r="DT5" s="15">
+      <c r="DT5" s="12">
         <f t="shared" si="30"/>
         <v>62127.175885416604</v>
       </c>
-      <c r="DU5" s="15">
+      <c r="DU5" s="12">
         <f t="shared" si="30"/>
         <v>64071.219036170274</v>
       </c>
-      <c r="DV5" s="15">
+      <c r="DV5" s="12">
         <f t="shared" si="30"/>
         <v>63420.322439372831</v>
       </c>
-      <c r="DW5" s="15">
+      <c r="DW5" s="12">
         <f t="shared" si="30"/>
         <v>64481.04990342191</v>
       </c>
-      <c r="DX5" s="15">
+      <c r="DX5" s="12">
         <f t="shared" si="30"/>
         <v>65876.418430783291</v>
       </c>
-      <c r="DY5" s="15">
+      <c r="DY5" s="12">
         <f t="shared" si="30"/>
         <v>66339.579134608008</v>
       </c>
-      <c r="DZ5" s="15">
+      <c r="DZ5" s="12">
         <f t="shared" si="30"/>
         <v>66950.66509228581</v>
       </c>
-      <c r="EA5" s="15">
+      <c r="EA5" s="12">
         <f t="shared" si="30"/>
         <v>70527.309909616655</v>
       </c>
-      <c r="EB5" s="15">
+      <c r="EB5" s="12">
         <f t="shared" si="30"/>
         <v>69433.601646875104</v>
       </c>
-      <c r="EC5" s="12">
+      <c r="EC5" s="10">
         <f t="shared" si="30"/>
         <v>70810.432843522096</v>
       </c>
-      <c r="ED5" s="15">
+      <c r="ED5" s="12">
         <f t="shared" si="30"/>
         <v>65357.909281899563</v>
       </c>
-      <c r="EE5" s="15">
+      <c r="EE5" s="12">
         <f t="shared" ref="EE5:EP5" si="31">EE3-EE4</f>
         <v>76298.479884356668</v>
       </c>
-      <c r="EF5" s="15">
+      <c r="EF5" s="12">
         <f t="shared" si="31"/>
         <v>68552.533550074004</v>
       </c>
-      <c r="EG5" s="15">
+      <c r="EG5" s="12">
         <f t="shared" si="31"/>
         <v>68899.789616489565</v>
       </c>
-      <c r="EH5" s="15">
+      <c r="EH5" s="12">
         <f t="shared" si="31"/>
         <v>69451.5918062696</v>
       </c>
-      <c r="EI5" s="15">
+      <c r="EI5" s="12">
         <f t="shared" si="31"/>
         <v>76776.016662622686</v>
       </c>
-      <c r="EJ5" s="15">
+      <c r="EJ5" s="12">
         <f t="shared" si="31"/>
         <v>70450.498908794529</v>
       </c>
-      <c r="EK5" s="15">
+      <c r="EK5" s="12">
         <f t="shared" si="31"/>
         <v>70554.940974786819</v>
       </c>
-      <c r="EL5" s="15">
+      <c r="EL5" s="12">
         <f t="shared" si="31"/>
         <v>72154.926906648267</v>
       </c>
-      <c r="EM5" s="15">
+      <c r="EM5" s="12">
         <f t="shared" si="31"/>
         <v>73801.428317134647</v>
       </c>
-      <c r="EN5" s="15">
+      <c r="EN5" s="12">
         <f t="shared" si="31"/>
         <v>74359.201945163513</v>
       </c>
-      <c r="EO5" s="12">
+      <c r="EO5" s="10">
         <f t="shared" si="31"/>
         <v>76190.47341107126</v>
       </c>
-      <c r="EP5" s="15">
+      <c r="EP5" s="12">
         <f t="shared" si="31"/>
         <v>70948.741536178451</v>
       </c>
-      <c r="EQ5" s="15">
+      <c r="EQ5" s="12">
         <f t="shared" ref="EQ5:FB5" si="32">EQ3-EQ4</f>
         <v>73164.043708000449</v>
       </c>
-      <c r="ER5" s="15">
+      <c r="ER5" s="12">
         <f t="shared" si="32"/>
         <v>76712.129290664219</v>
       </c>
-      <c r="ES5" s="15">
+      <c r="ES5" s="12">
         <f t="shared" si="32"/>
         <v>76713.521714964561</v>
       </c>
-      <c r="ET5" s="15">
+      <c r="ET5" s="12">
         <f t="shared" si="32"/>
         <v>78116.093817218149</v>
       </c>
-      <c r="EU5" s="15">
+      <c r="EU5" s="12">
         <f t="shared" si="32"/>
         <v>78233.022275943338</v>
       </c>
-      <c r="EV5" s="15">
+      <c r="EV5" s="12">
         <f t="shared" si="32"/>
         <v>78110.324336787075</v>
       </c>
-      <c r="EW5" s="15">
+      <c r="EW5" s="12">
         <f t="shared" si="32"/>
         <v>79008.488131520397</v>
       </c>
-      <c r="EX5" s="15">
+      <c r="EX5" s="12">
         <f t="shared" si="32"/>
         <v>80060.593780326351</v>
       </c>
-      <c r="EY5" s="15">
+      <c r="EY5" s="12">
         <f t="shared" si="32"/>
         <v>82448.878285499464</v>
       </c>
-      <c r="EZ5" s="15">
+      <c r="EZ5" s="12">
         <f t="shared" si="32"/>
         <v>83211.956883951148</v>
       </c>
-      <c r="FA5" s="12">
+      <c r="FA5" s="10">
         <f t="shared" si="32"/>
         <v>84390.973273438751</v>
       </c>
-      <c r="FB5" s="15">
+      <c r="FB5" s="12">
         <f t="shared" si="32"/>
         <v>80667.639303024189</v>
       </c>
-      <c r="FC5" s="15">
+      <c r="FC5" s="12">
         <f t="shared" ref="FC5:FN5" si="33">FC3-FC4</f>
         <v>81639.225752646133</v>
       </c>
-      <c r="FD5" s="15">
+      <c r="FD5" s="12">
         <f t="shared" si="33"/>
         <v>83373.852553193516</v>
       </c>
-      <c r="FE5" s="15">
+      <c r="FE5" s="12">
         <f t="shared" si="33"/>
         <v>85552.725409707287</v>
       </c>
-      <c r="FF5" s="15">
+      <c r="FF5" s="12">
         <f t="shared" si="33"/>
         <v>85011.268085845484</v>
       </c>
-      <c r="FG5" s="15">
+      <c r="FG5" s="12">
         <f t="shared" si="33"/>
         <v>85926.392538746717</v>
       </c>
-      <c r="FH5" s="15">
+      <c r="FH5" s="12">
         <f t="shared" si="33"/>
         <v>86668.542160671685</v>
       </c>
-      <c r="FI5" s="15">
+      <c r="FI5" s="12">
         <f t="shared" si="33"/>
         <v>87997.883308316173</v>
       </c>
-      <c r="FJ5" s="15">
+      <c r="FJ5" s="12">
         <f t="shared" si="33"/>
         <v>89038.857724905509</v>
       </c>
-      <c r="FK5" s="15">
+      <c r="FK5" s="12">
         <f t="shared" si="33"/>
         <v>90681.719348469851</v>
       </c>
-      <c r="FL5" s="15">
+      <c r="FL5" s="12">
         <f t="shared" si="33"/>
         <v>91526.645754888843</v>
       </c>
-      <c r="FM5" s="12">
+      <c r="FM5" s="10">
         <f t="shared" si="33"/>
         <v>92672.355873440596</v>
       </c>
-      <c r="FN5" s="15">
+      <c r="FN5" s="12">
         <f t="shared" si="33"/>
         <v>87276.103856114263</v>
       </c>
-      <c r="FO5" s="15">
+      <c r="FO5" s="12">
         <f t="shared" ref="FO5:FZ5" si="34">FO3-FO4</f>
         <v>88376.79400953115</v>
       </c>
-      <c r="FP5" s="15">
+      <c r="FP5" s="12">
         <f t="shared" si="34"/>
         <v>92045.07307932034</v>
       </c>
-      <c r="FQ5" s="15">
+      <c r="FQ5" s="12">
         <f t="shared" si="34"/>
         <v>89182.457968945077</v>
       </c>
-      <c r="FR5" s="15">
+      <c r="FR5" s="12">
         <f t="shared" si="34"/>
         <v>90469.061284520547</v>
       </c>
-      <c r="FS5" s="15">
+      <c r="FS5" s="12">
         <f t="shared" si="34"/>
         <v>91721.141028386948</v>
       </c>
-      <c r="FT5" s="15">
+      <c r="FT5" s="12">
         <f t="shared" si="34"/>
         <v>91507.483955697986</v>
       </c>
-      <c r="FU5" s="15">
+      <c r="FU5" s="12">
         <f t="shared" si="34"/>
         <v>92566.375657961718</v>
       </c>
-      <c r="FV5" s="15">
+      <c r="FV5" s="12">
         <f t="shared" si="34"/>
         <v>93320.644364483858</v>
       </c>
-      <c r="FW5" s="15">
+      <c r="FW5" s="12">
         <f t="shared" si="34"/>
         <v>93659.577249021837</v>
       </c>
-      <c r="FX5" s="15">
+      <c r="FX5" s="12">
         <f t="shared" si="34"/>
         <v>95536.52705862897</v>
       </c>
-      <c r="FY5" s="12">
+      <c r="FY5" s="10">
         <f t="shared" si="34"/>
         <v>95717.789429975557</v>
       </c>
-      <c r="FZ5" s="15">
+      <c r="FZ5" s="12">
         <f t="shared" si="34"/>
         <v>88847.094588272565</v>
       </c>
-      <c r="GA5" s="15">
+      <c r="GA5" s="12">
         <f t="shared" ref="GA5:GL5" si="35">GA3-GA4</f>
         <v>89210.604012758587</v>
       </c>
-      <c r="GB5" s="15">
+      <c r="GB5" s="12">
         <f t="shared" si="35"/>
         <v>94085.924491380822</v>
       </c>
-      <c r="GC5" s="15">
+      <c r="GC5" s="12">
         <f t="shared" si="35"/>
         <v>91005.600658501266</v>
       </c>
-      <c r="GD5" s="15">
+      <c r="GD5" s="12">
         <f t="shared" si="35"/>
         <v>92801.803344126049</v>
       </c>
-      <c r="GE5" s="15">
+      <c r="GE5" s="12">
         <f t="shared" si="35"/>
         <v>92802.708576341087</v>
       </c>
-      <c r="GF5" s="15">
+      <c r="GF5" s="12">
         <f t="shared" si="35"/>
         <v>93391.646485807403</v>
       </c>
-      <c r="GG5" s="15">
+      <c r="GG5" s="12">
         <f t="shared" si="35"/>
         <v>96407.126523216342</v>
       </c>
-      <c r="GH5" s="15">
+      <c r="GH5" s="12">
         <f t="shared" si="35"/>
         <v>96427.166911179607</v>
       </c>
-      <c r="GI5" s="15">
+      <c r="GI5" s="12">
         <f t="shared" si="35"/>
         <v>99976.378100543501</v>
       </c>
-      <c r="GJ5" s="15">
+      <c r="GJ5" s="12">
         <f t="shared" si="35"/>
         <v>101943.53681935374</v>
       </c>
-      <c r="GK5" s="12">
+      <c r="GK5" s="10">
         <f t="shared" si="35"/>
         <v>102894.66887897314</v>
       </c>
-      <c r="GL5" s="15">
+      <c r="GL5" s="12">
         <f t="shared" si="35"/>
         <v>88803.036098399578</v>
       </c>
-      <c r="GM5" s="15">
+      <c r="GM5" s="12">
         <f t="shared" ref="GM5:GX5" si="36">GM3-GM4</f>
         <v>87665.358051399176</v>
       </c>
-      <c r="GN5" s="15">
+      <c r="GN5" s="12">
         <f t="shared" si="36"/>
         <v>92987.367035127798</v>
       </c>
-      <c r="GO5" s="15">
+      <c r="GO5" s="12">
         <f t="shared" si="36"/>
         <v>90829.914995752741</v>
       </c>
-      <c r="GP5" s="15">
+      <c r="GP5" s="12">
         <f t="shared" si="36"/>
         <v>91689.0527315457</v>
       </c>
-      <c r="GQ5" s="15">
+      <c r="GQ5" s="12">
         <f t="shared" si="36"/>
         <v>92991.654208032516</v>
       </c>
-      <c r="GR5" s="15">
+      <c r="GR5" s="12">
         <f t="shared" si="36"/>
         <v>92738.876325323901</v>
       </c>
-      <c r="GS5" s="15">
+      <c r="GS5" s="12">
         <f t="shared" si="36"/>
         <v>93651.432786147052</v>
       </c>
-      <c r="GT5" s="15">
+      <c r="GT5" s="12">
         <f t="shared" si="36"/>
         <v>95155.420875545431</v>
       </c>
-      <c r="GU5" s="15">
+      <c r="GU5" s="12">
         <f t="shared" si="36"/>
         <v>94958.052665239549</v>
       </c>
-      <c r="GV5" s="15">
+      <c r="GV5" s="12">
         <f t="shared" si="36"/>
         <v>95922.835551542841</v>
       </c>
-      <c r="GW5" s="12">
+      <c r="GW5" s="10">
         <f t="shared" si="36"/>
         <v>95942.480772918701</v>
       </c>
-      <c r="GX5" s="15">
+      <c r="GX5" s="12">
         <f t="shared" si="36"/>
         <v>85905.709698259452</v>
       </c>
-      <c r="GY5" s="15">
+      <c r="GY5" s="12">
         <f t="shared" ref="GY5:HJ5" si="37">GY3-GY4</f>
         <v>87986.495878325339</v>
       </c>
-      <c r="GZ5" s="15">
+      <c r="GZ5" s="12">
         <f t="shared" si="37"/>
         <v>94599.481778269037</v>
       </c>
-      <c r="HA5" s="15">
+      <c r="HA5" s="12">
         <f t="shared" si="37"/>
         <v>90246.807229824175</v>
       </c>
-      <c r="HB5" s="15">
+      <c r="HB5" s="12">
         <f t="shared" si="37"/>
         <v>91273.682650800445</v>
       </c>
-      <c r="HC5" s="15">
+      <c r="HC5" s="12">
         <f t="shared" si="37"/>
         <v>94400.532468106641</v>
       </c>
-      <c r="HD5" s="15">
+      <c r="HD5" s="12">
         <f t="shared" si="37"/>
         <v>93537.841268891789</v>
       </c>
-      <c r="HE5" s="15">
+      <c r="HE5" s="12">
         <f t="shared" si="37"/>
         <v>95582.818413853092</v>
       </c>
-      <c r="HF5" s="15">
+      <c r="HF5" s="12">
         <f t="shared" si="37"/>
         <v>96911.156246851737</v>
       </c>
-      <c r="HG5" s="15">
+      <c r="HG5" s="12">
         <f t="shared" si="37"/>
         <v>98308.238070501728</v>
       </c>
-      <c r="HH5" s="15">
+      <c r="HH5" s="12">
         <f t="shared" si="37"/>
         <v>101024.11950229583</v>
       </c>
-      <c r="HI5" s="12">
+      <c r="HI5" s="10">
         <f t="shared" si="37"/>
         <v>101587.33567268436</v>
       </c>
-      <c r="HJ5" s="15">
+      <c r="HJ5" s="12">
         <f t="shared" si="37"/>
         <v>66914.270464972185</v>
       </c>
-      <c r="HK5" s="15">
+      <c r="HK5" s="12">
         <f t="shared" ref="HK5:HV5" si="38">HK3-HK4</f>
         <v>73661.193529983822</v>
       </c>
-      <c r="HL5" s="15">
+      <c r="HL5" s="12">
         <f t="shared" si="38"/>
         <v>82206.220842293784</v>
       </c>
-      <c r="HM5" s="15">
+      <c r="HM5" s="12">
         <f t="shared" si="38"/>
         <v>77782.766470181203</v>
       </c>
-      <c r="HN5" s="15">
+      <c r="HN5" s="12">
         <f t="shared" si="38"/>
         <v>80769.542201492412</v>
       </c>
-      <c r="HO5" s="15">
+      <c r="HO5" s="12">
         <f t="shared" si="38"/>
         <v>84653.665187893086</v>
       </c>
-      <c r="HP5" s="15">
+      <c r="HP5" s="12">
         <f t="shared" si="38"/>
         <v>89699.529724068925</v>
       </c>
-      <c r="HQ5" s="15">
+      <c r="HQ5" s="12">
         <f t="shared" si="38"/>
         <v>96966.138879175633</v>
       </c>
-      <c r="HR5" s="15">
+      <c r="HR5" s="12">
         <f t="shared" si="38"/>
         <v>99917.241888593067</v>
       </c>
-      <c r="HS5" s="15">
+      <c r="HS5" s="12">
         <f t="shared" si="38"/>
         <v>103229.56859549366</v>
       </c>
-      <c r="HT5" s="15">
+      <c r="HT5" s="12">
         <f t="shared" si="38"/>
         <v>110985.91069964178</v>
       </c>
-      <c r="HU5" s="12">
+      <c r="HU5" s="10">
         <f t="shared" si="38"/>
         <v>110961.31280302293</v>
       </c>
-      <c r="HV5" s="15">
+      <c r="HV5" s="12">
         <f t="shared" si="38"/>
         <v>68248.617111566418</v>
       </c>
-      <c r="HW5" s="15">
+      <c r="HW5" s="12">
         <f t="shared" ref="HW5:IH5" si="39">HW3-HW4</f>
         <v>69541.411850963545</v>
       </c>
-      <c r="HX5" s="15">
+      <c r="HX5" s="12">
         <f t="shared" si="39"/>
         <v>75190.638694146561</v>
       </c>
-      <c r="HY5" s="15">
+      <c r="HY5" s="12">
         <f t="shared" si="39"/>
         <v>85140.482514303454</v>
       </c>
-      <c r="HZ5" s="15">
+      <c r="HZ5" s="12">
         <f t="shared" si="39"/>
         <v>89676.164517673227</v>
       </c>
-      <c r="IA5" s="15">
+      <c r="IA5" s="12">
         <f t="shared" si="39"/>
         <v>86430.490638816598</v>
       </c>
-      <c r="IB5" s="15">
+      <c r="IB5" s="12">
         <f t="shared" si="39"/>
         <v>90774.414098144218</v>
       </c>
-      <c r="IC5" s="15">
+      <c r="IC5" s="12">
         <f t="shared" si="39"/>
         <v>104778.12543802116</v>
       </c>
-      <c r="ID5" s="15">
+      <c r="ID5" s="12">
         <f t="shared" si="39"/>
         <v>107552.59002637367</v>
       </c>
-      <c r="IE5" s="15">
+      <c r="IE5" s="12">
         <f t="shared" si="39"/>
         <v>113799.99961554249</v>
       </c>
-      <c r="IF5" s="15">
+      <c r="IF5" s="12">
         <f t="shared" si="39"/>
         <v>118764.31678860744</v>
       </c>
-      <c r="IG5" s="12">
+      <c r="IG5" s="10">
         <f t="shared" si="39"/>
         <v>122576.13093661885</v>
       </c>
-      <c r="IH5" s="15">
+      <c r="IH5" s="12">
         <f t="shared" si="39"/>
         <v>94643.362353678807</v>
       </c>
-      <c r="II5" s="15">
+      <c r="II5" s="12">
         <f t="shared" ref="II5:IS5" si="40">II3-II4</f>
         <v>95803.579024562088</v>
       </c>
-      <c r="IJ5" s="15">
+      <c r="IJ5" s="12">
         <f t="shared" si="40"/>
         <v>106273.00239702934</v>
       </c>
-      <c r="IK5" s="15">
+      <c r="IK5" s="12">
         <f t="shared" si="40"/>
         <v>106286.51266287739</v>
       </c>
-      <c r="IL5" s="15">
+      <c r="IL5" s="12">
         <f t="shared" si="40"/>
         <v>110730.69452935272</v>
       </c>
-      <c r="IM5" s="15">
+      <c r="IM5" s="12">
         <f t="shared" si="40"/>
         <v>109416.9518241912</v>
       </c>
-      <c r="IN5" s="15">
+      <c r="IN5" s="12">
         <f t="shared" si="40"/>
         <v>114801.62208622874</v>
       </c>
-      <c r="IO5" s="15">
+      <c r="IO5" s="12">
         <f t="shared" si="40"/>
         <v>119331.67220008938</v>
       </c>
-      <c r="IP5" s="15">
+      <c r="IP5" s="12">
         <f t="shared" si="40"/>
         <v>121270.53687104858</v>
       </c>
-      <c r="IQ5" s="15">
+      <c r="IQ5" s="12">
         <f t="shared" si="40"/>
         <v>124239.26859417274</v>
       </c>
-      <c r="IR5" s="15">
+      <c r="IR5" s="12">
         <f t="shared" si="40"/>
         <v>124044.85398852898</v>
       </c>
-      <c r="IS5" s="12">
+      <c r="IS5" s="10">
         <f t="shared" si="40"/>
         <v>127113.49521247484</v>
       </c>
     </row>
-    <row r="7" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="IT7" t="s">
-        <v>20</v>
+    <row r="6" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="D6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="F6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="H6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="M6" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="R6" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="S6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="T6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="U6" s="7">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="V6" s="7">
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="W6" s="7">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="X6" s="7">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="Y6" s="11">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="AB6" s="7">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="AC6" s="7">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="AF6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="AG6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="AH6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="AI6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="AJ6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AK6" s="11">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AL6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AM6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AN6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AO6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AP6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AQ6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="AR6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="AS6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="AT6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="AU6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="AV6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="AW6" s="11">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AX6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AY6" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="AZ6" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BA6" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="BB6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="BC6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="BD6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="BE6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="BF6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="BG6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="BH6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BI6" s="11">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BJ6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BK6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BL6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BM6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BN6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BO6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BP6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BQ6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BR6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BS6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BT6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BU6" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="BV6" s="7">
+        <v>0.03</v>
+      </c>
+      <c r="BW6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="BX6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BY6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="BZ6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="CA6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="CB6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="CC6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="CD6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="CE6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="CF6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="CG6" s="16">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="CH6" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="CI6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="CJ6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="CK6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="CL6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="CM6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="CN6" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="CO6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="CP6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="CQ6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="CR6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="CS6" s="11">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="CT6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="CU6" s="7">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="CV6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="CW6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="CX6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="CY6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="CZ6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DA6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DB6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DC6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DD6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DE6" s="16">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DF6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DG6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DH6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DI6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="DJ6" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="DK6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="DL6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="DM6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="DN6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DO6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DP6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DQ6" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DR6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DS6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DT6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DU6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DV6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DW6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DX6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DY6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="DZ6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="EA6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="EB6" s="7">
+        <v>5.5E-2</v>
+      </c>
+      <c r="EC6" s="16">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="ED6" s="7">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="EE6" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="EF6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="EG6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="EH6" s="7">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="EI6" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="EJ6" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="EK6" s="7">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="EL6" s="7">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="EM6" s="7">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="EN6" s="7">
+        <v>7.7499999999999999E-2</v>
+      </c>
+      <c r="EO6" s="16">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="EP6" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="EQ6" s="7">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="ER6" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="ES6" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="ET6" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="EU6" s="7">
+        <v>6.25E-2</v>
+      </c>
+      <c r="EV6" s="7">
+        <v>5.5E-2</v>
+      </c>
+      <c r="EW6" s="7">
+        <v>5.5E-2</v>
+      </c>
+      <c r="EX6" s="7">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="EY6" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="EZ6" s="7">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="FA6" s="16">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="FB6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="FC6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="FD6" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="FE6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FF6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FG6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FH6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FI6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FJ6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FK6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FL6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FM6" s="16">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FN6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FO6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FP6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FQ6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FR6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FS6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FT6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FU6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FV6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FW6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FX6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FY6" s="16">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="FZ6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="GA6" s="7">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="GB6" s="7">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="GC6" s="7">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="GD6" s="7">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="GE6" s="7">
+        <v>2.75E-2</v>
+      </c>
+      <c r="GF6" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="GG6" s="7">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="GH6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GI6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GJ6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GK6" s="16">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GL6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GM6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GN6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GO6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GP6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GQ6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GR6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GS6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GT6" s="7">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="GU6" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="GV6" s="7">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="GW6" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="GX6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="GY6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="GZ6" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="HA6" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="HB6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="HC6" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="HD6" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="HE6" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="HF6" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="HG6" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="HH6" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="HI6" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="HJ6" s="7">
+        <v>0.1275</v>
+      </c>
+      <c r="HK6" s="7">
+        <v>0.1275</v>
+      </c>
+      <c r="HL6" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="HM6" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="HN6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HO6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HP6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HQ6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HR6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HS6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HT6" s="7">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="HU6" s="16">
+        <v>0.13</v>
+      </c>
+      <c r="HV6" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="HW6" s="7">
+        <v>0.1275</v>
+      </c>
+      <c r="HX6" s="7">
+        <v>0.1225</v>
+      </c>
+      <c r="HY6" s="7">
+        <v>0.1225</v>
+      </c>
+      <c r="HZ6" s="7">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="IA6" s="7">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="IB6" s="7">
+        <v>0.1125</v>
+      </c>
+      <c r="IC6" s="7">
+        <v>0.1075</v>
+      </c>
+      <c r="ID6" s="7">
+        <v>0.1075</v>
+      </c>
+      <c r="IE6" s="7">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="IF6" s="7">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="IG6" s="16">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="IH6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="II6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="IJ6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="IK6" s="7">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="IL6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IM6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IN6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IO6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IP6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IQ6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IR6" s="7">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="IS6" s="16">
+        <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="AS8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="AT8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="AU8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="AW8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="AX8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="AZ8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="BA8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="BB8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="BC8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="BD8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="BE8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="BF8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="BG8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="BI8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="BJ8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="BK8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="BL8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="BO8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="BP8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="BQ8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="BR8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="BS8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="BU8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="BV8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="BW8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="BX8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="BY8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="BZ8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="CA8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="CB8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="CC8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="CD8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="CE8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="CG8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="CH8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="CI8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="CJ8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="CK8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="CL8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="CM8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="CN8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="CO8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="CP8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="CQ8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="CS8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="CT8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="CU8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="CV8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="CW8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="CX8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="CY8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="CZ8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="DA8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="DB8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="DC8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="DD8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="DE8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="DF8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="DG8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="DH8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="DI8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="DJ8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="DK8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="DL8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="DM8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="DN8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="DO8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="DP8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="DQ8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="DR8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="DS8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="DT8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="DU8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="DV8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="DW8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="DX8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="DY8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="DZ8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="EA8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="EB8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="EC8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="ED8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="EE8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="EF8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="EG8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="EH8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="EI8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="EJ8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="EK8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="EL8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="EM8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="EN8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="EO8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="EP8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="EQ8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="ER8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="ES8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="ET8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="EU8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="EV8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="EW8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="EX8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="EY8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="EZ8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="FA8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="FB8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="FC8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="FD8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="FE8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="FF8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="FG8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="FH8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="FI8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="FJ8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="FK8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="FL8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="FM8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="FN8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="FO8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="FP8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="FQ8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="FR8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="FS8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="FT8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="FU8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="FV8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="FW8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="FX8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="FY8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="FZ8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="GA8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="GB8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="GC8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="GD8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="GE8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="GF8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="GG8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="GH8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="GI8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="GJ8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="GK8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="GL8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="GM8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="GN8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="GO8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="GP8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="GQ8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="GR8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="GS8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="GT8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="GU8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="GV8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="GW8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="GX8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="GY8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="GZ8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="HA8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="HB8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="HC8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="HD8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="HE8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="HF8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="HG8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="HH8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="HI8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="HJ8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="HK8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="HL8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="HM8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="HN8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="HO8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="HP8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="HQ8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="HR8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="HS8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="HT8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="HU8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="HV8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="HW8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="HX8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="HY8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="HZ8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="IA8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="IB8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="IC8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="ID8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="IE8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="IF8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="IG8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="IH8" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="II8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="IJ8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="IK8" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="IL8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="IM8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="IN8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="IO8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="IP8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="IQ8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="IR8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="IS8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="IT8" s="21" t="s">
-        <v>19</v>
-      </c>
+    <row r="7" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
     </row>
-    <row r="9" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="C9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="D9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="E9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="F9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="G9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="H9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="I9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="M9" s="14">
-        <v>0.06</v>
-      </c>
-      <c r="N9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="O9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="R9" s="9">
-        <v>6.25E-2</v>
-      </c>
-      <c r="S9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="T9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="U9" s="9">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="V9" s="9">
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="W9" s="9">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="X9" s="9">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="Y9" s="14">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="Z9" s="9">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="AA9" s="9">
-        <v>0.08</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>8.2500000000000004E-2</v>
-      </c>
-      <c r="AC9" s="9">
-        <v>8.2500000000000004E-2</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="AE9" s="9">
-        <v>0.09</v>
-      </c>
-      <c r="AF9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="AG9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="AH9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="AI9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="AJ9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="AK9" s="14">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="AL9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="AM9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="AN9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="AO9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="AP9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="AQ9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="AR9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="AS9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="AT9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="AU9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="AV9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="AW9" s="14">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="AX9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="AY9" s="9">
-        <v>0.09</v>
-      </c>
-      <c r="AZ9" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BA9" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="BB9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="BC9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="BD9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="BE9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="BF9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="BG9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="BH9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BI9" s="14">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BJ9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BK9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BL9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BM9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BN9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BO9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BP9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BQ9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BR9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BS9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BT9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BU9" s="14">
-        <v>0.03</v>
-      </c>
-      <c r="BV9" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="BW9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="BX9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BY9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="BZ9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="CA9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="CB9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="CC9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="CD9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="CE9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="CF9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="CG9" s="20">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="CH9" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="CI9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="CJ9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="CK9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="CL9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="CM9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="CN9" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="CO9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="CP9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="CQ9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="CR9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="CS9" s="14">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="CT9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="CU9" s="9">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="CV9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="CW9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="CX9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="CY9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="CZ9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DA9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DB9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DC9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DD9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DE9" s="20">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DF9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DG9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DH9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="DI9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="DJ9" s="9">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="DK9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="DL9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="DM9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="DN9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DO9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DP9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DQ9" s="20">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DR9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DS9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DT9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DU9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DV9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DW9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DX9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DY9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="DZ9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="EA9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="EB9" s="9">
-        <v>5.5E-2</v>
-      </c>
-      <c r="EC9" s="20">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="ED9" s="9">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="EE9" s="9">
-        <v>6.25E-2</v>
-      </c>
-      <c r="EF9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="EG9" s="9">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="EH9" s="9">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="EI9" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="EJ9" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="EK9" s="9">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="EL9" s="9">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="EM9" s="9">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="EN9" s="9">
-        <v>7.7499999999999999E-2</v>
-      </c>
-      <c r="EO9" s="20">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="EP9" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="EQ9" s="9">
-        <v>7.2499999999999995E-2</v>
-      </c>
-      <c r="ER9" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="ES9" s="9">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="ET9" s="9">
-        <v>6.25E-2</v>
-      </c>
-      <c r="EU9" s="9">
-        <v>6.25E-2</v>
-      </c>
-      <c r="EV9" s="9">
-        <v>5.5E-2</v>
-      </c>
-      <c r="EW9" s="9">
-        <v>5.5E-2</v>
-      </c>
-      <c r="EX9" s="9">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="EY9" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="EZ9" s="9">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="FA9" s="20">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="FB9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="FC9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="FD9" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="FE9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FF9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FG9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FH9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FI9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FJ9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FK9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FL9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FM9" s="20">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FN9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FO9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FP9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FQ9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FR9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FS9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FT9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FU9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FV9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FW9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FX9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FY9" s="20">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="FZ9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="GA9" s="9">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="GB9" s="9">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="GC9" s="9">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="GD9" s="9">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="GE9" s="9">
-        <v>2.75E-2</v>
-      </c>
-      <c r="GF9" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="GG9" s="9">
-        <v>2.2499999999999999E-2</v>
-      </c>
-      <c r="GH9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GI9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GJ9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GK9" s="20">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GL9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GM9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GN9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GO9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GP9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GQ9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GR9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GS9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GT9" s="9">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="GU9" s="9">
-        <v>0.02</v>
-      </c>
-      <c r="GV9" s="9">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="GW9" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="GX9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="GY9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="GZ9" s="9">
-        <v>0.04</v>
-      </c>
-      <c r="HA9" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="HB9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="HC9" s="9">
-        <v>0.06</v>
-      </c>
-      <c r="HD9" s="9">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="HE9" s="9">
-        <v>0.09</v>
-      </c>
-      <c r="HF9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="HG9" s="9">
-        <v>0.11</v>
-      </c>
-      <c r="HH9" s="9">
-        <v>0.11</v>
-      </c>
-      <c r="HI9" s="20">
-        <v>0.12</v>
-      </c>
-      <c r="HJ9" s="9">
-        <v>0.1275</v>
-      </c>
-      <c r="HK9" s="9">
-        <v>0.1275</v>
-      </c>
-      <c r="HL9" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="HM9" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="HN9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HO9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HP9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HQ9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HR9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HS9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HT9" s="9">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="HU9" s="20">
-        <v>0.13</v>
-      </c>
-      <c r="HV9" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="HW9" s="9">
-        <v>0.1275</v>
-      </c>
-      <c r="HX9" s="9">
-        <v>0.1225</v>
-      </c>
-      <c r="HY9" s="9">
-        <v>0.1225</v>
-      </c>
-      <c r="HZ9" s="9">
-        <v>0.11749999999999999</v>
-      </c>
-      <c r="IA9" s="9">
-        <v>0.11749999999999999</v>
-      </c>
-      <c r="IB9" s="9">
-        <v>0.1125</v>
-      </c>
-      <c r="IC9" s="9">
-        <v>0.1075</v>
-      </c>
-      <c r="ID9" s="9">
-        <v>0.1075</v>
-      </c>
-      <c r="IE9" s="9">
-        <v>0.10249999999999999</v>
-      </c>
-      <c r="IF9" s="9">
-        <v>9.7500000000000003E-2</v>
-      </c>
-      <c r="IG9" s="20">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="IH9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="II9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="IJ9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="IK9" s="9">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="IL9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IM9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IN9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IO9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IP9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IQ9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IR9" s="9">
-        <v>9.2499999999999999E-2</v>
-      </c>
-      <c r="IS9" s="20">
-        <v>9.2499999999999999E-2</v>
-      </c>
+    <row r="8" spans="1:254" x14ac:dyDescent="0.3">
+      <c r="BV8" s="15"/>
+      <c r="BW8" s="15"/>
+      <c r="BX8" s="15"/>
+      <c r="BY8" s="15"/>
+      <c r="BZ8" s="15"/>
+      <c r="CA8" s="15"/>
+      <c r="CB8" s="15"/>
+      <c r="CC8" s="15"/>
+      <c r="CD8" s="15"/>
+      <c r="CE8" s="15"/>
+      <c r="CF8" s="15"/>
+      <c r="CG8" s="15"/>
     </row>
-    <row r="10" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="Y10" s="1"/>
-    </row>
-    <row r="11" spans="1:254" x14ac:dyDescent="0.25">
-      <c r="BV11" s="19"/>
-      <c r="BW11" s="19"/>
-      <c r="BX11" s="19"/>
-      <c r="BY11" s="19"/>
-      <c r="BZ11" s="19"/>
-      <c r="CA11" s="19"/>
-      <c r="CB11" s="19"/>
-      <c r="CC11" s="19"/>
-      <c r="CD11" s="19"/>
-      <c r="CE11" s="19"/>
-      <c r="CF11" s="19"/>
-      <c r="CG11" s="19"/>
-    </row>
-    <row r="20" spans="86:253" x14ac:dyDescent="0.25">
-      <c r="CH20" s="19"/>
-      <c r="CI20" s="19"/>
-      <c r="CJ20" s="19"/>
-      <c r="CK20" s="19"/>
-      <c r="CL20" s="19"/>
-      <c r="CM20" s="19"/>
-      <c r="CN20" s="19"/>
-      <c r="CO20" s="19"/>
-      <c r="CP20" s="19"/>
-      <c r="CQ20" s="19"/>
-      <c r="CR20" s="19"/>
-      <c r="CS20" s="19"/>
-      <c r="CT20" s="19"/>
-      <c r="CU20" s="19"/>
-      <c r="CV20" s="19"/>
-      <c r="CW20" s="19"/>
-      <c r="CX20" s="19"/>
-      <c r="CY20" s="19"/>
-      <c r="CZ20" s="19"/>
-      <c r="DA20" s="19"/>
-      <c r="DB20" s="19"/>
-      <c r="DC20" s="19"/>
-      <c r="DD20" s="19"/>
-      <c r="DE20" s="19"/>
-      <c r="DF20" s="19"/>
-      <c r="DG20" s="19"/>
-      <c r="DH20" s="19"/>
-      <c r="DI20" s="19"/>
-      <c r="DJ20" s="19"/>
-      <c r="DK20" s="19"/>
-      <c r="DL20" s="19"/>
-      <c r="DM20" s="19"/>
-      <c r="DN20" s="19"/>
-      <c r="DO20" s="19"/>
-      <c r="DP20" s="19"/>
-      <c r="DQ20" s="19"/>
-      <c r="DR20" s="19"/>
-      <c r="DS20" s="19"/>
-      <c r="DT20" s="19"/>
-      <c r="DU20" s="19"/>
-      <c r="DV20" s="19"/>
-      <c r="DW20" s="19"/>
-      <c r="DX20" s="19"/>
-      <c r="DY20" s="19"/>
-      <c r="DZ20" s="19"/>
-      <c r="EA20" s="19"/>
-      <c r="EB20" s="19"/>
-      <c r="EC20" s="19"/>
-      <c r="ED20" s="19"/>
-      <c r="EE20" s="19"/>
-      <c r="EF20" s="19"/>
-      <c r="EG20" s="19"/>
-      <c r="EH20" s="19"/>
-      <c r="EI20" s="19"/>
-      <c r="EJ20" s="19"/>
-      <c r="EK20" s="19"/>
-      <c r="EL20" s="19"/>
-      <c r="EM20" s="19"/>
-      <c r="EN20" s="19"/>
-      <c r="EO20" s="19"/>
-      <c r="EP20" s="19"/>
-      <c r="EQ20" s="19"/>
-      <c r="ER20" s="19"/>
-      <c r="ES20" s="19"/>
-      <c r="ET20" s="19"/>
-      <c r="EU20" s="19"/>
-      <c r="EV20" s="19"/>
-      <c r="EW20" s="19"/>
-      <c r="EX20" s="19"/>
-      <c r="EY20" s="19"/>
-      <c r="EZ20" s="19"/>
-      <c r="FA20" s="19"/>
-      <c r="FB20" s="19"/>
-      <c r="FC20" s="19"/>
-      <c r="FD20" s="19"/>
-      <c r="FE20" s="19"/>
-      <c r="FF20" s="19"/>
-      <c r="FG20" s="19"/>
-      <c r="FH20" s="19"/>
-      <c r="FI20" s="19"/>
-      <c r="FJ20" s="19"/>
-      <c r="FK20" s="19"/>
-      <c r="FL20" s="19"/>
-      <c r="FM20" s="19"/>
-      <c r="FN20" s="19"/>
-      <c r="FO20" s="19"/>
-      <c r="FP20" s="19"/>
-      <c r="FQ20" s="19"/>
-      <c r="FR20" s="19"/>
-      <c r="FS20" s="19"/>
-      <c r="FT20" s="19"/>
-      <c r="FU20" s="19"/>
-      <c r="FV20" s="19"/>
-      <c r="FW20" s="19"/>
-      <c r="FX20" s="19"/>
-      <c r="FY20" s="19"/>
-      <c r="FZ20" s="19"/>
-      <c r="GA20" s="19"/>
-      <c r="GB20" s="19"/>
-      <c r="GC20" s="19"/>
-      <c r="GD20" s="19"/>
-      <c r="GE20" s="19"/>
-      <c r="GF20" s="19"/>
-      <c r="GG20" s="19"/>
-      <c r="GH20" s="19"/>
-      <c r="GI20" s="19"/>
-      <c r="GJ20" s="19"/>
-      <c r="GK20" s="19"/>
-      <c r="GL20" s="19"/>
-      <c r="GM20" s="19"/>
-      <c r="GN20" s="19"/>
-      <c r="GO20" s="19"/>
-      <c r="GP20" s="19"/>
-      <c r="GQ20" s="19"/>
-      <c r="GR20" s="19"/>
-      <c r="GS20" s="19"/>
-      <c r="GT20" s="19"/>
-      <c r="GU20" s="19"/>
-      <c r="GV20" s="19"/>
-      <c r="GW20" s="19"/>
-      <c r="GX20" s="19"/>
-      <c r="GY20" s="19"/>
-      <c r="GZ20" s="19"/>
-      <c r="HA20" s="19"/>
-      <c r="HB20" s="19"/>
-      <c r="HC20" s="19"/>
-      <c r="HD20" s="19"/>
-      <c r="HE20" s="19"/>
-      <c r="HF20" s="19"/>
-      <c r="HG20" s="19"/>
-      <c r="HH20" s="19"/>
-      <c r="HI20" s="19"/>
-      <c r="HJ20" s="19"/>
-      <c r="HK20" s="19"/>
-      <c r="HL20" s="19"/>
-      <c r="HM20" s="19"/>
-      <c r="HN20" s="19"/>
-      <c r="HO20" s="19"/>
-      <c r="HP20" s="19"/>
-      <c r="HQ20" s="19"/>
-      <c r="HR20" s="19"/>
-      <c r="HS20" s="19"/>
-      <c r="HT20" s="19"/>
-      <c r="HU20" s="19"/>
-      <c r="HV20" s="19"/>
-      <c r="HW20" s="19"/>
-      <c r="HX20" s="19"/>
-      <c r="HY20" s="19"/>
-      <c r="HZ20" s="19"/>
-      <c r="IA20" s="19"/>
-      <c r="IB20" s="19"/>
-      <c r="IC20" s="19"/>
-      <c r="ID20" s="19"/>
-      <c r="IE20" s="19"/>
-      <c r="IF20" s="19"/>
-      <c r="IG20" s="19"/>
-      <c r="IH20" s="19"/>
-      <c r="II20" s="19"/>
-      <c r="IJ20" s="19"/>
-      <c r="IK20" s="19"/>
-      <c r="IL20" s="19"/>
-      <c r="IM20" s="19"/>
-      <c r="IN20" s="19"/>
-      <c r="IO20" s="19"/>
-      <c r="IP20" s="19"/>
-      <c r="IQ20" s="19"/>
-      <c r="IR20" s="19"/>
-      <c r="IS20" s="19"/>
+    <row r="17" spans="86:253" x14ac:dyDescent="0.3">
+      <c r="CH17" s="15"/>
+      <c r="CI17" s="15"/>
+      <c r="CJ17" s="15"/>
+      <c r="CK17" s="15"/>
+      <c r="CL17" s="15"/>
+      <c r="CM17" s="15"/>
+      <c r="CN17" s="15"/>
+      <c r="CO17" s="15"/>
+      <c r="CP17" s="15"/>
+      <c r="CQ17" s="15"/>
+      <c r="CR17" s="15"/>
+      <c r="CS17" s="15"/>
+      <c r="CT17" s="15"/>
+      <c r="CU17" s="15"/>
+      <c r="CV17" s="15"/>
+      <c r="CW17" s="15"/>
+      <c r="CX17" s="15"/>
+      <c r="CY17" s="15"/>
+      <c r="CZ17" s="15"/>
+      <c r="DA17" s="15"/>
+      <c r="DB17" s="15"/>
+      <c r="DC17" s="15"/>
+      <c r="DD17" s="15"/>
+      <c r="DE17" s="15"/>
+      <c r="DF17" s="15"/>
+      <c r="DG17" s="15"/>
+      <c r="DH17" s="15"/>
+      <c r="DI17" s="15"/>
+      <c r="DJ17" s="15"/>
+      <c r="DK17" s="15"/>
+      <c r="DL17" s="15"/>
+      <c r="DM17" s="15"/>
+      <c r="DN17" s="15"/>
+      <c r="DO17" s="15"/>
+      <c r="DP17" s="15"/>
+      <c r="DQ17" s="15"/>
+      <c r="DR17" s="15"/>
+      <c r="DS17" s="15"/>
+      <c r="DT17" s="15"/>
+      <c r="DU17" s="15"/>
+      <c r="DV17" s="15"/>
+      <c r="DW17" s="15"/>
+      <c r="DX17" s="15"/>
+      <c r="DY17" s="15"/>
+      <c r="DZ17" s="15"/>
+      <c r="EA17" s="15"/>
+      <c r="EB17" s="15"/>
+      <c r="EC17" s="15"/>
+      <c r="ED17" s="15"/>
+      <c r="EE17" s="15"/>
+      <c r="EF17" s="15"/>
+      <c r="EG17" s="15"/>
+      <c r="EH17" s="15"/>
+      <c r="EI17" s="15"/>
+      <c r="EJ17" s="15"/>
+      <c r="EK17" s="15"/>
+      <c r="EL17" s="15"/>
+      <c r="EM17" s="15"/>
+      <c r="EN17" s="15"/>
+      <c r="EO17" s="15"/>
+      <c r="EP17" s="15"/>
+      <c r="EQ17" s="15"/>
+      <c r="ER17" s="15"/>
+      <c r="ES17" s="15"/>
+      <c r="ET17" s="15"/>
+      <c r="EU17" s="15"/>
+      <c r="EV17" s="15"/>
+      <c r="EW17" s="15"/>
+      <c r="EX17" s="15"/>
+      <c r="EY17" s="15"/>
+      <c r="EZ17" s="15"/>
+      <c r="FA17" s="15"/>
+      <c r="FB17" s="15"/>
+      <c r="FC17" s="15"/>
+      <c r="FD17" s="15"/>
+      <c r="FE17" s="15"/>
+      <c r="FF17" s="15"/>
+      <c r="FG17" s="15"/>
+      <c r="FH17" s="15"/>
+      <c r="FI17" s="15"/>
+      <c r="FJ17" s="15"/>
+      <c r="FK17" s="15"/>
+      <c r="FL17" s="15"/>
+      <c r="FM17" s="15"/>
+      <c r="FN17" s="15"/>
+      <c r="FO17" s="15"/>
+      <c r="FP17" s="15"/>
+      <c r="FQ17" s="15"/>
+      <c r="FR17" s="15"/>
+      <c r="FS17" s="15"/>
+      <c r="FT17" s="15"/>
+      <c r="FU17" s="15"/>
+      <c r="FV17" s="15"/>
+      <c r="FW17" s="15"/>
+      <c r="FX17" s="15"/>
+      <c r="FY17" s="15"/>
+      <c r="FZ17" s="15"/>
+      <c r="GA17" s="15"/>
+      <c r="GB17" s="15"/>
+      <c r="GC17" s="15"/>
+      <c r="GD17" s="15"/>
+      <c r="GE17" s="15"/>
+      <c r="GF17" s="15"/>
+      <c r="GG17" s="15"/>
+      <c r="GH17" s="15"/>
+      <c r="GI17" s="15"/>
+      <c r="GJ17" s="15"/>
+      <c r="GK17" s="15"/>
+      <c r="GL17" s="15"/>
+      <c r="GM17" s="15"/>
+      <c r="GN17" s="15"/>
+      <c r="GO17" s="15"/>
+      <c r="GP17" s="15"/>
+      <c r="GQ17" s="15"/>
+      <c r="GR17" s="15"/>
+      <c r="GS17" s="15"/>
+      <c r="GT17" s="15"/>
+      <c r="GU17" s="15"/>
+      <c r="GV17" s="15"/>
+      <c r="GW17" s="15"/>
+      <c r="GX17" s="15"/>
+      <c r="GY17" s="15"/>
+      <c r="GZ17" s="15"/>
+      <c r="HA17" s="15"/>
+      <c r="HB17" s="15"/>
+      <c r="HC17" s="15"/>
+      <c r="HD17" s="15"/>
+      <c r="HE17" s="15"/>
+      <c r="HF17" s="15"/>
+      <c r="HG17" s="15"/>
+      <c r="HH17" s="15"/>
+      <c r="HI17" s="15"/>
+      <c r="HJ17" s="15"/>
+      <c r="HK17" s="15"/>
+      <c r="HL17" s="15"/>
+      <c r="HM17" s="15"/>
+      <c r="HN17" s="15"/>
+      <c r="HO17" s="15"/>
+      <c r="HP17" s="15"/>
+      <c r="HQ17" s="15"/>
+      <c r="HR17" s="15"/>
+      <c r="HS17" s="15"/>
+      <c r="HT17" s="15"/>
+      <c r="HU17" s="15"/>
+      <c r="HV17" s="15"/>
+      <c r="HW17" s="15"/>
+      <c r="HX17" s="15"/>
+      <c r="HY17" s="15"/>
+      <c r="HZ17" s="15"/>
+      <c r="IA17" s="15"/>
+      <c r="IB17" s="15"/>
+      <c r="IC17" s="15"/>
+      <c r="ID17" s="15"/>
+      <c r="IE17" s="15"/>
+      <c r="IF17" s="15"/>
+      <c r="IG17" s="15"/>
+      <c r="IH17" s="15"/>
+      <c r="II17" s="15"/>
+      <c r="IJ17" s="15"/>
+      <c r="IK17" s="15"/>
+      <c r="IL17" s="15"/>
+      <c r="IM17" s="15"/>
+      <c r="IN17" s="15"/>
+      <c r="IO17" s="15"/>
+      <c r="IP17" s="15"/>
+      <c r="IQ17" s="15"/>
+      <c r="IR17" s="15"/>
+      <c r="IS17" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C26042-18BD-4273-A3AF-A99E92D17BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9EC72C-5655-4B2E-9D22-857055252AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="18">
   <si>
     <t>AÑO</t>
   </si>
@@ -96,10 +96,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -407,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7710FB4-1D75-4856-9D30-3BF005362D8B}">
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -5290,7 +5296,140 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>2026</v>
+      </c>
+      <c r="B254" t="s">
+        <v>5</v>
+      </c>
+      <c r="F254">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>2026</v>
+      </c>
+      <c r="B255" t="s">
+        <v>6</v>
+      </c>
+      <c r="F255">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>2026</v>
+      </c>
+      <c r="B256" t="s">
+        <v>7</v>
+      </c>
+      <c r="F256">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>2026</v>
+      </c>
+      <c r="B257" t="s">
+        <v>8</v>
+      </c>
+      <c r="F257">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>2026</v>
+      </c>
+      <c r="B258" t="s">
+        <v>9</v>
+      </c>
+      <c r="F258">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>2026</v>
+      </c>
+      <c r="B259" t="s">
+        <v>10</v>
+      </c>
+      <c r="F259">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>2026</v>
+      </c>
+      <c r="B260" t="s">
+        <v>11</v>
+      </c>
+      <c r="F260">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>2026</v>
+      </c>
+      <c r="B261" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>2026</v>
+      </c>
+      <c r="B262" t="s">
+        <v>13</v>
+      </c>
+      <c r="F262">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>2026</v>
+      </c>
+      <c r="B263" t="s">
+        <v>14</v>
+      </c>
+      <c r="F263">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>2026</v>
+      </c>
+      <c r="B264" t="s">
+        <v>15</v>
+      </c>
+      <c r="F264">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>2026</v>
+      </c>
+      <c r="B265" t="s">
+        <v>16</v>
+      </c>
+      <c r="F265">
+        <v>0.13</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9EC72C-5655-4B2E-9D22-857055252AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12AC859-9DFD-45F0-A457-EBE9C56A033A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,16 +114,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -127,14 +144,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -413,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7710FB4-1D75-4856-9D30-3BF005362D8B}">
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:DZ265"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -443,13 +497,13 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="4">
         <v>32790.077908983025</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="4">
         <v>14093.620264434951</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="4">
         <v>18696.457644548074</v>
       </c>
       <c r="F2">
@@ -463,13 +517,13 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>32128.51999336536</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>13900.049437858104</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>18228.470555507258</v>
       </c>
       <c r="F3">
@@ -483,13 +537,13 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>37128.281537396892</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>14386.374721816268</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>22741.906815580624</v>
       </c>
       <c r="F4">
@@ -503,13 +557,13 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>36248.373382015947</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>14315.991990494918</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>21932.381391521027</v>
       </c>
       <c r="F5">
@@ -523,13 +577,13 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>35987.711776337484</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>14489.77260139857</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>21497.939174938914</v>
       </c>
       <c r="F6">
@@ -543,13 +597,13 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>34904.228120450076</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>14418.028754992763</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>20486.199365457313</v>
       </c>
       <c r="F7">
@@ -563,13 +617,13 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>36037.159659434183</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>14617.887918750595</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>21419.271740683587</v>
       </c>
       <c r="F8">
@@ -583,13 +637,13 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>34312.458634863899</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>14679.565901569938</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>19632.89273329396</v>
       </c>
       <c r="F9">
@@ -603,13 +657,13 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>33945.279755463183</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>14598.086221905707</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>19347.193533557474</v>
       </c>
       <c r="F10">
@@ -623,13 +677,13 @@
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>35289.013715147557</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>14801.535549246313</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>20487.478165901244</v>
       </c>
       <c r="F11">
@@ -643,13 +697,13 @@
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>34484.083313307143</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
         <v>14709.143342629954</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>19774.939970677187</v>
       </c>
       <c r="F12">
@@ -663,13 +717,13 @@
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>36786.444008420447</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>14927.300526272693</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>21859.143482147752</v>
       </c>
       <c r="F13">
@@ -683,13 +737,13 @@
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>30695.298207016058</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="4">
         <v>11929.845301432179</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>18765.452905583879</v>
       </c>
       <c r="F14">
@@ -703,13 +757,13 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>30416.557877666655</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>11612.756042107814</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>18803.801835558843</v>
       </c>
       <c r="F15">
@@ -723,13 +777,13 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>33697.311141683407</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="4">
         <v>12219.583536825376</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>21477.727604858032</v>
       </c>
       <c r="F16">
@@ -743,13 +797,13 @@
       <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="4">
         <v>34520.567238962773</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="4">
         <v>12256.670245216828</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>22263.896993745944</v>
       </c>
       <c r="F17">
@@ -763,13 +817,13 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>33517.787777975129</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>12541.310986274913</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>20976.476791700217</v>
       </c>
       <c r="F18">
@@ -783,13 +837,13 @@
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4">
         <v>33378.235074134049</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="4">
         <v>12569.501682184005</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>20808.733391950045</v>
       </c>
       <c r="F19">
@@ -803,13 +857,13 @@
       <c r="B20" t="s">
         <v>11</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="4">
         <v>34680.569732790282</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="4">
         <v>12841.25629590105</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>21839.313436889232</v>
       </c>
       <c r="F20">
@@ -823,13 +877,13 @@
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="4">
         <v>34500.370875939581</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="4">
         <v>12965.784595218889</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>21534.586280720694</v>
       </c>
       <c r="F21">
@@ -843,13 +897,13 @@
       <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="4">
         <v>34105.142513812476</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="4">
         <v>12942.554453523537</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
         <v>21162.588060288937</v>
       </c>
       <c r="F22">
@@ -863,13 +917,13 @@
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="4">
         <v>35446.46405673134</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="4">
         <v>13227.573975810654</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>22218.890080920686</v>
       </c>
       <c r="F23">
@@ -883,13 +937,13 @@
       <c r="B24" t="s">
         <v>15</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4">
         <v>35438.632976379384</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>13180.06665324112</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>22258.566323138264</v>
       </c>
       <c r="F24">
@@ -903,13 +957,13 @@
       <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="4">
         <v>35205.804590990723</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>13561.188079865475</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>21644.616511125249</v>
       </c>
       <c r="F25">
@@ -923,6 +977,9 @@
       <c r="B26" t="s">
         <v>5</v>
       </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
       <c r="F26">
         <v>7.7499999999999999E-2</v>
       </c>
@@ -934,6 +991,9 @@
       <c r="B27" t="s">
         <v>6</v>
       </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
       <c r="F27">
         <v>0.08</v>
       </c>
@@ -945,6 +1005,9 @@
       <c r="B28" t="s">
         <v>7</v>
       </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
       <c r="F28">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -956,6 +1019,9 @@
       <c r="B29" t="s">
         <v>8</v>
       </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
       <c r="F29">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -967,6 +1033,9 @@
       <c r="B30" t="s">
         <v>9</v>
       </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
       <c r="F30">
         <v>8.7499999999999994E-2</v>
       </c>
@@ -978,6 +1047,9 @@
       <c r="B31" t="s">
         <v>10</v>
       </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
       <c r="F31">
         <v>0.09</v>
       </c>
@@ -989,6 +1061,9 @@
       <c r="B32" t="s">
         <v>11</v>
       </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
       <c r="F32">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1000,6 +1075,9 @@
       <c r="B33" t="s">
         <v>12</v>
       </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
       <c r="F33">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1011,6 +1089,9 @@
       <c r="B34" t="s">
         <v>13</v>
       </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
       <c r="F34">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1022,6 +1103,9 @@
       <c r="B35" t="s">
         <v>14</v>
       </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
       <c r="F35">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1033,6 +1117,9 @@
       <c r="B36" t="s">
         <v>15</v>
       </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
       <c r="F36">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1044,6 +1131,9 @@
       <c r="B37" t="s">
         <v>16</v>
       </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
       <c r="F37">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1055,13 +1145,13 @@
       <c r="B38" t="s">
         <v>5</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="4">
         <v>48702.885915624407</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
         <v>16148.406349484414</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>32554.479566139991</v>
       </c>
       <c r="F38">
@@ -1075,13 +1165,13 @@
       <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="4">
         <v>49126.667453218142</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>16443.325839939072</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="4">
         <v>32683.34161327907</v>
       </c>
       <c r="F39">
@@ -1095,13 +1185,13 @@
       <c r="B40" t="s">
         <v>7</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="4">
         <v>52658.899769440875</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="4">
         <v>17195.569465043904</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="4">
         <v>35463.330304396972</v>
       </c>
       <c r="F40">
@@ -1115,13 +1205,13 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="4">
         <v>52171.507684440585</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="4">
         <v>17324.651314703486</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>34846.856369737099</v>
       </c>
       <c r="F41">
@@ -1135,13 +1225,13 @@
       <c r="B42" t="s">
         <v>9</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="4">
         <v>53819.20806508878</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="4">
         <v>17943.698743044526</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>35875.50932204425</v>
       </c>
       <c r="F42">
@@ -1155,13 +1245,13 @@
       <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="4">
         <v>54771.35983740518</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="4">
         <v>18257.877630002175</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>36513.482207403009</v>
       </c>
       <c r="F43">
@@ -1175,13 +1265,13 @@
       <c r="B44" t="s">
         <v>11</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="4">
         <v>57141.011161915405</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="4">
         <v>18629.571163170131</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>38511.439998745278</v>
       </c>
       <c r="F44">
@@ -1195,13 +1285,13 @@
       <c r="B45" t="s">
         <v>12</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="4">
         <v>58398.548847401966</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="4">
         <v>18862.976621251128</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>39535.572226150834</v>
       </c>
       <c r="F45">
@@ -1215,13 +1305,13 @@
       <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="4">
         <v>59436.635763009799</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
         <v>18742.834521805442</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="4">
         <v>40693.801241204361</v>
       </c>
       <c r="F46">
@@ -1235,13 +1325,13 @@
       <c r="B47" t="s">
         <v>14</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="4">
         <v>61032.265569597606</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="4">
         <v>18969.628297434101</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="4">
         <v>42062.637272163505</v>
       </c>
       <c r="F47">
@@ -1255,13 +1345,13 @@
       <c r="B48" t="s">
         <v>15</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="4">
         <v>61699.402000504619</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
         <v>18548.792210220268</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="4">
         <v>43150.609790284347</v>
       </c>
       <c r="F48">
@@ -1275,13 +1365,13 @@
       <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="4">
         <v>62378.801356091462</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="4">
         <v>18806.491239585608</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="4">
         <v>43572.310116505854</v>
       </c>
       <c r="F49">
@@ -1295,13 +1385,13 @@
       <c r="B50" t="s">
         <v>5</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="4">
         <v>61331.798002306605</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="4">
         <v>21230.248937401037</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="4">
         <v>40101.549064905572</v>
       </c>
       <c r="F50">
@@ -1315,13 +1405,13 @@
       <c r="B51" t="s">
         <v>6</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="4">
         <v>60674.786562767847</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="4">
         <v>20717.547625202518</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="4">
         <v>39957.238937565329</v>
       </c>
       <c r="F51">
@@ -1335,13 +1425,13 @@
       <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="4">
         <v>65608.881801703508</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>20494.133882468475</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="4">
         <v>45114.747919235029</v>
       </c>
       <c r="F52">
@@ -1355,13 +1445,13 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="4">
         <v>64808.020317109447</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="4">
         <v>21507.966944576099</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="4">
         <v>43300.053372533352</v>
       </c>
       <c r="F53">
@@ -1375,13 +1465,13 @@
       <c r="B54" t="s">
         <v>9</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="4">
         <v>66398.538399304147</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="4">
         <v>22099.402830220311</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="4">
         <v>44299.135569083839</v>
       </c>
       <c r="F54">
@@ -1395,13 +1485,13 @@
       <c r="B55" t="s">
         <v>10</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="4">
         <v>66731.439805295973</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="4">
         <v>21685.169748274333</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="4">
         <v>45046.27005702164</v>
       </c>
       <c r="F55">
@@ -1415,13 +1505,13 @@
       <c r="B56" t="s">
         <v>11</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="4">
         <v>67152.326625880232</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="4">
         <v>21792.670334259845</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="4">
         <v>45359.656291620384</v>
       </c>
       <c r="F56">
@@ -1435,13 +1525,13 @@
       <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="4">
         <v>69223.898253083564</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>22880.901615861691</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="4">
         <v>46342.996637221877</v>
       </c>
       <c r="F57">
@@ -1455,13 +1545,13 @@
       <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="4">
         <v>69391.287762713371</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="4">
         <v>22594.048218141899</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="4">
         <v>46797.239544571472</v>
       </c>
       <c r="F58">
@@ -1475,13 +1565,13 @@
       <c r="B59" t="s">
         <v>14</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="4">
         <v>71003.94222564307</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="4">
         <v>22816.505932854223</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="4">
         <v>48187.436292788843</v>
       </c>
       <c r="F59">
@@ -1495,13 +1585,13 @@
       <c r="B60" t="s">
         <v>15</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="4">
         <v>72013.463669955192</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="4">
         <v>22396.657885139241</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="4">
         <v>49616.805784815951</v>
       </c>
       <c r="F60">
@@ -1515,13 +1605,13 @@
       <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="4">
         <v>82593.712888649694</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="4">
         <v>23570.554673733128</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="4">
         <v>59023.158214916562</v>
       </c>
       <c r="F61">
@@ -1535,13 +1625,13 @@
       <c r="B62" t="s">
         <v>5</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="4">
         <v>56511.270921737152</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="4">
         <v>13973.354689899539</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="4">
         <v>42537.916231837611</v>
       </c>
       <c r="F62">
@@ -1555,13 +1645,13 @@
       <c r="B63" t="s">
         <v>6</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="4">
         <v>55643.0021232695</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="4">
         <v>13111.962749757122</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="4">
         <v>42531.03937351238</v>
       </c>
       <c r="F63">
@@ -1575,13 +1665,13 @@
       <c r="B64" t="s">
         <v>7</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="4">
         <v>63497.384954216272</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>12987.052039227068</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="4">
         <v>50510.332914989202</v>
       </c>
       <c r="F64">
@@ -1595,13 +1685,13 @@
       <c r="B65" t="s">
         <v>8</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="4">
         <v>58537.33033389756</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>13182.136468922454</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="4">
         <v>45355.19386497511</v>
       </c>
       <c r="F65">
@@ -1615,13 +1705,13 @@
       <c r="B66" t="s">
         <v>9</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="4">
         <v>60571.264168359397</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="4">
         <v>13793.82312956908</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="4">
         <v>46777.441038790319</v>
       </c>
       <c r="F66">
@@ -1635,13 +1725,13 @@
       <c r="B67" t="s">
         <v>10</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="4">
         <v>61455.772903641722</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="4">
         <v>14246.441988221199</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="4">
         <v>47209.33091542052</v>
       </c>
       <c r="F67">
@@ -1655,13 +1745,13 @@
       <c r="B68" t="s">
         <v>11</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="4">
         <v>66337.000703474798</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="4">
         <v>14766.058660192595</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="4">
         <v>51570.942043282201</v>
       </c>
       <c r="F68">
@@ -1675,13 +1765,13 @@
       <c r="B69" t="s">
         <v>12</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="4">
         <v>66243.467107830395</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="4">
         <v>15048.606484654056</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="4">
         <v>51194.860623176341</v>
       </c>
       <c r="F69">
@@ -1695,13 +1785,13 @@
       <c r="B70" t="s">
         <v>13</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="4">
         <v>65126.618559629576</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="4">
         <v>15210.191904310497</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="4">
         <v>49916.426655319083</v>
       </c>
       <c r="F70">
@@ -1715,13 +1805,13 @@
       <c r="B71" t="s">
         <v>14</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="4">
         <v>65809.724506028433</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="4">
         <v>15886.610114547811</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="4">
         <v>49923.114391480623</v>
       </c>
       <c r="F71">
@@ -1735,13 +1825,13 @@
       <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="4">
         <v>68812.047016905606</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="4">
         <v>16182.411607081516</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="4">
         <v>52629.635409824092</v>
       </c>
       <c r="F72">
@@ -1755,13 +1845,13 @@
       <c r="B73" t="s">
         <v>16</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="4">
         <v>75367.344535418175</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="4">
         <v>16917.932998585416</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="4">
         <v>58449.411536832762</v>
       </c>
       <c r="F73">
@@ -1775,13 +1865,13 @@
       <c r="B74" t="s">
         <v>5</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="4">
         <v>61650.117977190799</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="4">
         <v>12096.026018327382</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="4">
         <v>49554.091958863413</v>
       </c>
       <c r="F74">
@@ -1795,13 +1885,13 @@
       <c r="B75" t="s">
         <v>6</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="4">
         <v>69276.649879479344</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="4">
         <v>11692.651175314717</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="4">
         <v>57583.998704164624</v>
       </c>
       <c r="F75">
@@ -1815,13 +1905,13 @@
       <c r="B76" t="s">
         <v>7</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="4">
         <v>58076.795237136474</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="4">
         <v>12217.076010635725</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="4">
         <v>45859.719226500747</v>
       </c>
       <c r="F76">
@@ -1835,13 +1925,13 @@
       <c r="B77" t="s">
         <v>8</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="4">
         <v>57135.374455117715</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="4">
         <v>12623.063472337913</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="4">
         <v>44512.310982779803</v>
       </c>
       <c r="F77">
@@ -1855,13 +1945,13 @@
       <c r="B78" t="s">
         <v>9</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="4">
         <v>62480.582996670542</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="4">
         <v>13079.571061754499</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="4">
         <v>49401.011934916045</v>
       </c>
       <c r="F78">
@@ -1875,13 +1965,13 @@
       <c r="B79" t="s">
         <v>10</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="4">
         <v>58484.775860981325</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="4">
         <v>13248.582537934368</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="4">
         <v>45236.193323046959</v>
       </c>
       <c r="F79">
@@ -1895,13 +1985,13 @@
       <c r="B80" t="s">
         <v>11</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="4">
         <v>59196.954618506999</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="4">
         <v>14099.122997477327</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="4">
         <v>45097.831621029676</v>
       </c>
       <c r="F80">
@@ -1915,13 +2005,13 @@
       <c r="B81" t="s">
         <v>12</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="4">
         <v>60484.095847184246</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="4">
         <v>14561.340864337599</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="4">
         <v>45922.754982846644</v>
       </c>
       <c r="F81">
@@ -1935,13 +2025,13 @@
       <c r="B82" t="s">
         <v>13</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="4">
         <v>61384.625898967228</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="4">
         <v>14758.735738501069</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="4">
         <v>46625.890160466159</v>
       </c>
       <c r="F82">
@@ -1955,13 +2045,13 @@
       <c r="B83" t="s">
         <v>14</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="4">
         <v>62885.479902983796</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="4">
         <v>15579.885690979034</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="4">
         <v>47305.594212004762</v>
       </c>
       <c r="F83">
@@ -1975,13 +2065,13 @@
       <c r="B84" t="s">
         <v>15</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="4">
         <v>63364.685394820444</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="4">
         <v>15498.626382091608</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="4">
         <v>47866.059012728838</v>
       </c>
       <c r="F84">
@@ -1995,13 +2085,13 @@
       <c r="B85" t="s">
         <v>16</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="4">
         <v>65927.099982887041</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="4">
         <v>15818.548852178592</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="4">
         <v>50108.551130708453</v>
       </c>
       <c r="F85">
@@ -2015,9 +2105,11 @@
       <c r="B86" t="s">
         <v>5</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="4">
         <v>63725.229914205935</v>
       </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
       <c r="F86">
         <v>0.05</v>
       </c>
@@ -2029,9 +2121,11 @@
       <c r="B87" t="s">
         <v>6</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="4">
         <v>65415.265259352978</v>
       </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
       <c r="F87">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2043,9 +2137,11 @@
       <c r="B88" t="s">
         <v>7</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="4">
         <v>70368.514697734805</v>
       </c>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
       <c r="F88">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2057,9 +2153,11 @@
       <c r="B89" t="s">
         <v>8</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="4">
         <v>69374.077526891735</v>
       </c>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
       <c r="F89">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2071,9 +2169,11 @@
       <c r="B90" t="s">
         <v>9</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="4">
         <v>70818.204072076362</v>
       </c>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
       <c r="F90">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2085,9 +2185,11 @@
       <c r="B91" t="s">
         <v>10</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="4">
         <v>69888.728750856215</v>
       </c>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
       <c r="F91">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2099,9 +2201,11 @@
       <c r="B92" t="s">
         <v>11</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="4">
         <v>71207.490530704876</v>
       </c>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
       <c r="F92">
         <v>0.05</v>
       </c>
@@ -2113,9 +2217,11 @@
       <c r="B93" t="s">
         <v>12</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="4">
         <v>72055.689724337324</v>
       </c>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
       <c r="F93">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2127,9 +2233,11 @@
       <c r="B94" t="s">
         <v>13</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="4">
         <v>72919.743963731147</v>
       </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
       <c r="F94">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2141,9 +2249,11 @@
       <c r="B95" t="s">
         <v>14</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="4">
         <v>75234.579967030309</v>
       </c>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
       <c r="F95">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2155,9 +2265,11 @@
       <c r="B96" t="s">
         <v>15</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="4">
         <v>75289.523450518114</v>
       </c>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
       <c r="F96">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -2169,9 +2281,11 @@
       <c r="B97" t="s">
         <v>16</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="4">
         <v>79405.445935437034</v>
       </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
       <c r="F97">
         <v>4.2500000000000003E-2</v>
       </c>
@@ -2183,13 +2297,13 @@
       <c r="B98" t="s">
         <v>5</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="4">
         <v>82128.103555092719</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="4">
         <v>20606.475300367747</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="4">
         <v>61521.628254724972</v>
       </c>
       <c r="F98">
@@ -2203,13 +2317,13 @@
       <c r="B99" t="s">
         <v>6</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="4">
         <v>79724.534947023261</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="4">
         <v>19258.418337713854</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="4">
         <v>60466.116609309407</v>
       </c>
       <c r="F99">
@@ -2223,13 +2337,13 @@
       <c r="B100" t="s">
         <v>7</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="4">
         <v>90636.787861366858</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="4">
         <v>20352.877932465653</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="4">
         <v>70283.909928901208</v>
       </c>
       <c r="F100">
@@ -2243,13 +2357,13 @@
       <c r="B101" t="s">
         <v>8</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="4">
         <v>78875.848020440608</v>
       </c>
-      <c r="D101">
+      <c r="D101" s="4">
         <v>20908.511983224253</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="4">
         <v>57967.336037216359</v>
       </c>
       <c r="F101">
@@ -2263,13 +2377,13 @@
       <c r="B102" t="s">
         <v>9</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="4">
         <v>84316.561715054748</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="4">
         <v>21464.27168116441</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="4">
         <v>62852.290033890342</v>
       </c>
       <c r="F102">
@@ -2283,13 +2397,13 @@
       <c r="B103" t="s">
         <v>10</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="4">
         <v>81591.628930762308</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="4">
         <v>20951.35566565302</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="4">
         <v>60640.273265109288</v>
       </c>
       <c r="F103">
@@ -2303,13 +2417,13 @@
       <c r="B104" t="s">
         <v>11</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="4">
         <v>82143.602919138953</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="4">
         <v>22312.822677317752</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="4">
         <v>59830.780241821201</v>
       </c>
       <c r="F104">
@@ -2323,13 +2437,13 @@
       <c r="B105" t="s">
         <v>12</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="4">
         <v>82372.110876232255</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="4">
         <v>22737.4821369575</v>
       </c>
-      <c r="E105">
+      <c r="E105" s="4">
         <v>59634.628739274754</v>
       </c>
       <c r="F105">
@@ -2343,13 +2457,13 @@
       <c r="B106" t="s">
         <v>13</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="4">
         <v>83426.735220732327</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="4">
         <v>22464.958446245542</v>
       </c>
-      <c r="E106">
+      <c r="E106" s="4">
         <v>60961.776774486789</v>
       </c>
       <c r="F106">
@@ -2363,13 +2477,13 @@
       <c r="B107" t="s">
         <v>14</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="4">
         <v>85756.241653853765</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="4">
         <v>23124.219879069002</v>
       </c>
-      <c r="E107">
+      <c r="E107" s="4">
         <v>62632.021774784764</v>
       </c>
       <c r="F107">
@@ -2383,13 +2497,13 @@
       <c r="B108" t="s">
         <v>15</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="4">
         <v>86588.919003799107</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="4">
         <v>23246.408345336917</v>
       </c>
-      <c r="E108">
+      <c r="E108" s="4">
         <v>63342.51065846219</v>
       </c>
       <c r="F108">
@@ -2403,13 +2517,13 @@
       <c r="B109" t="s">
         <v>16</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="4">
         <v>87389.131249876067</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="4">
         <v>23444.684997952456</v>
       </c>
-      <c r="E109">
+      <c r="E109" s="4">
         <v>63944.446251923611</v>
       </c>
       <c r="F109">
@@ -2423,13 +2537,13 @@
       <c r="B110" t="s">
         <v>5</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="4">
         <v>75661.628297290517</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="4">
         <v>18254.639711403248</v>
       </c>
-      <c r="E110">
+      <c r="E110" s="4">
         <v>57406.988585887273</v>
       </c>
       <c r="F110">
@@ -2443,13 +2557,13 @@
       <c r="B111" t="s">
         <v>6</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="4">
         <v>74663.431089441758</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="4">
         <v>17305.906696277838</v>
       </c>
-      <c r="E111">
+      <c r="E111" s="4">
         <v>57357.52439316392</v>
       </c>
       <c r="F111">
@@ -2463,333 +2577,1431 @@
       <c r="B112" t="s">
         <v>7</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="4">
         <v>77748.724676647937</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="4">
         <v>18360.549261275373</v>
       </c>
-      <c r="E112">
+      <c r="E112" s="4">
         <v>59388.175415372563</v>
       </c>
       <c r="F112">
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2014</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="4">
         <v>81918.32014703007</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="4">
         <v>18567.845016223509</v>
       </c>
-      <c r="E113">
+      <c r="E113" s="4">
         <v>63350.475130806561</v>
       </c>
       <c r="F113">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2014</v>
       </c>
       <c r="B114" t="s">
         <v>9</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="4">
         <v>79936.927433566729</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="4">
         <v>19333.665587871212</v>
       </c>
-      <c r="E114">
+      <c r="E114" s="4">
         <v>60603.261845695517</v>
       </c>
       <c r="F114">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2014</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="4">
         <v>80986.672704775876</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="4">
         <v>19118.779101501372</v>
       </c>
-      <c r="E115">
+      <c r="E115" s="4">
         <v>61867.893603274504</v>
       </c>
       <c r="F115">
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2014</v>
       </c>
       <c r="B116" t="s">
         <v>11</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="4">
         <v>82157.333083374542</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="4">
         <v>20520.263036306296</v>
       </c>
-      <c r="E116">
+      <c r="E116" s="4">
         <v>61637.07004706825</v>
       </c>
       <c r="F116">
         <v>0.04</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2014</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="4">
         <v>83188.122126282455</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="4">
         <v>21627.188010330829</v>
       </c>
-      <c r="E117">
+      <c r="E117" s="4">
         <v>61560.934115951626</v>
       </c>
       <c r="F117">
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2014</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="4">
         <v>85693.698487573871</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="4">
         <v>22248.690953455389</v>
       </c>
-      <c r="E118">
+      <c r="E118" s="4">
         <v>63445.007534118486</v>
       </c>
       <c r="F118">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2014</v>
       </c>
       <c r="B119" t="s">
         <v>14</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="4">
         <v>86354.455163383638</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="4">
         <v>24047.825938781352</v>
       </c>
-      <c r="E119">
+      <c r="E119" s="4">
         <v>62306.629224602286</v>
       </c>
       <c r="F119">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2014</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="4">
         <v>92969.208679682037</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="4">
         <v>24016.71427782948</v>
       </c>
-      <c r="E120">
+      <c r="E120" s="4">
         <v>68952.494401852557</v>
       </c>
       <c r="F120">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2014</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="4">
         <v>88718.739659897241</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="4">
         <v>24262.250361025668</v>
       </c>
-      <c r="E121">
+      <c r="E121" s="4">
         <v>64456.489298871573</v>
       </c>
       <c r="F121">
         <v>4.4999999999999998E-2</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I121" s="3">
+        <v>81159.76346175003</v>
+      </c>
+      <c r="J121" s="1">
+        <v>82713.761696080008</v>
+      </c>
+      <c r="K121" s="1">
+        <v>83948.018517999997</v>
+      </c>
+      <c r="L121" s="1">
+        <v>85120.711910999991</v>
+      </c>
+      <c r="M121" s="1">
+        <v>110922.72586500001</v>
+      </c>
+      <c r="N121" s="1">
+        <v>123371.21351311001</v>
+      </c>
+      <c r="O121" s="1">
+        <v>133093.31922899999</v>
+      </c>
+      <c r="P121" s="1">
+        <v>42994.594308889988</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>104266.888657</v>
+      </c>
+      <c r="R121" s="1">
+        <v>104229.48909100002</v>
+      </c>
+      <c r="S121" s="1">
+        <v>103818.62562800001</v>
+      </c>
+      <c r="T121" s="1">
+        <v>99674.036412999994</v>
+      </c>
+      <c r="U121" s="1">
+        <v>113205.491565</v>
+      </c>
+      <c r="V121" s="1">
+        <v>108152.695545</v>
+      </c>
+      <c r="W121" s="1">
+        <v>110794.26754649998</v>
+      </c>
+      <c r="X121" s="1">
+        <v>107378.78004900001</v>
+      </c>
+      <c r="Y121" s="1">
+        <v>108204.43721600001</v>
+      </c>
+      <c r="Z121" s="1">
+        <v>116180.137313</v>
+      </c>
+      <c r="AA121" s="1">
+        <v>107296.76061000001</v>
+      </c>
+      <c r="AB121" s="1">
+        <v>107657.629265</v>
+      </c>
+      <c r="AC121" s="1">
+        <v>107398.25651100003</v>
+      </c>
+      <c r="AD121" s="1">
+        <v>105472.14983700002</v>
+      </c>
+      <c r="AE121" s="1">
+        <v>106806.00375700003</v>
+      </c>
+      <c r="AF121" s="1">
+        <v>107689.120717</v>
+      </c>
+      <c r="AG121" s="1">
+        <v>107967.03632900001</v>
+      </c>
+      <c r="AH121" s="1">
+        <v>109730.02317499999</v>
+      </c>
+      <c r="AI121" s="1">
+        <v>108210.17232199998</v>
+      </c>
+      <c r="AJ121" s="1">
+        <v>107807.518679</v>
+      </c>
+      <c r="AK121" s="1">
+        <v>112172.42679</v>
+      </c>
+      <c r="AL121" s="1">
+        <v>110712.26686999999</v>
+      </c>
+      <c r="AM121" s="1">
+        <v>111355.04839200001</v>
+      </c>
+      <c r="AN121" s="1">
+        <v>115517.33253599999</v>
+      </c>
+      <c r="AO121" s="1">
+        <v>113301.148403</v>
+      </c>
+      <c r="AP121" s="1">
+        <v>114975.85828299998</v>
+      </c>
+      <c r="AQ121" s="1">
+        <v>116217.76634099998</v>
+      </c>
+      <c r="AR121" s="1">
+        <v>118938.66359899998</v>
+      </c>
+      <c r="AS121" s="1">
+        <v>119807.181121</v>
+      </c>
+      <c r="AT121" s="1">
+        <v>121082.37949200001</v>
+      </c>
+      <c r="AU121" s="1">
+        <v>119778.41886799999</v>
+      </c>
+      <c r="AV121" s="1">
+        <v>118274.87509999999</v>
+      </c>
+      <c r="AW121" s="1">
+        <v>123174.88595600001</v>
+      </c>
+      <c r="AX121" s="1">
+        <v>122885.27039999999</v>
+      </c>
+      <c r="AY121" s="1">
+        <v>123832.58759799998</v>
+      </c>
+      <c r="AZ121" s="1">
+        <v>124330.89199999999</v>
+      </c>
+      <c r="BA121" s="1">
+        <v>120900.93006499999</v>
+      </c>
+      <c r="BB121" s="1">
+        <v>122543.73404000001</v>
+      </c>
+      <c r="BC121" s="1">
+        <v>121556.85282900001</v>
+      </c>
+      <c r="BD121" s="1">
+        <v>119896.29622600001</v>
+      </c>
+      <c r="BE121" s="1">
+        <v>120501.64427700001</v>
+      </c>
+      <c r="BF121" s="1">
+        <v>122841.510928</v>
+      </c>
+      <c r="BG121" s="1">
+        <v>118262.07046100001</v>
+      </c>
+      <c r="BH121" s="1">
+        <v>118590.68042000002</v>
+      </c>
+      <c r="BI121" s="1">
+        <v>120029.84432199999</v>
+      </c>
+      <c r="BJ121" s="1">
+        <v>118416.11503299999</v>
+      </c>
+      <c r="BK121" s="1">
+        <v>114355.97771899999</v>
+      </c>
+      <c r="BL121" s="1">
+        <v>113295.776115</v>
+      </c>
+      <c r="BM121" s="1">
+        <v>112406.50498199997</v>
+      </c>
+      <c r="BN121" s="1">
+        <v>109760.80439199998</v>
+      </c>
+      <c r="BO121" s="1">
+        <v>111985.722643</v>
+      </c>
+      <c r="BP121" s="1">
+        <v>110144.94806200001</v>
+      </c>
+      <c r="BQ121" s="1">
+        <v>108684.469468</v>
+      </c>
+      <c r="BR121" s="1">
+        <v>108842.308766</v>
+      </c>
+      <c r="BS121" s="1">
+        <v>106098.971676</v>
+      </c>
+      <c r="BT121" s="1">
+        <v>107679.28383600002</v>
+      </c>
+      <c r="BU121" s="1">
+        <v>108746.98419299998</v>
+      </c>
+      <c r="BV121" s="1">
+        <v>108108.65055199999</v>
+      </c>
+      <c r="BW121" s="1">
+        <v>107677.15315400001</v>
+      </c>
+      <c r="BX121" s="1">
+        <v>108629.09941799998</v>
+      </c>
+      <c r="BY121" s="1">
+        <v>108159.477396</v>
+      </c>
+      <c r="BZ121" s="1">
+        <v>107561.67380399999</v>
+      </c>
+      <c r="CA121" s="1">
+        <v>108647.325967</v>
+      </c>
+      <c r="CB121" s="1">
+        <v>109374.51839499998</v>
+      </c>
+      <c r="CC121" s="1">
+        <v>111597.73594300001</v>
+      </c>
+      <c r="CD121" s="1">
+        <v>112799.90611599997</v>
+      </c>
+      <c r="CE121" s="1">
+        <v>114506.42076700002</v>
+      </c>
+      <c r="CF121" s="1">
+        <v>115609.23216699999</v>
+      </c>
+      <c r="CG121" s="1">
+        <v>121564.61326299999</v>
+      </c>
+      <c r="CH121" s="1">
+        <v>124502.79102299998</v>
+      </c>
+      <c r="CI121" s="1">
+        <v>130241.22939000001</v>
+      </c>
+      <c r="CJ121" s="1">
+        <v>135158.87485299999</v>
+      </c>
+      <c r="CK121" s="1">
+        <v>139554.831014</v>
+      </c>
+      <c r="CL121" s="1">
+        <v>145863.28002099998</v>
+      </c>
+      <c r="CM121" s="1">
+        <v>149741.76946800001</v>
+      </c>
+      <c r="CN121" s="1">
+        <v>155148.75574899997</v>
+      </c>
+      <c r="CO121" s="1">
+        <v>162206.32550200002</v>
+      </c>
+      <c r="CP121" s="1">
+        <v>169493.75084299999</v>
+      </c>
+      <c r="CQ121" s="1">
+        <v>172606.542025</v>
+      </c>
+      <c r="CR121" s="1">
+        <v>172269.92544000002</v>
+      </c>
+      <c r="CS121" s="1">
+        <v>179317.37406100001</v>
+      </c>
+      <c r="CT121" s="1">
+        <v>177762.618694</v>
+      </c>
+      <c r="CU121" s="1">
+        <v>177999.60600800003</v>
+      </c>
+      <c r="CV121" s="1">
+        <v>174695.00902300002</v>
+      </c>
+      <c r="CW121" s="1">
+        <v>175504.81138500001</v>
+      </c>
+      <c r="CX121" s="1">
+        <v>179353.89728199999</v>
+      </c>
+      <c r="CY121" s="1">
+        <v>175450.95360900005</v>
+      </c>
+      <c r="CZ121" s="1">
+        <v>175533.81570000001</v>
+      </c>
+      <c r="DA121" s="1">
+        <v>173283.30884899999</v>
+      </c>
+      <c r="DB121" s="1">
+        <v>173179.29312100002</v>
+      </c>
+      <c r="DC121" s="1">
+        <v>172440.77686899999</v>
+      </c>
+      <c r="DD121" s="1">
+        <v>173896.45034700003</v>
+      </c>
+      <c r="DE121" s="1">
+        <v>175954.340314</v>
+      </c>
+      <c r="DF121" s="1">
+        <v>172354.70471099997</v>
+      </c>
+      <c r="DG121" s="1">
+        <v>167914.85365300003</v>
+      </c>
+      <c r="DH121" s="1">
+        <v>162885.57630000002</v>
+      </c>
+      <c r="DI121" s="1">
+        <v>162310.32736200001</v>
+      </c>
+      <c r="DJ121" s="1">
+        <v>160281.91200600003</v>
+      </c>
+      <c r="DK121" s="1">
+        <v>158754.50757300001</v>
+      </c>
+      <c r="DL121" s="1">
+        <v>159513.468322</v>
+      </c>
+      <c r="DM121" s="1">
+        <v>160796.890136</v>
+      </c>
+      <c r="DN121" s="1">
+        <v>161839.87166100001</v>
+      </c>
+      <c r="DO121" s="1">
+        <v>168546.15433799999</v>
+      </c>
+      <c r="DP121" s="1">
+        <v>161663.12574699998</v>
+      </c>
+      <c r="DQ121" s="1">
+        <v>171949.527856</v>
+      </c>
+      <c r="DR121" s="1">
+        <v>171680.15847100003</v>
+      </c>
+      <c r="DS121" s="1">
+        <v>175242.98612800002</v>
+      </c>
+      <c r="DT121" s="1">
+        <v>173756.45211400001</v>
+      </c>
+      <c r="DU121" s="1">
+        <v>177611.878669</v>
+      </c>
+      <c r="DV121" s="1">
+        <v>178549.12228600003</v>
+      </c>
+      <c r="DW121" s="1">
+        <v>179403.45495200003</v>
+      </c>
+      <c r="DX121" s="1">
+        <v>180527.38270400002</v>
+      </c>
+      <c r="DY121" s="1">
+        <v>182156.29664399999</v>
+      </c>
+      <c r="DZ121" s="1">
+        <v>190722.42398099997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2015</v>
       </c>
       <c r="B122" t="s">
         <v>5</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="4">
         <v>81104.713611400774</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="4">
         <v>20618.745536820454</v>
       </c>
-      <c r="E122">
+      <c r="E122" s="4">
         <v>60485.96807458032</v>
       </c>
       <c r="F122">
         <v>4.4999999999999998E-2</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I122" s="3">
+        <v>25681.573973339997</v>
+      </c>
+      <c r="J122" s="1">
+        <v>27042.351269680003</v>
+      </c>
+      <c r="K122" s="1">
+        <v>28065.733887999995</v>
+      </c>
+      <c r="L122" s="1">
+        <v>29264.341014999998</v>
+      </c>
+      <c r="M122" s="1">
+        <v>32878.917699999991</v>
+      </c>
+      <c r="N122" s="1">
+        <v>34663.411336999998</v>
+      </c>
+      <c r="O122" s="1">
+        <v>37177.40969</v>
+      </c>
+      <c r="P122" s="1">
+        <v>38035.21396400001</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>39970.546859000002</v>
+      </c>
+      <c r="R122" s="1">
+        <v>40804.789896000009</v>
+      </c>
+      <c r="S122" s="1">
+        <v>41085.689405999998</v>
+      </c>
+      <c r="T122" s="1">
+        <v>43624.468536</v>
+      </c>
+      <c r="U122" s="1">
+        <v>42559.011853000011</v>
+      </c>
+      <c r="V122" s="1">
+        <v>43146.437588000008</v>
+      </c>
+      <c r="W122" s="1">
+        <v>43652.097158390003</v>
+      </c>
+      <c r="X122" s="1">
+        <v>40277.140068000001</v>
+      </c>
+      <c r="Y122" s="1">
+        <v>41497.490763000002</v>
+      </c>
+      <c r="Z122" s="1">
+        <v>38578.836761999963</v>
+      </c>
+      <c r="AA122" s="1">
+        <v>38331.305578</v>
+      </c>
+      <c r="AB122" s="1">
+        <v>34075.932967000001</v>
+      </c>
+      <c r="AC122" s="1">
+        <v>33178.814491000005</v>
+      </c>
+      <c r="AD122" s="1">
+        <v>31816.9827</v>
+      </c>
+      <c r="AE122" s="1">
+        <v>31143.417265999997</v>
+      </c>
+      <c r="AF122" s="1">
+        <v>30892.543975999997</v>
+      </c>
+      <c r="AG122" s="1">
+        <v>30087.126321</v>
+      </c>
+      <c r="AH122" s="1">
+        <v>29543.848790999993</v>
+      </c>
+      <c r="AI122" s="1">
+        <v>30193.952205000005</v>
+      </c>
+      <c r="AJ122" s="1">
+        <v>28916.706235999998</v>
+      </c>
+      <c r="AK122" s="1">
+        <v>30325.053654000003</v>
+      </c>
+      <c r="AL122" s="1">
+        <v>29730.311683000004</v>
+      </c>
+      <c r="AM122" s="1">
+        <v>29908.714478999998</v>
+      </c>
+      <c r="AN122" s="1">
+        <v>30122.491545000001</v>
+      </c>
+      <c r="AO122" s="1">
+        <v>30707.629485999994</v>
+      </c>
+      <c r="AP122" s="1">
+        <v>31277.826622000004</v>
+      </c>
+      <c r="AQ122" s="1">
+        <v>31443.534651999998</v>
+      </c>
+      <c r="AR122" s="1">
+        <v>32309.224536999998</v>
+      </c>
+      <c r="AS122" s="1">
+        <v>31949.527981999996</v>
+      </c>
+      <c r="AT122" s="1">
+        <v>33133.251284999998</v>
+      </c>
+      <c r="AU122" s="1">
+        <v>33108.165737999996</v>
+      </c>
+      <c r="AV122" s="1">
+        <v>32508.165452000001</v>
+      </c>
+      <c r="AW122" s="1">
+        <v>35956.871963999998</v>
+      </c>
+      <c r="AX122" s="1">
+        <v>34823.922981000003</v>
+      </c>
+      <c r="AY122" s="1">
+        <v>36166.774099999995</v>
+      </c>
+      <c r="AZ122" s="1">
+        <v>36305.866878999994</v>
+      </c>
+      <c r="BA122" s="1">
+        <v>35675.594138</v>
+      </c>
+      <c r="BB122" s="1">
+        <v>35925.061013999999</v>
+      </c>
+      <c r="BC122" s="1">
+        <v>35148.023977000004</v>
+      </c>
+      <c r="BD122" s="1">
+        <v>35294.833906</v>
+      </c>
+      <c r="BE122" s="1">
+        <v>34496.899754000005</v>
+      </c>
+      <c r="BF122" s="1">
+        <v>35565.831188999982</v>
+      </c>
+      <c r="BG122" s="1">
+        <v>35895.134258000006</v>
+      </c>
+      <c r="BH122" s="1">
+        <v>34231.951384</v>
+      </c>
+      <c r="BI122" s="1">
+        <v>35881.747689999997</v>
+      </c>
+      <c r="BJ122" s="1">
+        <v>34531.262443</v>
+      </c>
+      <c r="BK122" s="1">
+        <v>32588.379384</v>
+      </c>
+      <c r="BL122" s="1">
+        <v>29363.061617000003</v>
+      </c>
+      <c r="BM122" s="1">
+        <v>28652.342639999992</v>
+      </c>
+      <c r="BN122" s="1">
+        <v>27160.901342999998</v>
+      </c>
+      <c r="BO122" s="1">
+        <v>25930.569550999997</v>
+      </c>
+      <c r="BP122" s="1">
+        <v>23877.360955</v>
+      </c>
+      <c r="BQ122" s="1">
+        <v>22786.922939000004</v>
+      </c>
+      <c r="BR122" s="1">
+        <v>21622.953148000001</v>
+      </c>
+      <c r="BS122" s="1">
+        <v>20561.676224999999</v>
+      </c>
+      <c r="BT122" s="1">
+        <v>19597.657601000003</v>
+      </c>
+      <c r="BU122" s="1">
+        <v>18656.268263999998</v>
+      </c>
+      <c r="BV122" s="1">
+        <v>18710.223129999998</v>
+      </c>
+      <c r="BW122" s="1">
+        <v>18229.080043999998</v>
+      </c>
+      <c r="BX122" s="1">
+        <v>18054.385029999998</v>
+      </c>
+      <c r="BY122" s="1">
+        <v>18815.057545000003</v>
+      </c>
+      <c r="BZ122" s="1">
+        <v>18923.119481999998</v>
+      </c>
+      <c r="CA122" s="1">
+        <v>19123.641464999997</v>
+      </c>
+      <c r="CB122" s="1">
+        <v>20595.290364</v>
+      </c>
+      <c r="CC122" s="1">
+        <v>22476.881816999998</v>
+      </c>
+      <c r="CD122" s="1">
+        <v>24230.764319000002</v>
+      </c>
+      <c r="CE122" s="1">
+        <v>26871.583562</v>
+      </c>
+      <c r="CF122" s="1">
+        <v>30885.441358</v>
+      </c>
+      <c r="CG122" s="1">
+        <v>35393.225683999997</v>
+      </c>
+      <c r="CH122" s="1">
+        <v>41959.420549000002</v>
+      </c>
+      <c r="CI122" s="1">
+        <v>52296.743537000002</v>
+      </c>
+      <c r="CJ122" s="1">
+        <v>56795.670142000003</v>
+      </c>
+      <c r="CK122" s="1">
+        <v>63340.391706000002</v>
+      </c>
+      <c r="CL122" s="1">
+        <v>73069.941114999994</v>
+      </c>
+      <c r="CM122" s="1">
+        <v>81962.483940000006</v>
+      </c>
+      <c r="CN122" s="1">
+        <v>90485.44526800001</v>
+      </c>
+      <c r="CO122" s="1">
+        <v>100496.64903000002</v>
+      </c>
+      <c r="CP122" s="1">
+        <v>110790.035829</v>
+      </c>
+      <c r="CQ122" s="1">
+        <v>121747.00737100003</v>
+      </c>
+      <c r="CR122" s="1">
+        <v>120619.95186999999</v>
+      </c>
+      <c r="CS122" s="1">
+        <v>127479.139069</v>
+      </c>
+      <c r="CT122" s="1">
+        <v>123845.117434</v>
+      </c>
+      <c r="CU122" s="1">
+        <v>125240.819994</v>
+      </c>
+      <c r="CV122" s="1">
+        <v>123406.250755</v>
+      </c>
+      <c r="CW122" s="1">
+        <v>125245.333701</v>
+      </c>
+      <c r="CX122" s="1">
+        <v>124546.41695899999</v>
+      </c>
+      <c r="CY122" s="1">
+        <v>124197.31178400002</v>
+      </c>
+      <c r="CZ122" s="1">
+        <v>120074.70995499998</v>
+      </c>
+      <c r="DA122" s="1">
+        <v>120903.91542200001</v>
+      </c>
+      <c r="DB122" s="1">
+        <v>119076.785443</v>
+      </c>
+      <c r="DC122" s="1">
+        <v>119354.420824</v>
+      </c>
+      <c r="DD122" s="1">
+        <v>116877.32098</v>
+      </c>
+      <c r="DE122" s="1">
+        <v>121611.212589</v>
+      </c>
+      <c r="DF122" s="1">
+        <v>109123.825512</v>
+      </c>
+      <c r="DG122" s="1">
+        <v>103635.200459</v>
+      </c>
+      <c r="DH122" s="1">
+        <v>99220.239413000003</v>
+      </c>
+      <c r="DI122" s="1">
+        <v>93603.785965000003</v>
+      </c>
+      <c r="DJ122" s="1">
+        <v>89349.247687999989</v>
+      </c>
+      <c r="DK122" s="1">
+        <v>87745.062993</v>
+      </c>
+      <c r="DL122" s="1">
+        <v>88094.420222999994</v>
+      </c>
+      <c r="DM122" s="1">
+        <v>85773.230616000001</v>
+      </c>
+      <c r="DN122" s="1">
+        <v>88432.947396000003</v>
+      </c>
+      <c r="DO122" s="1">
+        <v>89112.169872000013</v>
+      </c>
+      <c r="DP122" s="1">
+        <v>88987.694793000002</v>
+      </c>
+      <c r="DQ122" s="1">
+        <v>93954.423643999995</v>
+      </c>
+      <c r="DR122" s="1">
+        <v>93155.483485999997</v>
+      </c>
+      <c r="DS122" s="1">
+        <v>95300.280877000012</v>
+      </c>
+      <c r="DT122" s="1">
+        <v>93421.575291999994</v>
+      </c>
+      <c r="DU122" s="1">
+        <v>94327.325268999994</v>
+      </c>
+      <c r="DV122" s="1">
+        <v>95393.180770000006</v>
+      </c>
+      <c r="DW122" s="1">
+        <v>96400.383470000015</v>
+      </c>
+      <c r="DX122" s="1">
+        <v>98698.126669000005</v>
+      </c>
+      <c r="DY122" s="1">
+        <v>97830.733132000008</v>
+      </c>
+      <c r="DZ122" s="1">
+        <v>99910.595614999998</v>
+      </c>
+    </row>
+    <row r="123" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2015</v>
       </c>
       <c r="B123" t="s">
         <v>6</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="4">
         <v>79129.257307517881</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="4">
         <v>19717.93212574756</v>
       </c>
-      <c r="E123">
+      <c r="E123" s="4">
         <v>59411.32518177032</v>
       </c>
       <c r="F123">
         <v>4.4999999999999998E-2</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I123" s="3">
+        <v>55478.189488410033</v>
+      </c>
+      <c r="J123" s="1">
+        <v>55671.410426400005</v>
+      </c>
+      <c r="K123" s="2">
+        <v>55882.284630000002</v>
+      </c>
+      <c r="L123" s="2">
+        <v>55856.370895999993</v>
+      </c>
+      <c r="M123" s="2">
+        <v>78043.808165000024</v>
+      </c>
+      <c r="N123" s="2">
+        <v>88707.80217611001</v>
+      </c>
+      <c r="O123" s="2">
+        <v>95915.909538999986</v>
+      </c>
+      <c r="P123" s="2">
+        <v>4959.380344889978</v>
+      </c>
+      <c r="Q123" s="2">
+        <v>64296.341798000001</v>
+      </c>
+      <c r="R123" s="2">
+        <v>63424.699195000016</v>
+      </c>
+      <c r="S123" s="2">
+        <v>62732.936222000011</v>
+      </c>
+      <c r="T123" s="2">
+        <v>56049.567876999994</v>
+      </c>
+      <c r="U123" s="2">
+        <v>70646.479712</v>
+      </c>
+      <c r="V123" s="1">
+        <v>65006.257956999987</v>
+      </c>
+      <c r="W123" s="2">
+        <v>67142.170388109982</v>
+      </c>
+      <c r="X123" s="2">
+        <v>67101.639981000015</v>
+      </c>
+      <c r="Y123" s="2">
+        <v>66706.946453000011</v>
+      </c>
+      <c r="Z123" s="2">
+        <v>77601.300551000037</v>
+      </c>
+      <c r="AA123" s="2">
+        <v>68965.455032000013</v>
+      </c>
+      <c r="AB123" s="2">
+        <v>73581.696297999995</v>
+      </c>
+      <c r="AC123" s="2">
+        <v>74219.442020000017</v>
+      </c>
+      <c r="AD123" s="2">
+        <v>73655.167137000011</v>
+      </c>
+      <c r="AE123" s="2">
+        <v>75662.586491000024</v>
+      </c>
+      <c r="AF123" s="2">
+        <v>76796.576740999997</v>
+      </c>
+      <c r="AG123" s="2">
+        <v>77879.910008000006</v>
+      </c>
+      <c r="AH123" s="1">
+        <v>80186.174383999998</v>
+      </c>
+      <c r="AI123" s="2">
+        <v>78016.220116999975</v>
+      </c>
+      <c r="AJ123" s="2">
+        <v>78890.812443000003</v>
+      </c>
+      <c r="AK123" s="2">
+        <v>81847.373135999995</v>
+      </c>
+      <c r="AL123" s="2">
+        <v>80981.955186999985</v>
+      </c>
+      <c r="AM123" s="2">
+        <v>81446.333913000009</v>
+      </c>
+      <c r="AN123" s="2">
+        <v>85394.84099099999</v>
+      </c>
+      <c r="AO123" s="2">
+        <v>82593.518917000009</v>
+      </c>
+      <c r="AP123" s="2">
+        <v>83698.031660999972</v>
+      </c>
+      <c r="AQ123" s="2">
+        <v>84774.231688999978</v>
+      </c>
+      <c r="AR123" s="2">
+        <v>86629.439061999976</v>
+      </c>
+      <c r="AS123" s="2">
+        <v>87857.653139000002</v>
+      </c>
+      <c r="AT123" s="1">
+        <v>87949.128207000002</v>
+      </c>
+      <c r="AU123" s="2">
+        <v>86670.253129999997</v>
+      </c>
+      <c r="AV123" s="2">
+        <v>85766.709647999989</v>
+      </c>
+      <c r="AW123" s="2">
+        <v>87218.013992000022</v>
+      </c>
+      <c r="AX123" s="2">
+        <v>88061.347418999998</v>
+      </c>
+      <c r="AY123" s="2">
+        <v>87665.813497999989</v>
+      </c>
+      <c r="AZ123" s="2">
+        <v>88025.025120999999</v>
+      </c>
+      <c r="BA123" s="2">
+        <v>85225.335926999993</v>
+      </c>
+      <c r="BB123" s="2">
+        <v>86618.673026000004</v>
+      </c>
+      <c r="BC123" s="2">
+        <v>86408.828852000006</v>
+      </c>
+      <c r="BD123" s="2">
+        <v>84601.462320000006</v>
+      </c>
+      <c r="BE123" s="2">
+        <v>86004.744523000001</v>
+      </c>
+      <c r="BF123" s="1">
+        <v>87275.679739000014</v>
+      </c>
+      <c r="BG123" s="2">
+        <v>82366.936203000005</v>
+      </c>
+      <c r="BH123" s="2">
+        <v>84358.729036000019</v>
+      </c>
+      <c r="BI123" s="2">
+        <v>84148.096632000001</v>
+      </c>
+      <c r="BJ123" s="2">
+        <v>83884.852589999995</v>
+      </c>
+      <c r="BK123" s="2">
+        <v>81767.598334999988</v>
+      </c>
+      <c r="BL123" s="2">
+        <v>83932.714498000001</v>
+      </c>
+      <c r="BM123" s="2">
+        <v>83754.162341999981</v>
+      </c>
+      <c r="BN123" s="2">
+        <v>82599.903048999986</v>
+      </c>
+      <c r="BO123" s="2">
+        <v>86055.153092000008</v>
+      </c>
+      <c r="BP123" s="2">
+        <v>86267.587107000014</v>
+      </c>
+      <c r="BQ123" s="2">
+        <v>85897.546528999985</v>
+      </c>
+      <c r="BR123" s="1">
+        <v>87219.355618000001</v>
+      </c>
+      <c r="BS123" s="2">
+        <v>85537.295450999998</v>
+      </c>
+      <c r="BT123" s="2">
+        <v>88081.626235000018</v>
+      </c>
+      <c r="BU123" s="2">
+        <v>90090.715928999984</v>
+      </c>
+      <c r="BV123" s="2">
+        <v>89398.427421999993</v>
+      </c>
+      <c r="BW123" s="2">
+        <v>89448.073110000012</v>
+      </c>
+      <c r="BX123" s="2">
+        <v>90574.714387999993</v>
+      </c>
+      <c r="BY123" s="2">
+        <v>89344.419850999999</v>
+      </c>
+      <c r="BZ123" s="2">
+        <v>88638.554321999996</v>
+      </c>
+      <c r="CA123" s="2">
+        <v>89523.684502000004</v>
+      </c>
+      <c r="CB123" s="2">
+        <v>88779.228030999977</v>
+      </c>
+      <c r="CC123" s="2">
+        <v>89120.854126000006</v>
+      </c>
+      <c r="CD123" s="1">
+        <v>88569.14179699996</v>
+      </c>
+      <c r="CE123" s="2">
+        <v>87634.837205000018</v>
+      </c>
+      <c r="CF123" s="2">
+        <v>84723.790808999998</v>
+      </c>
+      <c r="CG123" s="2">
+        <v>86171.387579000002</v>
+      </c>
+      <c r="CH123" s="2">
+        <v>82543.370473999981</v>
+      </c>
+      <c r="CI123" s="2">
+        <v>77944.485853000006</v>
+      </c>
+      <c r="CJ123" s="2">
+        <v>78363.204710999984</v>
+      </c>
+      <c r="CK123" s="2">
+        <v>76214.439308000001</v>
+      </c>
+      <c r="CL123" s="2">
+        <v>72793.33890599999</v>
+      </c>
+      <c r="CM123" s="2">
+        <v>67779.285528000008</v>
+      </c>
+      <c r="CN123" s="2">
+        <v>64663.310480999964</v>
+      </c>
+      <c r="CO123" s="2">
+        <v>61709.676472000006</v>
+      </c>
+      <c r="CP123" s="1">
+        <v>58703.715013999987</v>
+      </c>
+      <c r="CQ123" s="2">
+        <v>50859.534653999974</v>
+      </c>
+      <c r="CR123" s="2">
+        <v>51649.973570000031</v>
+      </c>
+      <c r="CS123" s="2">
+        <v>51838.234992000012</v>
+      </c>
+      <c r="CT123" s="2">
+        <v>53917.501260000005</v>
+      </c>
+      <c r="CU123" s="2">
+        <v>52758.786014000027</v>
+      </c>
+      <c r="CV123" s="2">
+        <v>51288.75826800002</v>
+      </c>
+      <c r="CW123" s="2">
+        <v>50259.477684000012</v>
+      </c>
+      <c r="CX123" s="2">
+        <v>54807.480322999996</v>
+      </c>
+      <c r="CY123" s="2">
+        <v>51253.641825000028</v>
+      </c>
+      <c r="CZ123" s="2">
+        <v>55459.105745000023</v>
+      </c>
+      <c r="DA123" s="2">
+        <v>52379.393426999988</v>
+      </c>
+      <c r="DB123" s="1">
+        <v>54102.507678000024</v>
+      </c>
+      <c r="DC123" s="2">
+        <v>53086.356044999993</v>
+      </c>
+      <c r="DD123" s="2">
+        <v>57019.12936700003</v>
+      </c>
+      <c r="DE123" s="2">
+        <v>54343.127724999998</v>
+      </c>
+      <c r="DF123" s="2">
+        <v>63230.879198999974</v>
+      </c>
+      <c r="DG123" s="2">
+        <v>64279.653194000028</v>
+      </c>
+      <c r="DH123" s="2">
+        <v>63665.336887000012</v>
+      </c>
+      <c r="DI123" s="2">
+        <v>68706.541397000008</v>
+      </c>
+      <c r="DJ123" s="2">
+        <v>70932.664318000039</v>
+      </c>
+      <c r="DK123" s="2">
+        <v>71009.44458000001</v>
+      </c>
+      <c r="DL123" s="2">
+        <v>71419.048099000007</v>
+      </c>
+      <c r="DM123" s="2">
+        <v>75023.659520000001</v>
+      </c>
+      <c r="DN123" s="1">
+        <v>73406.924265000009</v>
+      </c>
+      <c r="DO123" s="2">
+        <v>79433.98446599998</v>
+      </c>
+      <c r="DP123" s="2">
+        <v>72675.430953999981</v>
+      </c>
+      <c r="DQ123" s="2">
+        <v>77995.104212000006</v>
+      </c>
+      <c r="DR123" s="2">
+        <v>78524.674985000034</v>
+      </c>
+      <c r="DS123" s="2">
+        <v>79942.705251000007</v>
+      </c>
+      <c r="DT123" s="2">
+        <v>80334.87682200002</v>
+      </c>
+      <c r="DU123" s="2">
+        <v>83284.553400000004</v>
+      </c>
+      <c r="DV123" s="2">
+        <v>83155.941516000021</v>
+      </c>
+      <c r="DW123" s="2">
+        <v>83003.071482000014</v>
+      </c>
+      <c r="DX123" s="2">
+        <v>81829.256035000013</v>
+      </c>
+      <c r="DY123" s="2">
+        <v>84325.563511999979</v>
+      </c>
+      <c r="DZ123" s="1">
+        <v>90811.828365999972</v>
+      </c>
+    </row>
+    <row r="124" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2015</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="4">
         <v>83137.781314644322</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="4">
         <v>21010.605429227719</v>
       </c>
-      <c r="E124">
+      <c r="E124" s="4">
         <v>62127.175885416604</v>
       </c>
       <c r="F124">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2015</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="4">
         <v>85086.874362168484</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="4">
         <v>21015.65532599821</v>
       </c>
-      <c r="E125">
+      <c r="E125" s="4">
         <v>64071.219036170274</v>
       </c>
       <c r="F125">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2015</v>
       </c>
       <c r="B126" t="s">
         <v>9</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="4">
         <v>85512.985221940908</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="4">
         <v>22092.662782568077</v>
       </c>
-      <c r="E126">
+      <c r="E126" s="4">
         <v>63420.322439372831</v>
       </c>
       <c r="F126">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2015</v>
       </c>
       <c r="B127" t="s">
         <v>10</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="4">
         <v>85712.329610397734</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="4">
         <v>21231.279706975824</v>
       </c>
-      <c r="E127">
+      <c r="E127" s="4">
         <v>64481.04990342191</v>
       </c>
       <c r="F127">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:130" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2015</v>
       </c>
       <c r="B128" t="s">
         <v>11</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="4">
         <v>87644.021569282559</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="4">
         <v>21767.603138499264</v>
       </c>
-      <c r="E128">
+      <c r="E128" s="4">
         <v>65876.418430783291</v>
       </c>
       <c r="F128">
@@ -2803,13 +4015,13 @@
       <c r="B129" t="s">
         <v>12</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="4">
         <v>88634.974852048166</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="4">
         <v>22295.395717440166</v>
       </c>
-      <c r="E129">
+      <c r="E129" s="4">
         <v>66339.579134608008</v>
       </c>
       <c r="F129">
@@ -2823,13 +4035,13 @@
       <c r="B130" t="s">
         <v>13</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="4">
         <v>89190.834807761785</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="4">
         <v>22240.169715475982</v>
       </c>
-      <c r="E130">
+      <c r="E130" s="4">
         <v>66950.66509228581</v>
       </c>
       <c r="F130">
@@ -2843,13 +4055,13 @@
       <c r="B131" t="s">
         <v>14</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="4">
         <v>93530.233742057608</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="4">
         <v>23002.923832440949</v>
       </c>
-      <c r="E131">
+      <c r="E131" s="4">
         <v>70527.309909616655</v>
       </c>
       <c r="F131">
@@ -2863,14 +4075,14 @@
       <c r="B132" t="s">
         <v>15</v>
       </c>
-      <c r="C132">
-        <v>91582.97620584078</v>
-      </c>
-      <c r="D132">
-        <v>22149.374558965672</v>
-      </c>
-      <c r="E132">
-        <v>69433.601646875104</v>
+      <c r="C132" s="5">
+        <v>81159.76346175003</v>
+      </c>
+      <c r="D132" s="5">
+        <v>25681.573973339997</v>
+      </c>
+      <c r="E132" s="5">
+        <v>55478.189488410033</v>
       </c>
       <c r="F132">
         <v>5.5E-2</v>
@@ -2883,14 +4095,14 @@
       <c r="B133" t="s">
         <v>16</v>
       </c>
-      <c r="C133">
-        <v>92675.767449560211</v>
-      </c>
-      <c r="D133">
-        <v>21865.334606038112</v>
-      </c>
-      <c r="E133">
-        <v>70810.432843522096</v>
+      <c r="C133" s="6">
+        <v>82713.761696080008</v>
+      </c>
+      <c r="D133" s="6">
+        <v>27042.351269680003</v>
+      </c>
+      <c r="E133" s="6">
+        <v>55671.410426400005</v>
       </c>
       <c r="F133">
         <v>5.7500000000000002E-2</v>
@@ -2903,14 +4115,14 @@
       <c r="B134" t="s">
         <v>5</v>
       </c>
-      <c r="C134">
-        <v>94002.141922815194</v>
-      </c>
-      <c r="D134">
-        <v>28644.23264091563</v>
-      </c>
-      <c r="E134">
-        <v>65357.909281899563</v>
+      <c r="C134" s="6">
+        <v>83948.018517999997</v>
+      </c>
+      <c r="D134" s="6">
+        <v>28065.733887999995</v>
+      </c>
+      <c r="E134" s="7">
+        <v>55882.284630000002</v>
       </c>
       <c r="F134">
         <v>5.7500000000000002E-2</v>
@@ -2923,14 +4135,14 @@
       <c r="B135" t="s">
         <v>6</v>
       </c>
-      <c r="C135">
-        <v>105113.82329688196</v>
-      </c>
-      <c r="D135">
-        <v>28815.34341252529</v>
-      </c>
-      <c r="E135">
-        <v>76298.479884356668</v>
+      <c r="C135" s="6">
+        <v>85120.711910999991</v>
+      </c>
+      <c r="D135" s="6">
+        <v>29264.341014999998</v>
+      </c>
+      <c r="E135" s="7">
+        <v>55856.370895999993</v>
       </c>
       <c r="F135">
         <v>6.25E-2</v>
@@ -2943,14 +4155,14 @@
       <c r="B136" t="s">
         <v>7</v>
       </c>
-      <c r="C136">
-        <v>99048.733206051271</v>
-      </c>
-      <c r="D136">
-        <v>30496.199655977267</v>
-      </c>
-      <c r="E136">
-        <v>68552.533550074004</v>
+      <c r="C136" s="6">
+        <v>110922.72586500001</v>
+      </c>
+      <c r="D136" s="6">
+        <v>32878.917699999991</v>
+      </c>
+      <c r="E136" s="7">
+        <v>78043.808165000024</v>
       </c>
       <c r="F136">
         <v>6.5000000000000002E-2</v>
@@ -2963,14 +4175,14 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137">
-        <v>100308.00900040563</v>
-      </c>
-      <c r="D137">
-        <v>31408.219383916057</v>
-      </c>
-      <c r="E137">
-        <v>68899.789616489565</v>
+      <c r="C137" s="6">
+        <v>123371.21351311001</v>
+      </c>
+      <c r="D137" s="6">
+        <v>34663.411336999998</v>
+      </c>
+      <c r="E137" s="7">
+        <v>88707.80217611001</v>
       </c>
       <c r="F137">
         <v>6.5000000000000002E-2</v>
@@ -2983,14 +4195,14 @@
       <c r="B138" t="s">
         <v>9</v>
       </c>
-      <c r="C138">
-        <v>102346.79246108439</v>
-      </c>
-      <c r="D138">
-        <v>32895.200654814791</v>
-      </c>
-      <c r="E138">
-        <v>69451.5918062696</v>
+      <c r="C138" s="6">
+        <v>133093.31922899999</v>
+      </c>
+      <c r="D138" s="6">
+        <v>37177.40969</v>
+      </c>
+      <c r="E138" s="7">
+        <v>95915.909538999986</v>
       </c>
       <c r="F138">
         <v>7.2499999999999995E-2</v>
@@ -3003,14 +4215,14 @@
       <c r="B139" t="s">
         <v>10</v>
       </c>
-      <c r="C139">
-        <v>109585.26537884009</v>
-      </c>
-      <c r="D139">
-        <v>32809.248716217415</v>
-      </c>
-      <c r="E139">
-        <v>76776.016662622686</v>
+      <c r="C139" s="6">
+        <v>42994.594308889988</v>
+      </c>
+      <c r="D139" s="6">
+        <v>38035.21396400001</v>
+      </c>
+      <c r="E139" s="7">
+        <v>4959.380344889978</v>
       </c>
       <c r="F139">
         <v>7.4999999999999997E-2</v>
@@ -3023,14 +4235,14 @@
       <c r="B140" t="s">
         <v>11</v>
       </c>
-      <c r="C140">
-        <v>104784.66335598506</v>
-      </c>
-      <c r="D140">
-        <v>34334.164447190531</v>
-      </c>
-      <c r="E140">
-        <v>70450.498908794529</v>
+      <c r="C140" s="6">
+        <v>104266.888657</v>
+      </c>
+      <c r="D140" s="6">
+        <v>39970.546859000002</v>
+      </c>
+      <c r="E140" s="7">
+        <v>64296.341798000001</v>
       </c>
       <c r="F140">
         <v>7.4999999999999997E-2</v>
@@ -3043,14 +4255,14 @@
       <c r="B141" t="s">
         <v>12</v>
       </c>
-      <c r="C141">
-        <v>105669.02344344066</v>
-      </c>
-      <c r="D141">
-        <v>35114.08246865384</v>
-      </c>
-      <c r="E141">
-        <v>70554.940974786819</v>
+      <c r="C141" s="6">
+        <v>104229.48909100002</v>
+      </c>
+      <c r="D141" s="6">
+        <v>40804.789896000009</v>
+      </c>
+      <c r="E141" s="7">
+        <v>63424.699195000016</v>
       </c>
       <c r="F141">
         <v>7.7499999999999999E-2</v>
@@ -3063,14 +4275,14 @@
       <c r="B142" t="s">
         <v>13</v>
       </c>
-      <c r="C142">
-        <v>106979.28137642935</v>
-      </c>
-      <c r="D142">
-        <v>34824.354469781094</v>
-      </c>
-      <c r="E142">
-        <v>72154.926906648267</v>
+      <c r="C142" s="6">
+        <v>103818.62562800001</v>
+      </c>
+      <c r="D142" s="6">
+        <v>41085.689405999998</v>
+      </c>
+      <c r="E142" s="7">
+        <v>62732.936222000011</v>
       </c>
       <c r="F142">
         <v>7.7499999999999999E-2</v>
@@ -3083,14 +4295,14 @@
       <c r="B143" t="s">
         <v>14</v>
       </c>
-      <c r="C143">
-        <v>109727.74996320512</v>
-      </c>
-      <c r="D143">
-        <v>35926.321646070472</v>
-      </c>
-      <c r="E143">
-        <v>73801.428317134647</v>
+      <c r="C143" s="6">
+        <v>99674.036412999994</v>
+      </c>
+      <c r="D143" s="6">
+        <v>43624.468536</v>
+      </c>
+      <c r="E143" s="7">
+        <v>56049.567876999994</v>
       </c>
       <c r="F143">
         <v>7.7499999999999999E-2</v>
@@ -3103,14 +4315,14 @@
       <c r="B144" t="s">
         <v>15</v>
       </c>
-      <c r="C144">
-        <v>109428.79851727575</v>
-      </c>
-      <c r="D144">
-        <v>35069.596572112227</v>
-      </c>
-      <c r="E144">
-        <v>74359.201945163513</v>
+      <c r="C144" s="6">
+        <v>113205.491565</v>
+      </c>
+      <c r="D144" s="6">
+        <v>42559.011853000011</v>
+      </c>
+      <c r="E144" s="7">
+        <v>70646.479712</v>
       </c>
       <c r="F144">
         <v>7.7499999999999999E-2</v>
@@ -3123,14 +4335,14 @@
       <c r="B145" t="s">
         <v>16</v>
       </c>
-      <c r="C145">
-        <v>110919.09727981225</v>
-      </c>
-      <c r="D145">
-        <v>34728.623868740986</v>
-      </c>
-      <c r="E145">
-        <v>76190.47341107126</v>
+      <c r="C145" s="6">
+        <v>108152.695545</v>
+      </c>
+      <c r="D145" s="6">
+        <v>43146.437588000008</v>
+      </c>
+      <c r="E145" s="6">
+        <v>65006.257956999987</v>
       </c>
       <c r="F145">
         <v>7.4999999999999997E-2</v>
@@ -3143,14 +4355,14 @@
       <c r="B146" t="s">
         <v>5</v>
       </c>
-      <c r="C146">
-        <v>110046.25041353916</v>
-      </c>
-      <c r="D146">
-        <v>39097.508877360706</v>
-      </c>
-      <c r="E146">
-        <v>70948.741536178451</v>
+      <c r="C146" s="6">
+        <v>110794.26754649998</v>
+      </c>
+      <c r="D146" s="6">
+        <v>43652.097158390003</v>
+      </c>
+      <c r="E146" s="7">
+        <v>67142.170388109982</v>
       </c>
       <c r="F146">
         <v>7.4999999999999997E-2</v>
@@ -3163,14 +4375,14 @@
       <c r="B147" t="s">
         <v>6</v>
       </c>
-      <c r="C147">
-        <v>110451.60967493658</v>
-      </c>
-      <c r="D147">
-        <v>37287.565966936141</v>
-      </c>
-      <c r="E147">
-        <v>73164.043708000449</v>
+      <c r="C147" s="6">
+        <v>107378.78004900001</v>
+      </c>
+      <c r="D147" s="6">
+        <v>40277.140068000001</v>
+      </c>
+      <c r="E147" s="7">
+        <v>67101.639981000015</v>
       </c>
       <c r="F147">
         <v>7.2499999999999995E-2</v>
@@ -3183,14 +4395,14 @@
       <c r="B148" t="s">
         <v>7</v>
       </c>
-      <c r="C148">
-        <v>116046.67053989266</v>
-      </c>
-      <c r="D148">
-        <v>39334.541249228445</v>
-      </c>
-      <c r="E148">
-        <v>76712.129290664219</v>
+      <c r="C148" s="6">
+        <v>108204.43721600001</v>
+      </c>
+      <c r="D148" s="6">
+        <v>41497.490763000002</v>
+      </c>
+      <c r="E148" s="7">
+        <v>66706.946453000011</v>
       </c>
       <c r="F148">
         <v>7.0000000000000007E-2</v>
@@ -3203,14 +4415,14 @@
       <c r="B149" t="s">
         <v>8</v>
       </c>
-      <c r="C149">
-        <v>116278.28494302968</v>
-      </c>
-      <c r="D149">
-        <v>39564.763228065116</v>
-      </c>
-      <c r="E149">
-        <v>76713.521714964561</v>
+      <c r="C149" s="6">
+        <v>116180.137313</v>
+      </c>
+      <c r="D149" s="6">
+        <v>38578.836761999963</v>
+      </c>
+      <c r="E149" s="7">
+        <v>77601.300551000037</v>
       </c>
       <c r="F149">
         <v>7.0000000000000007E-2</v>
@@ -3223,14 +4435,14 @@
       <c r="B150" t="s">
         <v>9</v>
       </c>
-      <c r="C150">
-        <v>118270.08682325455</v>
-      </c>
-      <c r="D150">
-        <v>40153.993006036399</v>
-      </c>
-      <c r="E150">
-        <v>78116.093817218149</v>
+      <c r="C150" s="6">
+        <v>107296.76061000001</v>
+      </c>
+      <c r="D150" s="6">
+        <v>38331.305578</v>
+      </c>
+      <c r="E150" s="7">
+        <v>68965.455032000013</v>
       </c>
       <c r="F150">
         <v>6.25E-2</v>
@@ -3243,14 +4455,14 @@
       <c r="B151" t="s">
         <v>10</v>
       </c>
-      <c r="C151">
-        <v>117211.40887783363</v>
-      </c>
-      <c r="D151">
-        <v>38978.386601890292</v>
-      </c>
-      <c r="E151">
-        <v>78233.022275943338</v>
+      <c r="C151" s="6">
+        <v>107657.629265</v>
+      </c>
+      <c r="D151" s="6">
+        <v>34075.932967000001</v>
+      </c>
+      <c r="E151" s="7">
+        <v>73581.696297999995</v>
       </c>
       <c r="F151">
         <v>6.25E-2</v>
@@ -3263,14 +4475,14 @@
       <c r="B152" t="s">
         <v>11</v>
       </c>
-      <c r="C152">
-        <v>118196.96254894293</v>
-      </c>
-      <c r="D152">
-        <v>40086.638212155849</v>
-      </c>
-      <c r="E152">
-        <v>78110.324336787075</v>
+      <c r="C152" s="6">
+        <v>107398.25651100003</v>
+      </c>
+      <c r="D152" s="6">
+        <v>33178.814491000005</v>
+      </c>
+      <c r="E152" s="7">
+        <v>74219.442020000017</v>
       </c>
       <c r="F152">
         <v>5.5E-2</v>
@@ -3283,14 +4495,14 @@
       <c r="B153" t="s">
         <v>12</v>
       </c>
-      <c r="C153">
-        <v>120037.29332810911</v>
-      </c>
-      <c r="D153">
-        <v>41028.805196588721</v>
-      </c>
-      <c r="E153">
-        <v>79008.488131520397</v>
+      <c r="C153" s="6">
+        <v>105472.14983700002</v>
+      </c>
+      <c r="D153" s="6">
+        <v>31816.9827</v>
+      </c>
+      <c r="E153" s="7">
+        <v>73655.167137000011</v>
       </c>
       <c r="F153">
         <v>5.5E-2</v>
@@ -3303,14 +4515,14 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
-      <c r="C154">
-        <v>120845.25650947778</v>
-      </c>
-      <c r="D154">
-        <v>40784.662729151431</v>
-      </c>
-      <c r="E154">
-        <v>80060.593780326351</v>
+      <c r="C154" s="6">
+        <v>106806.00375700003</v>
+      </c>
+      <c r="D154" s="6">
+        <v>31143.417265999997</v>
+      </c>
+      <c r="E154" s="7">
+        <v>75662.586491000024</v>
       </c>
       <c r="F154">
         <v>5.2499999999999998E-2</v>
@@ -3323,14 +4535,14 @@
       <c r="B155" t="s">
         <v>14</v>
       </c>
-      <c r="C155">
-        <v>123472.37037692472</v>
-      </c>
-      <c r="D155">
-        <v>41023.492091425251</v>
-      </c>
-      <c r="E155">
-        <v>82448.878285499464</v>
+      <c r="C155" s="6">
+        <v>107689.120717</v>
+      </c>
+      <c r="D155" s="6">
+        <v>30892.543975999997</v>
+      </c>
+      <c r="E155" s="7">
+        <v>76796.576740999997</v>
       </c>
       <c r="F155">
         <v>0.05</v>
@@ -3343,14 +4555,14 @@
       <c r="B156" t="s">
         <v>15</v>
       </c>
-      <c r="C156">
-        <v>123229.85774917391</v>
-      </c>
-      <c r="D156">
-        <v>40017.900865222771</v>
-      </c>
-      <c r="E156">
-        <v>83211.956883951148</v>
+      <c r="C156" s="6">
+        <v>107967.03632900001</v>
+      </c>
+      <c r="D156" s="6">
+        <v>30087.126321</v>
+      </c>
+      <c r="E156" s="7">
+        <v>77879.910008000006</v>
       </c>
       <c r="F156">
         <v>4.7500000000000001E-2</v>
@@ -3363,14 +4575,14 @@
       <c r="B157" t="s">
         <v>16</v>
       </c>
-      <c r="C157">
-        <v>124781.59192890166</v>
-      </c>
-      <c r="D157">
-        <v>40390.618655462909</v>
-      </c>
-      <c r="E157">
-        <v>84390.973273438751</v>
+      <c r="C157" s="6">
+        <v>109730.02317499999</v>
+      </c>
+      <c r="D157" s="6">
+        <v>29543.848790999993</v>
+      </c>
+      <c r="E157" s="6">
+        <v>80186.174383999998</v>
       </c>
       <c r="F157">
         <v>4.7500000000000001E-2</v>
@@ -3383,14 +4595,14 @@
       <c r="B158" t="s">
         <v>5</v>
       </c>
-      <c r="C158">
-        <v>111766.75973875808</v>
-      </c>
-      <c r="D158">
-        <v>31099.12043573389</v>
-      </c>
-      <c r="E158">
-        <v>80667.639303024189</v>
+      <c r="C158" s="6">
+        <v>108210.17232199998</v>
+      </c>
+      <c r="D158" s="6">
+        <v>30193.952205000005</v>
+      </c>
+      <c r="E158" s="7">
+        <v>78016.220116999975</v>
       </c>
       <c r="F158">
         <v>4.4999999999999998E-2</v>
@@ -3403,14 +4615,14 @@
       <c r="B159" t="s">
         <v>6</v>
       </c>
-      <c r="C159">
-        <v>111455.1811916062</v>
-      </c>
-      <c r="D159">
-        <v>29815.955438960074</v>
-      </c>
-      <c r="E159">
-        <v>81639.225752646133</v>
+      <c r="C159" s="6">
+        <v>107807.518679</v>
+      </c>
+      <c r="D159" s="6">
+        <v>28916.706235999998</v>
+      </c>
+      <c r="E159" s="7">
+        <v>78890.812443000003</v>
       </c>
       <c r="F159">
         <v>4.4999999999999998E-2</v>
@@ -3423,14 +4635,14 @@
       <c r="B160" t="s">
         <v>7</v>
       </c>
-      <c r="C160">
-        <v>114055.37609214673</v>
-      </c>
-      <c r="D160">
-        <v>30681.523538953217</v>
-      </c>
-      <c r="E160">
-        <v>83373.852553193516</v>
+      <c r="C160" s="6">
+        <v>112172.42679</v>
+      </c>
+      <c r="D160" s="6">
+        <v>30325.053654000003</v>
+      </c>
+      <c r="E160" s="7">
+        <v>81847.373135999995</v>
       </c>
       <c r="F160">
         <v>4.4999999999999998E-2</v>
@@ -3443,14 +4655,14 @@
       <c r="B161" t="s">
         <v>8</v>
       </c>
-      <c r="C161">
-        <v>115746.66478627927</v>
-      </c>
-      <c r="D161">
-        <v>30193.939376571991</v>
-      </c>
-      <c r="E161">
-        <v>85552.725409707287</v>
+      <c r="C161" s="6">
+        <v>110712.26686999999</v>
+      </c>
+      <c r="D161" s="6">
+        <v>29730.311683000004</v>
+      </c>
+      <c r="E161" s="7">
+        <v>80981.955186999985</v>
       </c>
       <c r="F161">
         <v>4.2500000000000003E-2</v>
@@ -3463,14 +4675,14 @@
       <c r="B162" t="s">
         <v>9</v>
       </c>
-      <c r="C162">
-        <v>115144.86392548197</v>
-      </c>
-      <c r="D162">
-        <v>30133.595839636491</v>
-      </c>
-      <c r="E162">
-        <v>85011.268085845484</v>
+      <c r="C162" s="6">
+        <v>111355.04839200001</v>
+      </c>
+      <c r="D162" s="6">
+        <v>29908.714478999998</v>
+      </c>
+      <c r="E162" s="7">
+        <v>81446.333913000009</v>
       </c>
       <c r="F162">
         <v>4.2500000000000003E-2</v>
@@ -3483,14 +4695,14 @@
       <c r="B163" t="s">
         <v>10</v>
       </c>
-      <c r="C163">
-        <v>115913.91510009723</v>
-      </c>
-      <c r="D163">
-        <v>29987.522561350521</v>
-      </c>
-      <c r="E163">
-        <v>85926.392538746717</v>
+      <c r="C163" s="6">
+        <v>115517.33253599999</v>
+      </c>
+      <c r="D163" s="6">
+        <v>30122.491545000001</v>
+      </c>
+      <c r="E163" s="7">
+        <v>85394.84099099999</v>
       </c>
       <c r="F163">
         <v>4.2500000000000003E-2</v>
@@ -3503,14 +4715,14 @@
       <c r="B164" t="s">
         <v>11</v>
       </c>
-      <c r="C164">
-        <v>117374.50767059723</v>
-      </c>
-      <c r="D164">
-        <v>30705.965509925551</v>
-      </c>
-      <c r="E164">
-        <v>86668.542160671685</v>
+      <c r="C164" s="6">
+        <v>113301.148403</v>
+      </c>
+      <c r="D164" s="6">
+        <v>30707.629485999994</v>
+      </c>
+      <c r="E164" s="7">
+        <v>82593.518917000009</v>
       </c>
       <c r="F164">
         <v>4.2500000000000003E-2</v>
@@ -3523,14 +4735,14 @@
       <c r="B165" t="s">
         <v>12</v>
       </c>
-      <c r="C165">
-        <v>119147.34203527408</v>
-      </c>
-      <c r="D165">
-        <v>31149.458726957899</v>
-      </c>
-      <c r="E165">
-        <v>87997.883308316173</v>
+      <c r="C165" s="6">
+        <v>114975.85828299998</v>
+      </c>
+      <c r="D165" s="6">
+        <v>31277.826622000004</v>
+      </c>
+      <c r="E165" s="7">
+        <v>83698.031660999972</v>
       </c>
       <c r="F165">
         <v>4.2500000000000003E-2</v>
@@ -3543,14 +4755,14 @@
       <c r="B166" t="s">
         <v>13</v>
       </c>
-      <c r="C166">
-        <v>120192.36494956026</v>
-      </c>
-      <c r="D166">
-        <v>31153.507224654746</v>
-      </c>
-      <c r="E166">
-        <v>89038.857724905509</v>
+      <c r="C166" s="6">
+        <v>116217.76634099998</v>
+      </c>
+      <c r="D166" s="6">
+        <v>31443.534651999998</v>
+      </c>
+      <c r="E166" s="7">
+        <v>84774.231688999978</v>
       </c>
       <c r="F166">
         <v>4.2500000000000003E-2</v>
@@ -3563,14 +4775,14 @@
       <c r="B167" t="s">
         <v>14</v>
       </c>
-      <c r="C167">
-        <v>122677.65001584658</v>
-      </c>
-      <c r="D167">
-        <v>31995.930667376728</v>
-      </c>
-      <c r="E167">
-        <v>90681.719348469851</v>
+      <c r="C167" s="6">
+        <v>118938.66359899998</v>
+      </c>
+      <c r="D167" s="6">
+        <v>32309.224536999998</v>
+      </c>
+      <c r="E167" s="7">
+        <v>86629.439061999976</v>
       </c>
       <c r="F167">
         <v>4.2500000000000003E-2</v>
@@ -3583,14 +4795,14 @@
       <c r="B168" t="s">
         <v>15</v>
       </c>
-      <c r="C168">
-        <v>123233.65715497665</v>
-      </c>
-      <c r="D168">
-        <v>31707.011400087806</v>
-      </c>
-      <c r="E168">
-        <v>91526.645754888843</v>
+      <c r="C168" s="6">
+        <v>119807.181121</v>
+      </c>
+      <c r="D168" s="6">
+        <v>31949.527981999996</v>
+      </c>
+      <c r="E168" s="7">
+        <v>87857.653139000002</v>
       </c>
       <c r="F168">
         <v>4.2500000000000003E-2</v>
@@ -3603,14 +4815,14 @@
       <c r="B169" t="s">
         <v>16</v>
       </c>
-      <c r="C169">
-        <v>124854.34105056558</v>
-      </c>
-      <c r="D169">
-        <v>32181.985177124989</v>
-      </c>
-      <c r="E169">
-        <v>92672.355873440596</v>
+      <c r="C169" s="6">
+        <v>121082.37949200001</v>
+      </c>
+      <c r="D169" s="6">
+        <v>33133.251284999998</v>
+      </c>
+      <c r="E169" s="6">
+        <v>87949.128207000002</v>
       </c>
       <c r="F169">
         <v>4.2500000000000003E-2</v>
@@ -3623,14 +4835,14 @@
       <c r="B170" t="s">
         <v>5</v>
       </c>
-      <c r="C170">
-        <v>121465.31637029511</v>
-      </c>
-      <c r="D170">
-        <v>34189.212514180857</v>
-      </c>
-      <c r="E170">
-        <v>87276.103856114263</v>
+      <c r="C170" s="6">
+        <v>119778.41886799999</v>
+      </c>
+      <c r="D170" s="6">
+        <v>33108.165737999996</v>
+      </c>
+      <c r="E170" s="7">
+        <v>86670.253129999997</v>
       </c>
       <c r="F170">
         <v>4.2500000000000003E-2</v>
@@ -3643,14 +4855,14 @@
       <c r="B171" t="s">
         <v>6</v>
       </c>
-      <c r="C171">
-        <v>121648.62054242735</v>
-      </c>
-      <c r="D171">
-        <v>33271.826532896201</v>
-      </c>
-      <c r="E171">
-        <v>88376.79400953115</v>
+      <c r="C171" s="6">
+        <v>118274.87509999999</v>
+      </c>
+      <c r="D171" s="6">
+        <v>32508.165452000001</v>
+      </c>
+      <c r="E171" s="7">
+        <v>85766.709647999989</v>
       </c>
       <c r="F171">
         <v>4.2500000000000003E-2</v>
@@ -3663,14 +4875,14 @@
       <c r="B172" t="s">
         <v>7</v>
       </c>
-      <c r="C172">
-        <v>126746.69000807041</v>
-      </c>
-      <c r="D172">
-        <v>34701.616928750067</v>
-      </c>
-      <c r="E172">
-        <v>92045.07307932034</v>
+      <c r="C172" s="6">
+        <v>123174.88595600001</v>
+      </c>
+      <c r="D172" s="6">
+        <v>35956.871963999998</v>
+      </c>
+      <c r="E172" s="7">
+        <v>87218.013992000022</v>
       </c>
       <c r="F172">
         <v>4.2500000000000003E-2</v>
@@ -3683,14 +4895,14 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173">
-        <v>123751.86369757801</v>
-      </c>
-      <c r="D173">
-        <v>34569.405728632933</v>
-      </c>
-      <c r="E173">
-        <v>89182.457968945077</v>
+      <c r="C173" s="6">
+        <v>122885.27039999999</v>
+      </c>
+      <c r="D173" s="6">
+        <v>34823.922981000003</v>
+      </c>
+      <c r="E173" s="7">
+        <v>88061.347418999998</v>
       </c>
       <c r="F173">
         <v>4.2500000000000003E-2</v>
@@ -3703,14 +4915,14 @@
       <c r="B174" t="s">
         <v>9</v>
       </c>
-      <c r="C174">
-        <v>125891.86988606205</v>
-      </c>
-      <c r="D174">
-        <v>35422.80860154151</v>
-      </c>
-      <c r="E174">
-        <v>90469.061284520547</v>
+      <c r="C174" s="6">
+        <v>123832.58759799998</v>
+      </c>
+      <c r="D174" s="6">
+        <v>36166.774099999995</v>
+      </c>
+      <c r="E174" s="7">
+        <v>87665.813497999989</v>
       </c>
       <c r="F174">
         <v>4.2500000000000003E-2</v>
@@ -3723,14 +4935,14 @@
       <c r="B175" t="s">
         <v>10</v>
       </c>
-      <c r="C175">
-        <v>127389.52684381041</v>
-      </c>
-      <c r="D175">
-        <v>35668.385815423462</v>
-      </c>
-      <c r="E175">
-        <v>91721.141028386948</v>
+      <c r="C175" s="6">
+        <v>124330.89199999999</v>
+      </c>
+      <c r="D175" s="6">
+        <v>36305.866878999994</v>
+      </c>
+      <c r="E175" s="7">
+        <v>88025.025120999999</v>
       </c>
       <c r="F175">
         <v>4.2500000000000003E-2</v>
@@ -3743,14 +4955,14 @@
       <c r="B176" t="s">
         <v>11</v>
       </c>
-      <c r="C176">
-        <v>128289.67096645222</v>
-      </c>
-      <c r="D176">
-        <v>36782.187010754235</v>
-      </c>
-      <c r="E176">
-        <v>91507.483955697986</v>
+      <c r="C176" s="6">
+        <v>120900.93006499999</v>
+      </c>
+      <c r="D176" s="6">
+        <v>35675.594138</v>
+      </c>
+      <c r="E176" s="7">
+        <v>85225.335926999993</v>
       </c>
       <c r="F176">
         <v>4.2500000000000003E-2</v>
@@ -3763,14 +4975,14 @@
       <c r="B177" t="s">
         <v>12</v>
       </c>
-      <c r="C177">
-        <v>130315.2769492926</v>
-      </c>
-      <c r="D177">
-        <v>37748.901291330883</v>
-      </c>
-      <c r="E177">
-        <v>92566.375657961718</v>
+      <c r="C177" s="6">
+        <v>122543.73404000001</v>
+      </c>
+      <c r="D177" s="6">
+        <v>35925.061013999999</v>
+      </c>
+      <c r="E177" s="7">
+        <v>86618.673026000004</v>
       </c>
       <c r="F177">
         <v>4.2500000000000003E-2</v>
@@ -3783,14 +4995,14 @@
       <c r="B178" t="s">
         <v>13</v>
       </c>
-      <c r="C178">
-        <v>131617.87462823477</v>
-      </c>
-      <c r="D178">
-        <v>38297.230263750906</v>
-      </c>
-      <c r="E178">
-        <v>93320.644364483858</v>
+      <c r="C178" s="6">
+        <v>121556.85282900001</v>
+      </c>
+      <c r="D178" s="6">
+        <v>35148.023977000004</v>
+      </c>
+      <c r="E178" s="7">
+        <v>86408.828852000006</v>
       </c>
       <c r="F178">
         <v>4.2500000000000003E-2</v>
@@ -3803,14 +5015,14 @@
       <c r="B179" t="s">
         <v>14</v>
       </c>
-      <c r="C179">
-        <v>133381.38044527266</v>
-      </c>
-      <c r="D179">
-        <v>39721.803196250825</v>
-      </c>
-      <c r="E179">
-        <v>93659.577249021837</v>
+      <c r="C179" s="6">
+        <v>119896.29622600001</v>
+      </c>
+      <c r="D179" s="6">
+        <v>35294.833906</v>
+      </c>
+      <c r="E179" s="7">
+        <v>84601.462320000006</v>
       </c>
       <c r="F179">
         <v>4.2500000000000003E-2</v>
@@ -3823,14 +5035,14 @@
       <c r="B180" t="s">
         <v>15</v>
       </c>
-      <c r="C180">
-        <v>135099.31163825435</v>
-      </c>
-      <c r="D180">
-        <v>39562.784579625382</v>
-      </c>
-      <c r="E180">
-        <v>95536.52705862897</v>
+      <c r="C180" s="6">
+        <v>120501.64427700001</v>
+      </c>
+      <c r="D180" s="6">
+        <v>34496.899754000005</v>
+      </c>
+      <c r="E180" s="7">
+        <v>86004.744523000001</v>
       </c>
       <c r="F180">
         <v>4.2500000000000003E-2</v>
@@ -3843,14 +5055,14 @@
       <c r="B181" t="s">
         <v>16</v>
       </c>
-      <c r="C181">
-        <v>135786.94734105302</v>
-      </c>
-      <c r="D181">
-        <v>40069.157911077462</v>
-      </c>
-      <c r="E181">
-        <v>95717.789429975557</v>
+      <c r="C181" s="6">
+        <v>122841.510928</v>
+      </c>
+      <c r="D181" s="6">
+        <v>35565.831188999982</v>
+      </c>
+      <c r="E181" s="6">
+        <v>87275.679739000014</v>
       </c>
       <c r="F181">
         <v>4.2500000000000003E-2</v>
@@ -3863,14 +5075,14 @@
       <c r="B182" t="s">
         <v>5</v>
       </c>
-      <c r="C182">
-        <v>124923.91745179573</v>
-      </c>
-      <c r="D182">
-        <v>36076.822863523164</v>
-      </c>
-      <c r="E182">
-        <v>88847.094588272565</v>
+      <c r="C182" s="6">
+        <v>118262.07046100001</v>
+      </c>
+      <c r="D182" s="6">
+        <v>35895.134258000006</v>
+      </c>
+      <c r="E182" s="7">
+        <v>82366.936203000005</v>
       </c>
       <c r="F182">
         <v>4.2500000000000003E-2</v>
@@ -3883,14 +5095,14 @@
       <c r="B183" t="s">
         <v>6</v>
       </c>
-      <c r="C183">
-        <v>124827.16979065583</v>
-      </c>
-      <c r="D183">
-        <v>35616.565777897238</v>
-      </c>
-      <c r="E183">
-        <v>89210.604012758587</v>
+      <c r="C183" s="6">
+        <v>118590.68042000002</v>
+      </c>
+      <c r="D183" s="6">
+        <v>34231.951384</v>
+      </c>
+      <c r="E183" s="7">
+        <v>84358.729036000019</v>
       </c>
       <c r="F183">
         <v>4.2500000000000003E-2</v>
@@ -3903,14 +5115,14 @@
       <c r="B184" t="s">
         <v>7</v>
       </c>
-      <c r="C184">
-        <v>131211.29938636711</v>
-      </c>
-      <c r="D184">
-        <v>37125.374894986293</v>
-      </c>
-      <c r="E184">
-        <v>94085.924491380822</v>
+      <c r="C184" s="6">
+        <v>120029.84432199999</v>
+      </c>
+      <c r="D184" s="6">
+        <v>35881.747689999997</v>
+      </c>
+      <c r="E184" s="7">
+        <v>84148.096632000001</v>
       </c>
       <c r="F184">
         <v>3.7499999999999999E-2</v>
@@ -3923,14 +5135,14 @@
       <c r="B185" t="s">
         <v>8</v>
       </c>
-      <c r="C185">
-        <v>128177.39678431301</v>
-      </c>
-      <c r="D185">
-        <v>37171.79612581175</v>
-      </c>
-      <c r="E185">
-        <v>91005.600658501266</v>
+      <c r="C185" s="6">
+        <v>118416.11503299999</v>
+      </c>
+      <c r="D185" s="6">
+        <v>34531.262443</v>
+      </c>
+      <c r="E185" s="7">
+        <v>83884.852589999995</v>
       </c>
       <c r="F185">
         <v>3.7499999999999999E-2</v>
@@ -3943,14 +5155,14 @@
       <c r="B186" t="s">
         <v>9</v>
       </c>
-      <c r="C186">
-        <v>131102.6252164295</v>
-      </c>
-      <c r="D186">
-        <v>38300.821872303452</v>
-      </c>
-      <c r="E186">
-        <v>92801.803344126049</v>
+      <c r="C186" s="6">
+        <v>114355.97771899999</v>
+      </c>
+      <c r="D186" s="6">
+        <v>32588.379384</v>
+      </c>
+      <c r="E186" s="7">
+        <v>81767.598334999988</v>
       </c>
       <c r="F186">
         <v>3.2500000000000001E-2</v>
@@ -3963,14 +5175,14 @@
       <c r="B187" t="s">
         <v>10</v>
       </c>
-      <c r="C187">
-        <v>131499.05851101718</v>
-      </c>
-      <c r="D187">
-        <v>38696.349934676095</v>
-      </c>
-      <c r="E187">
-        <v>92802.708576341087</v>
+      <c r="C187" s="6">
+        <v>113295.776115</v>
+      </c>
+      <c r="D187" s="6">
+        <v>29363.061617000003</v>
+      </c>
+      <c r="E187" s="7">
+        <v>83932.714498000001</v>
       </c>
       <c r="F187">
         <v>2.75E-2</v>
@@ -3983,14 +5195,14 @@
       <c r="B188" t="s">
         <v>11</v>
       </c>
-      <c r="C188">
-        <v>133792.32531281721</v>
-      </c>
-      <c r="D188">
-        <v>40400.678827009811</v>
-      </c>
-      <c r="E188">
-        <v>93391.646485807403</v>
+      <c r="C188" s="6">
+        <v>112406.50498199997</v>
+      </c>
+      <c r="D188" s="6">
+        <v>28652.342639999992</v>
+      </c>
+      <c r="E188" s="7">
+        <v>83754.162341999981</v>
       </c>
       <c r="F188">
         <v>2.5000000000000001E-2</v>
@@ -4003,14 +5215,14 @@
       <c r="B189" t="s">
         <v>12</v>
       </c>
-      <c r="C189">
-        <v>137941.92761732748</v>
-      </c>
-      <c r="D189">
-        <v>41534.801094111142</v>
-      </c>
-      <c r="E189">
-        <v>96407.126523216342</v>
+      <c r="C189" s="6">
+        <v>109760.80439199998</v>
+      </c>
+      <c r="D189" s="6">
+        <v>27160.901342999998</v>
+      </c>
+      <c r="E189" s="7">
+        <v>82599.903048999986</v>
       </c>
       <c r="F189">
         <v>2.2499999999999999E-2</v>
@@ -4023,14 +5235,14 @@
       <c r="B190" t="s">
         <v>13</v>
       </c>
-      <c r="C190">
-        <v>138650.5588539459</v>
-      </c>
-      <c r="D190">
-        <v>42223.391942766299</v>
-      </c>
-      <c r="E190">
-        <v>96427.166911179607</v>
+      <c r="C190" s="6">
+        <v>111985.722643</v>
+      </c>
+      <c r="D190" s="6">
+        <v>25930.569550999997</v>
+      </c>
+      <c r="E190" s="7">
+        <v>86055.153092000008</v>
       </c>
       <c r="F190">
         <v>1.7500000000000002E-2</v>
@@ -4043,14 +5255,14 @@
       <c r="B191" t="s">
         <v>14</v>
       </c>
-      <c r="C191">
-        <v>144109.76682101368</v>
-      </c>
-      <c r="D191">
-        <v>44133.388720470175</v>
-      </c>
-      <c r="E191">
-        <v>99976.378100543501</v>
+      <c r="C191" s="6">
+        <v>110144.94806200001</v>
+      </c>
+      <c r="D191" s="6">
+        <v>23877.360955</v>
+      </c>
+      <c r="E191" s="7">
+        <v>86267.587107000014</v>
       </c>
       <c r="F191">
         <v>1.7500000000000002E-2</v>
@@ -4063,14 +5275,14 @@
       <c r="B192" t="s">
         <v>15</v>
       </c>
-      <c r="C192">
-        <v>146772.79121668485</v>
-      </c>
-      <c r="D192">
-        <v>44829.254397331111</v>
-      </c>
-      <c r="E192">
-        <v>101943.53681935374</v>
+      <c r="C192" s="6">
+        <v>108684.469468</v>
+      </c>
+      <c r="D192" s="6">
+        <v>22786.922939000004</v>
+      </c>
+      <c r="E192" s="7">
+        <v>85897.546528999985</v>
       </c>
       <c r="F192">
         <v>1.7500000000000002E-2</v>
@@ -4083,14 +5295,14 @@
       <c r="B193" t="s">
         <v>16</v>
       </c>
-      <c r="C193">
-        <v>149062.19419518736</v>
-      </c>
-      <c r="D193">
-        <v>46167.525316214211</v>
-      </c>
-      <c r="E193">
-        <v>102894.66887897314</v>
+      <c r="C193" s="6">
+        <v>108842.308766</v>
+      </c>
+      <c r="D193" s="6">
+        <v>21622.953148000001</v>
+      </c>
+      <c r="E193" s="6">
+        <v>87219.355618000001</v>
       </c>
       <c r="F193">
         <v>1.7500000000000002E-2</v>
@@ -4103,14 +5315,14 @@
       <c r="B194" t="s">
         <v>5</v>
       </c>
-      <c r="C194">
-        <v>110671.71154399018</v>
-      </c>
-      <c r="D194">
-        <v>21868.675445590598</v>
-      </c>
-      <c r="E194">
-        <v>88803.036098399578</v>
+      <c r="C194" s="6">
+        <v>106098.971676</v>
+      </c>
+      <c r="D194" s="6">
+        <v>20561.676224999999</v>
+      </c>
+      <c r="E194" s="7">
+        <v>85537.295450999998</v>
       </c>
       <c r="F194">
         <v>1.7500000000000002E-2</v>
@@ -4123,14 +5335,14 @@
       <c r="B195" t="s">
         <v>6</v>
       </c>
-      <c r="C195">
-        <v>109789.74791661922</v>
-      </c>
-      <c r="D195">
-        <v>22124.389865220044</v>
-      </c>
-      <c r="E195">
-        <v>87665.358051399176</v>
+      <c r="C195" s="6">
+        <v>107679.28383600002</v>
+      </c>
+      <c r="D195" s="6">
+        <v>19597.657601000003</v>
+      </c>
+      <c r="E195" s="7">
+        <v>88081.626235000018</v>
       </c>
       <c r="F195">
         <v>1.7500000000000002E-2</v>
@@ -4143,14 +5355,14 @@
       <c r="B196" t="s">
         <v>7</v>
       </c>
-      <c r="C196">
-        <v>114855.02821951879</v>
-      </c>
-      <c r="D196">
-        <v>21867.661184391</v>
-      </c>
-      <c r="E196">
-        <v>92987.367035127798</v>
+      <c r="C196" s="6">
+        <v>108746.98419299998</v>
+      </c>
+      <c r="D196" s="6">
+        <v>18656.268263999998</v>
+      </c>
+      <c r="E196" s="7">
+        <v>90090.715928999984</v>
       </c>
       <c r="F196">
         <v>1.7500000000000002E-2</v>
@@ -4163,14 +5375,14 @@
       <c r="B197" t="s">
         <v>8</v>
       </c>
-      <c r="C197">
-        <v>112220.30526581018</v>
-      </c>
-      <c r="D197">
-        <v>21390.390270057436</v>
-      </c>
-      <c r="E197">
-        <v>90829.914995752741</v>
+      <c r="C197" s="6">
+        <v>108108.65055199999</v>
+      </c>
+      <c r="D197" s="6">
+        <v>18710.223129999998</v>
+      </c>
+      <c r="E197" s="7">
+        <v>89398.427421999993</v>
       </c>
       <c r="F197">
         <v>1.7500000000000002E-2</v>
@@ -4183,14 +5395,14 @@
       <c r="B198" t="s">
         <v>9</v>
       </c>
-      <c r="C198">
-        <v>113494.85434162416</v>
-      </c>
-      <c r="D198">
-        <v>21805.801610078466</v>
-      </c>
-      <c r="E198">
-        <v>91689.0527315457</v>
+      <c r="C198" s="6">
+        <v>107677.15315400001</v>
+      </c>
+      <c r="D198" s="6">
+        <v>18229.080043999998</v>
+      </c>
+      <c r="E198" s="7">
+        <v>89448.073110000012</v>
       </c>
       <c r="F198">
         <v>1.7500000000000002E-2</v>
@@ -4203,14 +5415,14 @@
       <c r="B199" t="s">
         <v>10</v>
       </c>
-      <c r="C199">
-        <v>114477.43824170801</v>
-      </c>
-      <c r="D199">
-        <v>21485.784033675489</v>
-      </c>
-      <c r="E199">
-        <v>92991.654208032516</v>
+      <c r="C199" s="6">
+        <v>108629.09941799998</v>
+      </c>
+      <c r="D199" s="6">
+        <v>18054.385029999998</v>
+      </c>
+      <c r="E199" s="7">
+        <v>90574.714387999993</v>
       </c>
       <c r="F199">
         <v>1.7500000000000002E-2</v>
@@ -4223,14 +5435,14 @@
       <c r="B200" t="s">
         <v>11</v>
       </c>
-      <c r="C200">
-        <v>115497.71400717743</v>
-      </c>
-      <c r="D200">
-        <v>22758.837681853536</v>
-      </c>
-      <c r="E200">
-        <v>92738.876325323901</v>
+      <c r="C200" s="6">
+        <v>108159.477396</v>
+      </c>
+      <c r="D200" s="6">
+        <v>18815.057545000003</v>
+      </c>
+      <c r="E200" s="7">
+        <v>89344.419850999999</v>
       </c>
       <c r="F200">
         <v>1.7500000000000002E-2</v>
@@ -4243,14 +5455,14 @@
       <c r="B201" t="s">
         <v>12</v>
       </c>
-      <c r="C201">
-        <v>116669.23089703386</v>
-      </c>
-      <c r="D201">
-        <v>23017.798110886815</v>
-      </c>
-      <c r="E201">
-        <v>93651.432786147052</v>
+      <c r="C201" s="6">
+        <v>107561.67380399999</v>
+      </c>
+      <c r="D201" s="6">
+        <v>18923.119481999998</v>
+      </c>
+      <c r="E201" s="7">
+        <v>88638.554321999996</v>
       </c>
       <c r="F201">
         <v>1.7500000000000002E-2</v>
@@ -4263,14 +5475,14 @@
       <c r="B202" t="s">
         <v>13</v>
       </c>
-      <c r="C202">
-        <v>118003.68620703403</v>
-      </c>
-      <c r="D202">
-        <v>22848.265331488594</v>
-      </c>
-      <c r="E202">
-        <v>95155.420875545431</v>
+      <c r="C202" s="6">
+        <v>108647.325967</v>
+      </c>
+      <c r="D202" s="6">
+        <v>19123.641464999997</v>
+      </c>
+      <c r="E202" s="7">
+        <v>89523.684502000004</v>
       </c>
       <c r="F202">
         <v>1.7500000000000002E-2</v>
@@ -4283,14 +5495,14 @@
       <c r="B203" t="s">
         <v>14</v>
       </c>
-      <c r="C203">
-        <v>118447.8430856968</v>
-      </c>
-      <c r="D203">
-        <v>23489.790420457255</v>
-      </c>
-      <c r="E203">
-        <v>94958.052665239549</v>
+      <c r="C203" s="6">
+        <v>109374.51839499998</v>
+      </c>
+      <c r="D203" s="6">
+        <v>20595.290364</v>
+      </c>
+      <c r="E203" s="7">
+        <v>88779.228030999977</v>
       </c>
       <c r="F203">
         <v>0.02</v>
@@ -4303,14 +5515,14 @@
       <c r="B204" t="s">
         <v>15</v>
       </c>
-      <c r="C204">
-        <v>120127.62189555583</v>
-      </c>
-      <c r="D204">
-        <v>24204.786344012995</v>
-      </c>
-      <c r="E204">
-        <v>95922.835551542841</v>
+      <c r="C204" s="6">
+        <v>111597.73594300001</v>
+      </c>
+      <c r="D204" s="6">
+        <v>22476.881816999998</v>
+      </c>
+      <c r="E204" s="7">
+        <v>89120.854126000006</v>
       </c>
       <c r="F204">
         <v>2.5000000000000001E-2</v>
@@ -4323,14 +5535,14 @@
       <c r="B205" t="s">
         <v>16</v>
       </c>
-      <c r="C205">
-        <v>120606.2958580289</v>
-      </c>
-      <c r="D205">
-        <v>24663.8150851102</v>
-      </c>
-      <c r="E205">
-        <v>95942.480772918701</v>
+      <c r="C205" s="6">
+        <v>112799.90611599997</v>
+      </c>
+      <c r="D205" s="6">
+        <v>24230.764319000002</v>
+      </c>
+      <c r="E205" s="6">
+        <v>88569.14179699996</v>
       </c>
       <c r="F205">
         <v>0.03</v>
@@ -4343,14 +5555,14 @@
       <c r="B206" t="s">
         <v>5</v>
       </c>
-      <c r="C206">
-        <v>115220.00252379446</v>
-      </c>
-      <c r="D206">
-        <v>29314.292825535005</v>
-      </c>
-      <c r="E206">
-        <v>85905.709698259452</v>
+      <c r="C206" s="6">
+        <v>114506.42076700002</v>
+      </c>
+      <c r="D206" s="6">
+        <v>26871.583562</v>
+      </c>
+      <c r="E206" s="7">
+        <v>87634.837205000018</v>
       </c>
       <c r="F206">
         <v>0.04</v>
@@ -4363,14 +5575,14 @@
       <c r="B207" t="s">
         <v>6</v>
       </c>
-      <c r="C207">
-        <v>116159.96166897743</v>
-      </c>
-      <c r="D207">
-        <v>28173.465790652092</v>
-      </c>
-      <c r="E207">
-        <v>87986.495878325339</v>
+      <c r="C207" s="6">
+        <v>115609.23216699999</v>
+      </c>
+      <c r="D207" s="6">
+        <v>30885.441358</v>
+      </c>
+      <c r="E207" s="7">
+        <v>84723.790808999998</v>
       </c>
       <c r="F207">
         <v>0.04</v>
@@ -4383,14 +5595,14 @@
       <c r="B208" t="s">
         <v>7</v>
       </c>
-      <c r="C208">
-        <v>126448.1769818617</v>
-      </c>
-      <c r="D208">
-        <v>31848.695203592666</v>
-      </c>
-      <c r="E208">
-        <v>94599.481778269037</v>
+      <c r="C208" s="6">
+        <v>121564.61326299999</v>
+      </c>
+      <c r="D208" s="6">
+        <v>35393.225683999997</v>
+      </c>
+      <c r="E208" s="7">
+        <v>86171.387579000002</v>
       </c>
       <c r="F208">
         <v>0.04</v>
@@ -4403,14 +5615,14 @@
       <c r="B209" t="s">
         <v>8</v>
       </c>
-      <c r="C209">
-        <v>123123.12980628374</v>
-      </c>
-      <c r="D209">
-        <v>32876.32257645957</v>
-      </c>
-      <c r="E209">
-        <v>90246.807229824175</v>
+      <c r="C209" s="6">
+        <v>124502.79102299998</v>
+      </c>
+      <c r="D209" s="6">
+        <v>41959.420549000002</v>
+      </c>
+      <c r="E209" s="7">
+        <v>82543.370473999981</v>
       </c>
       <c r="F209">
         <v>0.05</v>
@@ -4423,14 +5635,14 @@
       <c r="B210" t="s">
         <v>9</v>
       </c>
-      <c r="C210">
-        <v>126329.88046460063</v>
-      </c>
-      <c r="D210">
-        <v>35056.19781380018</v>
-      </c>
-      <c r="E210">
-        <v>91273.682650800445</v>
+      <c r="C210" s="6">
+        <v>130241.22939000001</v>
+      </c>
+      <c r="D210" s="6">
+        <v>52296.743537000002</v>
+      </c>
+      <c r="E210" s="7">
+        <v>77944.485853000006</v>
       </c>
       <c r="F210">
         <v>0.06</v>
@@ -4443,14 +5655,14 @@
       <c r="B211" t="s">
         <v>10</v>
       </c>
-      <c r="C211">
-        <v>129474.71135746018</v>
-      </c>
-      <c r="D211">
-        <v>35074.178889353541</v>
-      </c>
-      <c r="E211">
-        <v>94400.532468106641</v>
+      <c r="C211" s="6">
+        <v>135158.87485299999</v>
+      </c>
+      <c r="D211" s="6">
+        <v>56795.670142000003</v>
+      </c>
+      <c r="E211" s="7">
+        <v>78363.204710999984</v>
       </c>
       <c r="F211">
         <v>0.06</v>
@@ -4463,14 +5675,14 @@
       <c r="B212" t="s">
         <v>11</v>
       </c>
-      <c r="C212">
-        <v>130692.43069344833</v>
-      </c>
-      <c r="D212">
-        <v>37154.589424556536</v>
-      </c>
-      <c r="E212">
-        <v>93537.841268891789</v>
+      <c r="C212" s="6">
+        <v>139554.831014</v>
+      </c>
+      <c r="D212" s="6">
+        <v>63340.391706000002</v>
+      </c>
+      <c r="E212" s="7">
+        <v>76214.439308000001</v>
       </c>
       <c r="F212">
         <v>7.4999999999999997E-2</v>
@@ -4483,14 +5695,14 @@
       <c r="B213" t="s">
         <v>12</v>
       </c>
-      <c r="C213">
-        <v>134278.89391026655</v>
-      </c>
-      <c r="D213">
-        <v>38696.075496413454</v>
-      </c>
-      <c r="E213">
-        <v>95582.818413853092</v>
+      <c r="C213" s="6">
+        <v>145863.28002099998</v>
+      </c>
+      <c r="D213" s="6">
+        <v>73069.941114999994</v>
+      </c>
+      <c r="E213" s="7">
+        <v>72793.33890599999</v>
       </c>
       <c r="F213">
         <v>0.09</v>
@@ -4503,14 +5715,14 @@
       <c r="B214" t="s">
         <v>13</v>
       </c>
-      <c r="C214">
-        <v>136149.26468689731</v>
-      </c>
-      <c r="D214">
-        <v>39238.108440045573</v>
-      </c>
-      <c r="E214">
-        <v>96911.156246851737</v>
+      <c r="C214" s="6">
+        <v>149741.76946800001</v>
+      </c>
+      <c r="D214" s="6">
+        <v>81962.483940000006</v>
+      </c>
+      <c r="E214" s="7">
+        <v>67779.285528000008</v>
       </c>
       <c r="F214">
         <v>0.1</v>
@@ -4523,14 +5735,14 @@
       <c r="B215" t="s">
         <v>14</v>
       </c>
-      <c r="C215">
-        <v>139919.22720250391</v>
-      </c>
-      <c r="D215">
-        <v>41610.989132002185</v>
-      </c>
-      <c r="E215">
-        <v>98308.238070501728</v>
+      <c r="C215" s="6">
+        <v>155148.75574899997</v>
+      </c>
+      <c r="D215" s="6">
+        <v>90485.44526800001</v>
+      </c>
+      <c r="E215" s="7">
+        <v>64663.310480999964</v>
       </c>
       <c r="F215">
         <v>0.11</v>
@@ -4543,14 +5755,14 @@
       <c r="B216" t="s">
         <v>15</v>
       </c>
-      <c r="C216">
-        <v>142288.46809269104</v>
-      </c>
-      <c r="D216">
-        <v>41264.348590395217</v>
-      </c>
-      <c r="E216">
-        <v>101024.11950229583</v>
+      <c r="C216" s="6">
+        <v>162206.32550200002</v>
+      </c>
+      <c r="D216" s="6">
+        <v>100496.64903000002</v>
+      </c>
+      <c r="E216" s="7">
+        <v>61709.676472000006</v>
       </c>
       <c r="F216">
         <v>0.11</v>
@@ -4563,14 +5775,14 @@
       <c r="B217" t="s">
         <v>16</v>
       </c>
-      <c r="C217">
-        <v>145135.13501523802</v>
-      </c>
-      <c r="D217">
-        <v>43547.799342553648</v>
-      </c>
-      <c r="E217">
-        <v>101587.33567268436</v>
+      <c r="C217" s="6">
+        <v>169493.75084299999</v>
+      </c>
+      <c r="D217" s="6">
+        <v>110790.035829</v>
+      </c>
+      <c r="E217" s="6">
+        <v>58703.715013999987</v>
       </c>
       <c r="F217">
         <v>0.12</v>
@@ -4583,14 +5795,14 @@
       <c r="B218" t="s">
         <v>5</v>
       </c>
-      <c r="C218">
-        <v>172145.82076901247</v>
-      </c>
-      <c r="D218">
-        <v>105231.55030404028</v>
-      </c>
-      <c r="E218">
-        <v>66914.270464972185</v>
+      <c r="C218" s="6">
+        <v>172606.542025</v>
+      </c>
+      <c r="D218" s="6">
+        <v>121747.00737100003</v>
+      </c>
+      <c r="E218" s="7">
+        <v>50859.534653999974</v>
       </c>
       <c r="F218">
         <v>0.1275</v>
@@ -4603,14 +5815,14 @@
       <c r="B219" t="s">
         <v>6</v>
       </c>
-      <c r="C219">
-        <v>173635.77103101369</v>
-      </c>
-      <c r="D219">
-        <v>99974.577501029868</v>
-      </c>
-      <c r="E219">
-        <v>73661.193529983822</v>
+      <c r="C219" s="6">
+        <v>172269.92544000002</v>
+      </c>
+      <c r="D219" s="6">
+        <v>120619.95186999999</v>
+      </c>
+      <c r="E219" s="7">
+        <v>51649.973570000031</v>
       </c>
       <c r="F219">
         <v>0.1275</v>
@@ -4623,14 +5835,14 @@
       <c r="B220" t="s">
         <v>7</v>
       </c>
-      <c r="C220">
-        <v>189277.99339600446</v>
-      </c>
-      <c r="D220">
-        <v>107071.77255371067</v>
-      </c>
-      <c r="E220">
-        <v>82206.220842293784</v>
+      <c r="C220" s="6">
+        <v>179317.37406100001</v>
+      </c>
+      <c r="D220" s="6">
+        <v>127479.139069</v>
+      </c>
+      <c r="E220" s="7">
+        <v>51838.234992000012</v>
       </c>
       <c r="F220">
         <v>0.13</v>
@@ -4643,14 +5855,14 @@
       <c r="B221" t="s">
         <v>8</v>
       </c>
-      <c r="C221">
-        <v>184012.47116155495</v>
-      </c>
-      <c r="D221">
-        <v>106229.70469137374</v>
-      </c>
-      <c r="E221">
-        <v>77782.766470181203</v>
+      <c r="C221" s="6">
+        <v>177762.618694</v>
+      </c>
+      <c r="D221" s="6">
+        <v>123845.117434</v>
+      </c>
+      <c r="E221" s="7">
+        <v>53917.501260000005</v>
       </c>
       <c r="F221">
         <v>0.13</v>
@@ -4663,14 +5875,14 @@
       <c r="B222" t="s">
         <v>9</v>
       </c>
-      <c r="C222">
-        <v>190200.48085718963</v>
-      </c>
-      <c r="D222">
-        <v>109430.93865569722</v>
-      </c>
-      <c r="E222">
-        <v>80769.542201492412</v>
+      <c r="C222" s="6">
+        <v>177999.60600800003</v>
+      </c>
+      <c r="D222" s="6">
+        <v>125240.819994</v>
+      </c>
+      <c r="E222" s="7">
+        <v>52758.786014000027</v>
       </c>
       <c r="F222">
         <v>0.13250000000000001</v>
@@ -4683,14 +5895,14 @@
       <c r="B223" t="s">
         <v>10</v>
       </c>
-      <c r="C223">
-        <v>192344.12311074746</v>
-      </c>
-      <c r="D223">
-        <v>107690.45792285437</v>
-      </c>
-      <c r="E223">
-        <v>84653.665187893086</v>
+      <c r="C223" s="6">
+        <v>174695.00902300002</v>
+      </c>
+      <c r="D223" s="6">
+        <v>123406.250755</v>
+      </c>
+      <c r="E223" s="7">
+        <v>51288.75826800002</v>
       </c>
       <c r="F223">
         <v>0.13250000000000001</v>
@@ -4703,14 +5915,14 @@
       <c r="B224" t="s">
         <v>11</v>
       </c>
-      <c r="C224">
-        <v>194560.40690211888</v>
-      </c>
-      <c r="D224">
-        <v>104860.87717804995</v>
-      </c>
-      <c r="E224">
-        <v>89699.529724068925</v>
+      <c r="C224" s="6">
+        <v>175504.81138500001</v>
+      </c>
+      <c r="D224" s="6">
+        <v>125245.333701</v>
+      </c>
+      <c r="E224" s="7">
+        <v>50259.477684000012</v>
       </c>
       <c r="F224">
         <v>0.13250000000000001</v>
@@ -4723,14 +5935,14 @@
       <c r="B225" t="s">
         <v>12</v>
       </c>
-      <c r="C225">
-        <v>198257.70303915458</v>
-      </c>
-      <c r="D225">
-        <v>101291.56415997895</v>
-      </c>
-      <c r="E225">
-        <v>96966.138879175633</v>
+      <c r="C225" s="6">
+        <v>179353.89728199999</v>
+      </c>
+      <c r="D225" s="6">
+        <v>124546.41695899999</v>
+      </c>
+      <c r="E225" s="7">
+        <v>54807.480322999996</v>
       </c>
       <c r="F225">
         <v>0.13250000000000001</v>
@@ -4743,14 +5955,14 @@
       <c r="B226" t="s">
         <v>13</v>
       </c>
-      <c r="C226">
-        <v>197783.92632597953</v>
-      </c>
-      <c r="D226">
-        <v>97866.684437386459</v>
-      </c>
-      <c r="E226">
-        <v>99917.241888593067</v>
+      <c r="C226" s="6">
+        <v>175450.95360900005</v>
+      </c>
+      <c r="D226" s="6">
+        <v>124197.31178400002</v>
+      </c>
+      <c r="E226" s="7">
+        <v>51253.641825000028</v>
       </c>
       <c r="F226">
         <v>0.13250000000000001</v>
@@ -4763,14 +5975,14 @@
       <c r="B227" t="s">
         <v>14</v>
       </c>
-      <c r="C227">
-        <v>201403.21685365605</v>
-      </c>
-      <c r="D227">
-        <v>98173.648258162386</v>
-      </c>
-      <c r="E227">
-        <v>103229.56859549366</v>
+      <c r="C227" s="6">
+        <v>175533.81570000001</v>
+      </c>
+      <c r="D227" s="6">
+        <v>120074.70995499998</v>
+      </c>
+      <c r="E227" s="7">
+        <v>55459.105745000023</v>
       </c>
       <c r="F227">
         <v>0.13250000000000001</v>
@@ -4783,14 +5995,14 @@
       <c r="B228" t="s">
         <v>15</v>
       </c>
-      <c r="C228">
-        <v>203302.19663741507</v>
-      </c>
-      <c r="D228">
-        <v>92316.285937773282</v>
-      </c>
-      <c r="E228">
-        <v>110985.91069964178</v>
+      <c r="C228" s="6">
+        <v>173283.30884899999</v>
+      </c>
+      <c r="D228" s="6">
+        <v>120903.91542200001</v>
+      </c>
+      <c r="E228" s="7">
+        <v>52379.393426999988</v>
       </c>
       <c r="F228">
         <v>0.13250000000000001</v>
@@ -4803,14 +6015,14 @@
       <c r="B229" t="s">
         <v>16</v>
       </c>
-      <c r="C229">
-        <v>202826.0394818903</v>
-      </c>
-      <c r="D229">
-        <v>91864.726678867373</v>
-      </c>
-      <c r="E229">
-        <v>110961.31280302293</v>
+      <c r="C229" s="6">
+        <v>173179.29312100002</v>
+      </c>
+      <c r="D229" s="6">
+        <v>119076.785443</v>
+      </c>
+      <c r="E229" s="6">
+        <v>54102.507678000024</v>
       </c>
       <c r="F229">
         <v>0.13</v>
@@ -4823,14 +6035,14 @@
       <c r="B230" t="s">
         <v>5</v>
       </c>
-      <c r="C230">
-        <v>184151.09840316817</v>
-      </c>
-      <c r="D230">
-        <v>115902.48129160175</v>
-      </c>
-      <c r="E230">
-        <v>68248.617111566418</v>
+      <c r="C230" s="6">
+        <v>172440.77686899999</v>
+      </c>
+      <c r="D230" s="6">
+        <v>119354.420824</v>
+      </c>
+      <c r="E230" s="7">
+        <v>53086.356044999993</v>
       </c>
       <c r="F230">
         <v>0.13</v>
@@ -4843,14 +6055,14 @@
       <c r="B231" t="s">
         <v>6</v>
       </c>
-      <c r="C231">
-        <v>177485.76815507616</v>
-      </c>
-      <c r="D231">
-        <v>107944.35630411262</v>
-      </c>
-      <c r="E231">
-        <v>69541.411850963545</v>
+      <c r="C231" s="6">
+        <v>173896.45034700003</v>
+      </c>
+      <c r="D231" s="6">
+        <v>116877.32098</v>
+      </c>
+      <c r="E231" s="7">
+        <v>57019.12936700003</v>
       </c>
       <c r="F231">
         <v>0.1275</v>
@@ -4863,14 +6075,14 @@
       <c r="B232" t="s">
         <v>7</v>
       </c>
-      <c r="C232">
-        <v>184853.61803973161</v>
-      </c>
-      <c r="D232">
-        <v>109662.97934558504</v>
-      </c>
-      <c r="E232">
-        <v>75190.638694146561</v>
+      <c r="C232" s="6">
+        <v>175954.340314</v>
+      </c>
+      <c r="D232" s="6">
+        <v>121611.212589</v>
+      </c>
+      <c r="E232" s="7">
+        <v>54343.127724999998</v>
       </c>
       <c r="F232">
         <v>0.1225</v>
@@ -4883,14 +6095,14 @@
       <c r="B233" t="s">
         <v>8</v>
       </c>
-      <c r="C233">
-        <v>188536.82765364769</v>
-      </c>
-      <c r="D233">
-        <v>103396.34513934424</v>
-      </c>
-      <c r="E233">
-        <v>85140.482514303454</v>
+      <c r="C233" s="6">
+        <v>172354.70471099997</v>
+      </c>
+      <c r="D233" s="6">
+        <v>109123.825512</v>
+      </c>
+      <c r="E233" s="7">
+        <v>63230.879198999974</v>
       </c>
       <c r="F233">
         <v>0.1225</v>
@@ -4903,14 +6115,14 @@
       <c r="B234" t="s">
         <v>9</v>
       </c>
-      <c r="C234">
-        <v>187880.85699738801</v>
-      </c>
-      <c r="D234">
-        <v>98204.69247971478</v>
-      </c>
-      <c r="E234">
-        <v>89676.164517673227</v>
+      <c r="C234" s="6">
+        <v>167914.85365300003</v>
+      </c>
+      <c r="D234" s="6">
+        <v>103635.200459</v>
+      </c>
+      <c r="E234" s="7">
+        <v>64279.653194000028</v>
       </c>
       <c r="F234">
         <v>0.11749999999999999</v>
@@ -4923,14 +6135,14 @@
       <c r="B235" t="s">
         <v>10</v>
       </c>
-      <c r="C235">
-        <v>182872.13028724998</v>
-      </c>
-      <c r="D235">
-        <v>96441.639648433382</v>
-      </c>
-      <c r="E235">
-        <v>86430.490638816598</v>
+      <c r="C235" s="6">
+        <v>162885.57630000002</v>
+      </c>
+      <c r="D235" s="6">
+        <v>99220.239413000003</v>
+      </c>
+      <c r="E235" s="7">
+        <v>63665.336887000012</v>
       </c>
       <c r="F235">
         <v>0.11749999999999999</v>
@@ -4943,14 +6155,14 @@
       <c r="B236" t="s">
         <v>11</v>
       </c>
-      <c r="C236">
-        <v>187245.8506458209</v>
-      </c>
-      <c r="D236">
-        <v>96471.436547676683</v>
-      </c>
-      <c r="E236">
-        <v>90774.414098144218</v>
+      <c r="C236" s="6">
+        <v>162310.32736200001</v>
+      </c>
+      <c r="D236" s="6">
+        <v>93603.785965000003</v>
+      </c>
+      <c r="E236" s="7">
+        <v>68706.541397000008</v>
       </c>
       <c r="F236">
         <v>0.1125</v>
@@ -4963,14 +6175,14 @@
       <c r="B237" t="s">
         <v>12</v>
       </c>
-      <c r="C237">
-        <v>197882.5025061295</v>
-      </c>
-      <c r="D237">
-        <v>93104.377068108341</v>
-      </c>
-      <c r="E237">
-        <v>104778.12543802116</v>
+      <c r="C237" s="6">
+        <v>160281.91200600003</v>
+      </c>
+      <c r="D237" s="6">
+        <v>89349.247687999989</v>
+      </c>
+      <c r="E237" s="7">
+        <v>70932.664318000039</v>
       </c>
       <c r="F237">
         <v>0.1075</v>
@@ -4983,14 +6195,14 @@
       <c r="B238" t="s">
         <v>13</v>
       </c>
-      <c r="C238">
-        <v>198711.18802637421</v>
-      </c>
-      <c r="D238">
-        <v>91158.598000000537</v>
-      </c>
-      <c r="E238">
-        <v>107552.59002637367</v>
+      <c r="C238" s="6">
+        <v>158754.50757300001</v>
+      </c>
+      <c r="D238" s="6">
+        <v>87745.062993</v>
+      </c>
+      <c r="E238" s="7">
+        <v>71009.44458000001</v>
       </c>
       <c r="F238">
         <v>0.1075</v>
@@ -5003,14 +6215,14 @@
       <c r="B239" t="s">
         <v>14</v>
       </c>
-      <c r="C239">
-        <v>204061.95118324066</v>
-      </c>
-      <c r="D239">
-        <v>90261.951567698168</v>
-      </c>
-      <c r="E239">
-        <v>113799.99961554249</v>
+      <c r="C239" s="6">
+        <v>159513.468322</v>
+      </c>
+      <c r="D239" s="6">
+        <v>88094.420222999994</v>
+      </c>
+      <c r="E239" s="7">
+        <v>71419.048099000007</v>
       </c>
       <c r="F239">
         <v>0.10249999999999999</v>
@@ -5023,14 +6235,14 @@
       <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240">
-        <v>204386.91615829297</v>
-      </c>
-      <c r="D240">
-        <v>85622.599369685529</v>
-      </c>
-      <c r="E240">
-        <v>118764.31678860744</v>
+      <c r="C240" s="6">
+        <v>160796.890136</v>
+      </c>
+      <c r="D240" s="6">
+        <v>85773.230616000001</v>
+      </c>
+      <c r="E240" s="7">
+        <v>75023.659520000001</v>
       </c>
       <c r="F240">
         <v>9.7500000000000003E-2</v>
@@ -5043,14 +6255,14 @@
       <c r="B241" t="s">
         <v>16</v>
       </c>
-      <c r="C241">
-        <v>209484.50737809532</v>
-      </c>
-      <c r="D241">
-        <v>86908.376441476474</v>
-      </c>
-      <c r="E241">
-        <v>122576.13093661885</v>
+      <c r="C241" s="6">
+        <v>161839.87166100001</v>
+      </c>
+      <c r="D241" s="6">
+        <v>88432.947396000003</v>
+      </c>
+      <c r="E241" s="6">
+        <v>73406.924265000009</v>
       </c>
       <c r="F241">
         <v>9.5000000000000001E-2</v>
@@ -5063,14 +6275,14 @@
       <c r="B242" t="s">
         <v>5</v>
       </c>
-      <c r="C242">
-        <v>179970.62287676529</v>
-      </c>
-      <c r="D242">
-        <v>85327.260523086487</v>
-      </c>
-      <c r="E242">
-        <v>94643.362353678807</v>
+      <c r="C242" s="6">
+        <v>168546.15433799999</v>
+      </c>
+      <c r="D242" s="6">
+        <v>89112.169872000013</v>
+      </c>
+      <c r="E242" s="7">
+        <v>79433.98446599998</v>
       </c>
       <c r="F242">
         <v>9.5000000000000001E-2</v>
@@ -5083,14 +6295,14 @@
       <c r="B243" t="s">
         <v>6</v>
       </c>
-      <c r="C243">
-        <v>176134.48565197026</v>
-      </c>
-      <c r="D243">
-        <v>80330.906627408171</v>
-      </c>
-      <c r="E243">
-        <v>95803.579024562088</v>
+      <c r="C243" s="6">
+        <v>161663.12574699998</v>
+      </c>
+      <c r="D243" s="6">
+        <v>88987.694793000002</v>
+      </c>
+      <c r="E243" s="7">
+        <v>72675.430953999981</v>
       </c>
       <c r="F243">
         <v>9.5000000000000001E-2</v>
@@ -5103,14 +6315,14 @@
       <c r="B244" t="s">
         <v>7</v>
       </c>
-      <c r="C244">
-        <v>189675.95295006272</v>
-      </c>
-      <c r="D244">
-        <v>83402.950553033384</v>
-      </c>
-      <c r="E244">
-        <v>106273.00239702934</v>
+      <c r="C244" s="6">
+        <v>171949.527856</v>
+      </c>
+      <c r="D244" s="6">
+        <v>93954.423643999995</v>
+      </c>
+      <c r="E244" s="7">
+        <v>77995.104212000006</v>
       </c>
       <c r="F244">
         <v>9.5000000000000001E-2</v>
@@ -5123,14 +6335,14 @@
       <c r="B245" t="s">
         <v>8</v>
       </c>
-      <c r="C245">
-        <v>182274.27632318679</v>
-      </c>
-      <c r="D245">
-        <v>75987.7636603094</v>
-      </c>
-      <c r="E245">
-        <v>106286.51266287739</v>
+      <c r="C245" s="6">
+        <v>171680.15847100003</v>
+      </c>
+      <c r="D245" s="6">
+        <v>93155.483485999997</v>
+      </c>
+      <c r="E245" s="7">
+        <v>78524.674985000034</v>
       </c>
       <c r="F245">
         <v>9.5000000000000001E-2</v>
@@ -5143,14 +6355,14 @@
       <c r="B246" t="s">
         <v>9</v>
       </c>
-      <c r="C246">
-        <v>185302.18837719891</v>
-      </c>
-      <c r="D246">
-        <v>74571.493847846185</v>
-      </c>
-      <c r="E246">
-        <v>110730.69452935272</v>
+      <c r="C246" s="6">
+        <v>175242.98612800002</v>
+      </c>
+      <c r="D246" s="6">
+        <v>95300.280877000012</v>
+      </c>
+      <c r="E246" s="7">
+        <v>79942.705251000007</v>
       </c>
       <c r="F246">
         <v>9.2499999999999999E-2</v>
@@ -5163,14 +6375,14 @@
       <c r="B247" t="s">
         <v>10</v>
       </c>
-      <c r="C247">
-        <v>182263.15441294626</v>
-      </c>
-      <c r="D247">
-        <v>72846.202588755055</v>
-      </c>
-      <c r="E247">
-        <v>109416.9518241912</v>
+      <c r="C247" s="6">
+        <v>173756.45211400001</v>
+      </c>
+      <c r="D247" s="6">
+        <v>93421.575291999994</v>
+      </c>
+      <c r="E247" s="7">
+        <v>80334.87682200002</v>
       </c>
       <c r="F247">
         <v>9.2499999999999999E-2</v>
@@ -5183,14 +6395,14 @@
       <c r="B248" t="s">
         <v>11</v>
       </c>
-      <c r="C248">
-        <v>186291.0539210673</v>
-      </c>
-      <c r="D248">
-        <v>71489.431834838557</v>
-      </c>
-      <c r="E248">
-        <v>114801.62208622874</v>
+      <c r="C248" s="6">
+        <v>177611.878669</v>
+      </c>
+      <c r="D248" s="6">
+        <v>94327.325268999994</v>
+      </c>
+      <c r="E248" s="7">
+        <v>83284.553400000004</v>
       </c>
       <c r="F248">
         <v>9.2499999999999999E-2</v>
@@ -5203,14 +6415,14 @@
       <c r="B249" t="s">
         <v>12</v>
       </c>
-      <c r="C249">
-        <v>188210.70411639023</v>
-      </c>
-      <c r="D249">
-        <v>68879.031916300853</v>
-      </c>
-      <c r="E249">
-        <v>119331.67220008938</v>
+      <c r="C249" s="6">
+        <v>178549.12228600003</v>
+      </c>
+      <c r="D249" s="6">
+        <v>95393.180770000006</v>
+      </c>
+      <c r="E249" s="7">
+        <v>83155.941516000021</v>
       </c>
       <c r="F249">
         <v>9.2499999999999999E-2</v>
@@ -5223,14 +6435,14 @@
       <c r="B250" t="s">
         <v>13</v>
       </c>
-      <c r="C250">
-        <v>188328.31622986845</v>
-      </c>
-      <c r="D250">
-        <v>67057.779358819869</v>
-      </c>
-      <c r="E250">
-        <v>121270.53687104858</v>
+      <c r="C250" s="6">
+        <v>179403.45495200003</v>
+      </c>
+      <c r="D250" s="6">
+        <v>96400.383470000015</v>
+      </c>
+      <c r="E250" s="7">
+        <v>83003.071482000014</v>
       </c>
       <c r="F250">
         <v>9.2499999999999999E-2</v>
@@ -5243,14 +6455,14 @@
       <c r="B251" t="s">
         <v>14</v>
       </c>
-      <c r="C251">
-        <v>189937.41801433597</v>
-      </c>
-      <c r="D251">
-        <v>65698.14942016323</v>
-      </c>
-      <c r="E251">
-        <v>124239.26859417274</v>
+      <c r="C251" s="6">
+        <v>180527.38270400002</v>
+      </c>
+      <c r="D251" s="6">
+        <v>98698.126669000005</v>
+      </c>
+      <c r="E251" s="7">
+        <v>81829.256035000013</v>
       </c>
       <c r="F251">
         <v>9.2499999999999999E-2</v>
@@ -5263,14 +6475,14 @@
       <c r="B252" t="s">
         <v>15</v>
       </c>
-      <c r="C252">
-        <v>188438.82639765972</v>
-      </c>
-      <c r="D252">
-        <v>64393.972409130743</v>
-      </c>
-      <c r="E252">
-        <v>124044.85398852898</v>
+      <c r="C252" s="6">
+        <v>182156.29664399999</v>
+      </c>
+      <c r="D252" s="6">
+        <v>97830.733132000008</v>
+      </c>
+      <c r="E252" s="7">
+        <v>84325.563511999979</v>
       </c>
       <c r="F252">
         <v>9.2499999999999999E-2</v>
@@ -5283,14 +6495,14 @@
       <c r="B253" t="s">
         <v>16</v>
       </c>
-      <c r="C253">
-        <v>192556.88572927966</v>
-      </c>
-      <c r="D253">
-        <v>65443.390516804815</v>
-      </c>
-      <c r="E253">
-        <v>127113.49521247484</v>
+      <c r="C253" s="6">
+        <v>190722.42398099997</v>
+      </c>
+      <c r="D253" s="6">
+        <v>99910.595614999998</v>
+      </c>
+      <c r="E253" s="6">
+        <v>90811.828365999972</v>
       </c>
       <c r="F253">
         <v>9.2499999999999999E-2</v>

--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12AC859-9DFD-45F0-A457-EBE9C56A033A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0133296E-8763-4944-8C29-DC19902EFC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,11 +177,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -467,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7710FB4-1D75-4856-9D30-3BF005362D8B}">
-  <dimension ref="A1:DZ265"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -497,13 +494,13 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="1">
         <v>32790.077908983025</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="1">
         <v>14093.620264434951</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="1">
         <v>18696.457644548074</v>
       </c>
       <c r="F2">
@@ -517,13 +514,13 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="1">
         <v>32128.51999336536</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="1">
         <v>13900.049437858104</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="1">
         <v>18228.470555507258</v>
       </c>
       <c r="F3">
@@ -537,13 +534,13 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="1">
         <v>37128.281537396892</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="1">
         <v>14386.374721816268</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="1">
         <v>22741.906815580624</v>
       </c>
       <c r="F4">
@@ -557,13 +554,13 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="1">
         <v>36248.373382015947</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="1">
         <v>14315.991990494918</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="1">
         <v>21932.381391521027</v>
       </c>
       <c r="F5">
@@ -577,13 +574,13 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="1">
         <v>35987.711776337484</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>14489.77260139857</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="1">
         <v>21497.939174938914</v>
       </c>
       <c r="F6">
@@ -597,13 +594,13 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="1">
         <v>34904.228120450076</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
         <v>14418.028754992763</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="1">
         <v>20486.199365457313</v>
       </c>
       <c r="F7">
@@ -617,13 +614,13 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="1">
         <v>36037.159659434183</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
         <v>14617.887918750595</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="1">
         <v>21419.271740683587</v>
       </c>
       <c r="F8">
@@ -637,13 +634,13 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="1">
         <v>34312.458634863899</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="1">
         <v>14679.565901569938</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="1">
         <v>19632.89273329396</v>
       </c>
       <c r="F9">
@@ -657,13 +654,13 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="1">
         <v>33945.279755463183</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="1">
         <v>14598.086221905707</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="1">
         <v>19347.193533557474</v>
       </c>
       <c r="F10">
@@ -677,13 +674,13 @@
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="1">
         <v>35289.013715147557</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="1">
         <v>14801.535549246313</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="1">
         <v>20487.478165901244</v>
       </c>
       <c r="F11">
@@ -697,13 +694,13 @@
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="1">
         <v>34484.083313307143</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="1">
         <v>14709.143342629954</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="1">
         <v>19774.939970677187</v>
       </c>
       <c r="F12">
@@ -717,13 +714,13 @@
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="1">
         <v>36786.444008420447</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="1">
         <v>14927.300526272693</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="1">
         <v>21859.143482147752</v>
       </c>
       <c r="F13">
@@ -737,13 +734,13 @@
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="1">
         <v>30695.298207016058</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="1">
         <v>11929.845301432179</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="1">
         <v>18765.452905583879</v>
       </c>
       <c r="F14">
@@ -757,13 +754,13 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="1">
         <v>30416.557877666655</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="1">
         <v>11612.756042107814</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="1">
         <v>18803.801835558843</v>
       </c>
       <c r="F15">
@@ -777,13 +774,13 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="1">
         <v>33697.311141683407</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="1">
         <v>12219.583536825376</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="1">
         <v>21477.727604858032</v>
       </c>
       <c r="F16">
@@ -797,13 +794,13 @@
       <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="1">
         <v>34520.567238962773</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="1">
         <v>12256.670245216828</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="1">
         <v>22263.896993745944</v>
       </c>
       <c r="F17">
@@ -817,13 +814,13 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="1">
         <v>33517.787777975129</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="1">
         <v>12541.310986274913</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="1">
         <v>20976.476791700217</v>
       </c>
       <c r="F18">
@@ -837,13 +834,13 @@
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="1">
         <v>33378.235074134049</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="1">
         <v>12569.501682184005</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="1">
         <v>20808.733391950045</v>
       </c>
       <c r="F19">
@@ -857,13 +854,13 @@
       <c r="B20" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="1">
         <v>34680.569732790282</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="1">
         <v>12841.25629590105</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="1">
         <v>21839.313436889232</v>
       </c>
       <c r="F20">
@@ -877,13 +874,13 @@
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="1">
         <v>34500.370875939581</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="1">
         <v>12965.784595218889</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="1">
         <v>21534.586280720694</v>
       </c>
       <c r="F21">
@@ -897,13 +894,13 @@
       <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="1">
         <v>34105.142513812476</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="1">
         <v>12942.554453523537</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="1">
         <v>21162.588060288937</v>
       </c>
       <c r="F22">
@@ -917,13 +914,13 @@
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="1">
         <v>35446.46405673134</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="1">
         <v>13227.573975810654</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="1">
         <v>22218.890080920686</v>
       </c>
       <c r="F23">
@@ -937,13 +934,13 @@
       <c r="B24" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="1">
         <v>35438.632976379384</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="1">
         <v>13180.06665324112</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="1">
         <v>22258.566323138264</v>
       </c>
       <c r="F24">
@@ -957,13 +954,13 @@
       <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="1">
         <v>35205.804590990723</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="1">
         <v>13561.188079865475</v>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="1">
         <v>21644.616511125249</v>
       </c>
       <c r="F25">
@@ -977,9 +974,9 @@
       <c r="B26" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
       <c r="F26">
         <v>7.7499999999999999E-2</v>
       </c>
@@ -991,9 +988,9 @@
       <c r="B27" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
       <c r="F27">
         <v>0.08</v>
       </c>
@@ -1005,9 +1002,9 @@
       <c r="B28" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="F28">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -1019,9 +1016,9 @@
       <c r="B29" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
       <c r="F29">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -1033,9 +1030,9 @@
       <c r="B30" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
       <c r="F30">
         <v>8.7499999999999994E-2</v>
       </c>
@@ -1047,9 +1044,9 @@
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31">
         <v>0.09</v>
       </c>
@@ -1061,9 +1058,9 @@
       <c r="B32" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
       <c r="F32">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1075,9 +1072,9 @@
       <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
       <c r="F33">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1089,9 +1086,9 @@
       <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
       <c r="F34">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1103,9 +1100,9 @@
       <c r="B35" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
       <c r="F35">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1117,9 +1114,9 @@
       <c r="B36" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
       <c r="F36">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1131,9 +1128,9 @@
       <c r="B37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
       <c r="F37">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1145,13 +1142,13 @@
       <c r="B38" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="1">
         <v>48702.885915624407</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="1">
         <v>16148.406349484414</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38" s="1">
         <v>32554.479566139991</v>
       </c>
       <c r="F38">
@@ -1165,13 +1162,13 @@
       <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="1">
         <v>49126.667453218142</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="1">
         <v>16443.325839939072</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="1">
         <v>32683.34161327907</v>
       </c>
       <c r="F39">
@@ -1185,13 +1182,13 @@
       <c r="B40" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="1">
         <v>52658.899769440875</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="1">
         <v>17195.569465043904</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E40" s="1">
         <v>35463.330304396972</v>
       </c>
       <c r="F40">
@@ -1205,13 +1202,13 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="1">
         <v>52171.507684440585</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="1">
         <v>17324.651314703486</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E41" s="1">
         <v>34846.856369737099</v>
       </c>
       <c r="F41">
@@ -1225,13 +1222,13 @@
       <c r="B42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="1">
         <v>53819.20806508878</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="1">
         <v>17943.698743044526</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="1">
         <v>35875.50932204425</v>
       </c>
       <c r="F42">
@@ -1245,13 +1242,13 @@
       <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="1">
         <v>54771.35983740518</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="1">
         <v>18257.877630002175</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="1">
         <v>36513.482207403009</v>
       </c>
       <c r="F43">
@@ -1265,13 +1262,13 @@
       <c r="B44" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="1">
         <v>57141.011161915405</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="1">
         <v>18629.571163170131</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="1">
         <v>38511.439998745278</v>
       </c>
       <c r="F44">
@@ -1285,13 +1282,13 @@
       <c r="B45" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="1">
         <v>58398.548847401966</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="1">
         <v>18862.976621251128</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="1">
         <v>39535.572226150834</v>
       </c>
       <c r="F45">
@@ -1305,13 +1302,13 @@
       <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="1">
         <v>59436.635763009799</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="1">
         <v>18742.834521805442</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="1">
         <v>40693.801241204361</v>
       </c>
       <c r="F46">
@@ -1325,13 +1322,13 @@
       <c r="B47" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="1">
         <v>61032.265569597606</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="1">
         <v>18969.628297434101</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="1">
         <v>42062.637272163505</v>
       </c>
       <c r="F47">
@@ -1345,13 +1342,13 @@
       <c r="B48" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="1">
         <v>61699.402000504619</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="1">
         <v>18548.792210220268</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="1">
         <v>43150.609790284347</v>
       </c>
       <c r="F48">
@@ -1365,13 +1362,13 @@
       <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="1">
         <v>62378.801356091462</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="1">
         <v>18806.491239585608</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="1">
         <v>43572.310116505854</v>
       </c>
       <c r="F49">
@@ -1385,13 +1382,13 @@
       <c r="B50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="1">
         <v>61331.798002306605</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="1">
         <v>21230.248937401037</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="1">
         <v>40101.549064905572</v>
       </c>
       <c r="F50">
@@ -1405,13 +1402,13 @@
       <c r="B51" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="1">
         <v>60674.786562767847</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="1">
         <v>20717.547625202518</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="1">
         <v>39957.238937565329</v>
       </c>
       <c r="F51">
@@ -1425,13 +1422,13 @@
       <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="1">
         <v>65608.881801703508</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="1">
         <v>20494.133882468475</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="1">
         <v>45114.747919235029</v>
       </c>
       <c r="F52">
@@ -1445,13 +1442,13 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="1">
         <v>64808.020317109447</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="1">
         <v>21507.966944576099</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="1">
         <v>43300.053372533352</v>
       </c>
       <c r="F53">
@@ -1465,13 +1462,13 @@
       <c r="B54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="1">
         <v>66398.538399304147</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="1">
         <v>22099.402830220311</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="1">
         <v>44299.135569083839</v>
       </c>
       <c r="F54">
@@ -1485,13 +1482,13 @@
       <c r="B55" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="1">
         <v>66731.439805295973</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="1">
         <v>21685.169748274333</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="1">
         <v>45046.27005702164</v>
       </c>
       <c r="F55">
@@ -1505,13 +1502,13 @@
       <c r="B56" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="1">
         <v>67152.326625880232</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="1">
         <v>21792.670334259845</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="1">
         <v>45359.656291620384</v>
       </c>
       <c r="F56">
@@ -1525,13 +1522,13 @@
       <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="1">
         <v>69223.898253083564</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="1">
         <v>22880.901615861691</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="1">
         <v>46342.996637221877</v>
       </c>
       <c r="F57">
@@ -1545,13 +1542,13 @@
       <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="1">
         <v>69391.287762713371</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="1">
         <v>22594.048218141899</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="1">
         <v>46797.239544571472</v>
       </c>
       <c r="F58">
@@ -1565,13 +1562,13 @@
       <c r="B59" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="1">
         <v>71003.94222564307</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="1">
         <v>22816.505932854223</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="1">
         <v>48187.436292788843</v>
       </c>
       <c r="F59">
@@ -1585,13 +1582,13 @@
       <c r="B60" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="1">
         <v>72013.463669955192</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="1">
         <v>22396.657885139241</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="1">
         <v>49616.805784815951</v>
       </c>
       <c r="F60">
@@ -1605,13 +1602,13 @@
       <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="1">
         <v>82593.712888649694</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="1">
         <v>23570.554673733128</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="1">
         <v>59023.158214916562</v>
       </c>
       <c r="F61">
@@ -1625,13 +1622,13 @@
       <c r="B62" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="1">
         <v>56511.270921737152</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="1">
         <v>13973.354689899539</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="1">
         <v>42537.916231837611</v>
       </c>
       <c r="F62">
@@ -1645,13 +1642,13 @@
       <c r="B63" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="1">
         <v>55643.0021232695</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="1">
         <v>13111.962749757122</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="1">
         <v>42531.03937351238</v>
       </c>
       <c r="F63">
@@ -1665,13 +1662,13 @@
       <c r="B64" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="1">
         <v>63497.384954216272</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="1">
         <v>12987.052039227068</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="1">
         <v>50510.332914989202</v>
       </c>
       <c r="F64">
@@ -1685,13 +1682,13 @@
       <c r="B65" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="1">
         <v>58537.33033389756</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="1">
         <v>13182.136468922454</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="1">
         <v>45355.19386497511</v>
       </c>
       <c r="F65">
@@ -1705,13 +1702,13 @@
       <c r="B66" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="1">
         <v>60571.264168359397</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="1">
         <v>13793.82312956908</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="1">
         <v>46777.441038790319</v>
       </c>
       <c r="F66">
@@ -1725,13 +1722,13 @@
       <c r="B67" t="s">
         <v>10</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="1">
         <v>61455.772903641722</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="1">
         <v>14246.441988221199</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="1">
         <v>47209.33091542052</v>
       </c>
       <c r="F67">
@@ -1745,13 +1742,13 @@
       <c r="B68" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="1">
         <v>66337.000703474798</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="1">
         <v>14766.058660192595</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="1">
         <v>51570.942043282201</v>
       </c>
       <c r="F68">
@@ -1765,13 +1762,13 @@
       <c r="B69" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="1">
         <v>66243.467107830395</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="1">
         <v>15048.606484654056</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="1">
         <v>51194.860623176341</v>
       </c>
       <c r="F69">
@@ -1785,13 +1782,13 @@
       <c r="B70" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="1">
         <v>65126.618559629576</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="1">
         <v>15210.191904310497</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="1">
         <v>49916.426655319083</v>
       </c>
       <c r="F70">
@@ -1805,13 +1802,13 @@
       <c r="B71" t="s">
         <v>14</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="1">
         <v>65809.724506028433</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="1">
         <v>15886.610114547811</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="1">
         <v>49923.114391480623</v>
       </c>
       <c r="F71">
@@ -1825,13 +1822,13 @@
       <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="1">
         <v>68812.047016905606</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="1">
         <v>16182.411607081516</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="1">
         <v>52629.635409824092</v>
       </c>
       <c r="F72">
@@ -1845,13 +1842,13 @@
       <c r="B73" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="1">
         <v>75367.344535418175</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="1">
         <v>16917.932998585416</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="1">
         <v>58449.411536832762</v>
       </c>
       <c r="F73">
@@ -1865,13 +1862,13 @@
       <c r="B74" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="1">
         <v>61650.117977190799</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="1">
         <v>12096.026018327382</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="1">
         <v>49554.091958863413</v>
       </c>
       <c r="F74">
@@ -1885,13 +1882,13 @@
       <c r="B75" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="1">
         <v>69276.649879479344</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="1">
         <v>11692.651175314717</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="1">
         <v>57583.998704164624</v>
       </c>
       <c r="F75">
@@ -1905,13 +1902,13 @@
       <c r="B76" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="1">
         <v>58076.795237136474</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="1">
         <v>12217.076010635725</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="1">
         <v>45859.719226500747</v>
       </c>
       <c r="F76">
@@ -1925,13 +1922,13 @@
       <c r="B77" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="1">
         <v>57135.374455117715</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="1">
         <v>12623.063472337913</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="1">
         <v>44512.310982779803</v>
       </c>
       <c r="F77">
@@ -1945,13 +1942,13 @@
       <c r="B78" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="1">
         <v>62480.582996670542</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="1">
         <v>13079.571061754499</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="1">
         <v>49401.011934916045</v>
       </c>
       <c r="F78">
@@ -1965,13 +1962,13 @@
       <c r="B79" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="1">
         <v>58484.775860981325</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="1">
         <v>13248.582537934368</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="1">
         <v>45236.193323046959</v>
       </c>
       <c r="F79">
@@ -1985,13 +1982,13 @@
       <c r="B80" t="s">
         <v>11</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="1">
         <v>59196.954618506999</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="1">
         <v>14099.122997477327</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E80" s="1">
         <v>45097.831621029676</v>
       </c>
       <c r="F80">
@@ -2005,13 +2002,13 @@
       <c r="B81" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="1">
         <v>60484.095847184246</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="1">
         <v>14561.340864337599</v>
       </c>
-      <c r="E81" s="4">
+      <c r="E81" s="1">
         <v>45922.754982846644</v>
       </c>
       <c r="F81">
@@ -2025,13 +2022,13 @@
       <c r="B82" t="s">
         <v>13</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="1">
         <v>61384.625898967228</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="1">
         <v>14758.735738501069</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E82" s="1">
         <v>46625.890160466159</v>
       </c>
       <c r="F82">
@@ -2045,13 +2042,13 @@
       <c r="B83" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="1">
         <v>62885.479902983796</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="1">
         <v>15579.885690979034</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="1">
         <v>47305.594212004762</v>
       </c>
       <c r="F83">
@@ -2065,13 +2062,13 @@
       <c r="B84" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="1">
         <v>63364.685394820444</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="1">
         <v>15498.626382091608</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="1">
         <v>47866.059012728838</v>
       </c>
       <c r="F84">
@@ -2085,13 +2082,13 @@
       <c r="B85" t="s">
         <v>16</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="1">
         <v>65927.099982887041</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="1">
         <v>15818.548852178592</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E85" s="1">
         <v>50108.551130708453</v>
       </c>
       <c r="F85">
@@ -2105,11 +2102,11 @@
       <c r="B86" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="1">
         <v>63725.229914205935</v>
       </c>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
       <c r="F86">
         <v>0.05</v>
       </c>
@@ -2121,11 +2118,11 @@
       <c r="B87" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="1">
         <v>65415.265259352978</v>
       </c>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
       <c r="F87">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2137,11 +2134,11 @@
       <c r="B88" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="1">
         <v>70368.514697734805</v>
       </c>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
       <c r="F88">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2153,11 +2150,11 @@
       <c r="B89" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="1">
         <v>69374.077526891735</v>
       </c>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
       <c r="F89">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2169,11 +2166,11 @@
       <c r="B90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="1">
         <v>70818.204072076362</v>
       </c>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
       <c r="F90">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2185,11 +2182,11 @@
       <c r="B91" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="1">
         <v>69888.728750856215</v>
       </c>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
       <c r="F91">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2201,11 +2198,11 @@
       <c r="B92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="1">
         <v>71207.490530704876</v>
       </c>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
       <c r="F92">
         <v>0.05</v>
       </c>
@@ -2217,11 +2214,11 @@
       <c r="B93" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="1">
         <v>72055.689724337324</v>
       </c>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
       <c r="F93">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2233,11 +2230,11 @@
       <c r="B94" t="s">
         <v>13</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="1">
         <v>72919.743963731147</v>
       </c>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
       <c r="F94">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2249,11 +2246,11 @@
       <c r="B95" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="1">
         <v>75234.579967030309</v>
       </c>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
       <c r="F95">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2265,11 +2262,11 @@
       <c r="B96" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="1">
         <v>75289.523450518114</v>
       </c>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
       <c r="F96">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -2281,11 +2278,11 @@
       <c r="B97" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="1">
         <v>79405.445935437034</v>
       </c>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
       <c r="F97">
         <v>4.2500000000000003E-2</v>
       </c>
@@ -2297,13 +2294,13 @@
       <c r="B98" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="1">
         <v>82128.103555092719</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="1">
         <v>20606.475300367747</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="1">
         <v>61521.628254724972</v>
       </c>
       <c r="F98">
@@ -2317,13 +2314,13 @@
       <c r="B99" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="1">
         <v>79724.534947023261</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="1">
         <v>19258.418337713854</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="1">
         <v>60466.116609309407</v>
       </c>
       <c r="F99">
@@ -2337,13 +2334,13 @@
       <c r="B100" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="1">
         <v>90636.787861366858</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="1">
         <v>20352.877932465653</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="1">
         <v>70283.909928901208</v>
       </c>
       <c r="F100">
@@ -2357,13 +2354,13 @@
       <c r="B101" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="1">
         <v>78875.848020440608</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101" s="1">
         <v>20908.511983224253</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="1">
         <v>57967.336037216359</v>
       </c>
       <c r="F101">
@@ -2377,13 +2374,13 @@
       <c r="B102" t="s">
         <v>9</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="1">
         <v>84316.561715054748</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="1">
         <v>21464.27168116441</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="1">
         <v>62852.290033890342</v>
       </c>
       <c r="F102">
@@ -2397,13 +2394,13 @@
       <c r="B103" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="1">
         <v>81591.628930762308</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="1">
         <v>20951.35566565302</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="1">
         <v>60640.273265109288</v>
       </c>
       <c r="F103">
@@ -2417,13 +2414,13 @@
       <c r="B104" t="s">
         <v>11</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="1">
         <v>82143.602919138953</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="1">
         <v>22312.822677317752</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="1">
         <v>59830.780241821201</v>
       </c>
       <c r="F104">
@@ -2437,13 +2434,13 @@
       <c r="B105" t="s">
         <v>12</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="1">
         <v>82372.110876232255</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="1">
         <v>22737.4821369575</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="1">
         <v>59634.628739274754</v>
       </c>
       <c r="F105">
@@ -2457,13 +2454,13 @@
       <c r="B106" t="s">
         <v>13</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="1">
         <v>83426.735220732327</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="1">
         <v>22464.958446245542</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="1">
         <v>60961.776774486789</v>
       </c>
       <c r="F106">
@@ -2477,13 +2474,13 @@
       <c r="B107" t="s">
         <v>14</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="1">
         <v>85756.241653853765</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107" s="1">
         <v>23124.219879069002</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="1">
         <v>62632.021774784764</v>
       </c>
       <c r="F107">
@@ -2497,13 +2494,13 @@
       <c r="B108" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="1">
         <v>86588.919003799107</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108" s="1">
         <v>23246.408345336917</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="1">
         <v>63342.51065846219</v>
       </c>
       <c r="F108">
@@ -2517,13 +2514,13 @@
       <c r="B109" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="1">
         <v>87389.131249876067</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109" s="1">
         <v>23444.684997952456</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="1">
         <v>63944.446251923611</v>
       </c>
       <c r="F109">
@@ -2537,13 +2534,13 @@
       <c r="B110" t="s">
         <v>5</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="1">
         <v>75661.628297290517</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110" s="1">
         <v>18254.639711403248</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="1">
         <v>57406.988585887273</v>
       </c>
       <c r="F110">
@@ -2557,13 +2554,13 @@
       <c r="B111" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="1">
         <v>74663.431089441758</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="1">
         <v>17305.906696277838</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="1">
         <v>57357.52439316392</v>
       </c>
       <c r="F111">
@@ -2577,1431 +2574,333 @@
       <c r="B112" t="s">
         <v>7</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="1">
         <v>77748.724676647937</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="1">
         <v>18360.549261275373</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="1">
         <v>59388.175415372563</v>
       </c>
       <c r="F112">
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2014</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="1">
         <v>81918.32014703007</v>
       </c>
-      <c r="D113" s="4">
+      <c r="D113" s="1">
         <v>18567.845016223509</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="1">
         <v>63350.475130806561</v>
       </c>
       <c r="F113">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2014</v>
       </c>
       <c r="B114" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="1">
         <v>79936.927433566729</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114" s="1">
         <v>19333.665587871212</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E114" s="1">
         <v>60603.261845695517</v>
       </c>
       <c r="F114">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2014</v>
       </c>
       <c r="B115" t="s">
         <v>10</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="1">
         <v>80986.672704775876</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115" s="1">
         <v>19118.779101501372</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E115" s="1">
         <v>61867.893603274504</v>
       </c>
       <c r="F115">
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2014</v>
       </c>
       <c r="B116" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="1">
         <v>82157.333083374542</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116" s="1">
         <v>20520.263036306296</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E116" s="1">
         <v>61637.07004706825</v>
       </c>
       <c r="F116">
         <v>0.04</v>
       </c>
     </row>
-    <row r="117" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2014</v>
       </c>
       <c r="B117" t="s">
         <v>12</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="1">
         <v>83188.122126282455</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117" s="1">
         <v>21627.188010330829</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E117" s="1">
         <v>61560.934115951626</v>
       </c>
       <c r="F117">
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2014</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="1">
         <v>85693.698487573871</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118" s="1">
         <v>22248.690953455389</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E118" s="1">
         <v>63445.007534118486</v>
       </c>
       <c r="F118">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2014</v>
       </c>
       <c r="B119" t="s">
         <v>14</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="1">
         <v>86354.455163383638</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="1">
         <v>24047.825938781352</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E119" s="1">
         <v>62306.629224602286</v>
       </c>
       <c r="F119">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2014</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="1">
         <v>92969.208679682037</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120" s="1">
         <v>24016.71427782948</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E120" s="1">
         <v>68952.494401852557</v>
       </c>
       <c r="F120">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>2014</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="1">
         <v>88718.739659897241</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121" s="1">
         <v>24262.250361025668</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E121" s="1">
         <v>64456.489298871573</v>
       </c>
       <c r="F121">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="I121" s="3">
-        <v>81159.76346175003</v>
-      </c>
-      <c r="J121" s="1">
-        <v>82713.761696080008</v>
-      </c>
-      <c r="K121" s="1">
-        <v>83948.018517999997</v>
-      </c>
-      <c r="L121" s="1">
-        <v>85120.711910999991</v>
-      </c>
-      <c r="M121" s="1">
-        <v>110922.72586500001</v>
-      </c>
-      <c r="N121" s="1">
-        <v>123371.21351311001</v>
-      </c>
-      <c r="O121" s="1">
-        <v>133093.31922899999</v>
-      </c>
-      <c r="P121" s="1">
-        <v>42994.594308889988</v>
-      </c>
-      <c r="Q121" s="1">
-        <v>104266.888657</v>
-      </c>
-      <c r="R121" s="1">
-        <v>104229.48909100002</v>
-      </c>
-      <c r="S121" s="1">
-        <v>103818.62562800001</v>
-      </c>
-      <c r="T121" s="1">
-        <v>99674.036412999994</v>
-      </c>
-      <c r="U121" s="1">
-        <v>113205.491565</v>
-      </c>
-      <c r="V121" s="1">
-        <v>108152.695545</v>
-      </c>
-      <c r="W121" s="1">
-        <v>110794.26754649998</v>
-      </c>
-      <c r="X121" s="1">
-        <v>107378.78004900001</v>
-      </c>
-      <c r="Y121" s="1">
-        <v>108204.43721600001</v>
-      </c>
-      <c r="Z121" s="1">
-        <v>116180.137313</v>
-      </c>
-      <c r="AA121" s="1">
-        <v>107296.76061000001</v>
-      </c>
-      <c r="AB121" s="1">
-        <v>107657.629265</v>
-      </c>
-      <c r="AC121" s="1">
-        <v>107398.25651100003</v>
-      </c>
-      <c r="AD121" s="1">
-        <v>105472.14983700002</v>
-      </c>
-      <c r="AE121" s="1">
-        <v>106806.00375700003</v>
-      </c>
-      <c r="AF121" s="1">
-        <v>107689.120717</v>
-      </c>
-      <c r="AG121" s="1">
-        <v>107967.03632900001</v>
-      </c>
-      <c r="AH121" s="1">
-        <v>109730.02317499999</v>
-      </c>
-      <c r="AI121" s="1">
-        <v>108210.17232199998</v>
-      </c>
-      <c r="AJ121" s="1">
-        <v>107807.518679</v>
-      </c>
-      <c r="AK121" s="1">
-        <v>112172.42679</v>
-      </c>
-      <c r="AL121" s="1">
-        <v>110712.26686999999</v>
-      </c>
-      <c r="AM121" s="1">
-        <v>111355.04839200001</v>
-      </c>
-      <c r="AN121" s="1">
-        <v>115517.33253599999</v>
-      </c>
-      <c r="AO121" s="1">
-        <v>113301.148403</v>
-      </c>
-      <c r="AP121" s="1">
-        <v>114975.85828299998</v>
-      </c>
-      <c r="AQ121" s="1">
-        <v>116217.76634099998</v>
-      </c>
-      <c r="AR121" s="1">
-        <v>118938.66359899998</v>
-      </c>
-      <c r="AS121" s="1">
-        <v>119807.181121</v>
-      </c>
-      <c r="AT121" s="1">
-        <v>121082.37949200001</v>
-      </c>
-      <c r="AU121" s="1">
-        <v>119778.41886799999</v>
-      </c>
-      <c r="AV121" s="1">
-        <v>118274.87509999999</v>
-      </c>
-      <c r="AW121" s="1">
-        <v>123174.88595600001</v>
-      </c>
-      <c r="AX121" s="1">
-        <v>122885.27039999999</v>
-      </c>
-      <c r="AY121" s="1">
-        <v>123832.58759799998</v>
-      </c>
-      <c r="AZ121" s="1">
-        <v>124330.89199999999</v>
-      </c>
-      <c r="BA121" s="1">
-        <v>120900.93006499999</v>
-      </c>
-      <c r="BB121" s="1">
-        <v>122543.73404000001</v>
-      </c>
-      <c r="BC121" s="1">
-        <v>121556.85282900001</v>
-      </c>
-      <c r="BD121" s="1">
-        <v>119896.29622600001</v>
-      </c>
-      <c r="BE121" s="1">
-        <v>120501.64427700001</v>
-      </c>
-      <c r="BF121" s="1">
-        <v>122841.510928</v>
-      </c>
-      <c r="BG121" s="1">
-        <v>118262.07046100001</v>
-      </c>
-      <c r="BH121" s="1">
-        <v>118590.68042000002</v>
-      </c>
-      <c r="BI121" s="1">
-        <v>120029.84432199999</v>
-      </c>
-      <c r="BJ121" s="1">
-        <v>118416.11503299999</v>
-      </c>
-      <c r="BK121" s="1">
-        <v>114355.97771899999</v>
-      </c>
-      <c r="BL121" s="1">
-        <v>113295.776115</v>
-      </c>
-      <c r="BM121" s="1">
-        <v>112406.50498199997</v>
-      </c>
-      <c r="BN121" s="1">
-        <v>109760.80439199998</v>
-      </c>
-      <c r="BO121" s="1">
-        <v>111985.722643</v>
-      </c>
-      <c r="BP121" s="1">
-        <v>110144.94806200001</v>
-      </c>
-      <c r="BQ121" s="1">
-        <v>108684.469468</v>
-      </c>
-      <c r="BR121" s="1">
-        <v>108842.308766</v>
-      </c>
-      <c r="BS121" s="1">
-        <v>106098.971676</v>
-      </c>
-      <c r="BT121" s="1">
-        <v>107679.28383600002</v>
-      </c>
-      <c r="BU121" s="1">
-        <v>108746.98419299998</v>
-      </c>
-      <c r="BV121" s="1">
-        <v>108108.65055199999</v>
-      </c>
-      <c r="BW121" s="1">
-        <v>107677.15315400001</v>
-      </c>
-      <c r="BX121" s="1">
-        <v>108629.09941799998</v>
-      </c>
-      <c r="BY121" s="1">
-        <v>108159.477396</v>
-      </c>
-      <c r="BZ121" s="1">
-        <v>107561.67380399999</v>
-      </c>
-      <c r="CA121" s="1">
-        <v>108647.325967</v>
-      </c>
-      <c r="CB121" s="1">
-        <v>109374.51839499998</v>
-      </c>
-      <c r="CC121" s="1">
-        <v>111597.73594300001</v>
-      </c>
-      <c r="CD121" s="1">
-        <v>112799.90611599997</v>
-      </c>
-      <c r="CE121" s="1">
-        <v>114506.42076700002</v>
-      </c>
-      <c r="CF121" s="1">
-        <v>115609.23216699999</v>
-      </c>
-      <c r="CG121" s="1">
-        <v>121564.61326299999</v>
-      </c>
-      <c r="CH121" s="1">
-        <v>124502.79102299998</v>
-      </c>
-      <c r="CI121" s="1">
-        <v>130241.22939000001</v>
-      </c>
-      <c r="CJ121" s="1">
-        <v>135158.87485299999</v>
-      </c>
-      <c r="CK121" s="1">
-        <v>139554.831014</v>
-      </c>
-      <c r="CL121" s="1">
-        <v>145863.28002099998</v>
-      </c>
-      <c r="CM121" s="1">
-        <v>149741.76946800001</v>
-      </c>
-      <c r="CN121" s="1">
-        <v>155148.75574899997</v>
-      </c>
-      <c r="CO121" s="1">
-        <v>162206.32550200002</v>
-      </c>
-      <c r="CP121" s="1">
-        <v>169493.75084299999</v>
-      </c>
-      <c r="CQ121" s="1">
-        <v>172606.542025</v>
-      </c>
-      <c r="CR121" s="1">
-        <v>172269.92544000002</v>
-      </c>
-      <c r="CS121" s="1">
-        <v>179317.37406100001</v>
-      </c>
-      <c r="CT121" s="1">
-        <v>177762.618694</v>
-      </c>
-      <c r="CU121" s="1">
-        <v>177999.60600800003</v>
-      </c>
-      <c r="CV121" s="1">
-        <v>174695.00902300002</v>
-      </c>
-      <c r="CW121" s="1">
-        <v>175504.81138500001</v>
-      </c>
-      <c r="CX121" s="1">
-        <v>179353.89728199999</v>
-      </c>
-      <c r="CY121" s="1">
-        <v>175450.95360900005</v>
-      </c>
-      <c r="CZ121" s="1">
-        <v>175533.81570000001</v>
-      </c>
-      <c r="DA121" s="1">
-        <v>173283.30884899999</v>
-      </c>
-      <c r="DB121" s="1">
-        <v>173179.29312100002</v>
-      </c>
-      <c r="DC121" s="1">
-        <v>172440.77686899999</v>
-      </c>
-      <c r="DD121" s="1">
-        <v>173896.45034700003</v>
-      </c>
-      <c r="DE121" s="1">
-        <v>175954.340314</v>
-      </c>
-      <c r="DF121" s="1">
-        <v>172354.70471099997</v>
-      </c>
-      <c r="DG121" s="1">
-        <v>167914.85365300003</v>
-      </c>
-      <c r="DH121" s="1">
-        <v>162885.57630000002</v>
-      </c>
-      <c r="DI121" s="1">
-        <v>162310.32736200001</v>
-      </c>
-      <c r="DJ121" s="1">
-        <v>160281.91200600003</v>
-      </c>
-      <c r="DK121" s="1">
-        <v>158754.50757300001</v>
-      </c>
-      <c r="DL121" s="1">
-        <v>159513.468322</v>
-      </c>
-      <c r="DM121" s="1">
-        <v>160796.890136</v>
-      </c>
-      <c r="DN121" s="1">
-        <v>161839.87166100001</v>
-      </c>
-      <c r="DO121" s="1">
-        <v>168546.15433799999</v>
-      </c>
-      <c r="DP121" s="1">
-        <v>161663.12574699998</v>
-      </c>
-      <c r="DQ121" s="1">
-        <v>171949.527856</v>
-      </c>
-      <c r="DR121" s="1">
-        <v>171680.15847100003</v>
-      </c>
-      <c r="DS121" s="1">
-        <v>175242.98612800002</v>
-      </c>
-      <c r="DT121" s="1">
-        <v>173756.45211400001</v>
-      </c>
-      <c r="DU121" s="1">
-        <v>177611.878669</v>
-      </c>
-      <c r="DV121" s="1">
-        <v>178549.12228600003</v>
-      </c>
-      <c r="DW121" s="1">
-        <v>179403.45495200003</v>
-      </c>
-      <c r="DX121" s="1">
-        <v>180527.38270400002</v>
-      </c>
-      <c r="DY121" s="1">
-        <v>182156.29664399999</v>
-      </c>
-      <c r="DZ121" s="1">
-        <v>190722.42398099997</v>
-      </c>
-    </row>
-    <row r="122" spans="1:130" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>2015</v>
       </c>
       <c r="B122" t="s">
         <v>5</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="1">
         <v>81104.713611400774</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122" s="1">
         <v>20618.745536820454</v>
       </c>
-      <c r="E122" s="4">
+      <c r="E122" s="1">
         <v>60485.96807458032</v>
       </c>
       <c r="F122">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="I122" s="3">
-        <v>25681.573973339997</v>
-      </c>
-      <c r="J122" s="1">
-        <v>27042.351269680003</v>
-      </c>
-      <c r="K122" s="1">
-        <v>28065.733887999995</v>
-      </c>
-      <c r="L122" s="1">
-        <v>29264.341014999998</v>
-      </c>
-      <c r="M122" s="1">
-        <v>32878.917699999991</v>
-      </c>
-      <c r="N122" s="1">
-        <v>34663.411336999998</v>
-      </c>
-      <c r="O122" s="1">
-        <v>37177.40969</v>
-      </c>
-      <c r="P122" s="1">
-        <v>38035.21396400001</v>
-      </c>
-      <c r="Q122" s="1">
-        <v>39970.546859000002</v>
-      </c>
-      <c r="R122" s="1">
-        <v>40804.789896000009</v>
-      </c>
-      <c r="S122" s="1">
-        <v>41085.689405999998</v>
-      </c>
-      <c r="T122" s="1">
-        <v>43624.468536</v>
-      </c>
-      <c r="U122" s="1">
-        <v>42559.011853000011</v>
-      </c>
-      <c r="V122" s="1">
-        <v>43146.437588000008</v>
-      </c>
-      <c r="W122" s="1">
-        <v>43652.097158390003</v>
-      </c>
-      <c r="X122" s="1">
-        <v>40277.140068000001</v>
-      </c>
-      <c r="Y122" s="1">
-        <v>41497.490763000002</v>
-      </c>
-      <c r="Z122" s="1">
-        <v>38578.836761999963</v>
-      </c>
-      <c r="AA122" s="1">
-        <v>38331.305578</v>
-      </c>
-      <c r="AB122" s="1">
-        <v>34075.932967000001</v>
-      </c>
-      <c r="AC122" s="1">
-        <v>33178.814491000005</v>
-      </c>
-      <c r="AD122" s="1">
-        <v>31816.9827</v>
-      </c>
-      <c r="AE122" s="1">
-        <v>31143.417265999997</v>
-      </c>
-      <c r="AF122" s="1">
-        <v>30892.543975999997</v>
-      </c>
-      <c r="AG122" s="1">
-        <v>30087.126321</v>
-      </c>
-      <c r="AH122" s="1">
-        <v>29543.848790999993</v>
-      </c>
-      <c r="AI122" s="1">
-        <v>30193.952205000005</v>
-      </c>
-      <c r="AJ122" s="1">
-        <v>28916.706235999998</v>
-      </c>
-      <c r="AK122" s="1">
-        <v>30325.053654000003</v>
-      </c>
-      <c r="AL122" s="1">
-        <v>29730.311683000004</v>
-      </c>
-      <c r="AM122" s="1">
-        <v>29908.714478999998</v>
-      </c>
-      <c r="AN122" s="1">
-        <v>30122.491545000001</v>
-      </c>
-      <c r="AO122" s="1">
-        <v>30707.629485999994</v>
-      </c>
-      <c r="AP122" s="1">
-        <v>31277.826622000004</v>
-      </c>
-      <c r="AQ122" s="1">
-        <v>31443.534651999998</v>
-      </c>
-      <c r="AR122" s="1">
-        <v>32309.224536999998</v>
-      </c>
-      <c r="AS122" s="1">
-        <v>31949.527981999996</v>
-      </c>
-      <c r="AT122" s="1">
-        <v>33133.251284999998</v>
-      </c>
-      <c r="AU122" s="1">
-        <v>33108.165737999996</v>
-      </c>
-      <c r="AV122" s="1">
-        <v>32508.165452000001</v>
-      </c>
-      <c r="AW122" s="1">
-        <v>35956.871963999998</v>
-      </c>
-      <c r="AX122" s="1">
-        <v>34823.922981000003</v>
-      </c>
-      <c r="AY122" s="1">
-        <v>36166.774099999995</v>
-      </c>
-      <c r="AZ122" s="1">
-        <v>36305.866878999994</v>
-      </c>
-      <c r="BA122" s="1">
-        <v>35675.594138</v>
-      </c>
-      <c r="BB122" s="1">
-        <v>35925.061013999999</v>
-      </c>
-      <c r="BC122" s="1">
-        <v>35148.023977000004</v>
-      </c>
-      <c r="BD122" s="1">
-        <v>35294.833906</v>
-      </c>
-      <c r="BE122" s="1">
-        <v>34496.899754000005</v>
-      </c>
-      <c r="BF122" s="1">
-        <v>35565.831188999982</v>
-      </c>
-      <c r="BG122" s="1">
-        <v>35895.134258000006</v>
-      </c>
-      <c r="BH122" s="1">
-        <v>34231.951384</v>
-      </c>
-      <c r="BI122" s="1">
-        <v>35881.747689999997</v>
-      </c>
-      <c r="BJ122" s="1">
-        <v>34531.262443</v>
-      </c>
-      <c r="BK122" s="1">
-        <v>32588.379384</v>
-      </c>
-      <c r="BL122" s="1">
-        <v>29363.061617000003</v>
-      </c>
-      <c r="BM122" s="1">
-        <v>28652.342639999992</v>
-      </c>
-      <c r="BN122" s="1">
-        <v>27160.901342999998</v>
-      </c>
-      <c r="BO122" s="1">
-        <v>25930.569550999997</v>
-      </c>
-      <c r="BP122" s="1">
-        <v>23877.360955</v>
-      </c>
-      <c r="BQ122" s="1">
-        <v>22786.922939000004</v>
-      </c>
-      <c r="BR122" s="1">
-        <v>21622.953148000001</v>
-      </c>
-      <c r="BS122" s="1">
-        <v>20561.676224999999</v>
-      </c>
-      <c r="BT122" s="1">
-        <v>19597.657601000003</v>
-      </c>
-      <c r="BU122" s="1">
-        <v>18656.268263999998</v>
-      </c>
-      <c r="BV122" s="1">
-        <v>18710.223129999998</v>
-      </c>
-      <c r="BW122" s="1">
-        <v>18229.080043999998</v>
-      </c>
-      <c r="BX122" s="1">
-        <v>18054.385029999998</v>
-      </c>
-      <c r="BY122" s="1">
-        <v>18815.057545000003</v>
-      </c>
-      <c r="BZ122" s="1">
-        <v>18923.119481999998</v>
-      </c>
-      <c r="CA122" s="1">
-        <v>19123.641464999997</v>
-      </c>
-      <c r="CB122" s="1">
-        <v>20595.290364</v>
-      </c>
-      <c r="CC122" s="1">
-        <v>22476.881816999998</v>
-      </c>
-      <c r="CD122" s="1">
-        <v>24230.764319000002</v>
-      </c>
-      <c r="CE122" s="1">
-        <v>26871.583562</v>
-      </c>
-      <c r="CF122" s="1">
-        <v>30885.441358</v>
-      </c>
-      <c r="CG122" s="1">
-        <v>35393.225683999997</v>
-      </c>
-      <c r="CH122" s="1">
-        <v>41959.420549000002</v>
-      </c>
-      <c r="CI122" s="1">
-        <v>52296.743537000002</v>
-      </c>
-      <c r="CJ122" s="1">
-        <v>56795.670142000003</v>
-      </c>
-      <c r="CK122" s="1">
-        <v>63340.391706000002</v>
-      </c>
-      <c r="CL122" s="1">
-        <v>73069.941114999994</v>
-      </c>
-      <c r="CM122" s="1">
-        <v>81962.483940000006</v>
-      </c>
-      <c r="CN122" s="1">
-        <v>90485.44526800001</v>
-      </c>
-      <c r="CO122" s="1">
-        <v>100496.64903000002</v>
-      </c>
-      <c r="CP122" s="1">
-        <v>110790.035829</v>
-      </c>
-      <c r="CQ122" s="1">
-        <v>121747.00737100003</v>
-      </c>
-      <c r="CR122" s="1">
-        <v>120619.95186999999</v>
-      </c>
-      <c r="CS122" s="1">
-        <v>127479.139069</v>
-      </c>
-      <c r="CT122" s="1">
-        <v>123845.117434</v>
-      </c>
-      <c r="CU122" s="1">
-        <v>125240.819994</v>
-      </c>
-      <c r="CV122" s="1">
-        <v>123406.250755</v>
-      </c>
-      <c r="CW122" s="1">
-        <v>125245.333701</v>
-      </c>
-      <c r="CX122" s="1">
-        <v>124546.41695899999</v>
-      </c>
-      <c r="CY122" s="1">
-        <v>124197.31178400002</v>
-      </c>
-      <c r="CZ122" s="1">
-        <v>120074.70995499998</v>
-      </c>
-      <c r="DA122" s="1">
-        <v>120903.91542200001</v>
-      </c>
-      <c r="DB122" s="1">
-        <v>119076.785443</v>
-      </c>
-      <c r="DC122" s="1">
-        <v>119354.420824</v>
-      </c>
-      <c r="DD122" s="1">
-        <v>116877.32098</v>
-      </c>
-      <c r="DE122" s="1">
-        <v>121611.212589</v>
-      </c>
-      <c r="DF122" s="1">
-        <v>109123.825512</v>
-      </c>
-      <c r="DG122" s="1">
-        <v>103635.200459</v>
-      </c>
-      <c r="DH122" s="1">
-        <v>99220.239413000003</v>
-      </c>
-      <c r="DI122" s="1">
-        <v>93603.785965000003</v>
-      </c>
-      <c r="DJ122" s="1">
-        <v>89349.247687999989</v>
-      </c>
-      <c r="DK122" s="1">
-        <v>87745.062993</v>
-      </c>
-      <c r="DL122" s="1">
-        <v>88094.420222999994</v>
-      </c>
-      <c r="DM122" s="1">
-        <v>85773.230616000001</v>
-      </c>
-      <c r="DN122" s="1">
-        <v>88432.947396000003</v>
-      </c>
-      <c r="DO122" s="1">
-        <v>89112.169872000013</v>
-      </c>
-      <c r="DP122" s="1">
-        <v>88987.694793000002</v>
-      </c>
-      <c r="DQ122" s="1">
-        <v>93954.423643999995</v>
-      </c>
-      <c r="DR122" s="1">
-        <v>93155.483485999997</v>
-      </c>
-      <c r="DS122" s="1">
-        <v>95300.280877000012</v>
-      </c>
-      <c r="DT122" s="1">
-        <v>93421.575291999994</v>
-      </c>
-      <c r="DU122" s="1">
-        <v>94327.325268999994</v>
-      </c>
-      <c r="DV122" s="1">
-        <v>95393.180770000006</v>
-      </c>
-      <c r="DW122" s="1">
-        <v>96400.383470000015</v>
-      </c>
-      <c r="DX122" s="1">
-        <v>98698.126669000005</v>
-      </c>
-      <c r="DY122" s="1">
-        <v>97830.733132000008</v>
-      </c>
-      <c r="DZ122" s="1">
-        <v>99910.595614999998</v>
-      </c>
-    </row>
-    <row r="123" spans="1:130" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>2015</v>
       </c>
       <c r="B123" t="s">
         <v>6</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="1">
         <v>79129.257307517881</v>
       </c>
-      <c r="D123" s="4">
+      <c r="D123" s="1">
         <v>19717.93212574756</v>
       </c>
-      <c r="E123" s="4">
+      <c r="E123" s="1">
         <v>59411.32518177032</v>
       </c>
       <c r="F123">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="I123" s="3">
-        <v>55478.189488410033</v>
-      </c>
-      <c r="J123" s="1">
-        <v>55671.410426400005</v>
-      </c>
-      <c r="K123" s="2">
-        <v>55882.284630000002</v>
-      </c>
-      <c r="L123" s="2">
-        <v>55856.370895999993</v>
-      </c>
-      <c r="M123" s="2">
-        <v>78043.808165000024</v>
-      </c>
-      <c r="N123" s="2">
-        <v>88707.80217611001</v>
-      </c>
-      <c r="O123" s="2">
-        <v>95915.909538999986</v>
-      </c>
-      <c r="P123" s="2">
-        <v>4959.380344889978</v>
-      </c>
-      <c r="Q123" s="2">
-        <v>64296.341798000001</v>
-      </c>
-      <c r="R123" s="2">
-        <v>63424.699195000016</v>
-      </c>
-      <c r="S123" s="2">
-        <v>62732.936222000011</v>
-      </c>
-      <c r="T123" s="2">
-        <v>56049.567876999994</v>
-      </c>
-      <c r="U123" s="2">
-        <v>70646.479712</v>
-      </c>
-      <c r="V123" s="1">
-        <v>65006.257956999987</v>
-      </c>
-      <c r="W123" s="2">
-        <v>67142.170388109982</v>
-      </c>
-      <c r="X123" s="2">
-        <v>67101.639981000015</v>
-      </c>
-      <c r="Y123" s="2">
-        <v>66706.946453000011</v>
-      </c>
-      <c r="Z123" s="2">
-        <v>77601.300551000037</v>
-      </c>
-      <c r="AA123" s="2">
-        <v>68965.455032000013</v>
-      </c>
-      <c r="AB123" s="2">
-        <v>73581.696297999995</v>
-      </c>
-      <c r="AC123" s="2">
-        <v>74219.442020000017</v>
-      </c>
-      <c r="AD123" s="2">
-        <v>73655.167137000011</v>
-      </c>
-      <c r="AE123" s="2">
-        <v>75662.586491000024</v>
-      </c>
-      <c r="AF123" s="2">
-        <v>76796.576740999997</v>
-      </c>
-      <c r="AG123" s="2">
-        <v>77879.910008000006</v>
-      </c>
-      <c r="AH123" s="1">
-        <v>80186.174383999998</v>
-      </c>
-      <c r="AI123" s="2">
-        <v>78016.220116999975</v>
-      </c>
-      <c r="AJ123" s="2">
-        <v>78890.812443000003</v>
-      </c>
-      <c r="AK123" s="2">
-        <v>81847.373135999995</v>
-      </c>
-      <c r="AL123" s="2">
-        <v>80981.955186999985</v>
-      </c>
-      <c r="AM123" s="2">
-        <v>81446.333913000009</v>
-      </c>
-      <c r="AN123" s="2">
-        <v>85394.84099099999</v>
-      </c>
-      <c r="AO123" s="2">
-        <v>82593.518917000009</v>
-      </c>
-      <c r="AP123" s="2">
-        <v>83698.031660999972</v>
-      </c>
-      <c r="AQ123" s="2">
-        <v>84774.231688999978</v>
-      </c>
-      <c r="AR123" s="2">
-        <v>86629.439061999976</v>
-      </c>
-      <c r="AS123" s="2">
-        <v>87857.653139000002</v>
-      </c>
-      <c r="AT123" s="1">
-        <v>87949.128207000002</v>
-      </c>
-      <c r="AU123" s="2">
-        <v>86670.253129999997</v>
-      </c>
-      <c r="AV123" s="2">
-        <v>85766.709647999989</v>
-      </c>
-      <c r="AW123" s="2">
-        <v>87218.013992000022</v>
-      </c>
-      <c r="AX123" s="2">
-        <v>88061.347418999998</v>
-      </c>
-      <c r="AY123" s="2">
-        <v>87665.813497999989</v>
-      </c>
-      <c r="AZ123" s="2">
-        <v>88025.025120999999</v>
-      </c>
-      <c r="BA123" s="2">
-        <v>85225.335926999993</v>
-      </c>
-      <c r="BB123" s="2">
-        <v>86618.673026000004</v>
-      </c>
-      <c r="BC123" s="2">
-        <v>86408.828852000006</v>
-      </c>
-      <c r="BD123" s="2">
-        <v>84601.462320000006</v>
-      </c>
-      <c r="BE123" s="2">
-        <v>86004.744523000001</v>
-      </c>
-      <c r="BF123" s="1">
-        <v>87275.679739000014</v>
-      </c>
-      <c r="BG123" s="2">
-        <v>82366.936203000005</v>
-      </c>
-      <c r="BH123" s="2">
-        <v>84358.729036000019</v>
-      </c>
-      <c r="BI123" s="2">
-        <v>84148.096632000001</v>
-      </c>
-      <c r="BJ123" s="2">
-        <v>83884.852589999995</v>
-      </c>
-      <c r="BK123" s="2">
-        <v>81767.598334999988</v>
-      </c>
-      <c r="BL123" s="2">
-        <v>83932.714498000001</v>
-      </c>
-      <c r="BM123" s="2">
-        <v>83754.162341999981</v>
-      </c>
-      <c r="BN123" s="2">
-        <v>82599.903048999986</v>
-      </c>
-      <c r="BO123" s="2">
-        <v>86055.153092000008</v>
-      </c>
-      <c r="BP123" s="2">
-        <v>86267.587107000014</v>
-      </c>
-      <c r="BQ123" s="2">
-        <v>85897.546528999985</v>
-      </c>
-      <c r="BR123" s="1">
-        <v>87219.355618000001</v>
-      </c>
-      <c r="BS123" s="2">
-        <v>85537.295450999998</v>
-      </c>
-      <c r="BT123" s="2">
-        <v>88081.626235000018</v>
-      </c>
-      <c r="BU123" s="2">
-        <v>90090.715928999984</v>
-      </c>
-      <c r="BV123" s="2">
-        <v>89398.427421999993</v>
-      </c>
-      <c r="BW123" s="2">
-        <v>89448.073110000012</v>
-      </c>
-      <c r="BX123" s="2">
-        <v>90574.714387999993</v>
-      </c>
-      <c r="BY123" s="2">
-        <v>89344.419850999999</v>
-      </c>
-      <c r="BZ123" s="2">
-        <v>88638.554321999996</v>
-      </c>
-      <c r="CA123" s="2">
-        <v>89523.684502000004</v>
-      </c>
-      <c r="CB123" s="2">
-        <v>88779.228030999977</v>
-      </c>
-      <c r="CC123" s="2">
-        <v>89120.854126000006</v>
-      </c>
-      <c r="CD123" s="1">
-        <v>88569.14179699996</v>
-      </c>
-      <c r="CE123" s="2">
-        <v>87634.837205000018</v>
-      </c>
-      <c r="CF123" s="2">
-        <v>84723.790808999998</v>
-      </c>
-      <c r="CG123" s="2">
-        <v>86171.387579000002</v>
-      </c>
-      <c r="CH123" s="2">
-        <v>82543.370473999981</v>
-      </c>
-      <c r="CI123" s="2">
-        <v>77944.485853000006</v>
-      </c>
-      <c r="CJ123" s="2">
-        <v>78363.204710999984</v>
-      </c>
-      <c r="CK123" s="2">
-        <v>76214.439308000001</v>
-      </c>
-      <c r="CL123" s="2">
-        <v>72793.33890599999</v>
-      </c>
-      <c r="CM123" s="2">
-        <v>67779.285528000008</v>
-      </c>
-      <c r="CN123" s="2">
-        <v>64663.310480999964</v>
-      </c>
-      <c r="CO123" s="2">
-        <v>61709.676472000006</v>
-      </c>
-      <c r="CP123" s="1">
-        <v>58703.715013999987</v>
-      </c>
-      <c r="CQ123" s="2">
-        <v>50859.534653999974</v>
-      </c>
-      <c r="CR123" s="2">
-        <v>51649.973570000031</v>
-      </c>
-      <c r="CS123" s="2">
-        <v>51838.234992000012</v>
-      </c>
-      <c r="CT123" s="2">
-        <v>53917.501260000005</v>
-      </c>
-      <c r="CU123" s="2">
-        <v>52758.786014000027</v>
-      </c>
-      <c r="CV123" s="2">
-        <v>51288.75826800002</v>
-      </c>
-      <c r="CW123" s="2">
-        <v>50259.477684000012</v>
-      </c>
-      <c r="CX123" s="2">
-        <v>54807.480322999996</v>
-      </c>
-      <c r="CY123" s="2">
-        <v>51253.641825000028</v>
-      </c>
-      <c r="CZ123" s="2">
-        <v>55459.105745000023</v>
-      </c>
-      <c r="DA123" s="2">
-        <v>52379.393426999988</v>
-      </c>
-      <c r="DB123" s="1">
-        <v>54102.507678000024</v>
-      </c>
-      <c r="DC123" s="2">
-        <v>53086.356044999993</v>
-      </c>
-      <c r="DD123" s="2">
-        <v>57019.12936700003</v>
-      </c>
-      <c r="DE123" s="2">
-        <v>54343.127724999998</v>
-      </c>
-      <c r="DF123" s="2">
-        <v>63230.879198999974</v>
-      </c>
-      <c r="DG123" s="2">
-        <v>64279.653194000028</v>
-      </c>
-      <c r="DH123" s="2">
-        <v>63665.336887000012</v>
-      </c>
-      <c r="DI123" s="2">
-        <v>68706.541397000008</v>
-      </c>
-      <c r="DJ123" s="2">
-        <v>70932.664318000039</v>
-      </c>
-      <c r="DK123" s="2">
-        <v>71009.44458000001</v>
-      </c>
-      <c r="DL123" s="2">
-        <v>71419.048099000007</v>
-      </c>
-      <c r="DM123" s="2">
-        <v>75023.659520000001</v>
-      </c>
-      <c r="DN123" s="1">
-        <v>73406.924265000009</v>
-      </c>
-      <c r="DO123" s="2">
-        <v>79433.98446599998</v>
-      </c>
-      <c r="DP123" s="2">
-        <v>72675.430953999981</v>
-      </c>
-      <c r="DQ123" s="2">
-        <v>77995.104212000006</v>
-      </c>
-      <c r="DR123" s="2">
-        <v>78524.674985000034</v>
-      </c>
-      <c r="DS123" s="2">
-        <v>79942.705251000007</v>
-      </c>
-      <c r="DT123" s="2">
-        <v>80334.87682200002</v>
-      </c>
-      <c r="DU123" s="2">
-        <v>83284.553400000004</v>
-      </c>
-      <c r="DV123" s="2">
-        <v>83155.941516000021</v>
-      </c>
-      <c r="DW123" s="2">
-        <v>83003.071482000014</v>
-      </c>
-      <c r="DX123" s="2">
-        <v>81829.256035000013</v>
-      </c>
-      <c r="DY123" s="2">
-        <v>84325.563511999979</v>
-      </c>
-      <c r="DZ123" s="1">
-        <v>90811.828365999972</v>
-      </c>
-    </row>
-    <row r="124" spans="1:130" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>2015</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="1">
         <v>83137.781314644322</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124" s="1">
         <v>21010.605429227719</v>
       </c>
-      <c r="E124" s="4">
+      <c r="E124" s="1">
         <v>62127.175885416604</v>
       </c>
       <c r="F124">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>2015</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="1">
         <v>85086.874362168484</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125" s="1">
         <v>21015.65532599821</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E125" s="1">
         <v>64071.219036170274</v>
       </c>
       <c r="F125">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>2015</v>
       </c>
       <c r="B126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126" s="1">
         <v>85512.985221940908</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126" s="1">
         <v>22092.662782568077</v>
       </c>
-      <c r="E126" s="4">
+      <c r="E126" s="1">
         <v>63420.322439372831</v>
       </c>
       <c r="F126">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>2015</v>
       </c>
       <c r="B127" t="s">
         <v>10</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127" s="1">
         <v>85712.329610397734</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127" s="1">
         <v>21231.279706975824</v>
       </c>
-      <c r="E127" s="4">
+      <c r="E127" s="1">
         <v>64481.04990342191</v>
       </c>
       <c r="F127">
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:130" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>2015</v>
       </c>
       <c r="B128" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="1">
         <v>87644.021569282559</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128" s="1">
         <v>21767.603138499264</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E128" s="1">
         <v>65876.418430783291</v>
       </c>
       <c r="F128">
@@ -4015,13 +2914,13 @@
       <c r="B129" t="s">
         <v>12</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="1">
         <v>88634.974852048166</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129" s="1">
         <v>22295.395717440166</v>
       </c>
-      <c r="E129" s="4">
+      <c r="E129" s="1">
         <v>66339.579134608008</v>
       </c>
       <c r="F129">
@@ -4035,13 +2934,13 @@
       <c r="B130" t="s">
         <v>13</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="1">
         <v>89190.834807761785</v>
       </c>
-      <c r="D130" s="4">
+      <c r="D130" s="1">
         <v>22240.169715475982</v>
       </c>
-      <c r="E130" s="4">
+      <c r="E130" s="1">
         <v>66950.66509228581</v>
       </c>
       <c r="F130">
@@ -4055,13 +2954,13 @@
       <c r="B131" t="s">
         <v>14</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131" s="1">
         <v>93530.233742057608</v>
       </c>
-      <c r="D131" s="4">
+      <c r="D131" s="1">
         <v>23002.923832440949</v>
       </c>
-      <c r="E131" s="4">
+      <c r="E131" s="1">
         <v>70527.309909616655</v>
       </c>
       <c r="F131">
@@ -4075,13 +2974,13 @@
       <c r="B132" t="s">
         <v>15</v>
       </c>
-      <c r="C132" s="5">
+      <c r="C132" s="2">
         <v>81159.76346175003</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="2">
         <v>25681.573973339997</v>
       </c>
-      <c r="E132" s="5">
+      <c r="E132" s="2">
         <v>55478.189488410033</v>
       </c>
       <c r="F132">
@@ -4095,13 +2994,13 @@
       <c r="B133" t="s">
         <v>16</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="3">
         <v>82713.761696080008</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="3">
         <v>27042.351269680003</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E133" s="3">
         <v>55671.410426400005</v>
       </c>
       <c r="F133">
@@ -4115,13 +3014,13 @@
       <c r="B134" t="s">
         <v>5</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="3">
         <v>83948.018517999997</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="3">
         <v>28065.733887999995</v>
       </c>
-      <c r="E134" s="7">
+      <c r="E134" s="4">
         <v>55882.284630000002</v>
       </c>
       <c r="F134">
@@ -4135,13 +3034,13 @@
       <c r="B135" t="s">
         <v>6</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="3">
         <v>85120.711910999991</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="3">
         <v>29264.341014999998</v>
       </c>
-      <c r="E135" s="7">
+      <c r="E135" s="4">
         <v>55856.370895999993</v>
       </c>
       <c r="F135">
@@ -4155,13 +3054,13 @@
       <c r="B136" t="s">
         <v>7</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="3">
         <v>110922.72586500001</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="3">
         <v>32878.917699999991</v>
       </c>
-      <c r="E136" s="7">
+      <c r="E136" s="4">
         <v>78043.808165000024</v>
       </c>
       <c r="F136">
@@ -4175,13 +3074,13 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="3">
         <v>123371.21351311001</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="3">
         <v>34663.411336999998</v>
       </c>
-      <c r="E137" s="7">
+      <c r="E137" s="4">
         <v>88707.80217611001</v>
       </c>
       <c r="F137">
@@ -4195,13 +3094,13 @@
       <c r="B138" t="s">
         <v>9</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="3">
         <v>133093.31922899999</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="3">
         <v>37177.40969</v>
       </c>
-      <c r="E138" s="7">
+      <c r="E138" s="4">
         <v>95915.909538999986</v>
       </c>
       <c r="F138">
@@ -4215,13 +3114,13 @@
       <c r="B139" t="s">
         <v>10</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="3">
         <v>42994.594308889988</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="3">
         <v>38035.21396400001</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E139" s="4">
         <v>4959.380344889978</v>
       </c>
       <c r="F139">
@@ -4235,13 +3134,13 @@
       <c r="B140" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="3">
         <v>104266.888657</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="3">
         <v>39970.546859000002</v>
       </c>
-      <c r="E140" s="7">
+      <c r="E140" s="4">
         <v>64296.341798000001</v>
       </c>
       <c r="F140">
@@ -4255,13 +3154,13 @@
       <c r="B141" t="s">
         <v>12</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="3">
         <v>104229.48909100002</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="3">
         <v>40804.789896000009</v>
       </c>
-      <c r="E141" s="7">
+      <c r="E141" s="4">
         <v>63424.699195000016</v>
       </c>
       <c r="F141">
@@ -4275,13 +3174,13 @@
       <c r="B142" t="s">
         <v>13</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="3">
         <v>103818.62562800001</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="3">
         <v>41085.689405999998</v>
       </c>
-      <c r="E142" s="7">
+      <c r="E142" s="4">
         <v>62732.936222000011</v>
       </c>
       <c r="F142">
@@ -4295,13 +3194,13 @@
       <c r="B143" t="s">
         <v>14</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="3">
         <v>99674.036412999994</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="3">
         <v>43624.468536</v>
       </c>
-      <c r="E143" s="7">
+      <c r="E143" s="4">
         <v>56049.567876999994</v>
       </c>
       <c r="F143">
@@ -4315,13 +3214,13 @@
       <c r="B144" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="3">
         <v>113205.491565</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="3">
         <v>42559.011853000011</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E144" s="4">
         <v>70646.479712</v>
       </c>
       <c r="F144">
@@ -4335,13 +3234,13 @@
       <c r="B145" t="s">
         <v>16</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="3">
         <v>108152.695545</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="3">
         <v>43146.437588000008</v>
       </c>
-      <c r="E145" s="6">
+      <c r="E145" s="3">
         <v>65006.257956999987</v>
       </c>
       <c r="F145">
@@ -4355,13 +3254,13 @@
       <c r="B146" t="s">
         <v>5</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="3">
         <v>110794.26754649998</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="3">
         <v>43652.097158390003</v>
       </c>
-      <c r="E146" s="7">
+      <c r="E146" s="4">
         <v>67142.170388109982</v>
       </c>
       <c r="F146">
@@ -4375,13 +3274,13 @@
       <c r="B147" t="s">
         <v>6</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="3">
         <v>107378.78004900001</v>
       </c>
-      <c r="D147" s="6">
+      <c r="D147" s="3">
         <v>40277.140068000001</v>
       </c>
-      <c r="E147" s="7">
+      <c r="E147" s="4">
         <v>67101.639981000015</v>
       </c>
       <c r="F147">
@@ -4395,13 +3294,13 @@
       <c r="B148" t="s">
         <v>7</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="3">
         <v>108204.43721600001</v>
       </c>
-      <c r="D148" s="6">
+      <c r="D148" s="3">
         <v>41497.490763000002</v>
       </c>
-      <c r="E148" s="7">
+      <c r="E148" s="4">
         <v>66706.946453000011</v>
       </c>
       <c r="F148">
@@ -4415,13 +3314,13 @@
       <c r="B149" t="s">
         <v>8</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="3">
         <v>116180.137313</v>
       </c>
-      <c r="D149" s="6">
+      <c r="D149" s="3">
         <v>38578.836761999963</v>
       </c>
-      <c r="E149" s="7">
+      <c r="E149" s="4">
         <v>77601.300551000037</v>
       </c>
       <c r="F149">
@@ -4435,13 +3334,13 @@
       <c r="B150" t="s">
         <v>9</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="3">
         <v>107296.76061000001</v>
       </c>
-      <c r="D150" s="6">
+      <c r="D150" s="3">
         <v>38331.305578</v>
       </c>
-      <c r="E150" s="7">
+      <c r="E150" s="4">
         <v>68965.455032000013</v>
       </c>
       <c r="F150">
@@ -4455,13 +3354,13 @@
       <c r="B151" t="s">
         <v>10</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="3">
         <v>107657.629265</v>
       </c>
-      <c r="D151" s="6">
+      <c r="D151" s="3">
         <v>34075.932967000001</v>
       </c>
-      <c r="E151" s="7">
+      <c r="E151" s="4">
         <v>73581.696297999995</v>
       </c>
       <c r="F151">
@@ -4475,13 +3374,13 @@
       <c r="B152" t="s">
         <v>11</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="3">
         <v>107398.25651100003</v>
       </c>
-      <c r="D152" s="6">
+      <c r="D152" s="3">
         <v>33178.814491000005</v>
       </c>
-      <c r="E152" s="7">
+      <c r="E152" s="4">
         <v>74219.442020000017</v>
       </c>
       <c r="F152">
@@ -4495,13 +3394,13 @@
       <c r="B153" t="s">
         <v>12</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="3">
         <v>105472.14983700002</v>
       </c>
-      <c r="D153" s="6">
+      <c r="D153" s="3">
         <v>31816.9827</v>
       </c>
-      <c r="E153" s="7">
+      <c r="E153" s="4">
         <v>73655.167137000011</v>
       </c>
       <c r="F153">
@@ -4515,13 +3414,13 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="3">
         <v>106806.00375700003</v>
       </c>
-      <c r="D154" s="6">
+      <c r="D154" s="3">
         <v>31143.417265999997</v>
       </c>
-      <c r="E154" s="7">
+      <c r="E154" s="4">
         <v>75662.586491000024</v>
       </c>
       <c r="F154">
@@ -4535,13 +3434,13 @@
       <c r="B155" t="s">
         <v>14</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="3">
         <v>107689.120717</v>
       </c>
-      <c r="D155" s="6">
+      <c r="D155" s="3">
         <v>30892.543975999997</v>
       </c>
-      <c r="E155" s="7">
+      <c r="E155" s="4">
         <v>76796.576740999997</v>
       </c>
       <c r="F155">
@@ -4555,13 +3454,13 @@
       <c r="B156" t="s">
         <v>15</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="3">
         <v>107967.03632900001</v>
       </c>
-      <c r="D156" s="6">
+      <c r="D156" s="3">
         <v>30087.126321</v>
       </c>
-      <c r="E156" s="7">
+      <c r="E156" s="4">
         <v>77879.910008000006</v>
       </c>
       <c r="F156">
@@ -4575,13 +3474,13 @@
       <c r="B157" t="s">
         <v>16</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="3">
         <v>109730.02317499999</v>
       </c>
-      <c r="D157" s="6">
+      <c r="D157" s="3">
         <v>29543.848790999993</v>
       </c>
-      <c r="E157" s="6">
+      <c r="E157" s="3">
         <v>80186.174383999998</v>
       </c>
       <c r="F157">
@@ -4595,13 +3494,13 @@
       <c r="B158" t="s">
         <v>5</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="3">
         <v>108210.17232199998</v>
       </c>
-      <c r="D158" s="6">
+      <c r="D158" s="3">
         <v>30193.952205000005</v>
       </c>
-      <c r="E158" s="7">
+      <c r="E158" s="4">
         <v>78016.220116999975</v>
       </c>
       <c r="F158">
@@ -4615,13 +3514,13 @@
       <c r="B159" t="s">
         <v>6</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="3">
         <v>107807.518679</v>
       </c>
-      <c r="D159" s="6">
+      <c r="D159" s="3">
         <v>28916.706235999998</v>
       </c>
-      <c r="E159" s="7">
+      <c r="E159" s="4">
         <v>78890.812443000003</v>
       </c>
       <c r="F159">
@@ -4635,13 +3534,13 @@
       <c r="B160" t="s">
         <v>7</v>
       </c>
-      <c r="C160" s="6">
+      <c r="C160" s="3">
         <v>112172.42679</v>
       </c>
-      <c r="D160" s="6">
+      <c r="D160" s="3">
         <v>30325.053654000003</v>
       </c>
-      <c r="E160" s="7">
+      <c r="E160" s="4">
         <v>81847.373135999995</v>
       </c>
       <c r="F160">
@@ -4655,13 +3554,13 @@
       <c r="B161" t="s">
         <v>8</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="3">
         <v>110712.26686999999</v>
       </c>
-      <c r="D161" s="6">
+      <c r="D161" s="3">
         <v>29730.311683000004</v>
       </c>
-      <c r="E161" s="7">
+      <c r="E161" s="4">
         <v>80981.955186999985</v>
       </c>
       <c r="F161">
@@ -4675,13 +3574,13 @@
       <c r="B162" t="s">
         <v>9</v>
       </c>
-      <c r="C162" s="6">
+      <c r="C162" s="3">
         <v>111355.04839200001</v>
       </c>
-      <c r="D162" s="6">
+      <c r="D162" s="3">
         <v>29908.714478999998</v>
       </c>
-      <c r="E162" s="7">
+      <c r="E162" s="4">
         <v>81446.333913000009</v>
       </c>
       <c r="F162">
@@ -4695,13 +3594,13 @@
       <c r="B163" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="6">
+      <c r="C163" s="3">
         <v>115517.33253599999</v>
       </c>
-      <c r="D163" s="6">
+      <c r="D163" s="3">
         <v>30122.491545000001</v>
       </c>
-      <c r="E163" s="7">
+      <c r="E163" s="4">
         <v>85394.84099099999</v>
       </c>
       <c r="F163">
@@ -4715,13 +3614,13 @@
       <c r="B164" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="6">
+      <c r="C164" s="3">
         <v>113301.148403</v>
       </c>
-      <c r="D164" s="6">
+      <c r="D164" s="3">
         <v>30707.629485999994</v>
       </c>
-      <c r="E164" s="7">
+      <c r="E164" s="4">
         <v>82593.518917000009</v>
       </c>
       <c r="F164">
@@ -4735,13 +3634,13 @@
       <c r="B165" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="6">
+      <c r="C165" s="3">
         <v>114975.85828299998</v>
       </c>
-      <c r="D165" s="6">
+      <c r="D165" s="3">
         <v>31277.826622000004</v>
       </c>
-      <c r="E165" s="7">
+      <c r="E165" s="4">
         <v>83698.031660999972</v>
       </c>
       <c r="F165">
@@ -4755,13 +3654,13 @@
       <c r="B166" t="s">
         <v>13</v>
       </c>
-      <c r="C166" s="6">
+      <c r="C166" s="3">
         <v>116217.76634099998</v>
       </c>
-      <c r="D166" s="6">
+      <c r="D166" s="3">
         <v>31443.534651999998</v>
       </c>
-      <c r="E166" s="7">
+      <c r="E166" s="4">
         <v>84774.231688999978</v>
       </c>
       <c r="F166">
@@ -4775,13 +3674,13 @@
       <c r="B167" t="s">
         <v>14</v>
       </c>
-      <c r="C167" s="6">
+      <c r="C167" s="3">
         <v>118938.66359899998</v>
       </c>
-      <c r="D167" s="6">
+      <c r="D167" s="3">
         <v>32309.224536999998</v>
       </c>
-      <c r="E167" s="7">
+      <c r="E167" s="4">
         <v>86629.439061999976</v>
       </c>
       <c r="F167">
@@ -4795,13 +3694,13 @@
       <c r="B168" t="s">
         <v>15</v>
       </c>
-      <c r="C168" s="6">
+      <c r="C168" s="3">
         <v>119807.181121</v>
       </c>
-      <c r="D168" s="6">
+      <c r="D168" s="3">
         <v>31949.527981999996</v>
       </c>
-      <c r="E168" s="7">
+      <c r="E168" s="4">
         <v>87857.653139000002</v>
       </c>
       <c r="F168">
@@ -4815,13 +3714,13 @@
       <c r="B169" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="6">
+      <c r="C169" s="3">
         <v>121082.37949200001</v>
       </c>
-      <c r="D169" s="6">
+      <c r="D169" s="3">
         <v>33133.251284999998</v>
       </c>
-      <c r="E169" s="6">
+      <c r="E169" s="3">
         <v>87949.128207000002</v>
       </c>
       <c r="F169">
@@ -4835,13 +3734,13 @@
       <c r="B170" t="s">
         <v>5</v>
       </c>
-      <c r="C170" s="6">
+      <c r="C170" s="3">
         <v>119778.41886799999</v>
       </c>
-      <c r="D170" s="6">
+      <c r="D170" s="3">
         <v>33108.165737999996</v>
       </c>
-      <c r="E170" s="7">
+      <c r="E170" s="4">
         <v>86670.253129999997</v>
       </c>
       <c r="F170">
@@ -4855,13 +3754,13 @@
       <c r="B171" t="s">
         <v>6</v>
       </c>
-      <c r="C171" s="6">
+      <c r="C171" s="3">
         <v>118274.87509999999</v>
       </c>
-      <c r="D171" s="6">
+      <c r="D171" s="3">
         <v>32508.165452000001</v>
       </c>
-      <c r="E171" s="7">
+      <c r="E171" s="4">
         <v>85766.709647999989</v>
       </c>
       <c r="F171">
@@ -4875,13 +3774,13 @@
       <c r="B172" t="s">
         <v>7</v>
       </c>
-      <c r="C172" s="6">
+      <c r="C172" s="3">
         <v>123174.88595600001</v>
       </c>
-      <c r="D172" s="6">
+      <c r="D172" s="3">
         <v>35956.871963999998</v>
       </c>
-      <c r="E172" s="7">
+      <c r="E172" s="4">
         <v>87218.013992000022</v>
       </c>
       <c r="F172">
@@ -4895,13 +3794,13 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" s="6">
+      <c r="C173" s="3">
         <v>122885.27039999999</v>
       </c>
-      <c r="D173" s="6">
+      <c r="D173" s="3">
         <v>34823.922981000003</v>
       </c>
-      <c r="E173" s="7">
+      <c r="E173" s="4">
         <v>88061.347418999998</v>
       </c>
       <c r="F173">
@@ -4915,13 +3814,13 @@
       <c r="B174" t="s">
         <v>9</v>
       </c>
-      <c r="C174" s="6">
+      <c r="C174" s="3">
         <v>123832.58759799998</v>
       </c>
-      <c r="D174" s="6">
+      <c r="D174" s="3">
         <v>36166.774099999995</v>
       </c>
-      <c r="E174" s="7">
+      <c r="E174" s="4">
         <v>87665.813497999989</v>
       </c>
       <c r="F174">
@@ -4935,13 +3834,13 @@
       <c r="B175" t="s">
         <v>10</v>
       </c>
-      <c r="C175" s="6">
+      <c r="C175" s="3">
         <v>124330.89199999999</v>
       </c>
-      <c r="D175" s="6">
+      <c r="D175" s="3">
         <v>36305.866878999994</v>
       </c>
-      <c r="E175" s="7">
+      <c r="E175" s="4">
         <v>88025.025120999999</v>
       </c>
       <c r="F175">
@@ -4955,13 +3854,13 @@
       <c r="B176" t="s">
         <v>11</v>
       </c>
-      <c r="C176" s="6">
+      <c r="C176" s="3">
         <v>120900.93006499999</v>
       </c>
-      <c r="D176" s="6">
+      <c r="D176" s="3">
         <v>35675.594138</v>
       </c>
-      <c r="E176" s="7">
+      <c r="E176" s="4">
         <v>85225.335926999993</v>
       </c>
       <c r="F176">
@@ -4975,13 +3874,13 @@
       <c r="B177" t="s">
         <v>12</v>
       </c>
-      <c r="C177" s="6">
+      <c r="C177" s="3">
         <v>122543.73404000001</v>
       </c>
-      <c r="D177" s="6">
+      <c r="D177" s="3">
         <v>35925.061013999999</v>
       </c>
-      <c r="E177" s="7">
+      <c r="E177" s="4">
         <v>86618.673026000004</v>
       </c>
       <c r="F177">
@@ -4995,13 +3894,13 @@
       <c r="B178" t="s">
         <v>13</v>
       </c>
-      <c r="C178" s="6">
+      <c r="C178" s="3">
         <v>121556.85282900001</v>
       </c>
-      <c r="D178" s="6">
+      <c r="D178" s="3">
         <v>35148.023977000004</v>
       </c>
-      <c r="E178" s="7">
+      <c r="E178" s="4">
         <v>86408.828852000006</v>
       </c>
       <c r="F178">
@@ -5015,13 +3914,13 @@
       <c r="B179" t="s">
         <v>14</v>
       </c>
-      <c r="C179" s="6">
+      <c r="C179" s="3">
         <v>119896.29622600001</v>
       </c>
-      <c r="D179" s="6">
+      <c r="D179" s="3">
         <v>35294.833906</v>
       </c>
-      <c r="E179" s="7">
+      <c r="E179" s="4">
         <v>84601.462320000006</v>
       </c>
       <c r="F179">
@@ -5035,13 +3934,13 @@
       <c r="B180" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="6">
+      <c r="C180" s="3">
         <v>120501.64427700001</v>
       </c>
-      <c r="D180" s="6">
+      <c r="D180" s="3">
         <v>34496.899754000005</v>
       </c>
-      <c r="E180" s="7">
+      <c r="E180" s="4">
         <v>86004.744523000001</v>
       </c>
       <c r="F180">
@@ -5055,13 +3954,13 @@
       <c r="B181" t="s">
         <v>16</v>
       </c>
-      <c r="C181" s="6">
+      <c r="C181" s="3">
         <v>122841.510928</v>
       </c>
-      <c r="D181" s="6">
+      <c r="D181" s="3">
         <v>35565.831188999982</v>
       </c>
-      <c r="E181" s="6">
+      <c r="E181" s="3">
         <v>87275.679739000014</v>
       </c>
       <c r="F181">
@@ -5075,13 +3974,13 @@
       <c r="B182" t="s">
         <v>5</v>
       </c>
-      <c r="C182" s="6">
+      <c r="C182" s="3">
         <v>118262.07046100001</v>
       </c>
-      <c r="D182" s="6">
+      <c r="D182" s="3">
         <v>35895.134258000006</v>
       </c>
-      <c r="E182" s="7">
+      <c r="E182" s="4">
         <v>82366.936203000005</v>
       </c>
       <c r="F182">
@@ -5095,13 +3994,13 @@
       <c r="B183" t="s">
         <v>6</v>
       </c>
-      <c r="C183" s="6">
+      <c r="C183" s="3">
         <v>118590.68042000002</v>
       </c>
-      <c r="D183" s="6">
+      <c r="D183" s="3">
         <v>34231.951384</v>
       </c>
-      <c r="E183" s="7">
+      <c r="E183" s="4">
         <v>84358.729036000019</v>
       </c>
       <c r="F183">
@@ -5115,13 +4014,13 @@
       <c r="B184" t="s">
         <v>7</v>
       </c>
-      <c r="C184" s="6">
+      <c r="C184" s="3">
         <v>120029.84432199999</v>
       </c>
-      <c r="D184" s="6">
+      <c r="D184" s="3">
         <v>35881.747689999997</v>
       </c>
-      <c r="E184" s="7">
+      <c r="E184" s="4">
         <v>84148.096632000001</v>
       </c>
       <c r="F184">
@@ -5135,13 +4034,13 @@
       <c r="B185" t="s">
         <v>8</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="3">
         <v>118416.11503299999</v>
       </c>
-      <c r="D185" s="6">
+      <c r="D185" s="3">
         <v>34531.262443</v>
       </c>
-      <c r="E185" s="7">
+      <c r="E185" s="4">
         <v>83884.852589999995</v>
       </c>
       <c r="F185">
@@ -5155,13 +4054,13 @@
       <c r="B186" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="3">
         <v>114355.97771899999</v>
       </c>
-      <c r="D186" s="6">
+      <c r="D186" s="3">
         <v>32588.379384</v>
       </c>
-      <c r="E186" s="7">
+      <c r="E186" s="4">
         <v>81767.598334999988</v>
       </c>
       <c r="F186">
@@ -5175,13 +4074,13 @@
       <c r="B187" t="s">
         <v>10</v>
       </c>
-      <c r="C187" s="6">
+      <c r="C187" s="3">
         <v>113295.776115</v>
       </c>
-      <c r="D187" s="6">
+      <c r="D187" s="3">
         <v>29363.061617000003</v>
       </c>
-      <c r="E187" s="7">
+      <c r="E187" s="4">
         <v>83932.714498000001</v>
       </c>
       <c r="F187">
@@ -5195,13 +4094,13 @@
       <c r="B188" t="s">
         <v>11</v>
       </c>
-      <c r="C188" s="6">
+      <c r="C188" s="3">
         <v>112406.50498199997</v>
       </c>
-      <c r="D188" s="6">
+      <c r="D188" s="3">
         <v>28652.342639999992</v>
       </c>
-      <c r="E188" s="7">
+      <c r="E188" s="4">
         <v>83754.162341999981</v>
       </c>
       <c r="F188">
@@ -5215,13 +4114,13 @@
       <c r="B189" t="s">
         <v>12</v>
       </c>
-      <c r="C189" s="6">
+      <c r="C189" s="3">
         <v>109760.80439199998</v>
       </c>
-      <c r="D189" s="6">
+      <c r="D189" s="3">
         <v>27160.901342999998</v>
       </c>
-      <c r="E189" s="7">
+      <c r="E189" s="4">
         <v>82599.903048999986</v>
       </c>
       <c r="F189">
@@ -5235,13 +4134,13 @@
       <c r="B190" t="s">
         <v>13</v>
       </c>
-      <c r="C190" s="6">
+      <c r="C190" s="3">
         <v>111985.722643</v>
       </c>
-      <c r="D190" s="6">
+      <c r="D190" s="3">
         <v>25930.569550999997</v>
       </c>
-      <c r="E190" s="7">
+      <c r="E190" s="4">
         <v>86055.153092000008</v>
       </c>
       <c r="F190">
@@ -5255,13 +4154,13 @@
       <c r="B191" t="s">
         <v>14</v>
       </c>
-      <c r="C191" s="6">
+      <c r="C191" s="3">
         <v>110144.94806200001</v>
       </c>
-      <c r="D191" s="6">
+      <c r="D191" s="3">
         <v>23877.360955</v>
       </c>
-      <c r="E191" s="7">
+      <c r="E191" s="4">
         <v>86267.587107000014</v>
       </c>
       <c r="F191">
@@ -5275,13 +4174,13 @@
       <c r="B192" t="s">
         <v>15</v>
       </c>
-      <c r="C192" s="6">
+      <c r="C192" s="3">
         <v>108684.469468</v>
       </c>
-      <c r="D192" s="6">
+      <c r="D192" s="3">
         <v>22786.922939000004</v>
       </c>
-      <c r="E192" s="7">
+      <c r="E192" s="4">
         <v>85897.546528999985</v>
       </c>
       <c r="F192">
@@ -5295,13 +4194,13 @@
       <c r="B193" t="s">
         <v>16</v>
       </c>
-      <c r="C193" s="6">
+      <c r="C193" s="3">
         <v>108842.308766</v>
       </c>
-      <c r="D193" s="6">
+      <c r="D193" s="3">
         <v>21622.953148000001</v>
       </c>
-      <c r="E193" s="6">
+      <c r="E193" s="3">
         <v>87219.355618000001</v>
       </c>
       <c r="F193">
@@ -5315,13 +4214,13 @@
       <c r="B194" t="s">
         <v>5</v>
       </c>
-      <c r="C194" s="6">
+      <c r="C194" s="3">
         <v>106098.971676</v>
       </c>
-      <c r="D194" s="6">
+      <c r="D194" s="3">
         <v>20561.676224999999</v>
       </c>
-      <c r="E194" s="7">
+      <c r="E194" s="4">
         <v>85537.295450999998</v>
       </c>
       <c r="F194">
@@ -5335,13 +4234,13 @@
       <c r="B195" t="s">
         <v>6</v>
       </c>
-      <c r="C195" s="6">
+      <c r="C195" s="3">
         <v>107679.28383600002</v>
       </c>
-      <c r="D195" s="6">
+      <c r="D195" s="3">
         <v>19597.657601000003</v>
       </c>
-      <c r="E195" s="7">
+      <c r="E195" s="4">
         <v>88081.626235000018</v>
       </c>
       <c r="F195">
@@ -5355,13 +4254,13 @@
       <c r="B196" t="s">
         <v>7</v>
       </c>
-      <c r="C196" s="6">
+      <c r="C196" s="3">
         <v>108746.98419299998</v>
       </c>
-      <c r="D196" s="6">
+      <c r="D196" s="3">
         <v>18656.268263999998</v>
       </c>
-      <c r="E196" s="7">
+      <c r="E196" s="4">
         <v>90090.715928999984</v>
       </c>
       <c r="F196">
@@ -5375,13 +4274,13 @@
       <c r="B197" t="s">
         <v>8</v>
       </c>
-      <c r="C197" s="6">
+      <c r="C197" s="3">
         <v>108108.65055199999</v>
       </c>
-      <c r="D197" s="6">
+      <c r="D197" s="3">
         <v>18710.223129999998</v>
       </c>
-      <c r="E197" s="7">
+      <c r="E197" s="4">
         <v>89398.427421999993</v>
       </c>
       <c r="F197">
@@ -5395,13 +4294,13 @@
       <c r="B198" t="s">
         <v>9</v>
       </c>
-      <c r="C198" s="6">
+      <c r="C198" s="3">
         <v>107677.15315400001</v>
       </c>
-      <c r="D198" s="6">
+      <c r="D198" s="3">
         <v>18229.080043999998</v>
       </c>
-      <c r="E198" s="7">
+      <c r="E198" s="4">
         <v>89448.073110000012</v>
       </c>
       <c r="F198">
@@ -5415,13 +4314,13 @@
       <c r="B199" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="6">
+      <c r="C199" s="3">
         <v>108629.09941799998</v>
       </c>
-      <c r="D199" s="6">
+      <c r="D199" s="3">
         <v>18054.385029999998</v>
       </c>
-      <c r="E199" s="7">
+      <c r="E199" s="4">
         <v>90574.714387999993</v>
       </c>
       <c r="F199">
@@ -5435,13 +4334,13 @@
       <c r="B200" t="s">
         <v>11</v>
       </c>
-      <c r="C200" s="6">
+      <c r="C200" s="3">
         <v>108159.477396</v>
       </c>
-      <c r="D200" s="6">
+      <c r="D200" s="3">
         <v>18815.057545000003</v>
       </c>
-      <c r="E200" s="7">
+      <c r="E200" s="4">
         <v>89344.419850999999</v>
       </c>
       <c r="F200">
@@ -5455,13 +4354,13 @@
       <c r="B201" t="s">
         <v>12</v>
       </c>
-      <c r="C201" s="6">
+      <c r="C201" s="3">
         <v>107561.67380399999</v>
       </c>
-      <c r="D201" s="6">
+      <c r="D201" s="3">
         <v>18923.119481999998</v>
       </c>
-      <c r="E201" s="7">
+      <c r="E201" s="4">
         <v>88638.554321999996</v>
       </c>
       <c r="F201">
@@ -5475,13 +4374,13 @@
       <c r="B202" t="s">
         <v>13</v>
       </c>
-      <c r="C202" s="6">
+      <c r="C202" s="3">
         <v>108647.325967</v>
       </c>
-      <c r="D202" s="6">
+      <c r="D202" s="3">
         <v>19123.641464999997</v>
       </c>
-      <c r="E202" s="7">
+      <c r="E202" s="4">
         <v>89523.684502000004</v>
       </c>
       <c r="F202">
@@ -5495,13 +4394,13 @@
       <c r="B203" t="s">
         <v>14</v>
       </c>
-      <c r="C203" s="6">
+      <c r="C203" s="3">
         <v>109374.51839499998</v>
       </c>
-      <c r="D203" s="6">
+      <c r="D203" s="3">
         <v>20595.290364</v>
       </c>
-      <c r="E203" s="7">
+      <c r="E203" s="4">
         <v>88779.228030999977</v>
       </c>
       <c r="F203">
@@ -5515,13 +4414,13 @@
       <c r="B204" t="s">
         <v>15</v>
       </c>
-      <c r="C204" s="6">
+      <c r="C204" s="3">
         <v>111597.73594300001</v>
       </c>
-      <c r="D204" s="6">
+      <c r="D204" s="3">
         <v>22476.881816999998</v>
       </c>
-      <c r="E204" s="7">
+      <c r="E204" s="4">
         <v>89120.854126000006</v>
       </c>
       <c r="F204">
@@ -5535,13 +4434,13 @@
       <c r="B205" t="s">
         <v>16</v>
       </c>
-      <c r="C205" s="6">
+      <c r="C205" s="3">
         <v>112799.90611599997</v>
       </c>
-      <c r="D205" s="6">
+      <c r="D205" s="3">
         <v>24230.764319000002</v>
       </c>
-      <c r="E205" s="6">
+      <c r="E205" s="3">
         <v>88569.14179699996</v>
       </c>
       <c r="F205">
@@ -5555,13 +4454,13 @@
       <c r="B206" t="s">
         <v>5</v>
       </c>
-      <c r="C206" s="6">
+      <c r="C206" s="3">
         <v>114506.42076700002</v>
       </c>
-      <c r="D206" s="6">
+      <c r="D206" s="3">
         <v>26871.583562</v>
       </c>
-      <c r="E206" s="7">
+      <c r="E206" s="4">
         <v>87634.837205000018</v>
       </c>
       <c r="F206">
@@ -5575,13 +4474,13 @@
       <c r="B207" t="s">
         <v>6</v>
       </c>
-      <c r="C207" s="6">
+      <c r="C207" s="3">
         <v>115609.23216699999</v>
       </c>
-      <c r="D207" s="6">
+      <c r="D207" s="3">
         <v>30885.441358</v>
       </c>
-      <c r="E207" s="7">
+      <c r="E207" s="4">
         <v>84723.790808999998</v>
       </c>
       <c r="F207">
@@ -5595,13 +4494,13 @@
       <c r="B208" t="s">
         <v>7</v>
       </c>
-      <c r="C208" s="6">
+      <c r="C208" s="3">
         <v>121564.61326299999</v>
       </c>
-      <c r="D208" s="6">
+      <c r="D208" s="3">
         <v>35393.225683999997</v>
       </c>
-      <c r="E208" s="7">
+      <c r="E208" s="4">
         <v>86171.387579000002</v>
       </c>
       <c r="F208">
@@ -5615,13 +4514,13 @@
       <c r="B209" t="s">
         <v>8</v>
       </c>
-      <c r="C209" s="6">
+      <c r="C209" s="3">
         <v>124502.79102299998</v>
       </c>
-      <c r="D209" s="6">
+      <c r="D209" s="3">
         <v>41959.420549000002</v>
       </c>
-      <c r="E209" s="7">
+      <c r="E209" s="4">
         <v>82543.370473999981</v>
       </c>
       <c r="F209">
@@ -5635,13 +4534,13 @@
       <c r="B210" t="s">
         <v>9</v>
       </c>
-      <c r="C210" s="6">
+      <c r="C210" s="3">
         <v>130241.22939000001</v>
       </c>
-      <c r="D210" s="6">
+      <c r="D210" s="3">
         <v>52296.743537000002</v>
       </c>
-      <c r="E210" s="7">
+      <c r="E210" s="4">
         <v>77944.485853000006</v>
       </c>
       <c r="F210">
@@ -5655,13 +4554,13 @@
       <c r="B211" t="s">
         <v>10</v>
       </c>
-      <c r="C211" s="6">
+      <c r="C211" s="3">
         <v>135158.87485299999</v>
       </c>
-      <c r="D211" s="6">
+      <c r="D211" s="3">
         <v>56795.670142000003</v>
       </c>
-      <c r="E211" s="7">
+      <c r="E211" s="4">
         <v>78363.204710999984</v>
       </c>
       <c r="F211">
@@ -5675,13 +4574,13 @@
       <c r="B212" t="s">
         <v>11</v>
       </c>
-      <c r="C212" s="6">
+      <c r="C212" s="3">
         <v>139554.831014</v>
       </c>
-      <c r="D212" s="6">
+      <c r="D212" s="3">
         <v>63340.391706000002</v>
       </c>
-      <c r="E212" s="7">
+      <c r="E212" s="4">
         <v>76214.439308000001</v>
       </c>
       <c r="F212">
@@ -5695,13 +4594,13 @@
       <c r="B213" t="s">
         <v>12</v>
       </c>
-      <c r="C213" s="6">
+      <c r="C213" s="3">
         <v>145863.28002099998</v>
       </c>
-      <c r="D213" s="6">
+      <c r="D213" s="3">
         <v>73069.941114999994</v>
       </c>
-      <c r="E213" s="7">
+      <c r="E213" s="4">
         <v>72793.33890599999</v>
       </c>
       <c r="F213">
@@ -5715,13 +4614,13 @@
       <c r="B214" t="s">
         <v>13</v>
       </c>
-      <c r="C214" s="6">
+      <c r="C214" s="3">
         <v>149741.76946800001</v>
       </c>
-      <c r="D214" s="6">
+      <c r="D214" s="3">
         <v>81962.483940000006</v>
       </c>
-      <c r="E214" s="7">
+      <c r="E214" s="4">
         <v>67779.285528000008</v>
       </c>
       <c r="F214">
@@ -5735,13 +4634,13 @@
       <c r="B215" t="s">
         <v>14</v>
       </c>
-      <c r="C215" s="6">
+      <c r="C215" s="3">
         <v>155148.75574899997</v>
       </c>
-      <c r="D215" s="6">
+      <c r="D215" s="3">
         <v>90485.44526800001</v>
       </c>
-      <c r="E215" s="7">
+      <c r="E215" s="4">
         <v>64663.310480999964</v>
       </c>
       <c r="F215">
@@ -5755,13 +4654,13 @@
       <c r="B216" t="s">
         <v>15</v>
       </c>
-      <c r="C216" s="6">
+      <c r="C216" s="3">
         <v>162206.32550200002</v>
       </c>
-      <c r="D216" s="6">
+      <c r="D216" s="3">
         <v>100496.64903000002</v>
       </c>
-      <c r="E216" s="7">
+      <c r="E216" s="4">
         <v>61709.676472000006</v>
       </c>
       <c r="F216">
@@ -5775,13 +4674,13 @@
       <c r="B217" t="s">
         <v>16</v>
       </c>
-      <c r="C217" s="6">
+      <c r="C217" s="3">
         <v>169493.75084299999</v>
       </c>
-      <c r="D217" s="6">
+      <c r="D217" s="3">
         <v>110790.035829</v>
       </c>
-      <c r="E217" s="6">
+      <c r="E217" s="3">
         <v>58703.715013999987</v>
       </c>
       <c r="F217">
@@ -5795,13 +4694,13 @@
       <c r="B218" t="s">
         <v>5</v>
       </c>
-      <c r="C218" s="6">
+      <c r="C218" s="3">
         <v>172606.542025</v>
       </c>
-      <c r="D218" s="6">
+      <c r="D218" s="3">
         <v>121747.00737100003</v>
       </c>
-      <c r="E218" s="7">
+      <c r="E218" s="4">
         <v>50859.534653999974</v>
       </c>
       <c r="F218">
@@ -5815,13 +4714,13 @@
       <c r="B219" t="s">
         <v>6</v>
       </c>
-      <c r="C219" s="6">
+      <c r="C219" s="3">
         <v>172269.92544000002</v>
       </c>
-      <c r="D219" s="6">
+      <c r="D219" s="3">
         <v>120619.95186999999</v>
       </c>
-      <c r="E219" s="7">
+      <c r="E219" s="4">
         <v>51649.973570000031</v>
       </c>
       <c r="F219">
@@ -5835,13 +4734,13 @@
       <c r="B220" t="s">
         <v>7</v>
       </c>
-      <c r="C220" s="6">
+      <c r="C220" s="3">
         <v>179317.37406100001</v>
       </c>
-      <c r="D220" s="6">
+      <c r="D220" s="3">
         <v>127479.139069</v>
       </c>
-      <c r="E220" s="7">
+      <c r="E220" s="4">
         <v>51838.234992000012</v>
       </c>
       <c r="F220">
@@ -5855,13 +4754,13 @@
       <c r="B221" t="s">
         <v>8</v>
       </c>
-      <c r="C221" s="6">
+      <c r="C221" s="3">
         <v>177762.618694</v>
       </c>
-      <c r="D221" s="6">
+      <c r="D221" s="3">
         <v>123845.117434</v>
       </c>
-      <c r="E221" s="7">
+      <c r="E221" s="4">
         <v>53917.501260000005</v>
       </c>
       <c r="F221">
@@ -5875,13 +4774,13 @@
       <c r="B222" t="s">
         <v>9</v>
       </c>
-      <c r="C222" s="6">
+      <c r="C222" s="3">
         <v>177999.60600800003</v>
       </c>
-      <c r="D222" s="6">
+      <c r="D222" s="3">
         <v>125240.819994</v>
       </c>
-      <c r="E222" s="7">
+      <c r="E222" s="4">
         <v>52758.786014000027</v>
       </c>
       <c r="F222">
@@ -5895,13 +4794,13 @@
       <c r="B223" t="s">
         <v>10</v>
       </c>
-      <c r="C223" s="6">
+      <c r="C223" s="3">
         <v>174695.00902300002</v>
       </c>
-      <c r="D223" s="6">
+      <c r="D223" s="3">
         <v>123406.250755</v>
       </c>
-      <c r="E223" s="7">
+      <c r="E223" s="4">
         <v>51288.75826800002</v>
       </c>
       <c r="F223">
@@ -5915,13 +4814,13 @@
       <c r="B224" t="s">
         <v>11</v>
       </c>
-      <c r="C224" s="6">
+      <c r="C224" s="3">
         <v>175504.81138500001</v>
       </c>
-      <c r="D224" s="6">
+      <c r="D224" s="3">
         <v>125245.333701</v>
       </c>
-      <c r="E224" s="7">
+      <c r="E224" s="4">
         <v>50259.477684000012</v>
       </c>
       <c r="F224">
@@ -5935,13 +4834,13 @@
       <c r="B225" t="s">
         <v>12</v>
       </c>
-      <c r="C225" s="6">
+      <c r="C225" s="3">
         <v>179353.89728199999</v>
       </c>
-      <c r="D225" s="6">
+      <c r="D225" s="3">
         <v>124546.41695899999</v>
       </c>
-      <c r="E225" s="7">
+      <c r="E225" s="4">
         <v>54807.480322999996</v>
       </c>
       <c r="F225">
@@ -5955,13 +4854,13 @@
       <c r="B226" t="s">
         <v>13</v>
       </c>
-      <c r="C226" s="6">
+      <c r="C226" s="3">
         <v>175450.95360900005</v>
       </c>
-      <c r="D226" s="6">
+      <c r="D226" s="3">
         <v>124197.31178400002</v>
       </c>
-      <c r="E226" s="7">
+      <c r="E226" s="4">
         <v>51253.641825000028</v>
       </c>
       <c r="F226">
@@ -5975,13 +4874,13 @@
       <c r="B227" t="s">
         <v>14</v>
       </c>
-      <c r="C227" s="6">
+      <c r="C227" s="3">
         <v>175533.81570000001</v>
       </c>
-      <c r="D227" s="6">
+      <c r="D227" s="3">
         <v>120074.70995499998</v>
       </c>
-      <c r="E227" s="7">
+      <c r="E227" s="4">
         <v>55459.105745000023</v>
       </c>
       <c r="F227">
@@ -5995,13 +4894,13 @@
       <c r="B228" t="s">
         <v>15</v>
       </c>
-      <c r="C228" s="6">
+      <c r="C228" s="3">
         <v>173283.30884899999</v>
       </c>
-      <c r="D228" s="6">
+      <c r="D228" s="3">
         <v>120903.91542200001</v>
       </c>
-      <c r="E228" s="7">
+      <c r="E228" s="4">
         <v>52379.393426999988</v>
       </c>
       <c r="F228">
@@ -6015,13 +4914,13 @@
       <c r="B229" t="s">
         <v>16</v>
       </c>
-      <c r="C229" s="6">
+      <c r="C229" s="3">
         <v>173179.29312100002</v>
       </c>
-      <c r="D229" s="6">
+      <c r="D229" s="3">
         <v>119076.785443</v>
       </c>
-      <c r="E229" s="6">
+      <c r="E229" s="3">
         <v>54102.507678000024</v>
       </c>
       <c r="F229">
@@ -6035,13 +4934,13 @@
       <c r="B230" t="s">
         <v>5</v>
       </c>
-      <c r="C230" s="6">
+      <c r="C230" s="3">
         <v>172440.77686899999</v>
       </c>
-      <c r="D230" s="6">
+      <c r="D230" s="3">
         <v>119354.420824</v>
       </c>
-      <c r="E230" s="7">
+      <c r="E230" s="4">
         <v>53086.356044999993</v>
       </c>
       <c r="F230">
@@ -6055,13 +4954,13 @@
       <c r="B231" t="s">
         <v>6</v>
       </c>
-      <c r="C231" s="6">
+      <c r="C231" s="3">
         <v>173896.45034700003</v>
       </c>
-      <c r="D231" s="6">
+      <c r="D231" s="3">
         <v>116877.32098</v>
       </c>
-      <c r="E231" s="7">
+      <c r="E231" s="4">
         <v>57019.12936700003</v>
       </c>
       <c r="F231">
@@ -6075,13 +4974,13 @@
       <c r="B232" t="s">
         <v>7</v>
       </c>
-      <c r="C232" s="6">
+      <c r="C232" s="3">
         <v>175954.340314</v>
       </c>
-      <c r="D232" s="6">
+      <c r="D232" s="3">
         <v>121611.212589</v>
       </c>
-      <c r="E232" s="7">
+      <c r="E232" s="4">
         <v>54343.127724999998</v>
       </c>
       <c r="F232">
@@ -6095,13 +4994,13 @@
       <c r="B233" t="s">
         <v>8</v>
       </c>
-      <c r="C233" s="6">
+      <c r="C233" s="3">
         <v>172354.70471099997</v>
       </c>
-      <c r="D233" s="6">
+      <c r="D233" s="3">
         <v>109123.825512</v>
       </c>
-      <c r="E233" s="7">
+      <c r="E233" s="4">
         <v>63230.879198999974</v>
       </c>
       <c r="F233">
@@ -6115,13 +5014,13 @@
       <c r="B234" t="s">
         <v>9</v>
       </c>
-      <c r="C234" s="6">
+      <c r="C234" s="3">
         <v>167914.85365300003</v>
       </c>
-      <c r="D234" s="6">
+      <c r="D234" s="3">
         <v>103635.200459</v>
       </c>
-      <c r="E234" s="7">
+      <c r="E234" s="4">
         <v>64279.653194000028</v>
       </c>
       <c r="F234">
@@ -6135,13 +5034,13 @@
       <c r="B235" t="s">
         <v>10</v>
       </c>
-      <c r="C235" s="6">
+      <c r="C235" s="3">
         <v>162885.57630000002</v>
       </c>
-      <c r="D235" s="6">
+      <c r="D235" s="3">
         <v>99220.239413000003</v>
       </c>
-      <c r="E235" s="7">
+      <c r="E235" s="4">
         <v>63665.336887000012</v>
       </c>
       <c r="F235">
@@ -6155,13 +5054,13 @@
       <c r="B236" t="s">
         <v>11</v>
       </c>
-      <c r="C236" s="6">
+      <c r="C236" s="3">
         <v>162310.32736200001</v>
       </c>
-      <c r="D236" s="6">
+      <c r="D236" s="3">
         <v>93603.785965000003</v>
       </c>
-      <c r="E236" s="7">
+      <c r="E236" s="4">
         <v>68706.541397000008</v>
       </c>
       <c r="F236">
@@ -6175,13 +5074,13 @@
       <c r="B237" t="s">
         <v>12</v>
       </c>
-      <c r="C237" s="6">
+      <c r="C237" s="3">
         <v>160281.91200600003</v>
       </c>
-      <c r="D237" s="6">
+      <c r="D237" s="3">
         <v>89349.247687999989</v>
       </c>
-      <c r="E237" s="7">
+      <c r="E237" s="4">
         <v>70932.664318000039</v>
       </c>
       <c r="F237">
@@ -6195,13 +5094,13 @@
       <c r="B238" t="s">
         <v>13</v>
       </c>
-      <c r="C238" s="6">
+      <c r="C238" s="3">
         <v>158754.50757300001</v>
       </c>
-      <c r="D238" s="6">
+      <c r="D238" s="3">
         <v>87745.062993</v>
       </c>
-      <c r="E238" s="7">
+      <c r="E238" s="4">
         <v>71009.44458000001</v>
       </c>
       <c r="F238">
@@ -6215,13 +5114,13 @@
       <c r="B239" t="s">
         <v>14</v>
       </c>
-      <c r="C239" s="6">
+      <c r="C239" s="3">
         <v>159513.468322</v>
       </c>
-      <c r="D239" s="6">
+      <c r="D239" s="3">
         <v>88094.420222999994</v>
       </c>
-      <c r="E239" s="7">
+      <c r="E239" s="4">
         <v>71419.048099000007</v>
       </c>
       <c r="F239">
@@ -6235,13 +5134,13 @@
       <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240" s="6">
+      <c r="C240" s="3">
         <v>160796.890136</v>
       </c>
-      <c r="D240" s="6">
+      <c r="D240" s="3">
         <v>85773.230616000001</v>
       </c>
-      <c r="E240" s="7">
+      <c r="E240" s="4">
         <v>75023.659520000001</v>
       </c>
       <c r="F240">
@@ -6255,13 +5154,13 @@
       <c r="B241" t="s">
         <v>16</v>
       </c>
-      <c r="C241" s="6">
+      <c r="C241" s="3">
         <v>161839.87166100001</v>
       </c>
-      <c r="D241" s="6">
+      <c r="D241" s="3">
         <v>88432.947396000003</v>
       </c>
-      <c r="E241" s="6">
+      <c r="E241" s="3">
         <v>73406.924265000009</v>
       </c>
       <c r="F241">
@@ -6275,13 +5174,13 @@
       <c r="B242" t="s">
         <v>5</v>
       </c>
-      <c r="C242" s="6">
+      <c r="C242" s="3">
         <v>168546.15433799999</v>
       </c>
-      <c r="D242" s="6">
+      <c r="D242" s="3">
         <v>89112.169872000013</v>
       </c>
-      <c r="E242" s="7">
+      <c r="E242" s="4">
         <v>79433.98446599998</v>
       </c>
       <c r="F242">
@@ -6295,13 +5194,13 @@
       <c r="B243" t="s">
         <v>6</v>
       </c>
-      <c r="C243" s="6">
+      <c r="C243" s="3">
         <v>161663.12574699998</v>
       </c>
-      <c r="D243" s="6">
+      <c r="D243" s="3">
         <v>88987.694793000002</v>
       </c>
-      <c r="E243" s="7">
+      <c r="E243" s="4">
         <v>72675.430953999981</v>
       </c>
       <c r="F243">
@@ -6315,13 +5214,13 @@
       <c r="B244" t="s">
         <v>7</v>
       </c>
-      <c r="C244" s="6">
+      <c r="C244" s="3">
         <v>171949.527856</v>
       </c>
-      <c r="D244" s="6">
+      <c r="D244" s="3">
         <v>93954.423643999995</v>
       </c>
-      <c r="E244" s="7">
+      <c r="E244" s="4">
         <v>77995.104212000006</v>
       </c>
       <c r="F244">
@@ -6335,13 +5234,13 @@
       <c r="B245" t="s">
         <v>8</v>
       </c>
-      <c r="C245" s="6">
+      <c r="C245" s="3">
         <v>171680.15847100003</v>
       </c>
-      <c r="D245" s="6">
+      <c r="D245" s="3">
         <v>93155.483485999997</v>
       </c>
-      <c r="E245" s="7">
+      <c r="E245" s="4">
         <v>78524.674985000034</v>
       </c>
       <c r="F245">
@@ -6355,13 +5254,13 @@
       <c r="B246" t="s">
         <v>9</v>
       </c>
-      <c r="C246" s="6">
+      <c r="C246" s="3">
         <v>175242.98612800002</v>
       </c>
-      <c r="D246" s="6">
+      <c r="D246" s="3">
         <v>95300.280877000012</v>
       </c>
-      <c r="E246" s="7">
+      <c r="E246" s="4">
         <v>79942.705251000007</v>
       </c>
       <c r="F246">
@@ -6375,13 +5274,13 @@
       <c r="B247" t="s">
         <v>10</v>
       </c>
-      <c r="C247" s="6">
+      <c r="C247" s="3">
         <v>173756.45211400001</v>
       </c>
-      <c r="D247" s="6">
+      <c r="D247" s="3">
         <v>93421.575291999994</v>
       </c>
-      <c r="E247" s="7">
+      <c r="E247" s="4">
         <v>80334.87682200002</v>
       </c>
       <c r="F247">
@@ -6395,13 +5294,13 @@
       <c r="B248" t="s">
         <v>11</v>
       </c>
-      <c r="C248" s="6">
+      <c r="C248" s="3">
         <v>177611.878669</v>
       </c>
-      <c r="D248" s="6">
+      <c r="D248" s="3">
         <v>94327.325268999994</v>
       </c>
-      <c r="E248" s="7">
+      <c r="E248" s="4">
         <v>83284.553400000004</v>
       </c>
       <c r="F248">
@@ -6415,13 +5314,13 @@
       <c r="B249" t="s">
         <v>12</v>
       </c>
-      <c r="C249" s="6">
+      <c r="C249" s="3">
         <v>178549.12228600003</v>
       </c>
-      <c r="D249" s="6">
+      <c r="D249" s="3">
         <v>95393.180770000006</v>
       </c>
-      <c r="E249" s="7">
+      <c r="E249" s="4">
         <v>83155.941516000021</v>
       </c>
       <c r="F249">
@@ -6435,13 +5334,13 @@
       <c r="B250" t="s">
         <v>13</v>
       </c>
-      <c r="C250" s="6">
+      <c r="C250" s="3">
         <v>179403.45495200003</v>
       </c>
-      <c r="D250" s="6">
+      <c r="D250" s="3">
         <v>96400.383470000015</v>
       </c>
-      <c r="E250" s="7">
+      <c r="E250" s="4">
         <v>83003.071482000014</v>
       </c>
       <c r="F250">
@@ -6455,13 +5354,13 @@
       <c r="B251" t="s">
         <v>14</v>
       </c>
-      <c r="C251" s="6">
+      <c r="C251" s="3">
         <v>180527.38270400002</v>
       </c>
-      <c r="D251" s="6">
+      <c r="D251" s="3">
         <v>98698.126669000005</v>
       </c>
-      <c r="E251" s="7">
+      <c r="E251" s="4">
         <v>81829.256035000013</v>
       </c>
       <c r="F251">
@@ -6475,13 +5374,13 @@
       <c r="B252" t="s">
         <v>15</v>
       </c>
-      <c r="C252" s="6">
+      <c r="C252" s="3">
         <v>182156.29664399999</v>
       </c>
-      <c r="D252" s="6">
+      <c r="D252" s="3">
         <v>97830.733132000008</v>
       </c>
-      <c r="E252" s="7">
+      <c r="E252" s="4">
         <v>84325.563511999979</v>
       </c>
       <c r="F252">
@@ -6495,13 +5394,13 @@
       <c r="B253" t="s">
         <v>16</v>
       </c>
-      <c r="C253" s="6">
+      <c r="C253" s="3">
         <v>190722.42398099997</v>
       </c>
-      <c r="D253" s="6">
+      <c r="D253" s="3">
         <v>99910.595614999998</v>
       </c>
-      <c r="E253" s="6">
+      <c r="E253" s="3">
         <v>90811.828365999972</v>
       </c>
       <c r="F253">

--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0133296E-8763-4944-8C29-DC19902EFC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60582726-0FD9-45F1-81B4-06B13D3569BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60582726-0FD9-45F1-81B4-06B13D3569BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F4AD0C-64F3-498D-985F-1EB515AE57FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="21">
   <si>
     <t>AÑO</t>
   </si>
@@ -90,6 +91,15 @@
   </si>
   <si>
     <t>TASA BANREP</t>
+  </si>
+  <si>
+    <t>año</t>
+  </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>pronostico</t>
   </si>
 </sst>
 </file>
@@ -177,7 +187,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -464,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7710FB4-1D75-4856-9D30-3BF005362D8B}">
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -494,13 +505,13 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>32790.077908983025</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>14093.620264434951</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>18696.457644548074</v>
       </c>
       <c r="F2">
@@ -514,13 +525,13 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>32128.51999336536</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>13900.049437858104</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>18228.470555507258</v>
       </c>
       <c r="F3">
@@ -534,13 +545,13 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>37128.281537396892</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>14386.374721816268</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>22741.906815580624</v>
       </c>
       <c r="F4">
@@ -554,13 +565,13 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>36248.373382015947</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>14315.991990494918</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>21932.381391521027</v>
       </c>
       <c r="F5">
@@ -574,13 +585,13 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>35987.711776337484</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>14489.77260139857</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>21497.939174938914</v>
       </c>
       <c r="F6">
@@ -594,13 +605,13 @@
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>34904.228120450076</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>14418.028754992763</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>20486.199365457313</v>
       </c>
       <c r="F7">
@@ -614,13 +625,13 @@
       <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>36037.159659434183</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="2">
         <v>14617.887918750595</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>21419.271740683587</v>
       </c>
       <c r="F8">
@@ -634,13 +645,13 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>34312.458634863899</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>14679.565901569938</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>19632.89273329396</v>
       </c>
       <c r="F9">
@@ -654,13 +665,13 @@
       <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>33945.279755463183</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>14598.086221905707</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>19347.193533557474</v>
       </c>
       <c r="F10">
@@ -674,13 +685,13 @@
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>35289.013715147557</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>14801.535549246313</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>20487.478165901244</v>
       </c>
       <c r="F11">
@@ -694,13 +705,13 @@
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>34484.083313307143</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>14709.143342629954</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>19774.939970677187</v>
       </c>
       <c r="F12">
@@ -714,13 +725,13 @@
       <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>36786.444008420447</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="2">
         <v>14927.300526272693</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>21859.143482147752</v>
       </c>
       <c r="F13">
@@ -734,13 +745,13 @@
       <c r="B14" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>30695.298207016058</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="2">
         <v>11929.845301432179</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>18765.452905583879</v>
       </c>
       <c r="F14">
@@ -754,13 +765,13 @@
       <c r="B15" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>30416.557877666655</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="2">
         <v>11612.756042107814</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>18803.801835558843</v>
       </c>
       <c r="F15">
@@ -774,13 +785,13 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>33697.311141683407</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2">
         <v>12219.583536825376</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>21477.727604858032</v>
       </c>
       <c r="F16">
@@ -794,13 +805,13 @@
       <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>34520.567238962773</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="2">
         <v>12256.670245216828</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>22263.896993745944</v>
       </c>
       <c r="F17">
@@ -814,13 +825,13 @@
       <c r="B18" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>33517.787777975129</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>12541.310986274913</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>20976.476791700217</v>
       </c>
       <c r="F18">
@@ -834,13 +845,13 @@
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>33378.235074134049</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2">
         <v>12569.501682184005</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>20808.733391950045</v>
       </c>
       <c r="F19">
@@ -854,13 +865,13 @@
       <c r="B20" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>34680.569732790282</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="2">
         <v>12841.25629590105</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>21839.313436889232</v>
       </c>
       <c r="F20">
@@ -874,13 +885,13 @@
       <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>34500.370875939581</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="2">
         <v>12965.784595218889</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>21534.586280720694</v>
       </c>
       <c r="F21">
@@ -894,13 +905,13 @@
       <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>34105.142513812476</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2">
         <v>12942.554453523537</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>21162.588060288937</v>
       </c>
       <c r="F22">
@@ -914,13 +925,13 @@
       <c r="B23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>35446.46405673134</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2">
         <v>13227.573975810654</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>22218.890080920686</v>
       </c>
       <c r="F23">
@@ -934,13 +945,13 @@
       <c r="B24" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>35438.632976379384</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="2">
         <v>13180.06665324112</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>22258.566323138264</v>
       </c>
       <c r="F24">
@@ -954,13 +965,13 @@
       <c r="B25" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>35205.804590990723</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="2">
         <v>13561.188079865475</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>21644.616511125249</v>
       </c>
       <c r="F25">
@@ -974,9 +985,9 @@
       <c r="B26" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="F26">
         <v>7.7499999999999999E-2</v>
       </c>
@@ -988,9 +999,9 @@
       <c r="B27" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
       <c r="F27">
         <v>0.08</v>
       </c>
@@ -1002,9 +1013,9 @@
       <c r="B28" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
       <c r="F28">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -1016,9 +1027,9 @@
       <c r="B29" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
       <c r="F29">
         <v>8.2500000000000004E-2</v>
       </c>
@@ -1030,9 +1041,9 @@
       <c r="B30" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
       <c r="F30">
         <v>8.7499999999999994E-2</v>
       </c>
@@ -1044,9 +1055,9 @@
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
       <c r="F31">
         <v>0.09</v>
       </c>
@@ -1058,9 +1069,9 @@
       <c r="B32" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
       <c r="F32">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1072,9 +1083,9 @@
       <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1086,9 +1097,9 @@
       <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
       <c r="F34">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1100,9 +1111,9 @@
       <c r="B35" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
       <c r="F35">
         <v>9.2499999999999999E-2</v>
       </c>
@@ -1114,9 +1125,9 @@
       <c r="B36" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
       <c r="F36">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1128,9 +1139,9 @@
       <c r="B37" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="F37">
         <v>9.5000000000000001E-2</v>
       </c>
@@ -1142,13 +1153,13 @@
       <c r="B38" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="2">
         <v>48702.885915624407</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="2">
         <v>16148.406349484414</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>32554.479566139991</v>
       </c>
       <c r="F38">
@@ -1162,13 +1173,13 @@
       <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="2">
         <v>49126.667453218142</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="2">
         <v>16443.325839939072</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>32683.34161327907</v>
       </c>
       <c r="F39">
@@ -1182,13 +1193,13 @@
       <c r="B40" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="2">
         <v>52658.899769440875</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="2">
         <v>17195.569465043904</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>35463.330304396972</v>
       </c>
       <c r="F40">
@@ -1202,13 +1213,13 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="2">
         <v>52171.507684440585</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="2">
         <v>17324.651314703486</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>34846.856369737099</v>
       </c>
       <c r="F41">
@@ -1222,13 +1233,13 @@
       <c r="B42" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="2">
         <v>53819.20806508878</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="2">
         <v>17943.698743044526</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>35875.50932204425</v>
       </c>
       <c r="F42">
@@ -1242,13 +1253,13 @@
       <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="2">
         <v>54771.35983740518</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="2">
         <v>18257.877630002175</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>36513.482207403009</v>
       </c>
       <c r="F43">
@@ -1262,13 +1273,13 @@
       <c r="B44" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="2">
         <v>57141.011161915405</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="2">
         <v>18629.571163170131</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>38511.439998745278</v>
       </c>
       <c r="F44">
@@ -1282,13 +1293,13 @@
       <c r="B45" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="2">
         <v>58398.548847401966</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <v>18862.976621251128</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>39535.572226150834</v>
       </c>
       <c r="F45">
@@ -1302,13 +1313,13 @@
       <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="2">
         <v>59436.635763009799</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="2">
         <v>18742.834521805442</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>40693.801241204361</v>
       </c>
       <c r="F46">
@@ -1322,13 +1333,13 @@
       <c r="B47" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="2">
         <v>61032.265569597606</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="2">
         <v>18969.628297434101</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>42062.637272163505</v>
       </c>
       <c r="F47">
@@ -1342,13 +1353,13 @@
       <c r="B48" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="2">
         <v>61699.402000504619</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="2">
         <v>18548.792210220268</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>43150.609790284347</v>
       </c>
       <c r="F48">
@@ -1362,13 +1373,13 @@
       <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="2">
         <v>62378.801356091462</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>18806.491239585608</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>43572.310116505854</v>
       </c>
       <c r="F49">
@@ -1382,13 +1393,13 @@
       <c r="B50" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="2">
         <v>61331.798002306605</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="2">
         <v>21230.248937401037</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>40101.549064905572</v>
       </c>
       <c r="F50">
@@ -1402,13 +1413,13 @@
       <c r="B51" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="2">
         <v>60674.786562767847</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="2">
         <v>20717.547625202518</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>39957.238937565329</v>
       </c>
       <c r="F51">
@@ -1422,13 +1433,13 @@
       <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="2">
         <v>65608.881801703508</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="2">
         <v>20494.133882468475</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>45114.747919235029</v>
       </c>
       <c r="F52">
@@ -1442,13 +1453,13 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="2">
         <v>64808.020317109447</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="2">
         <v>21507.966944576099</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>43300.053372533352</v>
       </c>
       <c r="F53">
@@ -1462,13 +1473,13 @@
       <c r="B54" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="2">
         <v>66398.538399304147</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="2">
         <v>22099.402830220311</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="2">
         <v>44299.135569083839</v>
       </c>
       <c r="F54">
@@ -1482,13 +1493,13 @@
       <c r="B55" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="2">
         <v>66731.439805295973</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="2">
         <v>21685.169748274333</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="2">
         <v>45046.27005702164</v>
       </c>
       <c r="F55">
@@ -1502,13 +1513,13 @@
       <c r="B56" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>67152.326625880232</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="2">
         <v>21792.670334259845</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>45359.656291620384</v>
       </c>
       <c r="F56">
@@ -1522,13 +1533,13 @@
       <c r="B57" t="s">
         <v>12</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="2">
         <v>69223.898253083564</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="2">
         <v>22880.901615861691</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>46342.996637221877</v>
       </c>
       <c r="F57">
@@ -1542,13 +1553,13 @@
       <c r="B58" t="s">
         <v>13</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="2">
         <v>69391.287762713371</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="2">
         <v>22594.048218141899</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>46797.239544571472</v>
       </c>
       <c r="F58">
@@ -1562,13 +1573,13 @@
       <c r="B59" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="2">
         <v>71003.94222564307</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="2">
         <v>22816.505932854223</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>48187.436292788843</v>
       </c>
       <c r="F59">
@@ -1582,13 +1593,13 @@
       <c r="B60" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="2">
         <v>72013.463669955192</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="2">
         <v>22396.657885139241</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>49616.805784815951</v>
       </c>
       <c r="F60">
@@ -1602,13 +1613,13 @@
       <c r="B61" t="s">
         <v>16</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="2">
         <v>82593.712888649694</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="2">
         <v>23570.554673733128</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>59023.158214916562</v>
       </c>
       <c r="F61">
@@ -1622,13 +1633,13 @@
       <c r="B62" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="2">
         <v>56511.270921737152</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="2">
         <v>13973.354689899539</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>42537.916231837611</v>
       </c>
       <c r="F62">
@@ -1642,13 +1653,13 @@
       <c r="B63" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="2">
         <v>55643.0021232695</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="2">
         <v>13111.962749757122</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="2">
         <v>42531.03937351238</v>
       </c>
       <c r="F63">
@@ -1662,13 +1673,13 @@
       <c r="B64" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="2">
         <v>63497.384954216272</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="2">
         <v>12987.052039227068</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="2">
         <v>50510.332914989202</v>
       </c>
       <c r="F64">
@@ -1682,13 +1693,13 @@
       <c r="B65" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="2">
         <v>58537.33033389756</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="2">
         <v>13182.136468922454</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="2">
         <v>45355.19386497511</v>
       </c>
       <c r="F65">
@@ -1702,13 +1713,13 @@
       <c r="B66" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="2">
         <v>60571.264168359397</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="2">
         <v>13793.82312956908</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="2">
         <v>46777.441038790319</v>
       </c>
       <c r="F66">
@@ -1722,13 +1733,13 @@
       <c r="B67" t="s">
         <v>10</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="2">
         <v>61455.772903641722</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="2">
         <v>14246.441988221199</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="2">
         <v>47209.33091542052</v>
       </c>
       <c r="F67">
@@ -1742,13 +1753,13 @@
       <c r="B68" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="2">
         <v>66337.000703474798</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="2">
         <v>14766.058660192595</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="2">
         <v>51570.942043282201</v>
       </c>
       <c r="F68">
@@ -1762,13 +1773,13 @@
       <c r="B69" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="2">
         <v>66243.467107830395</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="2">
         <v>15048.606484654056</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="2">
         <v>51194.860623176341</v>
       </c>
       <c r="F69">
@@ -1782,13 +1793,13 @@
       <c r="B70" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="2">
         <v>65126.618559629576</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="2">
         <v>15210.191904310497</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="2">
         <v>49916.426655319083</v>
       </c>
       <c r="F70">
@@ -1802,13 +1813,13 @@
       <c r="B71" t="s">
         <v>14</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="2">
         <v>65809.724506028433</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="2">
         <v>15886.610114547811</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>49923.114391480623</v>
       </c>
       <c r="F71">
@@ -1822,13 +1833,13 @@
       <c r="B72" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="2">
         <v>68812.047016905606</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="2">
         <v>16182.411607081516</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="2">
         <v>52629.635409824092</v>
       </c>
       <c r="F72">
@@ -1842,13 +1853,13 @@
       <c r="B73" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="2">
         <v>75367.344535418175</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="2">
         <v>16917.932998585416</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="2">
         <v>58449.411536832762</v>
       </c>
       <c r="F73">
@@ -1862,13 +1873,13 @@
       <c r="B74" t="s">
         <v>5</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="2">
         <v>61650.117977190799</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="2">
         <v>12096.026018327382</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="2">
         <v>49554.091958863413</v>
       </c>
       <c r="F74">
@@ -1882,13 +1893,13 @@
       <c r="B75" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="2">
         <v>69276.649879479344</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="2">
         <v>11692.651175314717</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="2">
         <v>57583.998704164624</v>
       </c>
       <c r="F75">
@@ -1902,13 +1913,13 @@
       <c r="B76" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="2">
         <v>58076.795237136474</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="2">
         <v>12217.076010635725</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="2">
         <v>45859.719226500747</v>
       </c>
       <c r="F76">
@@ -1922,13 +1933,13 @@
       <c r="B77" t="s">
         <v>8</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="2">
         <v>57135.374455117715</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="2">
         <v>12623.063472337913</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="2">
         <v>44512.310982779803</v>
       </c>
       <c r="F77">
@@ -1942,13 +1953,13 @@
       <c r="B78" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="2">
         <v>62480.582996670542</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78" s="2">
         <v>13079.571061754499</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78" s="2">
         <v>49401.011934916045</v>
       </c>
       <c r="F78">
@@ -1962,13 +1973,13 @@
       <c r="B79" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="2">
         <v>58484.775860981325</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="2">
         <v>13248.582537934368</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79" s="2">
         <v>45236.193323046959</v>
       </c>
       <c r="F79">
@@ -1982,13 +1993,13 @@
       <c r="B80" t="s">
         <v>11</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="2">
         <v>59196.954618506999</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80" s="2">
         <v>14099.122997477327</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80" s="2">
         <v>45097.831621029676</v>
       </c>
       <c r="F80">
@@ -2002,13 +2013,13 @@
       <c r="B81" t="s">
         <v>12</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="2">
         <v>60484.095847184246</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81" s="2">
         <v>14561.340864337599</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81" s="2">
         <v>45922.754982846644</v>
       </c>
       <c r="F81">
@@ -2022,13 +2033,13 @@
       <c r="B82" t="s">
         <v>13</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="2">
         <v>61384.625898967228</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82" s="2">
         <v>14758.735738501069</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82" s="2">
         <v>46625.890160466159</v>
       </c>
       <c r="F82">
@@ -2042,13 +2053,13 @@
       <c r="B83" t="s">
         <v>14</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="2">
         <v>62885.479902983796</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="2">
         <v>15579.885690979034</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83" s="2">
         <v>47305.594212004762</v>
       </c>
       <c r="F83">
@@ -2062,13 +2073,13 @@
       <c r="B84" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="2">
         <v>63364.685394820444</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84" s="2">
         <v>15498.626382091608</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84" s="2">
         <v>47866.059012728838</v>
       </c>
       <c r="F84">
@@ -2082,13 +2093,13 @@
       <c r="B85" t="s">
         <v>16</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="2">
         <v>65927.099982887041</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85" s="2">
         <v>15818.548852178592</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85" s="2">
         <v>50108.551130708453</v>
       </c>
       <c r="F85">
@@ -2102,11 +2113,11 @@
       <c r="B86" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="2">
         <v>63725.229914205935</v>
       </c>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
       <c r="F86">
         <v>0.05</v>
       </c>
@@ -2118,11 +2129,11 @@
       <c r="B87" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="2">
         <v>65415.265259352978</v>
       </c>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
       <c r="F87">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2134,11 +2145,11 @@
       <c r="B88" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="2">
         <v>70368.514697734805</v>
       </c>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
       <c r="F88">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2150,11 +2161,11 @@
       <c r="B89" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="2">
         <v>69374.077526891735</v>
       </c>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
       <c r="F89">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2166,11 +2177,11 @@
       <c r="B90" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="2">
         <v>70818.204072076362</v>
       </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
       <c r="F90">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2182,11 +2193,11 @@
       <c r="B91" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91" s="2">
         <v>69888.728750856215</v>
       </c>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
       <c r="F91">
         <v>5.2499999999999998E-2</v>
       </c>
@@ -2198,11 +2209,11 @@
       <c r="B92" t="s">
         <v>11</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="2">
         <v>71207.490530704876</v>
       </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
       <c r="F92">
         <v>0.05</v>
       </c>
@@ -2214,11 +2225,11 @@
       <c r="B93" t="s">
         <v>12</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="2">
         <v>72055.689724337324</v>
       </c>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
       <c r="F93">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2230,11 +2241,11 @@
       <c r="B94" t="s">
         <v>13</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="2">
         <v>72919.743963731147</v>
       </c>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
       <c r="F94">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2246,11 +2257,11 @@
       <c r="B95" t="s">
         <v>14</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95" s="2">
         <v>75234.579967030309</v>
       </c>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
       <c r="F95">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -2262,11 +2273,11 @@
       <c r="B96" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="2">
         <v>75289.523450518114</v>
       </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
       <c r="F96">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -2278,11 +2289,11 @@
       <c r="B97" t="s">
         <v>16</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="2">
         <v>79405.445935437034</v>
       </c>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
       <c r="F97">
         <v>4.2500000000000003E-2</v>
       </c>
@@ -2294,13 +2305,13 @@
       <c r="B98" t="s">
         <v>5</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="2">
         <v>82128.103555092719</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D98" s="2">
         <v>20606.475300367747</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98" s="2">
         <v>61521.628254724972</v>
       </c>
       <c r="F98">
@@ -2314,13 +2325,13 @@
       <c r="B99" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="2">
         <v>79724.534947023261</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D99" s="2">
         <v>19258.418337713854</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99" s="2">
         <v>60466.116609309407</v>
       </c>
       <c r="F99">
@@ -2334,13 +2345,13 @@
       <c r="B100" t="s">
         <v>7</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="2">
         <v>90636.787861366858</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D100" s="2">
         <v>20352.877932465653</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100" s="2">
         <v>70283.909928901208</v>
       </c>
       <c r="F100">
@@ -2354,13 +2365,13 @@
       <c r="B101" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101" s="2">
         <v>78875.848020440608</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D101" s="2">
         <v>20908.511983224253</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101" s="2">
         <v>57967.336037216359</v>
       </c>
       <c r="F101">
@@ -2374,13 +2385,13 @@
       <c r="B102" t="s">
         <v>9</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="2">
         <v>84316.561715054748</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D102" s="2">
         <v>21464.27168116441</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102" s="2">
         <v>62852.290033890342</v>
       </c>
       <c r="F102">
@@ -2394,13 +2405,13 @@
       <c r="B103" t="s">
         <v>10</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103" s="2">
         <v>81591.628930762308</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D103" s="2">
         <v>20951.35566565302</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103" s="2">
         <v>60640.273265109288</v>
       </c>
       <c r="F103">
@@ -2414,13 +2425,13 @@
       <c r="B104" t="s">
         <v>11</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="2">
         <v>82143.602919138953</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104" s="2">
         <v>22312.822677317752</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104" s="2">
         <v>59830.780241821201</v>
       </c>
       <c r="F104">
@@ -2434,13 +2445,13 @@
       <c r="B105" t="s">
         <v>12</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105" s="2">
         <v>82372.110876232255</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105" s="2">
         <v>22737.4821369575</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105" s="2">
         <v>59634.628739274754</v>
       </c>
       <c r="F105">
@@ -2454,13 +2465,13 @@
       <c r="B106" t="s">
         <v>13</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="2">
         <v>83426.735220732327</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D106" s="2">
         <v>22464.958446245542</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106" s="2">
         <v>60961.776774486789</v>
       </c>
       <c r="F106">
@@ -2474,13 +2485,13 @@
       <c r="B107" t="s">
         <v>14</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="2">
         <v>85756.241653853765</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D107" s="2">
         <v>23124.219879069002</v>
       </c>
-      <c r="E107" s="1">
+      <c r="E107" s="2">
         <v>62632.021774784764</v>
       </c>
       <c r="F107">
@@ -2494,13 +2505,13 @@
       <c r="B108" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108" s="2">
         <v>86588.919003799107</v>
       </c>
-      <c r="D108" s="1">
+      <c r="D108" s="2">
         <v>23246.408345336917</v>
       </c>
-      <c r="E108" s="1">
+      <c r="E108" s="2">
         <v>63342.51065846219</v>
       </c>
       <c r="F108">
@@ -2514,13 +2525,13 @@
       <c r="B109" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109" s="2">
         <v>87389.131249876067</v>
       </c>
-      <c r="D109" s="1">
+      <c r="D109" s="2">
         <v>23444.684997952456</v>
       </c>
-      <c r="E109" s="1">
+      <c r="E109" s="2">
         <v>63944.446251923611</v>
       </c>
       <c r="F109">
@@ -2534,13 +2545,13 @@
       <c r="B110" t="s">
         <v>5</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="2">
         <v>75661.628297290517</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D110" s="2">
         <v>18254.639711403248</v>
       </c>
-      <c r="E110" s="1">
+      <c r="E110" s="2">
         <v>57406.988585887273</v>
       </c>
       <c r="F110">
@@ -2554,13 +2565,13 @@
       <c r="B111" t="s">
         <v>6</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="2">
         <v>74663.431089441758</v>
       </c>
-      <c r="D111" s="1">
+      <c r="D111" s="2">
         <v>17305.906696277838</v>
       </c>
-      <c r="E111" s="1">
+      <c r="E111" s="2">
         <v>57357.52439316392</v>
       </c>
       <c r="F111">
@@ -2574,13 +2585,13 @@
       <c r="B112" t="s">
         <v>7</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="2">
         <v>77748.724676647937</v>
       </c>
-      <c r="D112" s="1">
+      <c r="D112" s="2">
         <v>18360.549261275373</v>
       </c>
-      <c r="E112" s="1">
+      <c r="E112" s="2">
         <v>59388.175415372563</v>
       </c>
       <c r="F112">
@@ -2594,13 +2605,13 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113" s="2">
         <v>81918.32014703007</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D113" s="2">
         <v>18567.845016223509</v>
       </c>
-      <c r="E113" s="1">
+      <c r="E113" s="2">
         <v>63350.475130806561</v>
       </c>
       <c r="F113">
@@ -2614,13 +2625,13 @@
       <c r="B114" t="s">
         <v>9</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="2">
         <v>79936.927433566729</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="2">
         <v>19333.665587871212</v>
       </c>
-      <c r="E114" s="1">
+      <c r="E114" s="2">
         <v>60603.261845695517</v>
       </c>
       <c r="F114">
@@ -2634,13 +2645,13 @@
       <c r="B115" t="s">
         <v>10</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="2">
         <v>80986.672704775876</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="2">
         <v>19118.779101501372</v>
       </c>
-      <c r="E115" s="1">
+      <c r="E115" s="2">
         <v>61867.893603274504</v>
       </c>
       <c r="F115">
@@ -2654,13 +2665,13 @@
       <c r="B116" t="s">
         <v>11</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="2">
         <v>82157.333083374542</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="2">
         <v>20520.263036306296</v>
       </c>
-      <c r="E116" s="1">
+      <c r="E116" s="2">
         <v>61637.07004706825</v>
       </c>
       <c r="F116">
@@ -2674,13 +2685,13 @@
       <c r="B117" t="s">
         <v>12</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="2">
         <v>83188.122126282455</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="2">
         <v>21627.188010330829</v>
       </c>
-      <c r="E117" s="1">
+      <c r="E117" s="2">
         <v>61560.934115951626</v>
       </c>
       <c r="F117">
@@ -2694,13 +2705,13 @@
       <c r="B118" t="s">
         <v>13</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="2">
         <v>85693.698487573871</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D118" s="2">
         <v>22248.690953455389</v>
       </c>
-      <c r="E118" s="1">
+      <c r="E118" s="2">
         <v>63445.007534118486</v>
       </c>
       <c r="F118">
@@ -2714,13 +2725,13 @@
       <c r="B119" t="s">
         <v>14</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="2">
         <v>86354.455163383638</v>
       </c>
-      <c r="D119" s="1">
+      <c r="D119" s="2">
         <v>24047.825938781352</v>
       </c>
-      <c r="E119" s="1">
+      <c r="E119" s="2">
         <v>62306.629224602286</v>
       </c>
       <c r="F119">
@@ -2734,13 +2745,13 @@
       <c r="B120" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120" s="2">
         <v>92969.208679682037</v>
       </c>
-      <c r="D120" s="1">
+      <c r="D120" s="2">
         <v>24016.71427782948</v>
       </c>
-      <c r="E120" s="1">
+      <c r="E120" s="2">
         <v>68952.494401852557</v>
       </c>
       <c r="F120">
@@ -2754,13 +2765,13 @@
       <c r="B121" t="s">
         <v>16</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121" s="2">
         <v>88718.739659897241</v>
       </c>
-      <c r="D121" s="1">
+      <c r="D121" s="2">
         <v>24262.250361025668</v>
       </c>
-      <c r="E121" s="1">
+      <c r="E121" s="2">
         <v>64456.489298871573</v>
       </c>
       <c r="F121">
@@ -2774,13 +2785,13 @@
       <c r="B122" t="s">
         <v>5</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122" s="2">
         <v>81104.713611400774</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D122" s="2">
         <v>20618.745536820454</v>
       </c>
-      <c r="E122" s="1">
+      <c r="E122" s="2">
         <v>60485.96807458032</v>
       </c>
       <c r="F122">
@@ -2794,13 +2805,13 @@
       <c r="B123" t="s">
         <v>6</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123" s="2">
         <v>79129.257307517881</v>
       </c>
-      <c r="D123" s="1">
+      <c r="D123" s="2">
         <v>19717.93212574756</v>
       </c>
-      <c r="E123" s="1">
+      <c r="E123" s="2">
         <v>59411.32518177032</v>
       </c>
       <c r="F123">
@@ -2814,13 +2825,13 @@
       <c r="B124" t="s">
         <v>7</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124" s="2">
         <v>83137.781314644322</v>
       </c>
-      <c r="D124" s="1">
+      <c r="D124" s="2">
         <v>21010.605429227719</v>
       </c>
-      <c r="E124" s="1">
+      <c r="E124" s="2">
         <v>62127.175885416604</v>
       </c>
       <c r="F124">
@@ -2834,13 +2845,13 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125" s="2">
         <v>85086.874362168484</v>
       </c>
-      <c r="D125" s="1">
+      <c r="D125" s="2">
         <v>21015.65532599821</v>
       </c>
-      <c r="E125" s="1">
+      <c r="E125" s="2">
         <v>64071.219036170274</v>
       </c>
       <c r="F125">
@@ -2854,13 +2865,13 @@
       <c r="B126" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="2">
         <v>85512.985221940908</v>
       </c>
-      <c r="D126" s="1">
+      <c r="D126" s="2">
         <v>22092.662782568077</v>
       </c>
-      <c r="E126" s="1">
+      <c r="E126" s="2">
         <v>63420.322439372831</v>
       </c>
       <c r="F126">
@@ -2874,13 +2885,13 @@
       <c r="B127" t="s">
         <v>10</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="2">
         <v>85712.329610397734</v>
       </c>
-      <c r="D127" s="1">
+      <c r="D127" s="2">
         <v>21231.279706975824</v>
       </c>
-      <c r="E127" s="1">
+      <c r="E127" s="2">
         <v>64481.04990342191</v>
       </c>
       <c r="F127">
@@ -2894,13 +2905,13 @@
       <c r="B128" t="s">
         <v>11</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="2">
         <v>87644.021569282559</v>
       </c>
-      <c r="D128" s="1">
+      <c r="D128" s="2">
         <v>21767.603138499264</v>
       </c>
-      <c r="E128" s="1">
+      <c r="E128" s="2">
         <v>65876.418430783291</v>
       </c>
       <c r="F128">
@@ -2914,13 +2925,13 @@
       <c r="B129" t="s">
         <v>12</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="2">
         <v>88634.974852048166</v>
       </c>
-      <c r="D129" s="1">
+      <c r="D129" s="2">
         <v>22295.395717440166</v>
       </c>
-      <c r="E129" s="1">
+      <c r="E129" s="2">
         <v>66339.579134608008</v>
       </c>
       <c r="F129">
@@ -2934,13 +2945,13 @@
       <c r="B130" t="s">
         <v>13</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="2">
         <v>89190.834807761785</v>
       </c>
-      <c r="D130" s="1">
+      <c r="D130" s="2">
         <v>22240.169715475982</v>
       </c>
-      <c r="E130" s="1">
+      <c r="E130" s="2">
         <v>66950.66509228581</v>
       </c>
       <c r="F130">
@@ -2954,13 +2965,13 @@
       <c r="B131" t="s">
         <v>14</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="2">
         <v>93530.233742057608</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D131" s="2">
         <v>23002.923832440949</v>
       </c>
-      <c r="E131" s="1">
+      <c r="E131" s="2">
         <v>70527.309909616655</v>
       </c>
       <c r="F131">
@@ -2974,13 +2985,13 @@
       <c r="B132" t="s">
         <v>15</v>
       </c>
-      <c r="C132" s="2">
+      <c r="C132" s="3">
         <v>81159.76346175003</v>
       </c>
-      <c r="D132" s="2">
+      <c r="D132" s="3">
         <v>25681.573973339997</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="3">
         <v>55478.189488410033</v>
       </c>
       <c r="F132">
@@ -2994,13 +3005,13 @@
       <c r="B133" t="s">
         <v>16</v>
       </c>
-      <c r="C133" s="3">
+      <c r="C133" s="4">
         <v>82713.761696080008</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133" s="4">
         <v>27042.351269680003</v>
       </c>
-      <c r="E133" s="3">
+      <c r="E133" s="4">
         <v>55671.410426400005</v>
       </c>
       <c r="F133">
@@ -3014,13 +3025,13 @@
       <c r="B134" t="s">
         <v>5</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134" s="4">
         <v>83948.018517999997</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134" s="4">
         <v>28065.733887999995</v>
       </c>
-      <c r="E134" s="4">
+      <c r="E134" s="5">
         <v>55882.284630000002</v>
       </c>
       <c r="F134">
@@ -3034,13 +3045,13 @@
       <c r="B135" t="s">
         <v>6</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135" s="4">
         <v>85120.711910999991</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135" s="4">
         <v>29264.341014999998</v>
       </c>
-      <c r="E135" s="4">
+      <c r="E135" s="5">
         <v>55856.370895999993</v>
       </c>
       <c r="F135">
@@ -3054,13 +3065,13 @@
       <c r="B136" t="s">
         <v>7</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136" s="4">
         <v>110922.72586500001</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136" s="4">
         <v>32878.917699999991</v>
       </c>
-      <c r="E136" s="4">
+      <c r="E136" s="5">
         <v>78043.808165000024</v>
       </c>
       <c r="F136">
@@ -3074,13 +3085,13 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137" s="4">
         <v>123371.21351311001</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137" s="4">
         <v>34663.411336999998</v>
       </c>
-      <c r="E137" s="4">
+      <c r="E137" s="5">
         <v>88707.80217611001</v>
       </c>
       <c r="F137">
@@ -3094,13 +3105,13 @@
       <c r="B138" t="s">
         <v>9</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138" s="4">
         <v>133093.31922899999</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138" s="4">
         <v>37177.40969</v>
       </c>
-      <c r="E138" s="4">
+      <c r="E138" s="5">
         <v>95915.909538999986</v>
       </c>
       <c r="F138">
@@ -3114,13 +3125,13 @@
       <c r="B139" t="s">
         <v>10</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139" s="4">
         <v>42994.594308889988</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D139" s="4">
         <v>38035.21396400001</v>
       </c>
-      <c r="E139" s="4">
+      <c r="E139" s="5">
         <v>4959.380344889978</v>
       </c>
       <c r="F139">
@@ -3134,13 +3145,13 @@
       <c r="B140" t="s">
         <v>11</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140" s="4">
         <v>104266.888657</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140" s="4">
         <v>39970.546859000002</v>
       </c>
-      <c r="E140" s="4">
+      <c r="E140" s="5">
         <v>64296.341798000001</v>
       </c>
       <c r="F140">
@@ -3154,13 +3165,13 @@
       <c r="B141" t="s">
         <v>12</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141" s="4">
         <v>104229.48909100002</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141" s="4">
         <v>40804.789896000009</v>
       </c>
-      <c r="E141" s="4">
+      <c r="E141" s="5">
         <v>63424.699195000016</v>
       </c>
       <c r="F141">
@@ -3174,13 +3185,13 @@
       <c r="B142" t="s">
         <v>13</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142" s="4">
         <v>103818.62562800001</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142" s="4">
         <v>41085.689405999998</v>
       </c>
-      <c r="E142" s="4">
+      <c r="E142" s="5">
         <v>62732.936222000011</v>
       </c>
       <c r="F142">
@@ -3194,13 +3205,13 @@
       <c r="B143" t="s">
         <v>14</v>
       </c>
-      <c r="C143" s="3">
+      <c r="C143" s="4">
         <v>99674.036412999994</v>
       </c>
-      <c r="D143" s="3">
+      <c r="D143" s="4">
         <v>43624.468536</v>
       </c>
-      <c r="E143" s="4">
+      <c r="E143" s="5">
         <v>56049.567876999994</v>
       </c>
       <c r="F143">
@@ -3214,13 +3225,13 @@
       <c r="B144" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="3">
+      <c r="C144" s="4">
         <v>113205.491565</v>
       </c>
-      <c r="D144" s="3">
+      <c r="D144" s="4">
         <v>42559.011853000011</v>
       </c>
-      <c r="E144" s="4">
+      <c r="E144" s="5">
         <v>70646.479712</v>
       </c>
       <c r="F144">
@@ -3234,13 +3245,13 @@
       <c r="B145" t="s">
         <v>16</v>
       </c>
-      <c r="C145" s="3">
+      <c r="C145" s="4">
         <v>108152.695545</v>
       </c>
-      <c r="D145" s="3">
+      <c r="D145" s="4">
         <v>43146.437588000008</v>
       </c>
-      <c r="E145" s="3">
+      <c r="E145" s="4">
         <v>65006.257956999987</v>
       </c>
       <c r="F145">
@@ -3254,13 +3265,13 @@
       <c r="B146" t="s">
         <v>5</v>
       </c>
-      <c r="C146" s="3">
+      <c r="C146" s="4">
         <v>110794.26754649998</v>
       </c>
-      <c r="D146" s="3">
+      <c r="D146" s="4">
         <v>43652.097158390003</v>
       </c>
-      <c r="E146" s="4">
+      <c r="E146" s="5">
         <v>67142.170388109982</v>
       </c>
       <c r="F146">
@@ -3274,13 +3285,13 @@
       <c r="B147" t="s">
         <v>6</v>
       </c>
-      <c r="C147" s="3">
+      <c r="C147" s="4">
         <v>107378.78004900001</v>
       </c>
-      <c r="D147" s="3">
+      <c r="D147" s="4">
         <v>40277.140068000001</v>
       </c>
-      <c r="E147" s="4">
+      <c r="E147" s="5">
         <v>67101.639981000015</v>
       </c>
       <c r="F147">
@@ -3294,13 +3305,13 @@
       <c r="B148" t="s">
         <v>7</v>
       </c>
-      <c r="C148" s="3">
+      <c r="C148" s="4">
         <v>108204.43721600001</v>
       </c>
-      <c r="D148" s="3">
+      <c r="D148" s="4">
         <v>41497.490763000002</v>
       </c>
-      <c r="E148" s="4">
+      <c r="E148" s="5">
         <v>66706.946453000011</v>
       </c>
       <c r="F148">
@@ -3314,13 +3325,13 @@
       <c r="B149" t="s">
         <v>8</v>
       </c>
-      <c r="C149" s="3">
+      <c r="C149" s="4">
         <v>116180.137313</v>
       </c>
-      <c r="D149" s="3">
+      <c r="D149" s="4">
         <v>38578.836761999963</v>
       </c>
-      <c r="E149" s="4">
+      <c r="E149" s="5">
         <v>77601.300551000037</v>
       </c>
       <c r="F149">
@@ -3334,13 +3345,13 @@
       <c r="B150" t="s">
         <v>9</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C150" s="4">
         <v>107296.76061000001</v>
       </c>
-      <c r="D150" s="3">
+      <c r="D150" s="4">
         <v>38331.305578</v>
       </c>
-      <c r="E150" s="4">
+      <c r="E150" s="5">
         <v>68965.455032000013</v>
       </c>
       <c r="F150">
@@ -3354,13 +3365,13 @@
       <c r="B151" t="s">
         <v>10</v>
       </c>
-      <c r="C151" s="3">
+      <c r="C151" s="4">
         <v>107657.629265</v>
       </c>
-      <c r="D151" s="3">
+      <c r="D151" s="4">
         <v>34075.932967000001</v>
       </c>
-      <c r="E151" s="4">
+      <c r="E151" s="5">
         <v>73581.696297999995</v>
       </c>
       <c r="F151">
@@ -3374,13 +3385,13 @@
       <c r="B152" t="s">
         <v>11</v>
       </c>
-      <c r="C152" s="3">
+      <c r="C152" s="4">
         <v>107398.25651100003</v>
       </c>
-      <c r="D152" s="3">
+      <c r="D152" s="4">
         <v>33178.814491000005</v>
       </c>
-      <c r="E152" s="4">
+      <c r="E152" s="5">
         <v>74219.442020000017</v>
       </c>
       <c r="F152">
@@ -3394,13 +3405,13 @@
       <c r="B153" t="s">
         <v>12</v>
       </c>
-      <c r="C153" s="3">
+      <c r="C153" s="4">
         <v>105472.14983700002</v>
       </c>
-      <c r="D153" s="3">
+      <c r="D153" s="4">
         <v>31816.9827</v>
       </c>
-      <c r="E153" s="4">
+      <c r="E153" s="5">
         <v>73655.167137000011</v>
       </c>
       <c r="F153">
@@ -3414,13 +3425,13 @@
       <c r="B154" t="s">
         <v>13</v>
       </c>
-      <c r="C154" s="3">
+      <c r="C154" s="4">
         <v>106806.00375700003</v>
       </c>
-      <c r="D154" s="3">
+      <c r="D154" s="4">
         <v>31143.417265999997</v>
       </c>
-      <c r="E154" s="4">
+      <c r="E154" s="5">
         <v>75662.586491000024</v>
       </c>
       <c r="F154">
@@ -3434,13 +3445,13 @@
       <c r="B155" t="s">
         <v>14</v>
       </c>
-      <c r="C155" s="3">
+      <c r="C155" s="4">
         <v>107689.120717</v>
       </c>
-      <c r="D155" s="3">
+      <c r="D155" s="4">
         <v>30892.543975999997</v>
       </c>
-      <c r="E155" s="4">
+      <c r="E155" s="5">
         <v>76796.576740999997</v>
       </c>
       <c r="F155">
@@ -3454,13 +3465,13 @@
       <c r="B156" t="s">
         <v>15</v>
       </c>
-      <c r="C156" s="3">
+      <c r="C156" s="4">
         <v>107967.03632900001</v>
       </c>
-      <c r="D156" s="3">
+      <c r="D156" s="4">
         <v>30087.126321</v>
       </c>
-      <c r="E156" s="4">
+      <c r="E156" s="5">
         <v>77879.910008000006</v>
       </c>
       <c r="F156">
@@ -3474,13 +3485,13 @@
       <c r="B157" t="s">
         <v>16</v>
       </c>
-      <c r="C157" s="3">
+      <c r="C157" s="4">
         <v>109730.02317499999</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D157" s="4">
         <v>29543.848790999993</v>
       </c>
-      <c r="E157" s="3">
+      <c r="E157" s="4">
         <v>80186.174383999998</v>
       </c>
       <c r="F157">
@@ -3494,13 +3505,13 @@
       <c r="B158" t="s">
         <v>5</v>
       </c>
-      <c r="C158" s="3">
+      <c r="C158" s="4">
         <v>108210.17232199998</v>
       </c>
-      <c r="D158" s="3">
+      <c r="D158" s="4">
         <v>30193.952205000005</v>
       </c>
-      <c r="E158" s="4">
+      <c r="E158" s="5">
         <v>78016.220116999975</v>
       </c>
       <c r="F158">
@@ -3514,13 +3525,13 @@
       <c r="B159" t="s">
         <v>6</v>
       </c>
-      <c r="C159" s="3">
+      <c r="C159" s="4">
         <v>107807.518679</v>
       </c>
-      <c r="D159" s="3">
+      <c r="D159" s="4">
         <v>28916.706235999998</v>
       </c>
-      <c r="E159" s="4">
+      <c r="E159" s="5">
         <v>78890.812443000003</v>
       </c>
       <c r="F159">
@@ -3534,13 +3545,13 @@
       <c r="B160" t="s">
         <v>7</v>
       </c>
-      <c r="C160" s="3">
+      <c r="C160" s="4">
         <v>112172.42679</v>
       </c>
-      <c r="D160" s="3">
+      <c r="D160" s="4">
         <v>30325.053654000003</v>
       </c>
-      <c r="E160" s="4">
+      <c r="E160" s="5">
         <v>81847.373135999995</v>
       </c>
       <c r="F160">
@@ -3554,13 +3565,13 @@
       <c r="B161" t="s">
         <v>8</v>
       </c>
-      <c r="C161" s="3">
+      <c r="C161" s="4">
         <v>110712.26686999999</v>
       </c>
-      <c r="D161" s="3">
+      <c r="D161" s="4">
         <v>29730.311683000004</v>
       </c>
-      <c r="E161" s="4">
+      <c r="E161" s="5">
         <v>80981.955186999985</v>
       </c>
       <c r="F161">
@@ -3574,13 +3585,13 @@
       <c r="B162" t="s">
         <v>9</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="4">
         <v>111355.04839200001</v>
       </c>
-      <c r="D162" s="3">
+      <c r="D162" s="4">
         <v>29908.714478999998</v>
       </c>
-      <c r="E162" s="4">
+      <c r="E162" s="5">
         <v>81446.333913000009</v>
       </c>
       <c r="F162">
@@ -3594,13 +3605,13 @@
       <c r="B163" t="s">
         <v>10</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="4">
         <v>115517.33253599999</v>
       </c>
-      <c r="D163" s="3">
+      <c r="D163" s="4">
         <v>30122.491545000001</v>
       </c>
-      <c r="E163" s="4">
+      <c r="E163" s="5">
         <v>85394.84099099999</v>
       </c>
       <c r="F163">
@@ -3614,13 +3625,13 @@
       <c r="B164" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="4">
         <v>113301.148403</v>
       </c>
-      <c r="D164" s="3">
+      <c r="D164" s="4">
         <v>30707.629485999994</v>
       </c>
-      <c r="E164" s="4">
+      <c r="E164" s="5">
         <v>82593.518917000009</v>
       </c>
       <c r="F164">
@@ -3634,13 +3645,13 @@
       <c r="B165" t="s">
         <v>12</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="4">
         <v>114975.85828299998</v>
       </c>
-      <c r="D165" s="3">
+      <c r="D165" s="4">
         <v>31277.826622000004</v>
       </c>
-      <c r="E165" s="4">
+      <c r="E165" s="5">
         <v>83698.031660999972</v>
       </c>
       <c r="F165">
@@ -3654,13 +3665,13 @@
       <c r="B166" t="s">
         <v>13</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="4">
         <v>116217.76634099998</v>
       </c>
-      <c r="D166" s="3">
+      <c r="D166" s="4">
         <v>31443.534651999998</v>
       </c>
-      <c r="E166" s="4">
+      <c r="E166" s="5">
         <v>84774.231688999978</v>
       </c>
       <c r="F166">
@@ -3674,13 +3685,13 @@
       <c r="B167" t="s">
         <v>14</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="4">
         <v>118938.66359899998</v>
       </c>
-      <c r="D167" s="3">
+      <c r="D167" s="4">
         <v>32309.224536999998</v>
       </c>
-      <c r="E167" s="4">
+      <c r="E167" s="5">
         <v>86629.439061999976</v>
       </c>
       <c r="F167">
@@ -3694,13 +3705,13 @@
       <c r="B168" t="s">
         <v>15</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="4">
         <v>119807.181121</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D168" s="4">
         <v>31949.527981999996</v>
       </c>
-      <c r="E168" s="4">
+      <c r="E168" s="5">
         <v>87857.653139000002</v>
       </c>
       <c r="F168">
@@ -3714,13 +3725,13 @@
       <c r="B169" t="s">
         <v>16</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="4">
         <v>121082.37949200001</v>
       </c>
-      <c r="D169" s="3">
+      <c r="D169" s="4">
         <v>33133.251284999998</v>
       </c>
-      <c r="E169" s="3">
+      <c r="E169" s="4">
         <v>87949.128207000002</v>
       </c>
       <c r="F169">
@@ -3734,13 +3745,13 @@
       <c r="B170" t="s">
         <v>5</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="4">
         <v>119778.41886799999</v>
       </c>
-      <c r="D170" s="3">
+      <c r="D170" s="4">
         <v>33108.165737999996</v>
       </c>
-      <c r="E170" s="4">
+      <c r="E170" s="5">
         <v>86670.253129999997</v>
       </c>
       <c r="F170">
@@ -3754,13 +3765,13 @@
       <c r="B171" t="s">
         <v>6</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="4">
         <v>118274.87509999999</v>
       </c>
-      <c r="D171" s="3">
+      <c r="D171" s="4">
         <v>32508.165452000001</v>
       </c>
-      <c r="E171" s="4">
+      <c r="E171" s="5">
         <v>85766.709647999989</v>
       </c>
       <c r="F171">
@@ -3774,13 +3785,13 @@
       <c r="B172" t="s">
         <v>7</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="4">
         <v>123174.88595600001</v>
       </c>
-      <c r="D172" s="3">
+      <c r="D172" s="4">
         <v>35956.871963999998</v>
       </c>
-      <c r="E172" s="4">
+      <c r="E172" s="5">
         <v>87218.013992000022</v>
       </c>
       <c r="F172">
@@ -3794,13 +3805,13 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="4">
         <v>122885.27039999999</v>
       </c>
-      <c r="D173" s="3">
+      <c r="D173" s="4">
         <v>34823.922981000003</v>
       </c>
-      <c r="E173" s="4">
+      <c r="E173" s="5">
         <v>88061.347418999998</v>
       </c>
       <c r="F173">
@@ -3814,13 +3825,13 @@
       <c r="B174" t="s">
         <v>9</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="4">
         <v>123832.58759799998</v>
       </c>
-      <c r="D174" s="3">
+      <c r="D174" s="4">
         <v>36166.774099999995</v>
       </c>
-      <c r="E174" s="4">
+      <c r="E174" s="5">
         <v>87665.813497999989</v>
       </c>
       <c r="F174">
@@ -3834,13 +3845,13 @@
       <c r="B175" t="s">
         <v>10</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="4">
         <v>124330.89199999999</v>
       </c>
-      <c r="D175" s="3">
+      <c r="D175" s="4">
         <v>36305.866878999994</v>
       </c>
-      <c r="E175" s="4">
+      <c r="E175" s="5">
         <v>88025.025120999999</v>
       </c>
       <c r="F175">
@@ -3854,13 +3865,13 @@
       <c r="B176" t="s">
         <v>11</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="4">
         <v>120900.93006499999</v>
       </c>
-      <c r="D176" s="3">
+      <c r="D176" s="4">
         <v>35675.594138</v>
       </c>
-      <c r="E176" s="4">
+      <c r="E176" s="5">
         <v>85225.335926999993</v>
       </c>
       <c r="F176">
@@ -3874,13 +3885,13 @@
       <c r="B177" t="s">
         <v>12</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="4">
         <v>122543.73404000001</v>
       </c>
-      <c r="D177" s="3">
+      <c r="D177" s="4">
         <v>35925.061013999999</v>
       </c>
-      <c r="E177" s="4">
+      <c r="E177" s="5">
         <v>86618.673026000004</v>
       </c>
       <c r="F177">
@@ -3894,13 +3905,13 @@
       <c r="B178" t="s">
         <v>13</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="4">
         <v>121556.85282900001</v>
       </c>
-      <c r="D178" s="3">
+      <c r="D178" s="4">
         <v>35148.023977000004</v>
       </c>
-      <c r="E178" s="4">
+      <c r="E178" s="5">
         <v>86408.828852000006</v>
       </c>
       <c r="F178">
@@ -3914,13 +3925,13 @@
       <c r="B179" t="s">
         <v>14</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="4">
         <v>119896.29622600001</v>
       </c>
-      <c r="D179" s="3">
+      <c r="D179" s="4">
         <v>35294.833906</v>
       </c>
-      <c r="E179" s="4">
+      <c r="E179" s="5">
         <v>84601.462320000006</v>
       </c>
       <c r="F179">
@@ -3934,13 +3945,13 @@
       <c r="B180" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="4">
         <v>120501.64427700001</v>
       </c>
-      <c r="D180" s="3">
+      <c r="D180" s="4">
         <v>34496.899754000005</v>
       </c>
-      <c r="E180" s="4">
+      <c r="E180" s="5">
         <v>86004.744523000001</v>
       </c>
       <c r="F180">
@@ -3954,13 +3965,13 @@
       <c r="B181" t="s">
         <v>16</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="4">
         <v>122841.510928</v>
       </c>
-      <c r="D181" s="3">
+      <c r="D181" s="4">
         <v>35565.831188999982</v>
       </c>
-      <c r="E181" s="3">
+      <c r="E181" s="4">
         <v>87275.679739000014</v>
       </c>
       <c r="F181">
@@ -3974,13 +3985,13 @@
       <c r="B182" t="s">
         <v>5</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="4">
         <v>118262.07046100001</v>
       </c>
-      <c r="D182" s="3">
+      <c r="D182" s="4">
         <v>35895.134258000006</v>
       </c>
-      <c r="E182" s="4">
+      <c r="E182" s="5">
         <v>82366.936203000005</v>
       </c>
       <c r="F182">
@@ -3994,13 +4005,13 @@
       <c r="B183" t="s">
         <v>6</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="4">
         <v>118590.68042000002</v>
       </c>
-      <c r="D183" s="3">
+      <c r="D183" s="4">
         <v>34231.951384</v>
       </c>
-      <c r="E183" s="4">
+      <c r="E183" s="5">
         <v>84358.729036000019</v>
       </c>
       <c r="F183">
@@ -4014,13 +4025,13 @@
       <c r="B184" t="s">
         <v>7</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="4">
         <v>120029.84432199999</v>
       </c>
-      <c r="D184" s="3">
+      <c r="D184" s="4">
         <v>35881.747689999997</v>
       </c>
-      <c r="E184" s="4">
+      <c r="E184" s="5">
         <v>84148.096632000001</v>
       </c>
       <c r="F184">
@@ -4034,13 +4045,13 @@
       <c r="B185" t="s">
         <v>8</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="4">
         <v>118416.11503299999</v>
       </c>
-      <c r="D185" s="3">
+      <c r="D185" s="4">
         <v>34531.262443</v>
       </c>
-      <c r="E185" s="4">
+      <c r="E185" s="5">
         <v>83884.852589999995</v>
       </c>
       <c r="F185">
@@ -4054,13 +4065,13 @@
       <c r="B186" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="4">
         <v>114355.97771899999</v>
       </c>
-      <c r="D186" s="3">
+      <c r="D186" s="4">
         <v>32588.379384</v>
       </c>
-      <c r="E186" s="4">
+      <c r="E186" s="5">
         <v>81767.598334999988</v>
       </c>
       <c r="F186">
@@ -4074,13 +4085,13 @@
       <c r="B187" t="s">
         <v>10</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="4">
         <v>113295.776115</v>
       </c>
-      <c r="D187" s="3">
+      <c r="D187" s="4">
         <v>29363.061617000003</v>
       </c>
-      <c r="E187" s="4">
+      <c r="E187" s="5">
         <v>83932.714498000001</v>
       </c>
       <c r="F187">
@@ -4094,13 +4105,13 @@
       <c r="B188" t="s">
         <v>11</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="4">
         <v>112406.50498199997</v>
       </c>
-      <c r="D188" s="3">
+      <c r="D188" s="4">
         <v>28652.342639999992</v>
       </c>
-      <c r="E188" s="4">
+      <c r="E188" s="5">
         <v>83754.162341999981</v>
       </c>
       <c r="F188">
@@ -4114,13 +4125,13 @@
       <c r="B189" t="s">
         <v>12</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="4">
         <v>109760.80439199998</v>
       </c>
-      <c r="D189" s="3">
+      <c r="D189" s="4">
         <v>27160.901342999998</v>
       </c>
-      <c r="E189" s="4">
+      <c r="E189" s="5">
         <v>82599.903048999986</v>
       </c>
       <c r="F189">
@@ -4134,13 +4145,13 @@
       <c r="B190" t="s">
         <v>13</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="4">
         <v>111985.722643</v>
       </c>
-      <c r="D190" s="3">
+      <c r="D190" s="4">
         <v>25930.569550999997</v>
       </c>
-      <c r="E190" s="4">
+      <c r="E190" s="5">
         <v>86055.153092000008</v>
       </c>
       <c r="F190">
@@ -4154,13 +4165,13 @@
       <c r="B191" t="s">
         <v>14</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="4">
         <v>110144.94806200001</v>
       </c>
-      <c r="D191" s="3">
+      <c r="D191" s="4">
         <v>23877.360955</v>
       </c>
-      <c r="E191" s="4">
+      <c r="E191" s="5">
         <v>86267.587107000014</v>
       </c>
       <c r="F191">
@@ -4174,13 +4185,13 @@
       <c r="B192" t="s">
         <v>15</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="4">
         <v>108684.469468</v>
       </c>
-      <c r="D192" s="3">
+      <c r="D192" s="4">
         <v>22786.922939000004</v>
       </c>
-      <c r="E192" s="4">
+      <c r="E192" s="5">
         <v>85897.546528999985</v>
       </c>
       <c r="F192">
@@ -4194,13 +4205,13 @@
       <c r="B193" t="s">
         <v>16</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="4">
         <v>108842.308766</v>
       </c>
-      <c r="D193" s="3">
+      <c r="D193" s="4">
         <v>21622.953148000001</v>
       </c>
-      <c r="E193" s="3">
+      <c r="E193" s="4">
         <v>87219.355618000001</v>
       </c>
       <c r="F193">
@@ -4214,13 +4225,13 @@
       <c r="B194" t="s">
         <v>5</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="4">
         <v>106098.971676</v>
       </c>
-      <c r="D194" s="3">
+      <c r="D194" s="4">
         <v>20561.676224999999</v>
       </c>
-      <c r="E194" s="4">
+      <c r="E194" s="5">
         <v>85537.295450999998</v>
       </c>
       <c r="F194">
@@ -4234,13 +4245,13 @@
       <c r="B195" t="s">
         <v>6</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="4">
         <v>107679.28383600002</v>
       </c>
-      <c r="D195" s="3">
+      <c r="D195" s="4">
         <v>19597.657601000003</v>
       </c>
-      <c r="E195" s="4">
+      <c r="E195" s="5">
         <v>88081.626235000018</v>
       </c>
       <c r="F195">
@@ -4254,13 +4265,13 @@
       <c r="B196" t="s">
         <v>7</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="4">
         <v>108746.98419299998</v>
       </c>
-      <c r="D196" s="3">
+      <c r="D196" s="4">
         <v>18656.268263999998</v>
       </c>
-      <c r="E196" s="4">
+      <c r="E196" s="5">
         <v>90090.715928999984</v>
       </c>
       <c r="F196">
@@ -4274,13 +4285,13 @@
       <c r="B197" t="s">
         <v>8</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="4">
         <v>108108.65055199999</v>
       </c>
-      <c r="D197" s="3">
+      <c r="D197" s="4">
         <v>18710.223129999998</v>
       </c>
-      <c r="E197" s="4">
+      <c r="E197" s="5">
         <v>89398.427421999993</v>
       </c>
       <c r="F197">
@@ -4294,13 +4305,13 @@
       <c r="B198" t="s">
         <v>9</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="4">
         <v>107677.15315400001</v>
       </c>
-      <c r="D198" s="3">
+      <c r="D198" s="4">
         <v>18229.080043999998</v>
       </c>
-      <c r="E198" s="4">
+      <c r="E198" s="5">
         <v>89448.073110000012</v>
       </c>
       <c r="F198">
@@ -4314,13 +4325,13 @@
       <c r="B199" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="4">
         <v>108629.09941799998</v>
       </c>
-      <c r="D199" s="3">
+      <c r="D199" s="4">
         <v>18054.385029999998</v>
       </c>
-      <c r="E199" s="4">
+      <c r="E199" s="5">
         <v>90574.714387999993</v>
       </c>
       <c r="F199">
@@ -4334,13 +4345,13 @@
       <c r="B200" t="s">
         <v>11</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="4">
         <v>108159.477396</v>
       </c>
-      <c r="D200" s="3">
+      <c r="D200" s="4">
         <v>18815.057545000003</v>
       </c>
-      <c r="E200" s="4">
+      <c r="E200" s="5">
         <v>89344.419850999999</v>
       </c>
       <c r="F200">
@@ -4354,13 +4365,13 @@
       <c r="B201" t="s">
         <v>12</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="4">
         <v>107561.67380399999</v>
       </c>
-      <c r="D201" s="3">
+      <c r="D201" s="4">
         <v>18923.119481999998</v>
       </c>
-      <c r="E201" s="4">
+      <c r="E201" s="5">
         <v>88638.554321999996</v>
       </c>
       <c r="F201">
@@ -4374,13 +4385,13 @@
       <c r="B202" t="s">
         <v>13</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="4">
         <v>108647.325967</v>
       </c>
-      <c r="D202" s="3">
+      <c r="D202" s="4">
         <v>19123.641464999997</v>
       </c>
-      <c r="E202" s="4">
+      <c r="E202" s="5">
         <v>89523.684502000004</v>
       </c>
       <c r="F202">
@@ -4394,13 +4405,13 @@
       <c r="B203" t="s">
         <v>14</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="4">
         <v>109374.51839499998</v>
       </c>
-      <c r="D203" s="3">
+      <c r="D203" s="4">
         <v>20595.290364</v>
       </c>
-      <c r="E203" s="4">
+      <c r="E203" s="5">
         <v>88779.228030999977</v>
       </c>
       <c r="F203">
@@ -4414,13 +4425,13 @@
       <c r="B204" t="s">
         <v>15</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="4">
         <v>111597.73594300001</v>
       </c>
-      <c r="D204" s="3">
+      <c r="D204" s="4">
         <v>22476.881816999998</v>
       </c>
-      <c r="E204" s="4">
+      <c r="E204" s="5">
         <v>89120.854126000006</v>
       </c>
       <c r="F204">
@@ -4434,13 +4445,13 @@
       <c r="B205" t="s">
         <v>16</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="4">
         <v>112799.90611599997</v>
       </c>
-      <c r="D205" s="3">
+      <c r="D205" s="4">
         <v>24230.764319000002</v>
       </c>
-      <c r="E205" s="3">
+      <c r="E205" s="4">
         <v>88569.14179699996</v>
       </c>
       <c r="F205">
@@ -4454,13 +4465,13 @@
       <c r="B206" t="s">
         <v>5</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="4">
         <v>114506.42076700002</v>
       </c>
-      <c r="D206" s="3">
+      <c r="D206" s="4">
         <v>26871.583562</v>
       </c>
-      <c r="E206" s="4">
+      <c r="E206" s="5">
         <v>87634.837205000018</v>
       </c>
       <c r="F206">
@@ -4474,13 +4485,13 @@
       <c r="B207" t="s">
         <v>6</v>
       </c>
-      <c r="C207" s="3">
+      <c r="C207" s="4">
         <v>115609.23216699999</v>
       </c>
-      <c r="D207" s="3">
+      <c r="D207" s="4">
         <v>30885.441358</v>
       </c>
-      <c r="E207" s="4">
+      <c r="E207" s="5">
         <v>84723.790808999998</v>
       </c>
       <c r="F207">
@@ -4494,13 +4505,13 @@
       <c r="B208" t="s">
         <v>7</v>
       </c>
-      <c r="C208" s="3">
+      <c r="C208" s="4">
         <v>121564.61326299999</v>
       </c>
-      <c r="D208" s="3">
+      <c r="D208" s="4">
         <v>35393.225683999997</v>
       </c>
-      <c r="E208" s="4">
+      <c r="E208" s="5">
         <v>86171.387579000002</v>
       </c>
       <c r="F208">
@@ -4514,13 +4525,13 @@
       <c r="B209" t="s">
         <v>8</v>
       </c>
-      <c r="C209" s="3">
+      <c r="C209" s="4">
         <v>124502.79102299998</v>
       </c>
-      <c r="D209" s="3">
+      <c r="D209" s="4">
         <v>41959.420549000002</v>
       </c>
-      <c r="E209" s="4">
+      <c r="E209" s="5">
         <v>82543.370473999981</v>
       </c>
       <c r="F209">
@@ -4534,13 +4545,13 @@
       <c r="B210" t="s">
         <v>9</v>
       </c>
-      <c r="C210" s="3">
+      <c r="C210" s="4">
         <v>130241.22939000001</v>
       </c>
-      <c r="D210" s="3">
+      <c r="D210" s="4">
         <v>52296.743537000002</v>
       </c>
-      <c r="E210" s="4">
+      <c r="E210" s="5">
         <v>77944.485853000006</v>
       </c>
       <c r="F210">
@@ -4554,13 +4565,13 @@
       <c r="B211" t="s">
         <v>10</v>
       </c>
-      <c r="C211" s="3">
+      <c r="C211" s="4">
         <v>135158.87485299999</v>
       </c>
-      <c r="D211" s="3">
+      <c r="D211" s="4">
         <v>56795.670142000003</v>
       </c>
-      <c r="E211" s="4">
+      <c r="E211" s="5">
         <v>78363.204710999984</v>
       </c>
       <c r="F211">
@@ -4574,13 +4585,13 @@
       <c r="B212" t="s">
         <v>11</v>
       </c>
-      <c r="C212" s="3">
+      <c r="C212" s="4">
         <v>139554.831014</v>
       </c>
-      <c r="D212" s="3">
+      <c r="D212" s="4">
         <v>63340.391706000002</v>
       </c>
-      <c r="E212" s="4">
+      <c r="E212" s="5">
         <v>76214.439308000001</v>
       </c>
       <c r="F212">
@@ -4594,13 +4605,13 @@
       <c r="B213" t="s">
         <v>12</v>
       </c>
-      <c r="C213" s="3">
+      <c r="C213" s="4">
         <v>145863.28002099998</v>
       </c>
-      <c r="D213" s="3">
+      <c r="D213" s="4">
         <v>73069.941114999994</v>
       </c>
-      <c r="E213" s="4">
+      <c r="E213" s="5">
         <v>72793.33890599999</v>
       </c>
       <c r="F213">
@@ -4614,13 +4625,13 @@
       <c r="B214" t="s">
         <v>13</v>
       </c>
-      <c r="C214" s="3">
+      <c r="C214" s="4">
         <v>149741.76946800001</v>
       </c>
-      <c r="D214" s="3">
+      <c r="D214" s="4">
         <v>81962.483940000006</v>
       </c>
-      <c r="E214" s="4">
+      <c r="E214" s="5">
         <v>67779.285528000008</v>
       </c>
       <c r="F214">
@@ -4634,13 +4645,13 @@
       <c r="B215" t="s">
         <v>14</v>
       </c>
-      <c r="C215" s="3">
+      <c r="C215" s="4">
         <v>155148.75574899997</v>
       </c>
-      <c r="D215" s="3">
+      <c r="D215" s="4">
         <v>90485.44526800001</v>
       </c>
-      <c r="E215" s="4">
+      <c r="E215" s="5">
         <v>64663.310480999964</v>
       </c>
       <c r="F215">
@@ -4654,13 +4665,13 @@
       <c r="B216" t="s">
         <v>15</v>
       </c>
-      <c r="C216" s="3">
+      <c r="C216" s="4">
         <v>162206.32550200002</v>
       </c>
-      <c r="D216" s="3">
+      <c r="D216" s="4">
         <v>100496.64903000002</v>
       </c>
-      <c r="E216" s="4">
+      <c r="E216" s="5">
         <v>61709.676472000006</v>
       </c>
       <c r="F216">
@@ -4674,13 +4685,13 @@
       <c r="B217" t="s">
         <v>16</v>
       </c>
-      <c r="C217" s="3">
+      <c r="C217" s="4">
         <v>169493.75084299999</v>
       </c>
-      <c r="D217" s="3">
+      <c r="D217" s="4">
         <v>110790.035829</v>
       </c>
-      <c r="E217" s="3">
+      <c r="E217" s="4">
         <v>58703.715013999987</v>
       </c>
       <c r="F217">
@@ -4694,13 +4705,13 @@
       <c r="B218" t="s">
         <v>5</v>
       </c>
-      <c r="C218" s="3">
+      <c r="C218" s="4">
         <v>172606.542025</v>
       </c>
-      <c r="D218" s="3">
+      <c r="D218" s="4">
         <v>121747.00737100003</v>
       </c>
-      <c r="E218" s="4">
+      <c r="E218" s="5">
         <v>50859.534653999974</v>
       </c>
       <c r="F218">
@@ -4714,13 +4725,13 @@
       <c r="B219" t="s">
         <v>6</v>
       </c>
-      <c r="C219" s="3">
+      <c r="C219" s="4">
         <v>172269.92544000002</v>
       </c>
-      <c r="D219" s="3">
+      <c r="D219" s="4">
         <v>120619.95186999999</v>
       </c>
-      <c r="E219" s="4">
+      <c r="E219" s="5">
         <v>51649.973570000031</v>
       </c>
       <c r="F219">
@@ -4734,13 +4745,13 @@
       <c r="B220" t="s">
         <v>7</v>
       </c>
-      <c r="C220" s="3">
+      <c r="C220" s="4">
         <v>179317.37406100001</v>
       </c>
-      <c r="D220" s="3">
+      <c r="D220" s="4">
         <v>127479.139069</v>
       </c>
-      <c r="E220" s="4">
+      <c r="E220" s="5">
         <v>51838.234992000012</v>
       </c>
       <c r="F220">
@@ -4754,13 +4765,13 @@
       <c r="B221" t="s">
         <v>8</v>
       </c>
-      <c r="C221" s="3">
+      <c r="C221" s="4">
         <v>177762.618694</v>
       </c>
-      <c r="D221" s="3">
+      <c r="D221" s="4">
         <v>123845.117434</v>
       </c>
-      <c r="E221" s="4">
+      <c r="E221" s="5">
         <v>53917.501260000005</v>
       </c>
       <c r="F221">
@@ -4774,13 +4785,13 @@
       <c r="B222" t="s">
         <v>9</v>
       </c>
-      <c r="C222" s="3">
+      <c r="C222" s="4">
         <v>177999.60600800003</v>
       </c>
-      <c r="D222" s="3">
+      <c r="D222" s="4">
         <v>125240.819994</v>
       </c>
-      <c r="E222" s="4">
+      <c r="E222" s="5">
         <v>52758.786014000027</v>
       </c>
       <c r="F222">
@@ -4794,13 +4805,13 @@
       <c r="B223" t="s">
         <v>10</v>
       </c>
-      <c r="C223" s="3">
+      <c r="C223" s="4">
         <v>174695.00902300002</v>
       </c>
-      <c r="D223" s="3">
+      <c r="D223" s="4">
         <v>123406.250755</v>
       </c>
-      <c r="E223" s="4">
+      <c r="E223" s="5">
         <v>51288.75826800002</v>
       </c>
       <c r="F223">
@@ -4814,13 +4825,13 @@
       <c r="B224" t="s">
         <v>11</v>
       </c>
-      <c r="C224" s="3">
+      <c r="C224" s="4">
         <v>175504.81138500001</v>
       </c>
-      <c r="D224" s="3">
+      <c r="D224" s="4">
         <v>125245.333701</v>
       </c>
-      <c r="E224" s="4">
+      <c r="E224" s="5">
         <v>50259.477684000012</v>
       </c>
       <c r="F224">
@@ -4834,13 +4845,13 @@
       <c r="B225" t="s">
         <v>12</v>
       </c>
-      <c r="C225" s="3">
+      <c r="C225" s="4">
         <v>179353.89728199999</v>
       </c>
-      <c r="D225" s="3">
+      <c r="D225" s="4">
         <v>124546.41695899999</v>
       </c>
-      <c r="E225" s="4">
+      <c r="E225" s="5">
         <v>54807.480322999996</v>
       </c>
       <c r="F225">
@@ -4854,13 +4865,13 @@
       <c r="B226" t="s">
         <v>13</v>
       </c>
-      <c r="C226" s="3">
+      <c r="C226" s="4">
         <v>175450.95360900005</v>
       </c>
-      <c r="D226" s="3">
+      <c r="D226" s="4">
         <v>124197.31178400002</v>
       </c>
-      <c r="E226" s="4">
+      <c r="E226" s="5">
         <v>51253.641825000028</v>
       </c>
       <c r="F226">
@@ -4874,13 +4885,13 @@
       <c r="B227" t="s">
         <v>14</v>
       </c>
-      <c r="C227" s="3">
+      <c r="C227" s="4">
         <v>175533.81570000001</v>
       </c>
-      <c r="D227" s="3">
+      <c r="D227" s="4">
         <v>120074.70995499998</v>
       </c>
-      <c r="E227" s="4">
+      <c r="E227" s="5">
         <v>55459.105745000023</v>
       </c>
       <c r="F227">
@@ -4894,13 +4905,13 @@
       <c r="B228" t="s">
         <v>15</v>
       </c>
-      <c r="C228" s="3">
+      <c r="C228" s="4">
         <v>173283.30884899999</v>
       </c>
-      <c r="D228" s="3">
+      <c r="D228" s="4">
         <v>120903.91542200001</v>
       </c>
-      <c r="E228" s="4">
+      <c r="E228" s="5">
         <v>52379.393426999988</v>
       </c>
       <c r="F228">
@@ -4914,13 +4925,13 @@
       <c r="B229" t="s">
         <v>16</v>
       </c>
-      <c r="C229" s="3">
+      <c r="C229" s="4">
         <v>173179.29312100002</v>
       </c>
-      <c r="D229" s="3">
+      <c r="D229" s="4">
         <v>119076.785443</v>
       </c>
-      <c r="E229" s="3">
+      <c r="E229" s="4">
         <v>54102.507678000024</v>
       </c>
       <c r="F229">
@@ -4934,13 +4945,13 @@
       <c r="B230" t="s">
         <v>5</v>
       </c>
-      <c r="C230" s="3">
+      <c r="C230" s="4">
         <v>172440.77686899999</v>
       </c>
-      <c r="D230" s="3">
+      <c r="D230" s="4">
         <v>119354.420824</v>
       </c>
-      <c r="E230" s="4">
+      <c r="E230" s="5">
         <v>53086.356044999993</v>
       </c>
       <c r="F230">
@@ -4954,13 +4965,13 @@
       <c r="B231" t="s">
         <v>6</v>
       </c>
-      <c r="C231" s="3">
+      <c r="C231" s="4">
         <v>173896.45034700003</v>
       </c>
-      <c r="D231" s="3">
+      <c r="D231" s="4">
         <v>116877.32098</v>
       </c>
-      <c r="E231" s="4">
+      <c r="E231" s="5">
         <v>57019.12936700003</v>
       </c>
       <c r="F231">
@@ -4974,13 +4985,13 @@
       <c r="B232" t="s">
         <v>7</v>
       </c>
-      <c r="C232" s="3">
+      <c r="C232" s="4">
         <v>175954.340314</v>
       </c>
-      <c r="D232" s="3">
+      <c r="D232" s="4">
         <v>121611.212589</v>
       </c>
-      <c r="E232" s="4">
+      <c r="E232" s="5">
         <v>54343.127724999998</v>
       </c>
       <c r="F232">
@@ -4994,13 +5005,13 @@
       <c r="B233" t="s">
         <v>8</v>
       </c>
-      <c r="C233" s="3">
+      <c r="C233" s="4">
         <v>172354.70471099997</v>
       </c>
-      <c r="D233" s="3">
+      <c r="D233" s="4">
         <v>109123.825512</v>
       </c>
-      <c r="E233" s="4">
+      <c r="E233" s="5">
         <v>63230.879198999974</v>
       </c>
       <c r="F233">
@@ -5014,13 +5025,13 @@
       <c r="B234" t="s">
         <v>9</v>
       </c>
-      <c r="C234" s="3">
+      <c r="C234" s="4">
         <v>167914.85365300003</v>
       </c>
-      <c r="D234" s="3">
+      <c r="D234" s="4">
         <v>103635.200459</v>
       </c>
-      <c r="E234" s="4">
+      <c r="E234" s="5">
         <v>64279.653194000028</v>
       </c>
       <c r="F234">
@@ -5034,13 +5045,13 @@
       <c r="B235" t="s">
         <v>10</v>
       </c>
-      <c r="C235" s="3">
+      <c r="C235" s="4">
         <v>162885.57630000002</v>
       </c>
-      <c r="D235" s="3">
+      <c r="D235" s="4">
         <v>99220.239413000003</v>
       </c>
-      <c r="E235" s="4">
+      <c r="E235" s="5">
         <v>63665.336887000012</v>
       </c>
       <c r="F235">
@@ -5054,13 +5065,13 @@
       <c r="B236" t="s">
         <v>11</v>
       </c>
-      <c r="C236" s="3">
+      <c r="C236" s="4">
         <v>162310.32736200001</v>
       </c>
-      <c r="D236" s="3">
+      <c r="D236" s="4">
         <v>93603.785965000003</v>
       </c>
-      <c r="E236" s="4">
+      <c r="E236" s="5">
         <v>68706.541397000008</v>
       </c>
       <c r="F236">
@@ -5074,13 +5085,13 @@
       <c r="B237" t="s">
         <v>12</v>
       </c>
-      <c r="C237" s="3">
+      <c r="C237" s="4">
         <v>160281.91200600003</v>
       </c>
-      <c r="D237" s="3">
+      <c r="D237" s="4">
         <v>89349.247687999989</v>
       </c>
-      <c r="E237" s="4">
+      <c r="E237" s="5">
         <v>70932.664318000039</v>
       </c>
       <c r="F237">
@@ -5094,13 +5105,13 @@
       <c r="B238" t="s">
         <v>13</v>
       </c>
-      <c r="C238" s="3">
+      <c r="C238" s="4">
         <v>158754.50757300001</v>
       </c>
-      <c r="D238" s="3">
+      <c r="D238" s="4">
         <v>87745.062993</v>
       </c>
-      <c r="E238" s="4">
+      <c r="E238" s="5">
         <v>71009.44458000001</v>
       </c>
       <c r="F238">
@@ -5114,13 +5125,13 @@
       <c r="B239" t="s">
         <v>14</v>
       </c>
-      <c r="C239" s="3">
+      <c r="C239" s="4">
         <v>159513.468322</v>
       </c>
-      <c r="D239" s="3">
+      <c r="D239" s="4">
         <v>88094.420222999994</v>
       </c>
-      <c r="E239" s="4">
+      <c r="E239" s="5">
         <v>71419.048099000007</v>
       </c>
       <c r="F239">
@@ -5134,13 +5145,13 @@
       <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240" s="3">
+      <c r="C240" s="4">
         <v>160796.890136</v>
       </c>
-      <c r="D240" s="3">
+      <c r="D240" s="4">
         <v>85773.230616000001</v>
       </c>
-      <c r="E240" s="4">
+      <c r="E240" s="5">
         <v>75023.659520000001</v>
       </c>
       <c r="F240">
@@ -5154,13 +5165,13 @@
       <c r="B241" t="s">
         <v>16</v>
       </c>
-      <c r="C241" s="3">
+      <c r="C241" s="4">
         <v>161839.87166100001</v>
       </c>
-      <c r="D241" s="3">
+      <c r="D241" s="4">
         <v>88432.947396000003</v>
       </c>
-      <c r="E241" s="3">
+      <c r="E241" s="4">
         <v>73406.924265000009</v>
       </c>
       <c r="F241">
@@ -5174,13 +5185,13 @@
       <c r="B242" t="s">
         <v>5</v>
       </c>
-      <c r="C242" s="3">
+      <c r="C242" s="4">
         <v>168546.15433799999</v>
       </c>
-      <c r="D242" s="3">
+      <c r="D242" s="4">
         <v>89112.169872000013</v>
       </c>
-      <c r="E242" s="4">
+      <c r="E242" s="5">
         <v>79433.98446599998</v>
       </c>
       <c r="F242">
@@ -5194,13 +5205,13 @@
       <c r="B243" t="s">
         <v>6</v>
       </c>
-      <c r="C243" s="3">
+      <c r="C243" s="4">
         <v>161663.12574699998</v>
       </c>
-      <c r="D243" s="3">
+      <c r="D243" s="4">
         <v>88987.694793000002</v>
       </c>
-      <c r="E243" s="4">
+      <c r="E243" s="5">
         <v>72675.430953999981</v>
       </c>
       <c r="F243">
@@ -5214,13 +5225,13 @@
       <c r="B244" t="s">
         <v>7</v>
       </c>
-      <c r="C244" s="3">
+      <c r="C244" s="4">
         <v>171949.527856</v>
       </c>
-      <c r="D244" s="3">
+      <c r="D244" s="4">
         <v>93954.423643999995</v>
       </c>
-      <c r="E244" s="4">
+      <c r="E244" s="5">
         <v>77995.104212000006</v>
       </c>
       <c r="F244">
@@ -5234,13 +5245,13 @@
       <c r="B245" t="s">
         <v>8</v>
       </c>
-      <c r="C245" s="3">
+      <c r="C245" s="4">
         <v>171680.15847100003</v>
       </c>
-      <c r="D245" s="3">
+      <c r="D245" s="4">
         <v>93155.483485999997</v>
       </c>
-      <c r="E245" s="4">
+      <c r="E245" s="5">
         <v>78524.674985000034</v>
       </c>
       <c r="F245">
@@ -5254,13 +5265,13 @@
       <c r="B246" t="s">
         <v>9</v>
       </c>
-      <c r="C246" s="3">
+      <c r="C246" s="4">
         <v>175242.98612800002</v>
       </c>
-      <c r="D246" s="3">
+      <c r="D246" s="4">
         <v>95300.280877000012</v>
       </c>
-      <c r="E246" s="4">
+      <c r="E246" s="5">
         <v>79942.705251000007</v>
       </c>
       <c r="F246">
@@ -5274,13 +5285,13 @@
       <c r="B247" t="s">
         <v>10</v>
       </c>
-      <c r="C247" s="3">
+      <c r="C247" s="4">
         <v>173756.45211400001</v>
       </c>
-      <c r="D247" s="3">
+      <c r="D247" s="4">
         <v>93421.575291999994</v>
       </c>
-      <c r="E247" s="4">
+      <c r="E247" s="5">
         <v>80334.87682200002</v>
       </c>
       <c r="F247">
@@ -5294,13 +5305,13 @@
       <c r="B248" t="s">
         <v>11</v>
       </c>
-      <c r="C248" s="3">
+      <c r="C248" s="4">
         <v>177611.878669</v>
       </c>
-      <c r="D248" s="3">
+      <c r="D248" s="4">
         <v>94327.325268999994</v>
       </c>
-      <c r="E248" s="4">
+      <c r="E248" s="5">
         <v>83284.553400000004</v>
       </c>
       <c r="F248">
@@ -5314,13 +5325,13 @@
       <c r="B249" t="s">
         <v>12</v>
       </c>
-      <c r="C249" s="3">
+      <c r="C249" s="4">
         <v>178549.12228600003</v>
       </c>
-      <c r="D249" s="3">
+      <c r="D249" s="4">
         <v>95393.180770000006</v>
       </c>
-      <c r="E249" s="4">
+      <c r="E249" s="5">
         <v>83155.941516000021</v>
       </c>
       <c r="F249">
@@ -5334,13 +5345,13 @@
       <c r="B250" t="s">
         <v>13</v>
       </c>
-      <c r="C250" s="3">
+      <c r="C250" s="4">
         <v>179403.45495200003</v>
       </c>
-      <c r="D250" s="3">
+      <c r="D250" s="4">
         <v>96400.383470000015</v>
       </c>
-      <c r="E250" s="4">
+      <c r="E250" s="5">
         <v>83003.071482000014</v>
       </c>
       <c r="F250">
@@ -5354,13 +5365,13 @@
       <c r="B251" t="s">
         <v>14</v>
       </c>
-      <c r="C251" s="3">
+      <c r="C251" s="4">
         <v>180527.38270400002</v>
       </c>
-      <c r="D251" s="3">
+      <c r="D251" s="4">
         <v>98698.126669000005</v>
       </c>
-      <c r="E251" s="4">
+      <c r="E251" s="5">
         <v>81829.256035000013</v>
       </c>
       <c r="F251">
@@ -5374,13 +5385,13 @@
       <c r="B252" t="s">
         <v>15</v>
       </c>
-      <c r="C252" s="3">
+      <c r="C252" s="4">
         <v>182156.29664399999</v>
       </c>
-      <c r="D252" s="3">
+      <c r="D252" s="4">
         <v>97830.733132000008</v>
       </c>
-      <c r="E252" s="4">
+      <c r="E252" s="5">
         <v>84325.563511999979</v>
       </c>
       <c r="F252">
@@ -5394,153 +5405,174 @@
       <c r="B253" t="s">
         <v>16</v>
       </c>
-      <c r="C253" s="3">
+      <c r="C253" s="4">
         <v>190722.42398099997</v>
       </c>
-      <c r="D253" s="3">
+      <c r="D253" s="4">
         <v>99910.595614999998</v>
       </c>
-      <c r="E253" s="3">
+      <c r="E253" s="4">
         <v>90811.828365999972</v>
       </c>
       <c r="F253">
         <v>9.2499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A254">
-        <v>2026</v>
-      </c>
-      <c r="B254" t="s">
-        <v>5</v>
-      </c>
-      <c r="F254">
-        <v>0.10249999999999999</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255">
-        <v>2026</v>
-      </c>
-      <c r="B255" t="s">
-        <v>6</v>
-      </c>
-      <c r="F255">
-        <v>0.10249999999999999</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256">
-        <v>2026</v>
-      </c>
-      <c r="B256" t="s">
-        <v>7</v>
-      </c>
-      <c r="F256">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A257">
-        <v>2026</v>
-      </c>
-      <c r="B257" t="s">
-        <v>8</v>
-      </c>
-      <c r="F257">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258">
-        <v>2026</v>
-      </c>
-      <c r="B258" t="s">
-        <v>9</v>
-      </c>
-      <c r="F258">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A259">
-        <v>2026</v>
-      </c>
-      <c r="B259" t="s">
-        <v>10</v>
-      </c>
-      <c r="F259">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260">
-        <v>2026</v>
-      </c>
-      <c r="B260" t="s">
-        <v>11</v>
-      </c>
-      <c r="F260">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261">
-        <v>2026</v>
-      </c>
-      <c r="B261" t="s">
-        <v>12</v>
-      </c>
-      <c r="F261">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A262">
-        <v>2026</v>
-      </c>
-      <c r="B262" t="s">
-        <v>13</v>
-      </c>
-      <c r="F262">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A263">
-        <v>2026</v>
-      </c>
-      <c r="B263" t="s">
-        <v>14</v>
-      </c>
-      <c r="F263">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A264">
-        <v>2026</v>
-      </c>
-      <c r="B264" t="s">
-        <v>15</v>
-      </c>
-      <c r="F264">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A265">
-        <v>2026</v>
-      </c>
-      <c r="B265" t="s">
-        <v>16</v>
-      </c>
-      <c r="F265">
-        <v>0.13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E4C5BE-1AF4-4D6A-B75D-B57727354DA9}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.10249999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/MARGEN FINANCIERO.xlsx
+++ b/MARGEN FINANCIERO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mauricio\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sala_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F4AD0C-64F3-498D-985F-1EB515AE57FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED71786B-6AC9-49ED-9D75-81D24B4EC717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -28,9 +28,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -108,7 +109,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -190,10 +191,10 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -476,9 +477,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7710FB4-1D75-4856-9D30-3BF005362D8B}">
   <dimension ref="A1:F253"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2005</v>
       </c>
@@ -518,7 +519,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2005</v>
       </c>
@@ -538,7 +539,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2005</v>
       </c>
@@ -558,7 +559,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2005</v>
       </c>
@@ -578,7 +579,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2005</v>
       </c>
@@ -598,7 +599,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2005</v>
       </c>
@@ -618,7 +619,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2005</v>
       </c>
@@ -638,7 +639,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2005</v>
       </c>
@@ -658,7 +659,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2005</v>
       </c>
@@ -678,7 +679,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2005</v>
       </c>
@@ -698,7 +699,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2005</v>
       </c>
@@ -718,7 +719,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2005</v>
       </c>
@@ -738,7 +739,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2006</v>
       </c>
@@ -758,7 +759,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2006</v>
       </c>
@@ -778,7 +779,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2006</v>
       </c>
@@ -798,7 +799,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2006</v>
       </c>
@@ -818,7 +819,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2006</v>
       </c>
@@ -838,7 +839,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2006</v>
       </c>
@@ -858,7 +859,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2006</v>
       </c>
@@ -878,7 +879,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2006</v>
       </c>
@@ -898,7 +899,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2006</v>
       </c>
@@ -918,7 +919,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2006</v>
       </c>
@@ -938,7 +939,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2006</v>
       </c>
@@ -958,7 +959,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2006</v>
       </c>
@@ -978,7 +979,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2007</v>
       </c>
@@ -992,7 +993,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2007</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2007</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2007</v>
       </c>
@@ -1034,7 +1035,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2007</v>
       </c>
@@ -1048,7 +1049,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2007</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2007</v>
       </c>
@@ -1076,7 +1077,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2007</v>
       </c>
@@ -1090,7 +1091,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2007</v>
       </c>
@@ -1104,7 +1105,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2007</v>
       </c>
@@ -1118,7 +1119,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2007</v>
       </c>
@@ -1132,7 +1133,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2007</v>
       </c>
@@ -1146,7 +1147,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2008</v>
       </c>
@@ -1166,7 +1167,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2008</v>
       </c>
@@ -1186,7 +1187,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2008</v>
       </c>
@@ -1206,7 +1207,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2008</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2008</v>
       </c>
@@ -1246,7 +1247,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2008</v>
       </c>
@@ -1266,7 +1267,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2008</v>
       </c>
@@ -1286,7 +1287,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2008</v>
       </c>
@@ -1306,7 +1307,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2008</v>
       </c>
@@ -1326,7 +1327,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2008</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2008</v>
       </c>
@@ -1366,7 +1367,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2008</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2009</v>
       </c>
@@ -1406,7 +1407,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2009</v>
       </c>
@@ -1426,7 +1427,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2009</v>
       </c>
@@ -1446,7 +1447,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2009</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2009</v>
       </c>
@@ -1486,7 +1487,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2009</v>
       </c>
@@ -1506,7 +1507,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2009</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2009</v>
       </c>
@@ -1546,7 +1547,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2009</v>
       </c>
@@ -1566,7 +1567,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2009</v>
       </c>
@@ -1586,7 +1587,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2009</v>
       </c>
@@ -1606,7 +1607,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2009</v>
       </c>
@@ -1626,7 +1627,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2010</v>
       </c>
@@ -1646,7 +1647,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2010</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2010</v>
       </c>
@@ -1686,7 +1687,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2010</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2010</v>
       </c>
@@ -1726,7 +1727,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2010</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2010</v>
       </c>
@@ -1766,7 +1767,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2010</v>
       </c>
@@ -1786,7 +1787,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2010</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2010</v>
       </c>
@@ -1826,7 +1827,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2010</v>
       </c>
@@ -1846,7 +1847,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2010</v>
       </c>
@@ -1866,7 +1867,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2011</v>
       </c>
@@ -1886,7 +1887,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2011</v>
       </c>
@@ -1906,7 +1907,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2011</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2011</v>
       </c>
@@ -1946,7 +1947,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2011</v>
       </c>
@@ -1966,7 +1967,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2011</v>
       </c>
@@ -1986,7 +1987,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2011</v>
       </c>
@@ -2006,7 +2007,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2011</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2011</v>
       </c>
@@ -2046,7 +2047,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>2011</v>
       </c>
@@ -2066,7 +2067,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>2011</v>
       </c>
@@ -2086,7 +2087,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2011</v>
       </c>
@@ -2106,7 +2107,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>2012</v>
       </c>
@@ -2122,7 +2123,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>2012</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2012</v>
       </c>
@@ -2154,7 +2155,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2012</v>
       </c>
@@ -2170,7 +2171,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2012</v>
       </c>
@@ -2186,7 +2187,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2012</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2012</v>
       </c>
@@ -2218,7 +2219,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2012</v>
       </c>
@@ -2234,7 +2235,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>2012</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2012</v>
       </c>
@@ -2266,7 +2267,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2012</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2012</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2013</v>
       </c>
@@ -2318,7 +2319,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2013</v>
       </c>
@@ -2338,7 +2339,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2013</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>2013</v>
       </c>
@@ -2378,7 +2379,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>2013</v>
       </c>
@@ -2398,7 +2399,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>2013</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>2013</v>
       </c>
@@ -2438,7 +2439,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>2013</v>
       </c>
@@ -2458,7 +2459,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2013</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2013</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2013</v>
       </c>
@@ -2518,7 +2519,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2013</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2014</v>
       </c>
@@ -2558,7 +2559,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2014</v>
       </c>
@@ -2578,7 +2579,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2014</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2014</v>
       </c>
@@ -2618,7 +2619,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2014</v>
       </c>
@@ -2638,7 +2639,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2014</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2014</v>
       </c>
@@ -2678,7 +2679,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2014</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2014</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2014</v>
       </c>
@@ -2738,7 +2739,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2014</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2014</v>
       </c>
@@ -2778,7 +2779,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2015</v>
       </c>
@@ -2798,7 +2799,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2015</v>
       </c>
@@ -2818,7 +2819,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2015</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2015</v>
       </c>
@@ -2858,7 +2859,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2015</v>
       </c>
@@ -2878,7 +2879,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2015</v>
       </c>
@@ -2898,7 +2899,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2015</v>
       </c>
@@ -2918,7 +2919,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2015</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2015</v>
       </c>
@@ -2958,7 +2959,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2015</v>
       </c>
@@ -2978,7 +2979,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2015</v>
       </c>
@@ -2998,7 +2999,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2015</v>
       </c>
@@ -3018,7 +3019,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2016</v>
       </c>
@@ -3038,7 +3039,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2016</v>
       </c>
@@ -3058,7 +3059,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2016</v>
       </c>
@@ -3078,7 +3079,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2016</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2016</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2016</v>
       </c>
@@ -3138,7 +3139,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>2016</v>
       </c>
@@ -3158,7 +3159,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2016</v>
       </c>
@@ -3178,7 +3179,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2016</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2016</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2016</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2016</v>
       </c>
@@ -3258,7 +3259,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2017</v>
       </c>
@@ -3278,7 +3279,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2017</v>
       </c>
@@ -3298,7 +3299,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2017</v>
       </c>
@@ -3318,7 +3319,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>2017</v>
       </c>
@@ -3338,7 +3339,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2017</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2017</v>
       </c>
@@ -3378,7 +3379,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2017</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2017</v>
       </c>
@@ -3418,7 +3419,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2017</v>
       </c>
@@ -3438,7 +3439,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2017</v>
       </c>
@@ -3458,7 +3459,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2017</v>
       </c>
@@ -3478,7 +3479,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>2017</v>
       </c>
@@ -3498,7 +3499,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2018</v>
       </c>
@@ -3518,7 +3519,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2018</v>
       </c>
@@ -3538,7 +3539,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2018</v>
       </c>
@@ -3558,7 +3559,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2018</v>
       </c>
@@ -3578,7 +3579,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2018</v>
       </c>
@@ -3598,7 +3599,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2018</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2018</v>
       </c>
@@ -3638,7 +3639,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2018</v>
       </c>
@@ -3658,7 +3659,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2018</v>
       </c>
@@ -3678,7 +3679,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2018</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2018</v>
       </c>
@@ -3718,7 +3719,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2018</v>
       </c>
@@ -3738,7 +3739,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2019</v>
       </c>
@@ -3758,7 +3759,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2019</v>
       </c>
@@ -3778,7 +3779,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2019</v>
       </c>
@@ -3798,7 +3799,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2019</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2019</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2019</v>
       </c>
@@ -3858,7 +3859,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2019</v>
       </c>
@@ -3878,7 +3879,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2019</v>
       </c>
@@ -3898,7 +3899,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2019</v>
       </c>
@@ -3918,7 +3919,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2019</v>
       </c>
@@ -3938,7 +3939,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2019</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2019</v>
       </c>
@@ -3978,7 +3979,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2020</v>
       </c>
@@ -3998,7 +3999,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2020</v>
       </c>
@@ -4018,7 +4019,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2020</v>
       </c>
@@ -4038,7 +4039,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2020</v>
       </c>
@@ -4058,7 +4059,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2020</v>
       </c>
@@ -4078,7 +4079,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2020</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2020</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2020</v>
       </c>
@@ -4138,7 +4139,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2020</v>
       </c>
@@ -4158,7 +4159,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>2020</v>
       </c>
@@ -4178,7 +4179,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>2020</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>2020</v>
       </c>
@@ -4218,7 +4219,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>2021</v>
       </c>
@@ -4238,7 +4239,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>2021</v>
       </c>
@@ -4258,7 +4259,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2021</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2021</v>
       </c>
@@ -4298,7 +4299,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2021</v>
       </c>
@@ -4318,7 +4319,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2021</v>
       </c>
@@ -4338,7 +4339,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>2021</v>
       </c>
@@ -4358,7 +4359,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>2021</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>2021</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>2021</v>
       </c>
@@ -4418,7 +4419,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>2021</v>
       </c>
@@ -4438,7 +4439,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2021</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2022</v>
       </c>
@@ -4478,7 +4479,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2022</v>
       </c>
@@ -4498,7 +4499,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2022</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>2022</v>
       </c>
@@ -4538,7 +4539,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>2022</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>2022</v>
       </c>
@@ -4578,7 +4579,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>2022</v>
       </c>
@@ -4598,7 +4599,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>2022</v>
       </c>
@@ -4618,7 +4619,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2022</v>
       </c>
@@ -4638,7 +4639,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2022</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2022</v>
       </c>
@@ -4678,7 +4679,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2022</v>
       </c>
@@ -4698,7 +4699,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>2023</v>
       </c>
@@ -4718,7 +4719,7 @@
         <v>0.1275</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>2023</v>
       </c>
@@ -4738,7 +4739,7 @@
         <v>0.1275</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>2023</v>
       </c>
@@ -4758,7 +4759,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>2023</v>
       </c>
@@ -4778,7 +4779,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>2023</v>
       </c>
@@ -4798,7 +4799,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2023</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2023</v>
       </c>
@@ -4838,7 +4839,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2023</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2023</v>
       </c>
@@ -4878,7 +4879,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>2023</v>
       </c>
@@ -4898,7 +4899,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>2023</v>
       </c>
@@ -4918,7 +4919,7 @@
         <v>0.13250000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>2023</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>2024</v>
       </c>
@@ -4958,7 +4959,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>2024</v>
       </c>
@@ -4978,7 +4979,7 @@
         <v>0.1275</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2024</v>
       </c>
@@ -4998,7 +4999,7 @@
         <v>0.1225</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2024</v>
       </c>
@@ -5018,7 +5019,7 @@
         <v>0.1225</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2024</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>0.11749999999999999</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2024</v>
       </c>
@@ -5058,7 +5059,7 @@
         <v>0.11749999999999999</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>2024</v>
       </c>
@@ -5078,7 +5079,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>2024</v>
       </c>
@@ -5098,7 +5099,7 @@
         <v>0.1075</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>2024</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>0.1075</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>2024</v>
       </c>
@@ -5138,7 +5139,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>2024</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2024</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2025</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2025</v>
       </c>
@@ -5218,7 +5219,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2025</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>2025</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>2025</v>
       </c>
@@ -5278,7 +5279,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>2025</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>2025</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2025</v>
       </c>
@@ -5338,7 +5339,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2025</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2025</v>
       </c>
@@ -5378,7 +5379,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2025</v>
       </c>
@@ -5398,7 +5399,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>2025</v>
       </c>
@@ -5427,9 +5428,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E4C5BE-1AF4-4D6A-B75D-B57727354DA9}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
@@ -5440,7 +5441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2026</v>
       </c>
@@ -5451,7 +5452,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2026</v>
       </c>
@@ -5459,10 +5460,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>0.10249999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2026</v>
       </c>
@@ -5470,10 +5471,10 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2026</v>
       </c>
@@ -5481,10 +5482,10 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2026</v>
       </c>
@@ -5492,10 +5493,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="1">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2026</v>
       </c>
@@ -5503,10 +5504,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2026</v>
       </c>
@@ -5514,10 +5515,10 @@
         <v>11</v>
       </c>
       <c r="C8" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2026</v>
       </c>
@@ -5525,10 +5526,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2026</v>
       </c>
@@ -5536,10 +5537,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="1">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2026</v>
       </c>
@@ -5547,10 +5548,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2026</v>
       </c>
@@ -5558,10 +5559,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="1">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>0.1275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2026</v>
       </c>
